--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51155D2-6B7B-4C9A-BD34-17F3F23F4AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
     <sheet name="Stage 3" sheetId="2" r:id="rId2"/>
     <sheet name="Obstacles" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="103">
   <si>
     <t>Marking type</t>
   </si>
@@ -75,247 +81,247 @@
     <t>TMP1S2f3:TMP1S2f3:1155218</t>
   </si>
   <si>
+    <t>TMP1S2e1:TMP1S2e1:1155215</t>
+  </si>
+  <si>
+    <t>TMP1S2e2:TMP1S2e2:1155214</t>
+  </si>
+  <si>
+    <t>TMP1S2e3:TMP1S2e3:1155213</t>
+  </si>
+  <si>
+    <t>TMP1S2e4:TMP1S2e4:1155212</t>
+  </si>
+  <si>
+    <t>TMP1S2d1:TMP1S2d1:1155210</t>
+  </si>
+  <si>
+    <t>TMP1S2d2:TMP1S2d2:1155209</t>
+  </si>
+  <si>
+    <t>TMP1S2d3:TMP1S2d3:1155208</t>
+  </si>
+  <si>
+    <t>TMP1S2d4:TMP1S2d4:1155207</t>
+  </si>
+  <si>
     <t>TMP1S2f4:TMP1S2f4:1155217</t>
   </si>
   <si>
-    <t>TMP1S2e1:TMP1S2e1:1155215</t>
-  </si>
-  <si>
-    <t>TMP1S2e2:TMP1S2e2:1155214</t>
-  </si>
-  <si>
-    <t>TMP1S2e3:TMP1S2e3:1155213</t>
-  </si>
-  <si>
-    <t>TMP1S2e4:TMP1S2e4:1155212</t>
-  </si>
-  <si>
-    <t>TMP1S2d1:TMP1S2d1:1155210</t>
-  </si>
-  <si>
-    <t>TMP1S2d2:TMP1S2d2:1155209</t>
-  </si>
-  <si>
-    <t>TMP1S2d3:TMP1S2d3:1155208</t>
-  </si>
-  <si>
-    <t>TMP1S2d4:TMP1S2d4:1155207</t>
+    <t>TMP1S2c2:TMP1S2c2:1155204</t>
+  </si>
+  <si>
+    <t>TMP1S2c3:TMP1S2c3:1155203</t>
+  </si>
+  <si>
+    <t>TMP1S2c4:TMP1S2c4:1155202</t>
+  </si>
+  <si>
+    <t>TMP1S2b1:TMP1S2b1:1155200</t>
+  </si>
+  <si>
+    <t>TMP1S2b2:TMP1S2b2:1155199</t>
+  </si>
+  <si>
+    <t>TMP1S2b3:TMP1S2b3:1155198</t>
+  </si>
+  <si>
+    <t>TMP1S2b4:TMP1S2b4:1155197</t>
+  </si>
+  <si>
+    <t>TMP1S2a1:TMP1S2a1:1155195</t>
+  </si>
+  <si>
+    <t>TMP1S2a2:TMP1S2a2:1155194</t>
+  </si>
+  <si>
+    <t>TMP1S2a3:TMP1S2a3:1155193</t>
   </si>
   <si>
     <t>TMP1S2c1:TMP1S2c1:1155205</t>
   </si>
   <si>
-    <t>TMP1S2c2:TMP1S2c2:1155204</t>
-  </si>
-  <si>
-    <t>TMP1S2c3:TMP1S2c3:1155203</t>
-  </si>
-  <si>
-    <t>TMP1S2c4:TMP1S2c4:1155202</t>
-  </si>
-  <si>
-    <t>TMP1S2b1:TMP1S2b1:1155200</t>
-  </si>
-  <si>
-    <t>TMP1S2b2:TMP1S2b2:1155199</t>
-  </si>
-  <si>
-    <t>TMP1S2b3:TMP1S2b3:1155198</t>
-  </si>
-  <si>
-    <t>TMP1S2b4:TMP1S2b4:1155197</t>
-  </si>
-  <si>
-    <t>TMP1S2a1:TMP1S2a1:1155195</t>
-  </si>
-  <si>
-    <t>TMP1S2a2:TMP1S2a2:1155194</t>
-  </si>
-  <si>
-    <t>TMP1S2a3:TMP1S2a3:1155193</t>
+    <t>TMP2S2c2:TMP2S2c2:1156962</t>
+  </si>
+  <si>
+    <t>TMP2S2c1:TMP2S2c1:1156963</t>
   </si>
   <si>
     <t>TMP2S2a1:TMP2S2a1:1155225</t>
   </si>
   <si>
+    <t>TMP2S2b1:TMP2S2b1:1155223</t>
+  </si>
+  <si>
+    <t>TMP2S2b2:TMP2S2b2:1155222</t>
+  </si>
+  <si>
     <t>TMP2S2a2:TMP2S2a2:1155224</t>
   </si>
   <si>
-    <t>TMP2S2b2:TMP2S2b2:1155222</t>
-  </si>
-  <si>
-    <t>TMP2S2b1:TMP2S2b1:1155223</t>
+    <t>TMP3S2b4:TMP3S2b4:1155227</t>
+  </si>
+  <si>
+    <t>TMP3S2b3:TMP3S2b3:1155228</t>
+  </si>
+  <si>
+    <t>TMP3S2b1:TMP3S2b1:1155229</t>
+  </si>
+  <si>
+    <t>TMP3S2b2:TMP3S2b2:1155230</t>
+  </si>
+  <si>
+    <t>TMP3S2a4:TMP3S2a4:1155231</t>
+  </si>
+  <si>
+    <t>TMP3S2a3:TMP3S2a3:1155232</t>
+  </si>
+  <si>
+    <t>TMP3S2a2:TMP3S2a2:1155233</t>
   </si>
   <si>
     <t>TMP3S2a1:TMP3S2a1:1155234</t>
   </si>
   <si>
-    <t>TMP3S2b4:TMP3S2b4:1155227</t>
-  </si>
-  <si>
-    <t>TMP3S2b3:TMP3S2b3:1155228</t>
-  </si>
-  <si>
-    <t>TMP3S2b1:TMP3S2b1:1155229</t>
-  </si>
-  <si>
-    <t>TMP3S2b2:TMP3S2b2:1155230</t>
-  </si>
-  <si>
-    <t>TMP3S2a4:TMP3S2a4:1155231</t>
-  </si>
-  <si>
-    <t>TMP3S2a3:TMP3S2a3:1155232</t>
-  </si>
-  <si>
-    <t>TMP3S2a2:TMP3S2a2:1155233</t>
+    <t>TMP4S2a1:TMP4S2a1:1155243</t>
+  </si>
+  <si>
+    <t>TMP4S2a2:TMP4S2a2:1155242</t>
+  </si>
+  <si>
+    <t>TMP4S2b1:TMP4S2b1:1155240</t>
+  </si>
+  <si>
+    <t>TMP4S2b2:TMP4S2b2:1155239</t>
+  </si>
+  <si>
+    <t>TMP4S2b4:TMP4S2b4:1155236</t>
+  </si>
+  <si>
+    <t>TMP4S2a4:TMP4S2a4:1155237</t>
+  </si>
+  <si>
+    <t>TMP4S2b3:TMP4S2b3:1155238</t>
   </si>
   <si>
     <t>TMP4S2a3:TMP4S2a3:1155241</t>
   </si>
   <si>
-    <t>TMP4S2a4:TMP4S2a4:1155237</t>
-  </si>
-  <si>
-    <t>TMP4S2a2:TMP4S2a2:1155242</t>
-  </si>
-  <si>
-    <t>TMP4S2a1:TMP4S2a1:1155243</t>
-  </si>
-  <si>
     <t>TMP5S2a1:TMP5S2a1:1155252</t>
   </si>
   <si>
     <t>TMP5S2b1:TMP5S2b1:1155251</t>
   </si>
   <si>
-    <t>TMP4S2b2:TMP4S2b2:1155239</t>
-  </si>
-  <si>
     <t>TMP5S2a2:TMP5S2a2:1155249</t>
   </si>
   <si>
-    <t>TMP4S2b4:TMP4S2b4:1155236</t>
-  </si>
-  <si>
-    <t>TMP4S2b3:TMP4S2b3:1155238</t>
-  </si>
-  <si>
-    <t>TMP4S2b1:TMP4S2b1:1155240</t>
+    <t>TMP5S2a3:TMP5S2a3:1155247</t>
+  </si>
+  <si>
+    <t>TMP5S2b4:TMP5S2b4:1155246</t>
+  </si>
+  <si>
+    <t>TMP5S2b3:TMP5S2b3:1155248</t>
+  </si>
+  <si>
+    <t>TMP5S2b2:TMP5S2b2:1155250</t>
   </si>
   <si>
     <t>TMP5S2a4:TMP5S2a4:1155245</t>
   </si>
   <si>
-    <t>TMP5S2b4:TMP5S2b4:1155246</t>
-  </si>
-  <si>
-    <t>TMP5S2a3:TMP5S2a3:1155247</t>
-  </si>
-  <si>
-    <t>TMP5S2b2:TMP5S2b2:1155250</t>
-  </si>
-  <si>
-    <t>TMP5S2b3:TMP5S2b3:1155248</t>
+    <t>TMP6S2a3:TMP6S2a3:1155254</t>
+  </si>
+  <si>
+    <t>TMP6S2a4:TMP6S2a4:1155255</t>
+  </si>
+  <si>
+    <t>TMP6S2a2:TMP6S2a2:1155256</t>
+  </si>
+  <si>
+    <t>TMP6S2a1:TMP6S2a1:1155257</t>
+  </si>
+  <si>
+    <t>TMP6S2b4:TMP6S2b4:1155259</t>
+  </si>
+  <si>
+    <t>TMP6S2b3:TMP6S2b3:1155260</t>
+  </si>
+  <si>
+    <t>TMP6S2b2:TMP6S2b2:1155261</t>
   </si>
   <si>
     <t>TMP6S2b1:TMP6S2b1:1155262</t>
   </si>
   <si>
-    <t>TMP6S2a3:TMP6S2a3:1155254</t>
-  </si>
-  <si>
-    <t>TMP6S2a4:TMP6S2a4:1155255</t>
-  </si>
-  <si>
-    <t>TMP6S2a2:TMP6S2a2:1155256</t>
-  </si>
-  <si>
-    <t>TMP6S2b3:TMP6S2b3:1155260</t>
-  </si>
-  <si>
-    <t>TMP6S2a1:TMP6S2a1:1155257</t>
-  </si>
-  <si>
-    <t>TMP6S2b4:TMP6S2b4:1155259</t>
-  </si>
-  <si>
-    <t>TMP6S2b2:TMP6S2b2:1155261</t>
-  </si>
-  <si>
     <t>TMP7S2c1:TMP7S2c1:1155276</t>
   </si>
   <si>
+    <t>TMP7S2d1:TMP7S2d1:1155271</t>
+  </si>
+  <si>
+    <t>TMP7S2c3:TMP7S2c3:1155274</t>
+  </si>
+  <si>
+    <t>TMP7S2d3:TMP7S2d3:1155273</t>
+  </si>
+  <si>
+    <t>TMP7S2d2:TMP7S2d2:1155272</t>
+  </si>
+  <si>
+    <t>TMP7S2a1:TMP7S2a1:1155269</t>
+  </si>
+  <si>
+    <t>TMP7S2a2:TMP7S2a2:1155268</t>
+  </si>
+  <si>
+    <t>TMP7S2a3:TMP7S2a3:1155267</t>
+  </si>
+  <si>
+    <t>TMP7S2b2:TMP7S2b2:1155265</t>
+  </si>
+  <si>
+    <t>TMP7S2b3:TMP7S2b3:1155264</t>
+  </si>
+  <si>
     <t>TMP7S2c2:TMP7S2c2:1155275</t>
   </si>
   <si>
-    <t>TMP7S2c3:TMP7S2c3:1155274</t>
-  </si>
-  <si>
-    <t>TMP7S2d2:TMP7S2d2:1155272</t>
-  </si>
-  <si>
-    <t>TMP7S2d1:TMP7S2d1:1155271</t>
-  </si>
-  <si>
-    <t>TMP7S2a1:TMP7S2a1:1155269</t>
-  </si>
-  <si>
-    <t>TMP7S2a3:TMP7S2a3:1155267</t>
-  </si>
-  <si>
     <t>TMP7S2b1:TMP7S2b1:1155266</t>
   </si>
   <si>
-    <t>TMP7S2b2:TMP7S2b2:1155265</t>
-  </si>
-  <si>
-    <t>TMP7S2b3:TMP7S2b3:1155264</t>
-  </si>
-  <si>
-    <t>TMP7S2d3:TMP7S2d3:1155273</t>
-  </si>
-  <si>
-    <t>TMP7S2a2:TMP7S2a2:1155268</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
-    <t>+</t>
-  </si>
-  <si>
     <t>blank</t>
   </si>
   <si>
     <t>Fitting</t>
   </si>
   <si>
+    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
+  </si>
+  <si>
     <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
   </si>
   <si>
-    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
+    <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
+  </si>
+  <si>
+    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+  </si>
+  <si>
+    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+  </si>
+  <si>
+    <t>BSS.GESSI,BM.49001:Default:1090988</t>
+  </si>
+  <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
   </si>
   <si>
     <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
-  </si>
-  <si>
-    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
-  </si>
-  <si>
-    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
-  </si>
-  <si>
-    <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
   <si>
     <t>Position X (mm)</t>
@@ -330,8 +336,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,13 +400,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -438,7 +452,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -472,6 +486,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -506,9 +521,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -681,11 +697,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O73"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +745,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>10</v>
       </c>
@@ -746,7 +762,7 @@
         <v>-1.35</v>
       </c>
       <c r="F2">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -755,7 +771,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -764,10 +780,10 @@
         <v>2.9</v>
       </c>
       <c r="M2">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>33</v>
       </c>
@@ -781,10 +797,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F3">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -793,7 +809,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -802,10 +818,10 @@
         <v>2.9</v>
       </c>
       <c r="M3">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>32</v>
       </c>
@@ -819,10 +835,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F4">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -831,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -840,10 +856,10 @@
         <v>2.9</v>
       </c>
       <c r="M4">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>31</v>
       </c>
@@ -857,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F5">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -869,7 +885,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -878,12 +894,12 @@
         <v>2.9</v>
       </c>
       <c r="M5">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -895,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.9350000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="F6">
-        <v>-0.775</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -907,7 +923,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -916,12 +932,12 @@
         <v>2.9</v>
       </c>
       <c r="M6">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -936,7 +952,7 @@
         <v>0.49</v>
       </c>
       <c r="F7">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -945,7 +961,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -954,12 +970,12 @@
         <v>2.9</v>
       </c>
       <c r="M7">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -974,7 +990,7 @@
         <v>0.49</v>
       </c>
       <c r="F8">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -983,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -992,12 +1008,12 @@
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1012,7 +1028,7 @@
         <v>0.49</v>
       </c>
       <c r="F9">
-        <v>-0.175</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1021,7 +1037,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1030,12 +1046,12 @@
         <v>2.9</v>
       </c>
       <c r="M9">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1047,10 +1063,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F10">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1059,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1068,12 +1084,12 @@
         <v>2.9</v>
       </c>
       <c r="M10">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1088,7 +1104,7 @@
         <v>0.47</v>
       </c>
       <c r="F11">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1097,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1106,12 +1122,12 @@
         <v>2.9</v>
       </c>
       <c r="M11">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1126,7 +1142,7 @@
         <v>0.47</v>
       </c>
       <c r="F12">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1135,7 +1151,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1144,12 +1160,12 @@
         <v>2.9</v>
       </c>
       <c r="M12">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1164,7 +1180,7 @@
         <v>0.47</v>
       </c>
       <c r="F13">
-        <v>-0.175</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1173,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1182,12 +1198,12 @@
         <v>2.9</v>
       </c>
       <c r="M13">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1199,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.47</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F14">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1211,7 +1227,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1220,12 +1236,12 @@
         <v>2.9</v>
       </c>
       <c r="M14">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1240,7 +1256,7 @@
         <v>-0.03</v>
       </c>
       <c r="F15">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1249,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1258,12 +1274,12 @@
         <v>2.9</v>
       </c>
       <c r="M15">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1278,7 +1294,7 @@
         <v>-0.03</v>
       </c>
       <c r="F16">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1287,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1296,12 +1312,12 @@
         <v>2.9</v>
       </c>
       <c r="M16">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1316,7 +1332,7 @@
         <v>-0.03</v>
       </c>
       <c r="F17">
-        <v>-0.175</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1325,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1334,12 +1350,12 @@
         <v>2.9</v>
       </c>
       <c r="M17">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1351,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>-0.775</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1363,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1372,12 +1388,12 @@
         <v>2.9</v>
       </c>
       <c r="M18">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1392,7 +1408,7 @@
         <v>-0.35</v>
       </c>
       <c r="F19">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1401,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1410,12 +1426,12 @@
         <v>2.9</v>
       </c>
       <c r="M19">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1430,7 +1446,7 @@
         <v>-0.35</v>
       </c>
       <c r="F20">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1439,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1448,12 +1464,12 @@
         <v>2.9</v>
       </c>
       <c r="M20">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1468,7 +1484,7 @@
         <v>-0.35</v>
       </c>
       <c r="F21">
-        <v>-0.175</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1477,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1486,12 +1502,12 @@
         <v>2.9</v>
       </c>
       <c r="M21">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1503,10 +1519,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>-0.35</v>
+        <v>-1.35</v>
       </c>
       <c r="F22">
-        <v>-0.775</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1515,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1524,12 +1540,12 @@
         <v>2.9</v>
       </c>
       <c r="M22">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1544,7 +1560,7 @@
         <v>-1.35</v>
       </c>
       <c r="F23">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1553,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1562,12 +1578,12 @@
         <v>2.9</v>
       </c>
       <c r="M23">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1582,7 +1598,7 @@
         <v>-1.35</v>
       </c>
       <c r="F24">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1591,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1600,12 +1616,12 @@
         <v>2.9</v>
       </c>
       <c r="M24">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1617,10 +1633,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>-1.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F25">
-        <v>-0.175</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1629,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1638,12 +1654,12 @@
         <v>2.9</v>
       </c>
       <c r="M25">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1652,13 +1668,13 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>-2.76</v>
+        <v>2.76</v>
       </c>
       <c r="E26">
-        <v>-0.5</v>
+        <v>0.15</v>
       </c>
       <c r="F26">
-        <v>-0.175</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1667,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1676,12 +1692,12 @@
         <v>1.34</v>
       </c>
       <c r="M26">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1690,13 +1706,13 @@
         <v>40</v>
       </c>
       <c r="D27">
-        <v>-2.76</v>
+        <v>2.76</v>
       </c>
       <c r="E27">
-        <v>-0.5</v>
+        <v>0.15</v>
       </c>
       <c r="F27">
-        <v>-0.775</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1705,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1714,12 +1730,12 @@
         <v>1.34</v>
       </c>
       <c r="M27">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1728,13 +1744,13 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>-2.76</v>
+        <v>2.76</v>
       </c>
       <c r="E28">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="F28">
-        <v>-0.775</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1743,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1752,10 +1768,10 @@
         <v>1.34</v>
       </c>
       <c r="M28">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>35</v>
       </c>
@@ -1766,13 +1782,13 @@
         <v>42</v>
       </c>
       <c r="D29">
-        <v>-2.76</v>
+        <v>2.76</v>
       </c>
       <c r="E29">
         <v>0.1</v>
       </c>
       <c r="F29">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1781,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1790,12 +1806,12 @@
         <v>1.34</v>
       </c>
       <c r="M29">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1804,36 +1820,36 @@
         <v>43</v>
       </c>
       <c r="D30">
-        <v>1.2</v>
+        <v>2.76</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F30">
-        <v>1.025</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="L30">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="M30">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1842,36 +1858,36 @@
         <v>44</v>
       </c>
       <c r="D31">
-        <v>1.2</v>
+        <v>2.76</v>
       </c>
       <c r="E31">
-        <v>0.445</v>
+        <v>-0.5</v>
       </c>
       <c r="F31">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="L31">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="M31">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -1883,10 +1899,10 @@
         <v>1.2</v>
       </c>
       <c r="E32">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F32">
-        <v>-0.175</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -1895,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1904,12 +1920,12 @@
         <v>0.96</v>
       </c>
       <c r="M32">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -1921,10 +1937,10 @@
         <v>1.2</v>
       </c>
       <c r="E33">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F33">
-        <v>1.025</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -1933,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1942,12 +1958,12 @@
         <v>0.96</v>
       </c>
       <c r="M33">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -1959,10 +1975,10 @@
         <v>1.2</v>
       </c>
       <c r="E34">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F34">
-        <v>0.425</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -1971,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1980,12 +1996,12 @@
         <v>0.96</v>
       </c>
       <c r="M34">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -1997,10 +2013,10 @@
         <v>1.2</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F35">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2009,7 +2025,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2018,12 +2034,12 @@
         <v>0.96</v>
       </c>
       <c r="M35">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2038,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>-0.175</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -2047,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2056,12 +2072,12 @@
         <v>0.96</v>
       </c>
       <c r="M36">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2076,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -2085,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2094,12 +2110,12 @@
         <v>0.96</v>
       </c>
       <c r="M37">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2108,36 +2124,36 @@
         <v>51</v>
       </c>
       <c r="D38">
+        <v>1.2</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="G38">
+        <v>3</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>90</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="L38">
         <v>0.96</v>
       </c>
-      <c r="E38">
-        <v>-0.3</v>
-      </c>
-      <c r="F38">
-        <v>-0.175</v>
-      </c>
-      <c r="G38">
-        <v>4</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>89</v>
-      </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-      <c r="L38">
-        <v>0.592</v>
-      </c>
       <c r="M38">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2146,36 +2162,36 @@
         <v>52</v>
       </c>
       <c r="D39">
+        <v>1.2</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>90</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="L39">
         <v>0.96</v>
       </c>
-      <c r="E39">
-        <v>-0.3</v>
-      </c>
-      <c r="F39">
-        <v>-0.775</v>
-      </c>
-      <c r="G39">
-        <v>4</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>89</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="L39">
-        <v>0.592</v>
-      </c>
       <c r="M39">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2184,13 +2200,13 @@
         <v>53</v>
       </c>
       <c r="D40">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="E40">
         <v>-0.3</v>
       </c>
       <c r="F40">
-        <v>0.425</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -2199,21 +2215,21 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M40">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2222,13 +2238,13 @@
         <v>54</v>
       </c>
       <c r="D41">
-        <v>0.96</v>
+        <v>1.8</v>
       </c>
       <c r="E41">
         <v>-0.3</v>
       </c>
       <c r="F41">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -2237,21 +2253,21 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="L41">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M41">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2260,36 +2276,36 @@
         <v>55</v>
       </c>
       <c r="D42">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E42">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>-0.775</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>1.94</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M42">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2298,36 +2314,36 @@
         <v>56</v>
       </c>
       <c r="D43">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E43">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>-0.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>1.94</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M43">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2336,36 +2352,36 @@
         <v>57</v>
       </c>
       <c r="D44">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="E44">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>0.425</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>1.94</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M44">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2374,36 +2390,36 @@
         <v>58</v>
       </c>
       <c r="D45">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E45">
-        <v>0.15</v>
+        <v>-0.3</v>
       </c>
       <c r="F45">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>1.94</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M45">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2412,36 +2428,36 @@
         <v>59</v>
       </c>
       <c r="D46">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="E46">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>-0.775</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>1.94</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M46">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2450,36 +2466,36 @@
         <v>60</v>
       </c>
       <c r="D47">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="E47">
-        <v>-0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="F47">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>1.94</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M47">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2488,13 +2504,13 @@
         <v>61</v>
       </c>
       <c r="D48">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="E48">
-        <v>-0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F48">
-        <v>1.025</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G48">
         <v>5</v>
@@ -2503,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2512,12 +2528,12 @@
         <v>1.94</v>
       </c>
       <c r="M48">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2526,13 +2542,13 @@
         <v>62</v>
       </c>
       <c r="D49">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E49">
-        <v>-0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F49">
-        <v>-0.775</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G49">
         <v>5</v>
@@ -2541,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2550,12 +2566,12 @@
         <v>1.94</v>
       </c>
       <c r="M49">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2564,13 +2580,13 @@
         <v>63</v>
       </c>
       <c r="D50">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E50">
-        <v>-0.9</v>
+        <v>0.15</v>
       </c>
       <c r="F50">
-        <v>-0.025</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G50">
         <v>5</v>
@@ -2579,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2588,10 +2604,10 @@
         <v>1.94</v>
       </c>
       <c r="M50">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>56</v>
       </c>
@@ -2602,13 +2618,13 @@
         <v>64</v>
       </c>
       <c r="D51">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E51">
         <v>-0.45</v>
       </c>
       <c r="F51">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -2617,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -2626,12 +2642,12 @@
         <v>1.94</v>
       </c>
       <c r="M51">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2640,13 +2656,13 @@
         <v>65</v>
       </c>
       <c r="D52">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E52">
-        <v>0.15</v>
+        <v>-0.9</v>
       </c>
       <c r="F52">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -2655,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2664,10 +2680,10 @@
         <v>1.94</v>
       </c>
       <c r="M52">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>57</v>
       </c>
@@ -2678,13 +2694,13 @@
         <v>66</v>
       </c>
       <c r="D53">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="E53">
         <v>-0.45</v>
       </c>
       <c r="F53">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -2693,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2702,12 +2718,12 @@
         <v>1.94</v>
       </c>
       <c r="M53">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2719,33 +2735,33 @@
         <v>1.8</v>
       </c>
       <c r="E54">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F54">
-        <v>1.05</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J54">
         <v>1</v>
       </c>
       <c r="L54">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M54">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2757,33 +2773,33 @@
         <v>1.8</v>
       </c>
       <c r="E55">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="F55">
-        <v>-0.75</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J55">
         <v>1</v>
       </c>
       <c r="L55">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M55">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2792,13 +2808,13 @@
         <v>69</v>
       </c>
       <c r="D56">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>-0.3</v>
       </c>
       <c r="F56">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G56">
         <v>6</v>
@@ -2807,21 +2823,21 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J56">
         <v>1</v>
       </c>
       <c r="L56">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M56">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2830,13 +2846,13 @@
         <v>70</v>
       </c>
       <c r="D57">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>-0.3</v>
       </c>
       <c r="F57">
-        <v>0.45</v>
+        <v>-0.15</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -2845,21 +2861,21 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J57">
         <v>1</v>
       </c>
       <c r="L57">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M57">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -2868,13 +2884,13 @@
         <v>71</v>
       </c>
       <c r="D58">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F58">
-        <v>-0.15</v>
+        <v>0.45</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -2883,19 +2899,19 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="L58">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M58">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>65</v>
       </c>
@@ -2906,7 +2922,7 @@
         <v>72</v>
       </c>
       <c r="D59">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>-0.3</v>
@@ -2921,19 +2937,19 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="L59">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M59">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>66</v>
       </c>
@@ -2944,7 +2960,7 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E60">
         <v>0.3</v>
@@ -2959,21 +2975,21 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
       <c r="L60">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M60">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -2982,13 +2998,13 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>0.3</v>
       </c>
       <c r="F61">
-        <v>0.45</v>
+        <v>-0.15</v>
       </c>
       <c r="G61">
         <v>6</v>
@@ -2997,21 +3013,21 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="L61">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M61">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3020,36 +3036,36 @@
         <v>75</v>
       </c>
       <c r="D62">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="F62">
-        <v>-0.025</v>
-      </c>
-      <c r="G62" t="s">
-        <v>87</v>
+        <v>0.45</v>
+      </c>
+      <c r="G62">
+        <v>6</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J62">
         <v>1</v>
       </c>
       <c r="L62">
-        <v>2.9</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M62">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3058,36 +3074,36 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F63">
-        <v>-0.025</v>
-      </c>
-      <c r="G63" t="s">
-        <v>87</v>
+        <v>1.05</v>
+      </c>
+      <c r="G63">
+        <v>6</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J63">
         <v>1</v>
       </c>
       <c r="L63">
-        <v>2.9</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M63">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3099,19 +3115,19 @@
         <v>0.72</v>
       </c>
       <c r="E64">
-        <v>0.15</v>
+        <v>1.05</v>
       </c>
       <c r="F64">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G64" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3120,12 +3136,12 @@
         <v>2.9</v>
       </c>
       <c r="M64">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3137,19 +3153,19 @@
         <v>0.12</v>
       </c>
       <c r="E65">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="F65">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G65" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3158,12 +3174,12 @@
         <v>2.9</v>
       </c>
       <c r="M65">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3172,22 +3188,22 @@
         <v>79</v>
       </c>
       <c r="D66">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E66">
-        <v>1.05</v>
+        <v>0.15</v>
       </c>
       <c r="F66">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G66" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3196,12 +3212,12 @@
         <v>2.9</v>
       </c>
       <c r="M66">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
@@ -3210,22 +3226,22 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>2.31</v>
+        <v>0.12</v>
       </c>
       <c r="E67">
-        <v>1.2</v>
+        <v>0.15</v>
       </c>
       <c r="F67">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G67" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3234,12 +3250,12 @@
         <v>2.9</v>
       </c>
       <c r="M67">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3248,22 +3264,22 @@
         <v>81</v>
       </c>
       <c r="D68">
-        <v>2.31</v>
+        <v>0.12</v>
       </c>
       <c r="E68">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="F68">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G68" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3272,12 +3288,12 @@
         <v>2.9</v>
       </c>
       <c r="M68">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
@@ -3286,22 +3302,22 @@
         <v>82</v>
       </c>
       <c r="D69">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="E69">
         <v>1.2</v>
       </c>
       <c r="F69">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G69" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3310,12 +3326,12 @@
         <v>2.9</v>
       </c>
       <c r="M69">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
@@ -3324,22 +3340,22 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="E70">
         <v>0.6</v>
       </c>
       <c r="F70">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G70" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3348,12 +3364,12 @@
         <v>2.9</v>
       </c>
       <c r="M70">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -3362,22 +3378,22 @@
         <v>84</v>
       </c>
       <c r="D71">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="E71">
         <v>0.15</v>
       </c>
       <c r="F71">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G71" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3386,12 +3402,12 @@
         <v>2.9</v>
       </c>
       <c r="M71">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -3400,22 +3416,22 @@
         <v>85</v>
       </c>
       <c r="D72">
-        <v>0.12</v>
+        <v>1.41</v>
       </c>
       <c r="E72">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="F72">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G72" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3424,12 +3440,12 @@
         <v>2.9</v>
       </c>
       <c r="M72">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B73" t="s">
         <v>14</v>
@@ -3438,31 +3454,107 @@
         <v>86</v>
       </c>
       <c r="D73">
-        <v>2.31</v>
+        <v>1.41</v>
       </c>
       <c r="E73">
+        <v>0.15</v>
+      </c>
+      <c r="F73">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="G73" t="s">
+        <v>89</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>90</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="L73">
+        <v>2.9</v>
+      </c>
+      <c r="M73">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>80</v>
+      </c>
+      <c r="B74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" t="s">
+        <v>87</v>
+      </c>
+      <c r="D74">
+        <v>0.72</v>
+      </c>
+      <c r="E74">
         <v>0.6</v>
       </c>
-      <c r="F73">
-        <v>-0.025</v>
-      </c>
-      <c r="G73" t="s">
-        <v>87</v>
-      </c>
-      <c r="H73">
-        <v>1</v>
-      </c>
-      <c r="I73" t="s">
+      <c r="F74">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="G74" t="s">
         <v>89</v>
       </c>
-      <c r="J73">
-        <v>1</v>
-      </c>
-      <c r="L73">
-        <v>2.9</v>
-      </c>
-      <c r="M73">
-        <v>1.932</v>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>90</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="L74">
+        <v>2.9</v>
+      </c>
+      <c r="M74">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>72</v>
+      </c>
+      <c r="B75" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
+        <v>88</v>
+      </c>
+      <c r="D75">
+        <v>1.41</v>
+      </c>
+      <c r="E75">
+        <v>1.2</v>
+      </c>
+      <c r="F75">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="G75" t="s">
+        <v>89</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>90</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>2.9</v>
+      </c>
+      <c r="M75">
+        <v>1.9319999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3471,11 +3563,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3519,24 +3611,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>235</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2">
-        <v>1.202</v>
+        <v>1.2</v>
       </c>
       <c r="E2">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="F2">
-        <v>-0.181</v>
+        <v>-0.05</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -3545,7 +3637,7 @@
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -3554,27 +3646,27 @@
         <v>0.96</v>
       </c>
       <c r="M2">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>166</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3">
         <v>1.2</v>
       </c>
       <c r="E3">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="F3">
-        <v>-0.05</v>
+        <v>-0.18099999999999999</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -3583,7 +3675,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3592,27 +3684,27 @@
         <v>0.96</v>
       </c>
       <c r="M3">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4">
-        <v>0.38</v>
+        <v>1.8</v>
       </c>
       <c r="E4">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>-0.725</v>
+        <v>0.125</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3621,7 +3713,7 @@
         <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -3630,197 +3722,197 @@
         <v>1.94</v>
       </c>
       <c r="M4">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D5">
-        <v>0.305</v>
+        <v>2.31</v>
       </c>
       <c r="E5">
-        <v>0.45</v>
+        <v>1.5049999999999999</v>
       </c>
       <c r="F5">
-        <v>-0.453</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="G5" t="s">
+        <v>89</v>
       </c>
       <c r="H5">
         <v>6</v>
       </c>
       <c r="I5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>2.9</v>
+      </c>
+      <c r="M5">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>235</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6">
+        <v>1.2849999999999999</v>
+      </c>
+      <c r="E6">
+        <v>1.5920000000000001</v>
+      </c>
+      <c r="F6">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="G6" t="s">
         <v>89</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1.94</v>
-      </c>
-      <c r="M5">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="1">
-        <v>231</v>
-      </c>
-      <c r="B6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6">
-        <v>0.492</v>
-      </c>
-      <c r="E6">
-        <v>-0.45</v>
-      </c>
-      <c r="F6">
-        <v>-0.175</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
       </c>
       <c r="H6">
         <v>6</v>
       </c>
       <c r="I6" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2.9</v>
+      </c>
+      <c r="M6">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>231</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7">
+        <v>2.31</v>
+      </c>
+      <c r="E7">
+        <v>1.74</v>
+      </c>
+      <c r="F7">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="G7" t="s">
         <v>89</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1.94</v>
-      </c>
-      <c r="M6">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="1">
-        <v>233</v>
-      </c>
-      <c r="B7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7">
-        <v>0.392</v>
-      </c>
-      <c r="E7">
-        <v>-0.575</v>
-      </c>
-      <c r="F7">
-        <v>-1.024</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
       </c>
       <c r="H7">
         <v>6</v>
       </c>
       <c r="I7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2.9</v>
+      </c>
+      <c r="M7">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>233</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8">
+        <v>1.41</v>
+      </c>
+      <c r="E8">
+        <v>1.6919999999999999</v>
+      </c>
+      <c r="F8">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="G8" t="s">
         <v>89</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1.94</v>
-      </c>
-      <c r="M7">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="1">
-        <v>229</v>
-      </c>
-      <c r="B8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8">
-        <v>0.54</v>
-      </c>
-      <c r="E8">
-        <v>0.45</v>
-      </c>
-      <c r="F8">
-        <v>-0.175</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
       </c>
       <c r="H8">
         <v>6</v>
       </c>
       <c r="I8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>2.9</v>
+      </c>
+      <c r="M8">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>230</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9">
+        <v>1.06</v>
+      </c>
+      <c r="E9">
+        <v>1.58</v>
+      </c>
+      <c r="F9">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="G9" t="s">
         <v>89</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1.94</v>
-      </c>
-      <c r="M8">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="1">
-        <v>236</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9">
-        <v>0.6</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0.125</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
       </c>
       <c r="H9">
         <v>6</v>
       </c>
       <c r="I9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M9">
-        <v>2.655</v>
+        <v>1.9319999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3829,11 +3921,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:O1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:15">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51155D2-6B7B-4C9A-BD34-17F3F23F4AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
     <sheet name="Stage 3" sheetId="2" r:id="rId2"/>
     <sheet name="Obstacles" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="105">
   <si>
     <t>Marking type</t>
   </si>
@@ -294,6 +288,9 @@
     <t>F</t>
   </si>
   <si>
+    <t>+</t>
+  </si>
+  <si>
     <t>blank</t>
   </si>
   <si>
@@ -322,6 +319,9 @@
   </si>
   <si>
     <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>Position X (mm)</t>
@@ -336,8 +336,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -400,21 +400,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -452,7 +444,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -486,7 +478,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -521,10 +512,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -697,11 +687,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O75"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -745,7 +735,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
         <v>10</v>
       </c>
@@ -762,7 +752,7 @@
         <v>-1.35</v>
       </c>
       <c r="F2">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -771,7 +761,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -780,10 +770,10 @@
         <v>2.9</v>
       </c>
       <c r="M2">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1">
         <v>33</v>
       </c>
@@ -797,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F3">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -809,7 +799,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -818,10 +808,10 @@
         <v>2.9</v>
       </c>
       <c r="M3">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1">
         <v>32</v>
       </c>
@@ -835,10 +825,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F4">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -847,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -856,10 +846,10 @@
         <v>2.9</v>
       </c>
       <c r="M4">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
         <v>31</v>
       </c>
@@ -873,10 +863,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F5">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -885,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -894,10 +884,10 @@
         <v>2.9</v>
       </c>
       <c r="M5">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
         <v>29</v>
       </c>
@@ -914,7 +904,7 @@
         <v>0.49</v>
       </c>
       <c r="F6">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -923,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -932,10 +922,10 @@
         <v>2.9</v>
       </c>
       <c r="M6">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
         <v>28</v>
       </c>
@@ -952,7 +942,7 @@
         <v>0.49</v>
       </c>
       <c r="F7">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -961,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -970,10 +960,10 @@
         <v>2.9</v>
       </c>
       <c r="M7">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>27</v>
       </c>
@@ -990,7 +980,7 @@
         <v>0.49</v>
       </c>
       <c r="F8">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -999,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1008,10 +998,10 @@
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
         <v>26</v>
       </c>
@@ -1028,7 +1018,7 @@
         <v>0.49</v>
       </c>
       <c r="F9">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1037,7 +1027,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1046,10 +1036,10 @@
         <v>2.9</v>
       </c>
       <c r="M9">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1">
         <v>25</v>
       </c>
@@ -1066,7 +1056,7 @@
         <v>0.47</v>
       </c>
       <c r="F10">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1075,7 +1065,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1084,10 +1074,10 @@
         <v>2.9</v>
       </c>
       <c r="M10">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1">
         <v>24</v>
       </c>
@@ -1104,7 +1094,7 @@
         <v>0.47</v>
       </c>
       <c r="F11">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1113,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1122,10 +1112,10 @@
         <v>2.9</v>
       </c>
       <c r="M11">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1">
         <v>23</v>
       </c>
@@ -1142,7 +1132,7 @@
         <v>0.47</v>
       </c>
       <c r="F12">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1151,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1160,10 +1150,10 @@
         <v>2.9</v>
       </c>
       <c r="M12">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1">
         <v>22</v>
       </c>
@@ -1180,7 +1170,7 @@
         <v>0.47</v>
       </c>
       <c r="F13">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1189,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1198,10 +1188,10 @@
         <v>2.9</v>
       </c>
       <c r="M13">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1">
         <v>30</v>
       </c>
@@ -1215,10 +1205,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F14">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1227,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1236,10 +1226,10 @@
         <v>2.9</v>
       </c>
       <c r="M14">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1">
         <v>20</v>
       </c>
@@ -1256,7 +1246,7 @@
         <v>-0.03</v>
       </c>
       <c r="F15">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1265,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1274,10 +1264,10 @@
         <v>2.9</v>
       </c>
       <c r="M15">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="1">
         <v>19</v>
       </c>
@@ -1294,7 +1284,7 @@
         <v>-0.03</v>
       </c>
       <c r="F16">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1303,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1312,10 +1302,10 @@
         <v>2.9</v>
       </c>
       <c r="M16">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>18</v>
       </c>
@@ -1332,7 +1322,7 @@
         <v>-0.03</v>
       </c>
       <c r="F17">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1341,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1350,10 +1340,10 @@
         <v>2.9</v>
       </c>
       <c r="M17">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1370,7 +1360,7 @@
         <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1379,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1388,10 +1378,10 @@
         <v>2.9</v>
       </c>
       <c r="M18">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -1408,7 +1398,7 @@
         <v>-0.35</v>
       </c>
       <c r="F19">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1417,7 +1407,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1426,10 +1416,10 @@
         <v>2.9</v>
       </c>
       <c r="M19">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>15</v>
       </c>
@@ -1446,7 +1436,7 @@
         <v>-0.35</v>
       </c>
       <c r="F20">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1455,7 +1445,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1464,10 +1454,10 @@
         <v>2.9</v>
       </c>
       <c r="M20">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>14</v>
       </c>
@@ -1484,7 +1474,7 @@
         <v>-0.35</v>
       </c>
       <c r="F21">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1493,7 +1483,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1502,10 +1492,10 @@
         <v>2.9</v>
       </c>
       <c r="M21">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>13</v>
       </c>
@@ -1522,7 +1512,7 @@
         <v>-1.35</v>
       </c>
       <c r="F22">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1531,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1540,10 +1530,10 @@
         <v>2.9</v>
       </c>
       <c r="M22">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <v>12</v>
       </c>
@@ -1560,7 +1550,7 @@
         <v>-1.35</v>
       </c>
       <c r="F23">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1569,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1578,10 +1568,10 @@
         <v>2.9</v>
       </c>
       <c r="M23">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>11</v>
       </c>
@@ -1598,7 +1588,7 @@
         <v>-1.35</v>
       </c>
       <c r="F24">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1607,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1616,10 +1606,10 @@
         <v>2.9</v>
       </c>
       <c r="M24">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -1636,7 +1626,7 @@
         <v>-0.03</v>
       </c>
       <c r="F25">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1645,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1654,10 +1644,10 @@
         <v>2.9</v>
       </c>
       <c r="M25">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
         <v>82</v>
       </c>
@@ -1674,7 +1664,7 @@
         <v>0.15</v>
       </c>
       <c r="F26">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1683,7 +1673,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1692,10 +1682,10 @@
         <v>1.34</v>
       </c>
       <c r="M26">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
         <v>83</v>
       </c>
@@ -1712,7 +1702,7 @@
         <v>0.15</v>
       </c>
       <c r="F27">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1721,7 +1711,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1730,10 +1720,10 @@
         <v>1.34</v>
       </c>
       <c r="M27">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
         <v>37</v>
       </c>
@@ -1750,7 +1740,7 @@
         <v>-0.5</v>
       </c>
       <c r="F28">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1759,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1768,10 +1758,10 @@
         <v>1.34</v>
       </c>
       <c r="M28">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
         <v>35</v>
       </c>
@@ -1788,7 +1778,7 @@
         <v>0.1</v>
       </c>
       <c r="F29">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1797,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1806,10 +1796,10 @@
         <v>1.34</v>
       </c>
       <c r="M29">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
         <v>34</v>
       </c>
@@ -1826,7 +1816,7 @@
         <v>0.1</v>
       </c>
       <c r="F30">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1835,7 +1825,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1844,10 +1834,10 @@
         <v>1.34</v>
       </c>
       <c r="M30">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
         <v>36</v>
       </c>
@@ -1864,7 +1854,7 @@
         <v>-0.5</v>
       </c>
       <c r="F31">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1873,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1882,10 +1872,10 @@
         <v>1.34</v>
       </c>
       <c r="M31">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
         <v>38</v>
       </c>
@@ -1899,10 +1889,10 @@
         <v>1.2</v>
       </c>
       <c r="E32">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="F32">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -1911,7 +1901,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1920,10 +1910,10 @@
         <v>0.96</v>
       </c>
       <c r="M32">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
         <v>39</v>
       </c>
@@ -1937,10 +1927,10 @@
         <v>1.2</v>
       </c>
       <c r="E33">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="F33">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -1949,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1958,10 +1948,10 @@
         <v>0.96</v>
       </c>
       <c r="M33">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
         <v>40</v>
       </c>
@@ -1975,10 +1965,10 @@
         <v>1.2</v>
       </c>
       <c r="E34">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="F34">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -1987,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1996,10 +1986,10 @@
         <v>0.96</v>
       </c>
       <c r="M34">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
         <v>41</v>
       </c>
@@ -2013,10 +2003,10 @@
         <v>1.2</v>
       </c>
       <c r="E35">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="F35">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2025,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2034,10 +2024,10 @@
         <v>0.96</v>
       </c>
       <c r="M35">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
         <v>42</v>
       </c>
@@ -2054,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -2063,7 +2053,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2072,10 +2062,10 @@
         <v>0.96</v>
       </c>
       <c r="M36">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1">
         <v>43</v>
       </c>
@@ -2092,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -2101,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2110,10 +2100,10 @@
         <v>0.96</v>
       </c>
       <c r="M37">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1">
         <v>44</v>
       </c>
@@ -2130,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G38">
         <v>3</v>
@@ -2139,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2148,10 +2138,10 @@
         <v>0.96</v>
       </c>
       <c r="M38">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
         <v>45</v>
       </c>
@@ -2168,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -2177,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2186,10 +2176,10 @@
         <v>0.96</v>
       </c>
       <c r="M39">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
         <v>53</v>
       </c>
@@ -2206,7 +2196,7 @@
         <v>-0.3</v>
       </c>
       <c r="F40">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -2215,19 +2205,19 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M40">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="1">
         <v>52</v>
       </c>
@@ -2244,7 +2234,7 @@
         <v>-0.3</v>
       </c>
       <c r="F41">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -2253,19 +2243,19 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="L41">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M41">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="1">
         <v>50</v>
       </c>
@@ -2282,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -2291,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M42">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="1">
         <v>49</v>
       </c>
@@ -2320,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -2329,19 +2319,19 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M43">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="1">
         <v>46</v>
       </c>
@@ -2358,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -2367,19 +2357,19 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M44">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="1">
         <v>47</v>
       </c>
@@ -2396,7 +2386,7 @@
         <v>-0.3</v>
       </c>
       <c r="F45">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -2405,19 +2395,19 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M45">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="1">
         <v>48</v>
       </c>
@@ -2434,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -2443,19 +2433,19 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M46">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="1">
         <v>51</v>
       </c>
@@ -2472,7 +2462,7 @@
         <v>-0.3</v>
       </c>
       <c r="F47">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -2481,19 +2471,19 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M47">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="1">
         <v>61</v>
       </c>
@@ -2510,7 +2500,7 @@
         <v>0.75</v>
       </c>
       <c r="F48">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G48">
         <v>5</v>
@@ -2519,7 +2509,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2528,10 +2518,10 @@
         <v>1.94</v>
       </c>
       <c r="M48">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="1">
         <v>60</v>
       </c>
@@ -2548,7 +2538,7 @@
         <v>0.75</v>
       </c>
       <c r="F49">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G49">
         <v>5</v>
@@ -2557,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2566,10 +2556,10 @@
         <v>1.94</v>
       </c>
       <c r="M49">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="1">
         <v>58</v>
       </c>
@@ -2586,7 +2576,7 @@
         <v>0.15</v>
       </c>
       <c r="F50">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G50">
         <v>5</v>
@@ -2595,7 +2585,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2604,10 +2594,10 @@
         <v>1.94</v>
       </c>
       <c r="M50">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="1">
         <v>56</v>
       </c>
@@ -2624,7 +2614,7 @@
         <v>-0.45</v>
       </c>
       <c r="F51">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -2633,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -2642,10 +2632,10 @@
         <v>1.94</v>
       </c>
       <c r="M51">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="1">
         <v>55</v>
       </c>
@@ -2662,7 +2652,7 @@
         <v>-0.9</v>
       </c>
       <c r="F52">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -2671,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2680,10 +2670,10 @@
         <v>1.94</v>
       </c>
       <c r="M52">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="1">
         <v>57</v>
       </c>
@@ -2700,7 +2690,7 @@
         <v>-0.45</v>
       </c>
       <c r="F53">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -2709,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2718,10 +2708,10 @@
         <v>1.94</v>
       </c>
       <c r="M53">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="1">
         <v>59</v>
       </c>
@@ -2738,7 +2728,7 @@
         <v>0.15</v>
       </c>
       <c r="F54">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G54">
         <v>5</v>
@@ -2747,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2756,10 +2746,10 @@
         <v>1.94</v>
       </c>
       <c r="M54">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2776,7 +2766,7 @@
         <v>-0.9</v>
       </c>
       <c r="F55">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G55">
         <v>5</v>
@@ -2785,7 +2775,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2794,10 +2784,10 @@
         <v>1.94</v>
       </c>
       <c r="M55">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="1">
         <v>62</v>
       </c>
@@ -2823,19 +2813,19 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J56">
         <v>1</v>
       </c>
       <c r="L56">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M56">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="1">
         <v>63</v>
       </c>
@@ -2861,19 +2851,19 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J57">
         <v>1</v>
       </c>
       <c r="L57">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M57">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="1">
         <v>64</v>
       </c>
@@ -2899,19 +2889,19 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="L58">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M58">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="1">
         <v>65</v>
       </c>
@@ -2937,19 +2927,19 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="L59">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M59">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="1">
         <v>66</v>
       </c>
@@ -2975,19 +2965,19 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
       <c r="L60">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M60">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="1">
         <v>67</v>
       </c>
@@ -3013,19 +3003,19 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="L61">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M61">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="1">
         <v>68</v>
       </c>
@@ -3051,19 +3041,19 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J62">
         <v>1</v>
       </c>
       <c r="L62">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M62">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="1">
         <v>69</v>
       </c>
@@ -3089,19 +3079,19 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J63">
         <v>1</v>
       </c>
       <c r="L63">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M63">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="1">
         <v>81</v>
       </c>
@@ -3118,7 +3108,7 @@
         <v>1.05</v>
       </c>
       <c r="F64">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G64" t="s">
         <v>89</v>
@@ -3127,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3136,10 +3126,10 @@
         <v>2.9</v>
       </c>
       <c r="M64">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="1">
         <v>76</v>
       </c>
@@ -3156,7 +3146,7 @@
         <v>1.05</v>
       </c>
       <c r="F65">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G65" t="s">
         <v>89</v>
@@ -3165,7 +3155,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3174,10 +3164,10 @@
         <v>2.9</v>
       </c>
       <c r="M65">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="1">
         <v>79</v>
       </c>
@@ -3194,7 +3184,7 @@
         <v>0.15</v>
       </c>
       <c r="F66">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G66" t="s">
         <v>89</v>
@@ -3203,7 +3193,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3212,10 +3202,10 @@
         <v>2.9</v>
       </c>
       <c r="M66">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="1">
         <v>78</v>
       </c>
@@ -3232,7 +3222,7 @@
         <v>0.15</v>
       </c>
       <c r="F67">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G67" t="s">
         <v>89</v>
@@ -3241,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3250,10 +3240,10 @@
         <v>2.9</v>
       </c>
       <c r="M67">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="1">
         <v>77</v>
       </c>
@@ -3270,7 +3260,7 @@
         <v>0.6</v>
       </c>
       <c r="F68">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G68" t="s">
         <v>89</v>
@@ -3279,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3288,10 +3278,10 @@
         <v>2.9</v>
       </c>
       <c r="M68">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="1">
         <v>75</v>
       </c>
@@ -3308,7 +3298,7 @@
         <v>1.2</v>
       </c>
       <c r="F69">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G69" t="s">
         <v>89</v>
@@ -3317,7 +3307,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3326,10 +3316,10 @@
         <v>2.9</v>
       </c>
       <c r="M69">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="1">
         <v>74</v>
       </c>
@@ -3346,7 +3336,7 @@
         <v>0.6</v>
       </c>
       <c r="F70">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G70" t="s">
         <v>89</v>
@@ -3355,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3364,10 +3354,10 @@
         <v>2.9</v>
       </c>
       <c r="M70">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="1">
         <v>73</v>
       </c>
@@ -3384,7 +3374,7 @@
         <v>0.15</v>
       </c>
       <c r="F71">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G71" t="s">
         <v>89</v>
@@ -3393,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3402,10 +3392,10 @@
         <v>2.9</v>
       </c>
       <c r="M71">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -3422,7 +3412,7 @@
         <v>0.6</v>
       </c>
       <c r="F72">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G72" t="s">
         <v>89</v>
@@ -3431,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3440,10 +3430,10 @@
         <v>2.9</v>
       </c>
       <c r="M72">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="1">
         <v>70</v>
       </c>
@@ -3460,7 +3450,7 @@
         <v>0.15</v>
       </c>
       <c r="F73">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G73" t="s">
         <v>89</v>
@@ -3469,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -3478,10 +3468,10 @@
         <v>2.9</v>
       </c>
       <c r="M73">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="1">
         <v>80</v>
       </c>
@@ -3498,7 +3488,7 @@
         <v>0.6</v>
       </c>
       <c r="F74">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G74" t="s">
         <v>89</v>
@@ -3507,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3516,10 +3506,10 @@
         <v>2.9</v>
       </c>
       <c r="M74">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="1">
         <v>72</v>
       </c>
@@ -3536,7 +3526,7 @@
         <v>1.2</v>
       </c>
       <c r="F75">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G75" t="s">
         <v>89</v>
@@ -3545,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -3554,7 +3544,7 @@
         <v>2.9</v>
       </c>
       <c r="M75">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
     </row>
   </sheetData>
@@ -3563,11 +3553,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3611,15 +3601,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
         <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D2">
         <v>1.2</v>
@@ -3637,7 +3627,7 @@
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -3646,27 +3636,27 @@
         <v>0.96</v>
       </c>
       <c r="M2">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1">
         <v>237</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D3">
-        <v>1.2</v>
+        <v>1.202</v>
       </c>
       <c r="E3">
         <v>0.16</v>
       </c>
       <c r="F3">
-        <v>-0.18099999999999999</v>
+        <v>-0.181</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -3675,7 +3665,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3684,18 +3674,18 @@
         <v>0.96</v>
       </c>
       <c r="M3">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1">
         <v>238</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4">
         <v>1.8</v>
@@ -3713,7 +3703,7 @@
         <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -3722,27 +3712,27 @@
         <v>1.94</v>
       </c>
       <c r="M4">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
         <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5">
         <v>2.31</v>
       </c>
       <c r="E5">
-        <v>1.5049999999999999</v>
+        <v>1.505</v>
       </c>
       <c r="F5">
-        <v>0.54700000000000004</v>
+        <v>0.547</v>
       </c>
       <c r="G5" t="s">
         <v>89</v>
@@ -3751,7 +3741,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -3760,27 +3750,27 @@
         <v>2.9</v>
       </c>
       <c r="M5">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
         <v>235</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6">
-        <v>1.2849999999999999</v>
+        <v>1.285</v>
       </c>
       <c r="E6">
-        <v>1.5920000000000001</v>
+        <v>1.592</v>
       </c>
       <c r="F6">
-        <v>-2.4E-2</v>
+        <v>-0.024</v>
       </c>
       <c r="G6" t="s">
         <v>89</v>
@@ -3789,7 +3779,7 @@
         <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -3798,18 +3788,18 @@
         <v>2.9</v>
       </c>
       <c r="M6">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
         <v>231</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7">
         <v>2.31</v>
@@ -3818,7 +3808,7 @@
         <v>1.74</v>
       </c>
       <c r="F7">
-        <v>0.82499999999999996</v>
+        <v>0.825</v>
       </c>
       <c r="G7" t="s">
         <v>89</v>
@@ -3827,7 +3817,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -3836,27 +3826,27 @@
         <v>2.9</v>
       </c>
       <c r="M7">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>233</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D8">
         <v>1.41</v>
       </c>
       <c r="E8">
-        <v>1.6919999999999999</v>
+        <v>1.692</v>
       </c>
       <c r="F8">
-        <v>0.82499999999999996</v>
+        <v>0.825</v>
       </c>
       <c r="G8" t="s">
         <v>89</v>
@@ -3865,7 +3855,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -3874,18 +3864,18 @@
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
         <v>230</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>1.06</v>
@@ -3894,7 +3884,7 @@
         <v>1.58</v>
       </c>
       <c r="F9">
-        <v>0.27500000000000002</v>
+        <v>0.275</v>
       </c>
       <c r="G9" t="s">
         <v>89</v>
@@ -3903,7 +3893,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -3912,7 +3902,7 @@
         <v>2.9</v>
       </c>
       <c r="M9">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
     </row>
   </sheetData>
@@ -3921,11 +3911,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:O1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3933,13 +3923,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="107">
   <si>
     <t>Marking type</t>
   </si>
@@ -63,226 +63,232 @@
     <t>Tile</t>
   </si>
   <si>
-    <t>TMP1S2a4:TMP1S2a4:1155192</t>
-  </si>
-  <si>
-    <t>TMP1S2f1:TMP1S2f1:1155220</t>
-  </si>
-  <si>
-    <t>TMP1S2f2:TMP1S2f2:1155219</t>
-  </si>
-  <si>
-    <t>TMP1S2f3:TMP1S2f3:1155218</t>
-  </si>
-  <si>
-    <t>TMP1S2e1:TMP1S2e1:1155215</t>
-  </si>
-  <si>
-    <t>TMP1S2e2:TMP1S2e2:1155214</t>
-  </si>
-  <si>
-    <t>TMP1S2e3:TMP1S2e3:1155213</t>
-  </si>
-  <si>
-    <t>TMP1S2e4:TMP1S2e4:1155212</t>
-  </si>
-  <si>
-    <t>TMP1S2d1:TMP1S2d1:1155210</t>
-  </si>
-  <si>
-    <t>TMP1S2d2:TMP1S2d2:1155209</t>
-  </si>
-  <si>
-    <t>TMP1S2d3:TMP1S2d3:1155208</t>
-  </si>
-  <si>
-    <t>TMP1S2d4:TMP1S2d4:1155207</t>
-  </si>
-  <si>
-    <t>TMP1S2f4:TMP1S2f4:1155217</t>
-  </si>
-  <si>
-    <t>TMP1S2c2:TMP1S2c2:1155204</t>
-  </si>
-  <si>
-    <t>TMP1S2c3:TMP1S2c3:1155203</t>
-  </si>
-  <si>
-    <t>TMP1S2c4:TMP1S2c4:1155202</t>
-  </si>
-  <si>
-    <t>TMP1S2b1:TMP1S2b1:1155200</t>
-  </si>
-  <si>
-    <t>TMP1S2b2:TMP1S2b2:1155199</t>
-  </si>
-  <si>
-    <t>TMP1S2b3:TMP1S2b3:1155198</t>
-  </si>
-  <si>
-    <t>TMP1S2b4:TMP1S2b4:1155197</t>
-  </si>
-  <si>
-    <t>TMP1S2a1:TMP1S2a1:1155195</t>
-  </si>
-  <si>
-    <t>TMP1S2a2:TMP1S2a2:1155194</t>
-  </si>
-  <si>
-    <t>TMP1S2a3:TMP1S2a3:1155193</t>
-  </si>
-  <si>
-    <t>TMP1S2c1:TMP1S2c1:1155205</t>
-  </si>
-  <si>
-    <t>TMP2S2c2:TMP2S2c2:1156962</t>
-  </si>
-  <si>
-    <t>TMP2S2c1:TMP2S2c1:1156963</t>
-  </si>
-  <si>
-    <t>TMP2S2a1:TMP2S2a1:1155225</t>
-  </si>
-  <si>
-    <t>TMP2S2b1:TMP2S2b1:1155223</t>
-  </si>
-  <si>
-    <t>TMP2S2b2:TMP2S2b2:1155222</t>
-  </si>
-  <si>
-    <t>TMP2S2a2:TMP2S2a2:1155224</t>
-  </si>
-  <si>
-    <t>TMP3S2b4:TMP3S2b4:1155227</t>
-  </si>
-  <si>
-    <t>TMP3S2b3:TMP3S2b3:1155228</t>
-  </si>
-  <si>
-    <t>TMP3S2b1:TMP3S2b1:1155229</t>
-  </si>
-  <si>
-    <t>TMP3S2b2:TMP3S2b2:1155230</t>
-  </si>
-  <si>
-    <t>TMP3S2a4:TMP3S2a4:1155231</t>
-  </si>
-  <si>
-    <t>TMP3S2a3:TMP3S2a3:1155232</t>
-  </si>
-  <si>
-    <t>TMP3S2a2:TMP3S2a2:1155233</t>
-  </si>
-  <si>
-    <t>TMP3S2a1:TMP3S2a1:1155234</t>
-  </si>
-  <si>
-    <t>TMP4S2a1:TMP4S2a1:1155243</t>
-  </si>
-  <si>
-    <t>TMP4S2a2:TMP4S2a2:1155242</t>
-  </si>
-  <si>
-    <t>TMP4S2b1:TMP4S2b1:1155240</t>
-  </si>
-  <si>
-    <t>TMP4S2b2:TMP4S2b2:1155239</t>
-  </si>
-  <si>
-    <t>TMP4S2b4:TMP4S2b4:1155236</t>
-  </si>
-  <si>
-    <t>TMP4S2a4:TMP4S2a4:1155237</t>
-  </si>
-  <si>
-    <t>TMP4S2b3:TMP4S2b3:1155238</t>
-  </si>
-  <si>
-    <t>TMP4S2a3:TMP4S2a3:1155241</t>
-  </si>
-  <si>
-    <t>TMP5S2a1:TMP5S2a1:1155252</t>
-  </si>
-  <si>
-    <t>TMP5S2b1:TMP5S2b1:1155251</t>
-  </si>
-  <si>
-    <t>TMP5S2a2:TMP5S2a2:1155249</t>
-  </si>
-  <si>
-    <t>TMP5S2a3:TMP5S2a3:1155247</t>
-  </si>
-  <si>
-    <t>TMP5S2b4:TMP5S2b4:1155246</t>
-  </si>
-  <si>
-    <t>TMP5S2b3:TMP5S2b3:1155248</t>
-  </si>
-  <si>
-    <t>TMP5S2b2:TMP5S2b2:1155250</t>
-  </si>
-  <si>
-    <t>TMP5S2a4:TMP5S2a4:1155245</t>
-  </si>
-  <si>
-    <t>TMP6S2a3:TMP6S2a3:1155254</t>
-  </si>
-  <si>
-    <t>TMP6S2a4:TMP6S2a4:1155255</t>
-  </si>
-  <si>
-    <t>TMP6S2a2:TMP6S2a2:1155256</t>
-  </si>
-  <si>
-    <t>TMP6S2a1:TMP6S2a1:1155257</t>
-  </si>
-  <si>
-    <t>TMP6S2b4:TMP6S2b4:1155259</t>
-  </si>
-  <si>
-    <t>TMP6S2b3:TMP6S2b3:1155260</t>
-  </si>
-  <si>
-    <t>TMP6S2b2:TMP6S2b2:1155261</t>
-  </si>
-  <si>
-    <t>TMP6S2b1:TMP6S2b1:1155262</t>
-  </si>
-  <si>
-    <t>TMP7S2c1:TMP7S2c1:1155276</t>
-  </si>
-  <si>
-    <t>TMP7S2d1:TMP7S2d1:1155271</t>
-  </si>
-  <si>
-    <t>TMP7S2c3:TMP7S2c3:1155274</t>
-  </si>
-  <si>
-    <t>TMP7S2d3:TMP7S2d3:1155273</t>
-  </si>
-  <si>
-    <t>TMP7S2d2:TMP7S2d2:1155272</t>
-  </si>
-  <si>
-    <t>TMP7S2a1:TMP7S2a1:1155269</t>
-  </si>
-  <si>
-    <t>TMP7S2a2:TMP7S2a2:1155268</t>
-  </si>
-  <si>
-    <t>TMP7S2a3:TMP7S2a3:1155267</t>
-  </si>
-  <si>
-    <t>TMP7S2b2:TMP7S2b2:1155265</t>
-  </si>
-  <si>
-    <t>TMP7S2b3:TMP7S2b3:1155264</t>
-  </si>
-  <si>
-    <t>TMP7S2c2:TMP7S2c2:1155275</t>
-  </si>
-  <si>
-    <t>TMP7S2b1:TMP7S2b1:1155266</t>
+    <t>TMP1S2c2</t>
+  </si>
+  <si>
+    <t>TMP1S2d3</t>
+  </si>
+  <si>
+    <t>TMP1S2d2</t>
+  </si>
+  <si>
+    <t>TMP1S2d1</t>
+  </si>
+  <si>
+    <t>TMP1S2c4</t>
+  </si>
+  <si>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
+    <t>TMP1S2e2</t>
+  </si>
+  <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
+    <t>TMP1S2b2</t>
+  </si>
+  <si>
+    <t>TMP1S2d4</t>
+  </si>
+  <si>
+    <t>TMP1S2b1</t>
+  </si>
+  <si>
+    <t>TMP1S2a3</t>
+  </si>
+  <si>
+    <t>TMP1S2a2</t>
+  </si>
+  <si>
+    <t>TMP1S2a1</t>
+  </si>
+  <si>
+    <t>TMP1S2e3</t>
+  </si>
+  <si>
+    <t>TMP1S2e4</t>
+  </si>
+  <si>
+    <t>TMP1S2f1</t>
+  </si>
+  <si>
+    <t>TMP1S2f2</t>
+  </si>
+  <si>
+    <t>TMP1S2f3</t>
+  </si>
+  <si>
+    <t>TMP1S2f4</t>
+  </si>
+  <si>
+    <t>TMP1S2a4</t>
+  </si>
+  <si>
+    <t>TMP1S2e1</t>
+  </si>
+  <si>
+    <t>TMP2S2c1</t>
+  </si>
+  <si>
+    <t>TMP2S2c3</t>
+  </si>
+  <si>
+    <t>TMP2S2c2</t>
+  </si>
+  <si>
+    <t>TMP2S2c4</t>
+  </si>
+  <si>
+    <t>TMP3S2a1</t>
+  </si>
+  <si>
+    <t>TMP3S2a2</t>
+  </si>
+  <si>
+    <t>TMP3S2a3</t>
+  </si>
+  <si>
+    <t>TMP3S2a4</t>
+  </si>
+  <si>
+    <t>TMP3S2b1</t>
+  </si>
+  <si>
+    <t>TMP3S2b3</t>
+  </si>
+  <si>
+    <t>TMP3S2b4</t>
+  </si>
+  <si>
+    <t>TMP3S2b2</t>
+  </si>
+  <si>
+    <t>TMP4S2b4</t>
+  </si>
+  <si>
+    <t>TMP4S2b3</t>
+  </si>
+  <si>
+    <t>TMP4S2a1</t>
+  </si>
+  <si>
+    <t>TMP4S2a2</t>
+  </si>
+  <si>
+    <t>TMP4S2a3</t>
+  </si>
+  <si>
+    <t>TMP4S2a4</t>
+  </si>
+  <si>
+    <t>TMP4S2b1</t>
+  </si>
+  <si>
+    <t>TMP4S2b2</t>
+  </si>
+  <si>
+    <t>TMP5S2a4</t>
+  </si>
+  <si>
+    <t>TMP5S2a3</t>
+  </si>
+  <si>
+    <t>TMP5S2a2</t>
+  </si>
+  <si>
+    <t>TMP5S2a1</t>
+  </si>
+  <si>
+    <t>TMP6S2b1</t>
+  </si>
+  <si>
+    <t>TMP6S2a1</t>
+  </si>
+  <si>
+    <t>TMP6S2a2</t>
+  </si>
+  <si>
+    <t>TMP6S2a3</t>
+  </si>
+  <si>
+    <t>TMP6S2a4</t>
+  </si>
+  <si>
+    <t>TMP6S2b4</t>
+  </si>
+  <si>
+    <t>TMP6S2b2</t>
+  </si>
+  <si>
+    <t>TMP6S2b3</t>
+  </si>
+  <si>
+    <t>TMP7S2b3</t>
+  </si>
+  <si>
+    <t>TMP7S2b4</t>
+  </si>
+  <si>
+    <t>TMP7S2b5</t>
+  </si>
+  <si>
+    <t>TMP7S2b6</t>
+  </si>
+  <si>
+    <t>TMP7S2b7</t>
+  </si>
+  <si>
+    <t>TMP7S2c1</t>
+  </si>
+  <si>
+    <t>TMP7S2c2</t>
+  </si>
+  <si>
+    <t>TMP7S2d1</t>
+  </si>
+  <si>
+    <t>TMP7S2b2</t>
+  </si>
+  <si>
+    <t>TMP7S2d2</t>
+  </si>
+  <si>
+    <t>TMP7S2b1</t>
+  </si>
+  <si>
+    <t>TMP7S2a6</t>
+  </si>
+  <si>
+    <t>TMP7S2a5</t>
+  </si>
+  <si>
+    <t>TMP7S2a4</t>
+  </si>
+  <si>
+    <t>TMP7S2a3</t>
+  </si>
+  <si>
+    <t>TMP7S2a2</t>
+  </si>
+  <si>
+    <t>TMP7S2a1</t>
+  </si>
+  <si>
+    <t>TMP7S2e1</t>
+  </si>
+  <si>
+    <t>TMP7S2a7</t>
+  </si>
+  <si>
+    <t>TMP7S2e2</t>
   </si>
   <si>
     <t>F</t>
@@ -297,12 +303,12 @@
     <t>Fitting</t>
   </si>
   <si>
+    <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
+  </si>
+  <si>
     <t>BSS.GESSI.SM.49079:29046000:1090989</t>
   </si>
   <si>
-    <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
-  </si>
-  <si>
     <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
   </si>
   <si>
@@ -312,10 +318,10 @@
     <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
   </si>
   <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+  </si>
+  <si>
     <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
   </si>
   <si>
     <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
@@ -688,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -737,7 +743,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -749,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-1.35</v>
+        <v>0.47</v>
       </c>
       <c r="F2">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -761,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -775,7 +781,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>33</v>
+        <v>179</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -787,10 +793,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F3">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -799,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -813,7 +819,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>32</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -825,10 +831,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F4">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -837,7 +843,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -851,7 +857,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>31</v>
+        <v>177</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -863,10 +869,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F5">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -875,7 +881,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -889,7 +895,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -901,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F6">
         <v>1.025</v>
@@ -913,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -927,7 +933,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>28</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -939,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F7">
         <v>0.425</v>
@@ -951,7 +957,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -965,7 +971,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -977,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="F8">
         <v>-0.175</v>
@@ -989,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1003,7 +1009,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1015,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F9">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1027,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1041,7 +1047,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1053,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F10">
         <v>1.025</v>
@@ -1065,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1079,7 +1085,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1091,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F11">
         <v>0.425</v>
@@ -1103,7 +1109,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1117,7 +1123,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>23</v>
+        <v>170</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1129,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F12">
         <v>-0.175</v>
@@ -1141,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1155,7 +1161,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1167,10 +1173,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F13">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1179,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1193,7 +1199,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>30</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1205,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.9350000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="F14">
         <v>-0.775</v>
@@ -1217,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1231,7 +1237,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1243,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-0.03</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F15">
         <v>0.425</v>
@@ -1255,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1269,7 +1275,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>19</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1281,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-0.03</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F16">
         <v>-0.175</v>
@@ -1293,7 +1299,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1307,7 +1313,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1319,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>-0.03</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F17">
         <v>-0.775</v>
@@ -1331,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1345,7 +1351,7 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1360,7 +1366,7 @@
         <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1369,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1383,7 +1389,7 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>16</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1398,7 +1404,7 @@
         <v>-0.35</v>
       </c>
       <c r="F19">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1407,7 +1413,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1421,7 +1427,7 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1433,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.35</v>
+        <v>-1.35</v>
       </c>
       <c r="F20">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1445,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1459,7 +1465,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1471,10 +1477,10 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>-0.35</v>
+        <v>-1.35</v>
       </c>
       <c r="F21">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1483,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1497,7 +1503,7 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1512,7 +1518,7 @@
         <v>-1.35</v>
       </c>
       <c r="F22">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1521,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1535,7 +1541,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1550,7 +1556,7 @@
         <v>-1.35</v>
       </c>
       <c r="F23">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1559,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1573,7 +1579,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1585,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F24">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1597,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1611,7 +1617,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1623,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F25">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1635,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1649,7 +1655,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1658,13 +1664,13 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0.15</v>
       </c>
       <c r="F26">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1673,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1687,7 +1693,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>83</v>
+        <v>191</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1696,13 +1702,13 @@
         <v>40</v>
       </c>
       <c r="D27">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0.15</v>
       </c>
       <c r="F27">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1711,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1725,7 +1731,7 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>37</v>
+        <v>190</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1734,10 +1740,10 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>-0.5</v>
+        <v>0.15</v>
       </c>
       <c r="F28">
         <v>-0.175</v>
@@ -1749,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1763,7 +1769,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -1772,13 +1778,13 @@
         <v>42</v>
       </c>
       <c r="D29">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F29">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1787,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1801,7 +1807,7 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>34</v>
+        <v>193</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1810,28 +1816,28 @@
         <v>43</v>
       </c>
       <c r="D30">
-        <v>2.76</v>
+        <v>0.6</v>
       </c>
       <c r="E30">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>-0.775</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="L30">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="M30">
         <v>2.655</v>
@@ -1839,7 +1845,7 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1848,28 +1854,28 @@
         <v>44</v>
       </c>
       <c r="D31">
-        <v>2.76</v>
+        <v>0.6</v>
       </c>
       <c r="E31">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="L31">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="M31">
         <v>2.655</v>
@@ -1877,7 +1883,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -1886,13 +1892,13 @@
         <v>45</v>
       </c>
       <c r="D32">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E32">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -1901,7 +1907,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1915,7 +1921,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>39</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -1924,13 +1930,13 @@
         <v>46</v>
       </c>
       <c r="D33">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E33">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -1939,7 +1945,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1953,7 +1959,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>40</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -1962,13 +1968,13 @@
         <v>47</v>
       </c>
       <c r="D34">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E34">
         <v>0.445</v>
       </c>
       <c r="F34">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -1977,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1991,7 +1997,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>41</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2000,7 +2006,7 @@
         <v>48</v>
       </c>
       <c r="D35">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E35">
         <v>0.445</v>
@@ -2015,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2029,7 +2035,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2038,10 +2044,10 @@
         <v>49</v>
       </c>
       <c r="D36">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>0.445</v>
       </c>
       <c r="F36">
         <v>1.025</v>
@@ -2053,7 +2059,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2067,7 +2073,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2076,10 +2082,10 @@
         <v>50</v>
       </c>
       <c r="D37">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.445</v>
       </c>
       <c r="F37">
         <v>-0.175</v>
@@ -2091,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2105,7 +2111,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>44</v>
+        <v>208</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2114,28 +2120,28 @@
         <v>51</v>
       </c>
       <c r="D38">
-        <v>1.2</v>
+        <v>0.96</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="L38">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M38">
         <v>2.655</v>
@@ -2143,7 +2149,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>45</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2152,28 +2158,28 @@
         <v>52</v>
       </c>
       <c r="D39">
-        <v>1.2</v>
+        <v>0.96</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M39">
         <v>2.655</v>
@@ -2181,7 +2187,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2190,13 +2196,13 @@
         <v>53</v>
       </c>
       <c r="D40">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="E40">
         <v>-0.3</v>
       </c>
       <c r="F40">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -2205,7 +2211,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2219,7 +2225,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>52</v>
+        <v>202</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2228,13 +2234,13 @@
         <v>54</v>
       </c>
       <c r="D41">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="E41">
         <v>-0.3</v>
       </c>
       <c r="F41">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -2243,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -2257,7 +2263,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>50</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2266,13 +2272,13 @@
         <v>55</v>
       </c>
       <c r="D42">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F42">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -2281,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2295,7 +2301,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2304,13 +2310,13 @@
         <v>56</v>
       </c>
       <c r="D43">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F43">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -2319,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2333,7 +2339,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>46</v>
+        <v>205</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2342,7 +2348,7 @@
         <v>57</v>
       </c>
       <c r="D44">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2357,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2371,7 +2377,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>47</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2380,13 +2386,13 @@
         <v>58</v>
       </c>
       <c r="D45">
-        <v>1.8</v>
+        <v>0.96</v>
       </c>
       <c r="E45">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -2395,7 +2401,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2409,7 +2415,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>48</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2418,28 +2424,28 @@
         <v>59</v>
       </c>
       <c r="D46">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F46">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M46">
         <v>2.655</v>
@@ -2447,7 +2453,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>51</v>
+        <v>211</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2456,28 +2462,28 @@
         <v>60</v>
       </c>
       <c r="D47">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>-0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F47">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M47">
         <v>2.655</v>
@@ -2485,7 +2491,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>61</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2494,10 +2500,10 @@
         <v>61</v>
       </c>
       <c r="D48">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>-0.775</v>
@@ -2509,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2523,7 +2529,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2532,13 +2538,13 @@
         <v>62</v>
       </c>
       <c r="D49">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="F49">
-        <v>-0.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G49">
         <v>5</v>
@@ -2547,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2561,7 +2567,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>58</v>
+        <v>217</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2570,28 +2576,28 @@
         <v>63</v>
       </c>
       <c r="D50">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>0.15</v>
+        <v>-0.3</v>
       </c>
       <c r="F50">
-        <v>-0.775</v>
+        <v>-0.75</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="L50">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M50">
         <v>2.655</v>
@@ -2599,7 +2605,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>56</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2608,28 +2614,28 @@
         <v>64</v>
       </c>
       <c r="D51">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>-0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F51">
-        <v>-0.775</v>
+        <v>-0.75</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="L51">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M51">
         <v>2.655</v>
@@ -2637,7 +2643,7 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2646,28 +2652,28 @@
         <v>65</v>
       </c>
       <c r="D52">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>-0.9</v>
+        <v>0.3</v>
       </c>
       <c r="F52">
-        <v>-0.025</v>
+        <v>-0.15</v>
       </c>
       <c r="G52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M52">
         <v>2.655</v>
@@ -2675,7 +2681,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2684,28 +2690,28 @@
         <v>66</v>
       </c>
       <c r="D53">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>-0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F53">
-        <v>-0.025</v>
+        <v>0.45</v>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M53">
         <v>2.655</v>
@@ -2713,7 +2719,7 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>59</v>
+        <v>216</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2722,28 +2728,28 @@
         <v>67</v>
       </c>
       <c r="D54">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="F54">
-        <v>-0.025</v>
+        <v>1.05</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J54">
         <v>1</v>
       </c>
       <c r="L54">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M54">
         <v>2.655</v>
@@ -2751,7 +2757,7 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>54</v>
+        <v>220</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2760,28 +2766,28 @@
         <v>68</v>
       </c>
       <c r="D55">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>-0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="F55">
-        <v>-0.775</v>
+        <v>1.05</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J55">
         <v>1</v>
       </c>
       <c r="L55">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M55">
         <v>2.655</v>
@@ -2789,7 +2795,7 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1">
-        <v>62</v>
+        <v>218</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2804,7 +2810,7 @@
         <v>-0.3</v>
       </c>
       <c r="F56">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G56">
         <v>6</v>
@@ -2813,7 +2819,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2827,7 +2833,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2842,7 +2848,7 @@
         <v>-0.3</v>
       </c>
       <c r="F57">
-        <v>-0.15</v>
+        <v>0.45</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -2851,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2865,7 +2871,7 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>64</v>
+        <v>230</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -2874,36 +2880,36 @@
         <v>71</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E58">
-        <v>-0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F58">
-        <v>0.45</v>
-      </c>
-      <c r="G58">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
+        <v>91</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="L58">
+        <v>2.9</v>
+      </c>
+      <c r="M58">
         <v>1.932</v>
-      </c>
-      <c r="M58">
-        <v>2.655</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>65</v>
+        <v>231</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -2912,36 +2918,36 @@
         <v>72</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E59">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F59">
-        <v>1.05</v>
-      </c>
-      <c r="G59">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
+        <v>91</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="L59">
+        <v>2.9</v>
+      </c>
+      <c r="M59">
         <v>1.932</v>
-      </c>
-      <c r="M59">
-        <v>2.655</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>66</v>
+        <v>232</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -2950,36 +2956,36 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E60">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="F60">
-        <v>-0.75</v>
-      </c>
-      <c r="G60">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
+        <v>91</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
       <c r="L60">
+        <v>2.9</v>
+      </c>
+      <c r="M60">
         <v>1.932</v>
-      </c>
-      <c r="M60">
-        <v>2.655</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>67</v>
+        <v>233</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -2988,36 +2994,36 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E61">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="F61">
-        <v>-0.15</v>
-      </c>
-      <c r="G61">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>91</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="L61">
+        <v>2.9</v>
+      </c>
+      <c r="M61">
         <v>1.932</v>
-      </c>
-      <c r="M61">
-        <v>2.655</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>68</v>
+        <v>234</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3026,36 +3032,36 @@
         <v>75</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="E62">
-        <v>0.3</v>
+        <v>1.05</v>
       </c>
       <c r="F62">
-        <v>0.45</v>
-      </c>
-      <c r="G62">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G62" t="s">
+        <v>91</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J62">
         <v>1</v>
       </c>
       <c r="L62">
+        <v>2.9</v>
+      </c>
+      <c r="M62">
         <v>1.932</v>
-      </c>
-      <c r="M62">
-        <v>2.655</v>
       </c>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1">
-        <v>69</v>
+        <v>235</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3064,36 +3070,36 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="E63">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F63">
-        <v>1.05</v>
-      </c>
-      <c r="G63">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
+        <v>91</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J63">
         <v>1</v>
       </c>
       <c r="L63">
+        <v>2.9</v>
+      </c>
+      <c r="M63">
         <v>1.932</v>
-      </c>
-      <c r="M63">
-        <v>2.655</v>
       </c>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1">
-        <v>81</v>
+        <v>236</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3102,22 +3108,22 @@
         <v>77</v>
       </c>
       <c r="D64">
-        <v>0.72</v>
+        <v>1.41</v>
       </c>
       <c r="E64">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="F64">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3131,7 +3137,7 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1">
-        <v>76</v>
+        <v>237</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3140,22 +3146,22 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>0.12</v>
+        <v>2.01</v>
       </c>
       <c r="E65">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="F65">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3169,7 +3175,7 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1">
-        <v>79</v>
+        <v>229</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3181,19 +3187,19 @@
         <v>0.72</v>
       </c>
       <c r="E66">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="F66">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3207,7 +3213,7 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="1">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
@@ -3216,22 +3222,22 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>0.12</v>
+        <v>2.01</v>
       </c>
       <c r="E67">
-        <v>0.15</v>
+        <v>1.2</v>
       </c>
       <c r="F67">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3245,7 +3251,7 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="1">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3254,22 +3260,22 @@
         <v>81</v>
       </c>
       <c r="D68">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E68">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F68">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3283,7 +3289,7 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="1">
-        <v>75</v>
+        <v>226</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
@@ -3292,22 +3298,22 @@
         <v>82</v>
       </c>
       <c r="D69">
-        <v>2.31</v>
+        <v>0.12</v>
       </c>
       <c r="E69">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F69">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3321,7 +3327,7 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="1">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
@@ -3330,22 +3336,22 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>2.31</v>
+        <v>0.12</v>
       </c>
       <c r="E70">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F70">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3359,7 +3365,7 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="1">
-        <v>73</v>
+        <v>224</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -3368,22 +3374,22 @@
         <v>84</v>
       </c>
       <c r="D71">
-        <v>2.31</v>
+        <v>0.12</v>
       </c>
       <c r="E71">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="F71">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3397,7 +3403,7 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="1">
-        <v>71</v>
+        <v>223</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -3406,22 +3412,22 @@
         <v>85</v>
       </c>
       <c r="D72">
-        <v>1.41</v>
+        <v>0.12</v>
       </c>
       <c r="E72">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="F72">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3435,7 +3441,7 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="1">
-        <v>70</v>
+        <v>222</v>
       </c>
       <c r="B73" t="s">
         <v>14</v>
@@ -3444,22 +3450,22 @@
         <v>86</v>
       </c>
       <c r="D73">
-        <v>1.41</v>
+        <v>0.12</v>
       </c>
       <c r="E73">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="F73">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -3473,7 +3479,7 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="1">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="B74" t="s">
         <v>14</v>
@@ -3482,22 +3488,22 @@
         <v>87</v>
       </c>
       <c r="D74">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E74">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F74">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3511,7 +3517,7 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="1">
-        <v>72</v>
+        <v>239</v>
       </c>
       <c r="B75" t="s">
         <v>14</v>
@@ -3520,30 +3526,106 @@
         <v>88</v>
       </c>
       <c r="D75">
-        <v>1.41</v>
+        <v>2.61</v>
       </c>
       <c r="E75">
+        <v>0.6</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75" t="s">
+        <v>91</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>93</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>2.9</v>
+      </c>
+      <c r="M75">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" s="1">
+        <v>227</v>
+      </c>
+      <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" t="s">
+        <v>89</v>
+      </c>
+      <c r="D76">
+        <v>0.12</v>
+      </c>
+      <c r="E76">
+        <v>1.05</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76" t="s">
+        <v>91</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76" t="s">
+        <v>93</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="L76">
+        <v>2.9</v>
+      </c>
+      <c r="M76">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77" s="1">
+        <v>240</v>
+      </c>
+      <c r="B77" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" t="s">
+        <v>90</v>
+      </c>
+      <c r="D77">
+        <v>2.61</v>
+      </c>
+      <c r="E77">
         <v>1.2</v>
       </c>
-      <c r="F75">
-        <v>-0.025</v>
-      </c>
-      <c r="G75" t="s">
-        <v>89</v>
-      </c>
-      <c r="H75">
-        <v>1</v>
-      </c>
-      <c r="I75" t="s">
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
         <v>91</v>
       </c>
-      <c r="J75">
-        <v>1</v>
-      </c>
-      <c r="L75">
-        <v>2.9</v>
-      </c>
-      <c r="M75">
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77" t="s">
+        <v>93</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="L77">
+        <v>2.9</v>
+      </c>
+      <c r="M77">
         <v>1.932</v>
       </c>
     </row>
@@ -3603,31 +3685,31 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D2">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="E2">
-        <v>0.21</v>
+        <v>0.023</v>
       </c>
       <c r="F2">
-        <v>-0.05</v>
+        <v>0.387</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
-      <c r="H2">
-        <v>6</v>
+      <c r="H2" t="s">
+        <v>103</v>
       </c>
       <c r="I2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -3641,31 +3723,31 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>237</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3">
-        <v>1.202</v>
+        <v>0.6</v>
       </c>
       <c r="E3">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="F3">
-        <v>-0.181</v>
+        <v>-0.05</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
-      <c r="H3">
-        <v>6</v>
+      <c r="H3" t="s">
+        <v>103</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3679,16 +3761,16 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>238</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D4">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3699,11 +3781,11 @@
       <c r="G4">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>6</v>
+      <c r="H4" t="s">
+        <v>103</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -3717,13 +3799,13 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5">
         <v>2.31</v>
@@ -3735,13 +3817,13 @@
         <v>0.547</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
+        <v>91</v>
+      </c>
+      <c r="H5" t="s">
+        <v>103</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -3755,13 +3837,13 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>235</v>
+        <v>161</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D6">
         <v>1.285</v>
@@ -3773,13 +3855,13 @@
         <v>-0.024</v>
       </c>
       <c r="G6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
+        <v>91</v>
+      </c>
+      <c r="H6" t="s">
+        <v>103</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -3793,31 +3875,31 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>231</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>2.31</v>
+        <v>1.41</v>
       </c>
       <c r="E7">
-        <v>1.74</v>
+        <v>1.692</v>
       </c>
       <c r="F7">
         <v>0.825</v>
       </c>
       <c r="G7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
+        <v>91</v>
+      </c>
+      <c r="H7" t="s">
+        <v>103</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -3831,31 +3913,31 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>233</v>
+        <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D8">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="E8">
-        <v>1.692</v>
+        <v>1.74</v>
       </c>
       <c r="F8">
         <v>0.825</v>
       </c>
       <c r="G8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8">
-        <v>6</v>
+        <v>91</v>
+      </c>
+      <c r="H8" t="s">
+        <v>103</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -3869,13 +3951,13 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D9">
         <v>1.06</v>
@@ -3887,13 +3969,13 @@
         <v>0.275</v>
       </c>
       <c r="G9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9">
-        <v>6</v>
+        <v>91</v>
+      </c>
+      <c r="H9" t="s">
+        <v>103</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -3923,13 +4005,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C36591-1451-4A01-B2B1-DB5BA471FFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
     <sheet name="Stage 3" sheetId="2" r:id="rId2"/>
     <sheet name="Obstacles" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="106">
   <si>
     <t>Marking type</t>
   </si>
@@ -292,9 +298,6 @@
   </si>
   <si>
     <t>F</t>
-  </si>
-  <si>
-    <t>+</t>
   </si>
   <si>
     <t>blank</t>
@@ -342,8 +345,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -406,13 +409,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -450,7 +461,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -484,6 +495,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -518,9 +530,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -693,11 +706,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O77"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -741,7 +757,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>174</v>
       </c>
@@ -758,7 +774,7 @@
         <v>0.47</v>
       </c>
       <c r="F2">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -767,7 +783,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -776,10 +792,10 @@
         <v>2.9</v>
       </c>
       <c r="M2">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>179</v>
       </c>
@@ -796,7 +812,7 @@
         <v>-0.03</v>
       </c>
       <c r="F3">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -805,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -814,10 +830,10 @@
         <v>2.9</v>
       </c>
       <c r="M3">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>178</v>
       </c>
@@ -834,7 +850,7 @@
         <v>-0.03</v>
       </c>
       <c r="F4">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -843,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -852,10 +868,10 @@
         <v>2.9</v>
       </c>
       <c r="M4">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>177</v>
       </c>
@@ -872,7 +888,7 @@
         <v>-0.03</v>
       </c>
       <c r="F5">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -881,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -890,10 +906,10 @@
         <v>2.9</v>
       </c>
       <c r="M5">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>176</v>
       </c>
@@ -910,7 +926,7 @@
         <v>0.47</v>
       </c>
       <c r="F6">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -919,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -928,10 +944,10 @@
         <v>2.9</v>
       </c>
       <c r="M6">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>175</v>
       </c>
@@ -948,7 +964,7 @@
         <v>0.47</v>
       </c>
       <c r="F7">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -957,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -966,10 +982,10 @@
         <v>2.9</v>
       </c>
       <c r="M7">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>182</v>
       </c>
@@ -986,7 +1002,7 @@
         <v>-0.35</v>
       </c>
       <c r="F8">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -995,7 +1011,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1004,10 +1020,10 @@
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>173</v>
       </c>
@@ -1024,7 +1040,7 @@
         <v>0.47</v>
       </c>
       <c r="F9">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1033,7 +1049,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1042,10 +1058,10 @@
         <v>2.9</v>
       </c>
       <c r="M9">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>172</v>
       </c>
@@ -1062,7 +1078,7 @@
         <v>0.49</v>
       </c>
       <c r="F10">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1071,7 +1087,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1080,10 +1096,10 @@
         <v>2.9</v>
       </c>
       <c r="M10">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>171</v>
       </c>
@@ -1100,7 +1116,7 @@
         <v>0.49</v>
       </c>
       <c r="F11">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1109,7 +1125,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1118,10 +1134,10 @@
         <v>2.9</v>
       </c>
       <c r="M11">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>170</v>
       </c>
@@ -1138,7 +1154,7 @@
         <v>0.49</v>
       </c>
       <c r="F12">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1147,7 +1163,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1156,10 +1172,10 @@
         <v>2.9</v>
       </c>
       <c r="M12">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>180</v>
       </c>
@@ -1176,7 +1192,7 @@
         <v>-0.03</v>
       </c>
       <c r="F13">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1185,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1194,10 +1210,10 @@
         <v>2.9</v>
       </c>
       <c r="M13">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>169</v>
       </c>
@@ -1214,7 +1230,7 @@
         <v>0.49</v>
       </c>
       <c r="F14">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1223,7 +1239,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1232,10 +1248,10 @@
         <v>2.9</v>
       </c>
       <c r="M14">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>167</v>
       </c>
@@ -1249,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F15">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1261,7 +1277,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1270,10 +1286,10 @@
         <v>2.9</v>
       </c>
       <c r="M15">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>166</v>
       </c>
@@ -1287,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F16">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1299,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1308,10 +1324,10 @@
         <v>2.9</v>
       </c>
       <c r="M16">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>165</v>
       </c>
@@ -1325,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F17">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1337,7 +1353,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1346,10 +1362,10 @@
         <v>2.9</v>
       </c>
       <c r="M17">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>183</v>
       </c>
@@ -1366,7 +1382,7 @@
         <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1375,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1384,10 +1400,10 @@
         <v>2.9</v>
       </c>
       <c r="M18">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>184</v>
       </c>
@@ -1404,7 +1420,7 @@
         <v>-0.35</v>
       </c>
       <c r="F19">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1413,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1422,10 +1438,10 @@
         <v>2.9</v>
       </c>
       <c r="M19">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>185</v>
       </c>
@@ -1442,7 +1458,7 @@
         <v>-1.35</v>
       </c>
       <c r="F20">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1451,7 +1467,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1460,10 +1476,10 @@
         <v>2.9</v>
       </c>
       <c r="M20">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>186</v>
       </c>
@@ -1480,7 +1496,7 @@
         <v>-1.35</v>
       </c>
       <c r="F21">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1489,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1498,10 +1514,10 @@
         <v>2.9</v>
       </c>
       <c r="M21">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>187</v>
       </c>
@@ -1518,7 +1534,7 @@
         <v>-1.35</v>
       </c>
       <c r="F22">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1527,7 +1543,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1536,10 +1552,10 @@
         <v>2.9</v>
       </c>
       <c r="M22">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>188</v>
       </c>
@@ -1556,7 +1572,7 @@
         <v>-1.35</v>
       </c>
       <c r="F23">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1565,7 +1581,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1574,10 +1590,10 @@
         <v>2.9</v>
       </c>
       <c r="M23">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>168</v>
       </c>
@@ -1591,10 +1607,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F24">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1603,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1612,10 +1628,10 @@
         <v>2.9</v>
       </c>
       <c r="M24">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>181</v>
       </c>
@@ -1632,7 +1648,7 @@
         <v>-0.35</v>
       </c>
       <c r="F25">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1641,7 +1657,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1650,10 +1666,10 @@
         <v>2.9</v>
       </c>
       <c r="M25">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>189</v>
       </c>
@@ -1670,7 +1686,7 @@
         <v>0.15</v>
       </c>
       <c r="F26">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1679,7 +1695,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1688,10 +1704,10 @@
         <v>1.34</v>
       </c>
       <c r="M26">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>191</v>
       </c>
@@ -1708,7 +1724,7 @@
         <v>0.15</v>
       </c>
       <c r="F27">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1717,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1726,10 +1742,10 @@
         <v>1.34</v>
       </c>
       <c r="M27">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>190</v>
       </c>
@@ -1746,7 +1762,7 @@
         <v>0.15</v>
       </c>
       <c r="F28">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1755,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1764,10 +1780,10 @@
         <v>1.34</v>
       </c>
       <c r="M28">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>192</v>
       </c>
@@ -1784,7 +1800,7 @@
         <v>0.15</v>
       </c>
       <c r="F29">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1793,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1802,10 +1818,10 @@
         <v>1.34</v>
       </c>
       <c r="M29">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>193</v>
       </c>
@@ -1822,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -1831,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1840,10 +1856,10 @@
         <v>0.96</v>
       </c>
       <c r="M30">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>194</v>
       </c>
@@ -1860,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -1869,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1878,10 +1894,10 @@
         <v>0.96</v>
       </c>
       <c r="M31">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>195</v>
       </c>
@@ -1898,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -1907,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1916,10 +1932,10 @@
         <v>0.96</v>
       </c>
       <c r="M32">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>196</v>
       </c>
@@ -1936,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -1945,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1954,10 +1970,10 @@
         <v>0.96</v>
       </c>
       <c r="M33">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>197</v>
       </c>
@@ -1971,10 +1987,10 @@
         <v>0.6</v>
       </c>
       <c r="E34">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F34">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -1983,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1992,10 +2008,10 @@
         <v>0.96</v>
       </c>
       <c r="M34">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>199</v>
       </c>
@@ -2009,10 +2025,10 @@
         <v>0.6</v>
       </c>
       <c r="E35">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F35">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2021,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2030,10 +2046,10 @@
         <v>0.96</v>
       </c>
       <c r="M35">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>200</v>
       </c>
@@ -2047,10 +2063,10 @@
         <v>0.6</v>
       </c>
       <c r="E36">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F36">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -2059,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2068,10 +2084,10 @@
         <v>0.96</v>
       </c>
       <c r="M36">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>198</v>
       </c>
@@ -2085,10 +2101,10 @@
         <v>0.6</v>
       </c>
       <c r="E37">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F37">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -2097,7 +2113,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2106,10 +2122,10 @@
         <v>0.96</v>
       </c>
       <c r="M37">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>208</v>
       </c>
@@ -2126,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G38">
         <v>4</v>
@@ -2135,19 +2151,19 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="L38">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M38">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>207</v>
       </c>
@@ -2164,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G39">
         <v>4</v>
@@ -2173,19 +2189,19 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M39">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>201</v>
       </c>
@@ -2202,7 +2218,7 @@
         <v>-0.3</v>
       </c>
       <c r="F40">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -2211,19 +2227,19 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M40">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>202</v>
       </c>
@@ -2240,7 +2256,7 @@
         <v>-0.3</v>
       </c>
       <c r="F41">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -2249,19 +2265,19 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="L41">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M41">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>203</v>
       </c>
@@ -2278,7 +2294,7 @@
         <v>-0.3</v>
       </c>
       <c r="F42">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -2287,19 +2303,19 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M42">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>204</v>
       </c>
@@ -2316,7 +2332,7 @@
         <v>-0.3</v>
       </c>
       <c r="F43">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -2325,19 +2341,19 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M43">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>205</v>
       </c>
@@ -2354,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -2363,19 +2379,19 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M44">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>206</v>
       </c>
@@ -2392,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -2401,19 +2417,19 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M45">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>212</v>
       </c>
@@ -2430,7 +2446,7 @@
         <v>0.9</v>
       </c>
       <c r="F46">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G46">
         <v>5</v>
@@ -2439,7 +2455,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -2448,10 +2464,10 @@
         <v>1.94</v>
       </c>
       <c r="M46">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>211</v>
       </c>
@@ -2468,7 +2484,7 @@
         <v>0.45</v>
       </c>
       <c r="F47">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G47">
         <v>5</v>
@@ -2477,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2486,10 +2502,10 @@
         <v>1.94</v>
       </c>
       <c r="M47">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>210</v>
       </c>
@@ -2506,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G48">
         <v>5</v>
@@ -2515,7 +2531,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2524,10 +2540,10 @@
         <v>1.94</v>
       </c>
       <c r="M48">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>209</v>
       </c>
@@ -2544,7 +2560,7 @@
         <v>-0.45</v>
       </c>
       <c r="F49">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G49">
         <v>5</v>
@@ -2553,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2562,10 +2578,10 @@
         <v>1.94</v>
       </c>
       <c r="M49">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>217</v>
       </c>
@@ -2591,19 +2607,19 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="L50">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M50">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>213</v>
       </c>
@@ -2629,19 +2645,19 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="L51">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M51">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>214</v>
       </c>
@@ -2667,19 +2683,19 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M52">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>215</v>
       </c>
@@ -2705,19 +2721,19 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M53">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>216</v>
       </c>
@@ -2743,19 +2759,19 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J54">
         <v>1</v>
       </c>
       <c r="L54">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M54">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>220</v>
       </c>
@@ -2781,19 +2797,19 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J55">
         <v>1</v>
       </c>
       <c r="L55">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M55">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>218</v>
       </c>
@@ -2819,19 +2835,19 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J56">
         <v>1</v>
       </c>
       <c r="L56">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M56">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>219</v>
       </c>
@@ -2857,19 +2873,19 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J57">
         <v>1</v>
       </c>
       <c r="L57">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M57">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>230</v>
       </c>
@@ -2895,7 +2911,7 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -2904,10 +2920,10 @@
         <v>2.9</v>
       </c>
       <c r="M58">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>231</v>
       </c>
@@ -2933,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -2942,10 +2958,10 @@
         <v>2.9</v>
       </c>
       <c r="M59">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>232</v>
       </c>
@@ -2971,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -2980,10 +2996,10 @@
         <v>2.9</v>
       </c>
       <c r="M60">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>233</v>
       </c>
@@ -3009,7 +3025,7 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -3018,10 +3034,10 @@
         <v>2.9</v>
       </c>
       <c r="M61">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>234</v>
       </c>
@@ -3047,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3056,10 +3072,10 @@
         <v>2.9</v>
       </c>
       <c r="M62">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>235</v>
       </c>
@@ -3085,7 +3101,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3094,10 +3110,10 @@
         <v>2.9</v>
       </c>
       <c r="M63">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>236</v>
       </c>
@@ -3123,7 +3139,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3132,10 +3148,10 @@
         <v>2.9</v>
       </c>
       <c r="M64">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>237</v>
       </c>
@@ -3146,7 +3162,7 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E65">
         <v>0.6</v>
@@ -3161,7 +3177,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3170,10 +3186,10 @@
         <v>2.9</v>
       </c>
       <c r="M65">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>229</v>
       </c>
@@ -3199,7 +3215,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3208,10 +3224,10 @@
         <v>2.9</v>
       </c>
       <c r="M66">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>238</v>
       </c>
@@ -3222,7 +3238,7 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E67">
         <v>1.2</v>
@@ -3237,7 +3253,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3246,10 +3262,10 @@
         <v>2.9</v>
       </c>
       <c r="M67">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>228</v>
       </c>
@@ -3275,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3284,10 +3300,10 @@
         <v>2.9</v>
       </c>
       <c r="M68">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>226</v>
       </c>
@@ -3313,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3322,10 +3338,10 @@
         <v>2.9</v>
       </c>
       <c r="M69">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>225</v>
       </c>
@@ -3351,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3360,10 +3376,10 @@
         <v>2.9</v>
       </c>
       <c r="M70">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>224</v>
       </c>
@@ -3389,7 +3405,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3398,10 +3414,10 @@
         <v>2.9</v>
       </c>
       <c r="M71">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>223</v>
       </c>
@@ -3427,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3436,10 +3452,10 @@
         <v>2.9</v>
       </c>
       <c r="M72">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>222</v>
       </c>
@@ -3465,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -3474,10 +3490,10 @@
         <v>2.9</v>
       </c>
       <c r="M73">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>221</v>
       </c>
@@ -3503,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3512,10 +3528,10 @@
         <v>2.9</v>
       </c>
       <c r="M74">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>239</v>
       </c>
@@ -3541,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -3550,10 +3566,10 @@
         <v>2.9</v>
       </c>
       <c r="M75">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>227</v>
       </c>
@@ -3579,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -3588,10 +3604,10 @@
         <v>2.9</v>
       </c>
       <c r="M76">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>240</v>
       </c>
@@ -3617,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -3626,7 +3642,7 @@
         <v>2.9</v>
       </c>
       <c r="M77">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3635,11 +3651,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="80.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3683,33 +3702,33 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>163</v>
       </c>
       <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s">
         <v>94</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
       </c>
       <c r="D2">
         <v>0.6</v>
       </c>
       <c r="E2">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="F2">
-        <v>0.387</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -3718,18 +3737,18 @@
         <v>0.96</v>
       </c>
       <c r="M2">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3">
         <v>0.6</v>
@@ -3744,10 +3763,10 @@
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3756,18 +3775,18 @@
         <v>0.96</v>
       </c>
       <c r="M3">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -3782,10 +3801,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -3794,36 +3813,36 @@
         <v>1.94</v>
       </c>
       <c r="M4">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5">
         <v>2.31</v>
       </c>
       <c r="E5">
-        <v>1.505</v>
+        <v>1.5049999999999999</v>
       </c>
       <c r="F5">
-        <v>0.547</v>
-      </c>
-      <c r="G5" t="s">
-        <v>91</v>
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
       </c>
       <c r="H5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -3832,36 +3851,36 @@
         <v>2.9</v>
       </c>
       <c r="M5">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>161</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6">
-        <v>1.285</v>
+        <v>1.2849999999999999</v>
       </c>
       <c r="E6">
-        <v>1.592</v>
+        <v>1.5920000000000001</v>
       </c>
       <c r="F6">
-        <v>-0.024</v>
-      </c>
-      <c r="G6" t="s">
-        <v>91</v>
+        <v>-2.4E-2</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -3870,36 +3889,36 @@
         <v>2.9</v>
       </c>
       <c r="M6">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>159</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7">
         <v>1.41</v>
       </c>
       <c r="E7">
-        <v>1.692</v>
+        <v>1.6919999999999999</v>
       </c>
       <c r="F7">
-        <v>0.825</v>
-      </c>
-      <c r="G7" t="s">
-        <v>91</v>
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -3908,18 +3927,18 @@
         <v>2.9</v>
       </c>
       <c r="M7">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>2.31</v>
@@ -3928,16 +3947,16 @@
         <v>1.74</v>
       </c>
       <c r="F8">
-        <v>0.825</v>
-      </c>
-      <c r="G8" t="s">
-        <v>91</v>
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -3946,18 +3965,18 @@
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>156</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9">
         <v>1.06</v>
@@ -3966,16 +3985,16 @@
         <v>1.58</v>
       </c>
       <c r="F9">
-        <v>0.275</v>
-      </c>
-      <c r="G9" t="s">
-        <v>91</v>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -3984,7 +4003,7 @@
         <v>2.9</v>
       </c>
       <c r="M9">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3993,11 +4012,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:O1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:15">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4005,13 +4024,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C36591-1451-4A01-B2B1-DB5BA471FFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
     <sheet name="Stage 3" sheetId="2" r:id="rId2"/>
     <sheet name="Obstacles" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="107">
   <si>
     <t>Marking type</t>
   </si>
@@ -298,6 +292,9 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>+</t>
   </si>
   <si>
     <t>blank</t>
@@ -345,8 +342,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,21 +406,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -461,7 +450,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -495,7 +484,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -530,10 +518,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -706,14 +693,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="4" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -757,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
         <v>174</v>
       </c>
@@ -774,7 +758,7 @@
         <v>0.47</v>
       </c>
       <c r="F2">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -783,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -792,10 +776,10 @@
         <v>2.9</v>
       </c>
       <c r="M2">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1">
         <v>179</v>
       </c>
@@ -812,7 +796,7 @@
         <v>-0.03</v>
       </c>
       <c r="F3">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -821,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -830,10 +814,10 @@
         <v>2.9</v>
       </c>
       <c r="M3">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1">
         <v>178</v>
       </c>
@@ -850,7 +834,7 @@
         <v>-0.03</v>
       </c>
       <c r="F4">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -859,7 +843,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -868,10 +852,10 @@
         <v>2.9</v>
       </c>
       <c r="M4">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
         <v>177</v>
       </c>
@@ -888,7 +872,7 @@
         <v>-0.03</v>
       </c>
       <c r="F5">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -897,7 +881,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -906,10 +890,10 @@
         <v>2.9</v>
       </c>
       <c r="M5">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
         <v>176</v>
       </c>
@@ -926,7 +910,7 @@
         <v>0.47</v>
       </c>
       <c r="F6">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -935,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -944,10 +928,10 @@
         <v>2.9</v>
       </c>
       <c r="M6">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
         <v>175</v>
       </c>
@@ -964,7 +948,7 @@
         <v>0.47</v>
       </c>
       <c r="F7">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -973,7 +957,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -982,10 +966,10 @@
         <v>2.9</v>
       </c>
       <c r="M7">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>182</v>
       </c>
@@ -1002,7 +986,7 @@
         <v>-0.35</v>
       </c>
       <c r="F8">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1011,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1020,10 +1004,10 @@
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
         <v>173</v>
       </c>
@@ -1040,7 +1024,7 @@
         <v>0.47</v>
       </c>
       <c r="F9">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1049,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1058,10 +1042,10 @@
         <v>2.9</v>
       </c>
       <c r="M9">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1">
         <v>172</v>
       </c>
@@ -1078,7 +1062,7 @@
         <v>0.49</v>
       </c>
       <c r="F10">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1087,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1096,10 +1080,10 @@
         <v>2.9</v>
       </c>
       <c r="M10">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1">
         <v>171</v>
       </c>
@@ -1116,7 +1100,7 @@
         <v>0.49</v>
       </c>
       <c r="F11">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1125,7 +1109,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1134,10 +1118,10 @@
         <v>2.9</v>
       </c>
       <c r="M11">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1">
         <v>170</v>
       </c>
@@ -1154,7 +1138,7 @@
         <v>0.49</v>
       </c>
       <c r="F12">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1163,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1172,10 +1156,10 @@
         <v>2.9</v>
       </c>
       <c r="M12">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1">
         <v>180</v>
       </c>
@@ -1192,7 +1176,7 @@
         <v>-0.03</v>
       </c>
       <c r="F13">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1201,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1210,10 +1194,10 @@
         <v>2.9</v>
       </c>
       <c r="M13">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1">
         <v>169</v>
       </c>
@@ -1230,7 +1214,7 @@
         <v>0.49</v>
       </c>
       <c r="F14">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1239,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1248,10 +1232,10 @@
         <v>2.9</v>
       </c>
       <c r="M14">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1">
         <v>167</v>
       </c>
@@ -1265,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F15">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1277,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1286,10 +1270,10 @@
         <v>2.9</v>
       </c>
       <c r="M15">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="1">
         <v>166</v>
       </c>
@@ -1303,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F16">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1315,7 +1299,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1324,10 +1308,10 @@
         <v>2.9</v>
       </c>
       <c r="M16">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>165</v>
       </c>
@@ -1341,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F17">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1353,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1362,10 +1346,10 @@
         <v>2.9</v>
       </c>
       <c r="M17">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>183</v>
       </c>
@@ -1382,7 +1366,7 @@
         <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1391,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1400,10 +1384,10 @@
         <v>2.9</v>
       </c>
       <c r="M18">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>184</v>
       </c>
@@ -1420,7 +1404,7 @@
         <v>-0.35</v>
       </c>
       <c r="F19">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1429,7 +1413,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1438,10 +1422,10 @@
         <v>2.9</v>
       </c>
       <c r="M19">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>185</v>
       </c>
@@ -1458,7 +1442,7 @@
         <v>-1.35</v>
       </c>
       <c r="F20">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1467,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1476,10 +1460,10 @@
         <v>2.9</v>
       </c>
       <c r="M20">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>186</v>
       </c>
@@ -1496,7 +1480,7 @@
         <v>-1.35</v>
       </c>
       <c r="F21">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1505,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1514,10 +1498,10 @@
         <v>2.9</v>
       </c>
       <c r="M21">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>187</v>
       </c>
@@ -1534,7 +1518,7 @@
         <v>-1.35</v>
       </c>
       <c r="F22">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1543,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1552,10 +1536,10 @@
         <v>2.9</v>
       </c>
       <c r="M22">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <v>188</v>
       </c>
@@ -1572,7 +1556,7 @@
         <v>-1.35</v>
       </c>
       <c r="F23">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1581,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1590,10 +1574,10 @@
         <v>2.9</v>
       </c>
       <c r="M23">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>168</v>
       </c>
@@ -1607,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F24">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1619,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1628,10 +1612,10 @@
         <v>2.9</v>
       </c>
       <c r="M24">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <v>181</v>
       </c>
@@ -1648,7 +1632,7 @@
         <v>-0.35</v>
       </c>
       <c r="F25">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1657,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1666,10 +1650,10 @@
         <v>2.9</v>
       </c>
       <c r="M25">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
         <v>189</v>
       </c>
@@ -1686,7 +1670,7 @@
         <v>0.15</v>
       </c>
       <c r="F26">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1695,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1704,10 +1688,10 @@
         <v>1.34</v>
       </c>
       <c r="M26">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
         <v>191</v>
       </c>
@@ -1724,7 +1708,7 @@
         <v>0.15</v>
       </c>
       <c r="F27">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1733,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1742,10 +1726,10 @@
         <v>1.34</v>
       </c>
       <c r="M27">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
         <v>190</v>
       </c>
@@ -1762,7 +1746,7 @@
         <v>0.15</v>
       </c>
       <c r="F28">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1771,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1780,10 +1764,10 @@
         <v>1.34</v>
       </c>
       <c r="M28">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
         <v>192</v>
       </c>
@@ -1800,7 +1784,7 @@
         <v>0.15</v>
       </c>
       <c r="F29">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1809,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1818,10 +1802,10 @@
         <v>1.34</v>
       </c>
       <c r="M29">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
         <v>193</v>
       </c>
@@ -1838,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -1847,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1856,10 +1840,10 @@
         <v>0.96</v>
       </c>
       <c r="M30">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
         <v>194</v>
       </c>
@@ -1876,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -1885,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1894,10 +1878,10 @@
         <v>0.96</v>
       </c>
       <c r="M31">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
         <v>195</v>
       </c>
@@ -1914,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -1923,7 +1907,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1932,10 +1916,10 @@
         <v>0.96</v>
       </c>
       <c r="M32">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
         <v>196</v>
       </c>
@@ -1952,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -1961,7 +1945,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1970,10 +1954,10 @@
         <v>0.96</v>
       </c>
       <c r="M33">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
         <v>197</v>
       </c>
@@ -1987,10 +1971,10 @@
         <v>0.6</v>
       </c>
       <c r="E34">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="F34">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -1999,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2008,10 +1992,10 @@
         <v>0.96</v>
       </c>
       <c r="M34">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
         <v>199</v>
       </c>
@@ -2025,10 +2009,10 @@
         <v>0.6</v>
       </c>
       <c r="E35">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="F35">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2037,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2046,10 +2030,10 @@
         <v>0.96</v>
       </c>
       <c r="M35">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
         <v>200</v>
       </c>
@@ -2063,10 +2047,10 @@
         <v>0.6</v>
       </c>
       <c r="E36">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="F36">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -2075,7 +2059,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2084,10 +2068,10 @@
         <v>0.96</v>
       </c>
       <c r="M36">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1">
         <v>198</v>
       </c>
@@ -2101,10 +2085,10 @@
         <v>0.6</v>
       </c>
       <c r="E37">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="F37">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -2113,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2122,10 +2106,10 @@
         <v>0.96</v>
       </c>
       <c r="M37">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1">
         <v>208</v>
       </c>
@@ -2142,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G38">
         <v>4</v>
@@ -2151,19 +2135,19 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="L38">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M38">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
         <v>207</v>
       </c>
@@ -2180,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G39">
         <v>4</v>
@@ -2189,19 +2173,19 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M39">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
         <v>201</v>
       </c>
@@ -2218,7 +2202,7 @@
         <v>-0.3</v>
       </c>
       <c r="F40">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -2227,19 +2211,19 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M40">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="1">
         <v>202</v>
       </c>
@@ -2256,7 +2240,7 @@
         <v>-0.3</v>
       </c>
       <c r="F41">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -2265,19 +2249,19 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="L41">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M41">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="1">
         <v>203</v>
       </c>
@@ -2294,7 +2278,7 @@
         <v>-0.3</v>
       </c>
       <c r="F42">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -2303,19 +2287,19 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M42">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="1">
         <v>204</v>
       </c>
@@ -2332,7 +2316,7 @@
         <v>-0.3</v>
       </c>
       <c r="F43">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -2341,19 +2325,19 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M43">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="1">
         <v>205</v>
       </c>
@@ -2370,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -2379,19 +2363,19 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M44">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="1">
         <v>206</v>
       </c>
@@ -2408,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -2417,19 +2401,19 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M45">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="1">
         <v>212</v>
       </c>
@@ -2446,7 +2430,7 @@
         <v>0.9</v>
       </c>
       <c r="F46">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G46">
         <v>5</v>
@@ -2455,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -2464,10 +2448,10 @@
         <v>1.94</v>
       </c>
       <c r="M46">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="1">
         <v>211</v>
       </c>
@@ -2484,7 +2468,7 @@
         <v>0.45</v>
       </c>
       <c r="F47">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G47">
         <v>5</v>
@@ -2493,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2502,10 +2486,10 @@
         <v>1.94</v>
       </c>
       <c r="M47">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="1">
         <v>210</v>
       </c>
@@ -2522,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G48">
         <v>5</v>
@@ -2531,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2540,10 +2524,10 @@
         <v>1.94</v>
       </c>
       <c r="M48">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="1">
         <v>209</v>
       </c>
@@ -2560,7 +2544,7 @@
         <v>-0.45</v>
       </c>
       <c r="F49">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G49">
         <v>5</v>
@@ -2569,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2578,10 +2562,10 @@
         <v>1.94</v>
       </c>
       <c r="M49">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="1">
         <v>217</v>
       </c>
@@ -2607,19 +2591,19 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="L50">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M50">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="1">
         <v>213</v>
       </c>
@@ -2645,19 +2629,19 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="L51">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M51">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="1">
         <v>214</v>
       </c>
@@ -2683,19 +2667,19 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M52">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="1">
         <v>215</v>
       </c>
@@ -2721,19 +2705,19 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M53">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="1">
         <v>216</v>
       </c>
@@ -2759,19 +2743,19 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J54">
         <v>1</v>
       </c>
       <c r="L54">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M54">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="1">
         <v>220</v>
       </c>
@@ -2797,19 +2781,19 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J55">
         <v>1</v>
       </c>
       <c r="L55">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M55">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="1">
         <v>218</v>
       </c>
@@ -2835,19 +2819,19 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J56">
         <v>1</v>
       </c>
       <c r="L56">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M56">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="1">
         <v>219</v>
       </c>
@@ -2873,19 +2857,19 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J57">
         <v>1</v>
       </c>
       <c r="L57">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M57">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="1">
         <v>230</v>
       </c>
@@ -2911,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -2920,10 +2904,10 @@
         <v>2.9</v>
       </c>
       <c r="M58">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="1">
         <v>231</v>
       </c>
@@ -2949,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -2958,10 +2942,10 @@
         <v>2.9</v>
       </c>
       <c r="M59">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="1">
         <v>232</v>
       </c>
@@ -2987,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -2996,10 +2980,10 @@
         <v>2.9</v>
       </c>
       <c r="M60">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="1">
         <v>233</v>
       </c>
@@ -3025,7 +3009,7 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -3034,10 +3018,10 @@
         <v>2.9</v>
       </c>
       <c r="M61">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="1">
         <v>234</v>
       </c>
@@ -3063,7 +3047,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3072,10 +3056,10 @@
         <v>2.9</v>
       </c>
       <c r="M62">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="1">
         <v>235</v>
       </c>
@@ -3101,7 +3085,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3110,10 +3094,10 @@
         <v>2.9</v>
       </c>
       <c r="M63">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="1">
         <v>236</v>
       </c>
@@ -3139,7 +3123,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3148,10 +3132,10 @@
         <v>2.9</v>
       </c>
       <c r="M64">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="1">
         <v>237</v>
       </c>
@@ -3162,7 +3146,7 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>2.0099999999999998</v>
+        <v>2.01</v>
       </c>
       <c r="E65">
         <v>0.6</v>
@@ -3177,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3186,10 +3170,10 @@
         <v>2.9</v>
       </c>
       <c r="M65">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="1">
         <v>229</v>
       </c>
@@ -3215,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3224,10 +3208,10 @@
         <v>2.9</v>
       </c>
       <c r="M66">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="1">
         <v>238</v>
       </c>
@@ -3238,7 +3222,7 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>2.0099999999999998</v>
+        <v>2.01</v>
       </c>
       <c r="E67">
         <v>1.2</v>
@@ -3253,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3262,10 +3246,10 @@
         <v>2.9</v>
       </c>
       <c r="M67">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="1">
         <v>228</v>
       </c>
@@ -3291,7 +3275,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3300,10 +3284,10 @@
         <v>2.9</v>
       </c>
       <c r="M68">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="1">
         <v>226</v>
       </c>
@@ -3329,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3338,10 +3322,10 @@
         <v>2.9</v>
       </c>
       <c r="M69">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="1">
         <v>225</v>
       </c>
@@ -3367,7 +3351,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3376,10 +3360,10 @@
         <v>2.9</v>
       </c>
       <c r="M70">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="1">
         <v>224</v>
       </c>
@@ -3405,7 +3389,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3414,10 +3398,10 @@
         <v>2.9</v>
       </c>
       <c r="M71">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="1">
         <v>223</v>
       </c>
@@ -3443,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3452,10 +3436,10 @@
         <v>2.9</v>
       </c>
       <c r="M72">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="1">
         <v>222</v>
       </c>
@@ -3481,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -3490,10 +3474,10 @@
         <v>2.9</v>
       </c>
       <c r="M73">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="1">
         <v>221</v>
       </c>
@@ -3519,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3528,10 +3512,10 @@
         <v>2.9</v>
       </c>
       <c r="M74">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="1">
         <v>239</v>
       </c>
@@ -3557,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -3566,10 +3550,10 @@
         <v>2.9</v>
       </c>
       <c r="M75">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="1">
         <v>227</v>
       </c>
@@ -3595,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -3604,10 +3588,10 @@
         <v>2.9</v>
       </c>
       <c r="M76">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="1">
         <v>240</v>
       </c>
@@ -3633,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -3642,7 +3626,7 @@
         <v>2.9</v>
       </c>
       <c r="M77">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
     </row>
   </sheetData>
@@ -3651,14 +3635,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="80.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3702,33 +3683,33 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
         <v>163</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2">
         <v>0.6</v>
       </c>
       <c r="E2">
-        <v>2.3E-2</v>
+        <v>0.023</v>
       </c>
       <c r="F2">
-        <v>0.38700000000000001</v>
+        <v>0.387</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -3737,18 +3718,18 @@
         <v>0.96</v>
       </c>
       <c r="M2">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1">
         <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3">
         <v>0.6</v>
@@ -3763,10 +3744,10 @@
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3775,18 +3756,18 @@
         <v>0.96</v>
       </c>
       <c r="M3">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1">
         <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -3801,10 +3782,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -3813,36 +3794,36 @@
         <v>1.94</v>
       </c>
       <c r="M4">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D5">
         <v>2.31</v>
       </c>
       <c r="E5">
-        <v>1.5049999999999999</v>
+        <v>1.505</v>
       </c>
       <c r="F5">
-        <v>0.54700000000000004</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
+        <v>0.547</v>
+      </c>
+      <c r="G5" t="s">
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -3851,36 +3832,36 @@
         <v>2.9</v>
       </c>
       <c r="M5">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
         <v>161</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D6">
-        <v>1.2849999999999999</v>
+        <v>1.285</v>
       </c>
       <c r="E6">
-        <v>1.5920000000000001</v>
+        <v>1.592</v>
       </c>
       <c r="F6">
-        <v>-2.4E-2</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
+        <v>-0.024</v>
+      </c>
+      <c r="G6" t="s">
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -3889,36 +3870,36 @@
         <v>2.9</v>
       </c>
       <c r="M6">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
         <v>159</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>1.41</v>
       </c>
       <c r="E7">
-        <v>1.6919999999999999</v>
+        <v>1.692</v>
       </c>
       <c r="F7">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
+        <v>0.825</v>
+      </c>
+      <c r="G7" t="s">
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -3927,18 +3908,18 @@
         <v>2.9</v>
       </c>
       <c r="M7">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8">
         <v>2.31</v>
@@ -3947,16 +3928,16 @@
         <v>1.74</v>
       </c>
       <c r="F8">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
+        <v>0.825</v>
+      </c>
+      <c r="G8" t="s">
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -3965,18 +3946,18 @@
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
         <v>156</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D9">
         <v>1.06</v>
@@ -3985,16 +3966,16 @@
         <v>1.58</v>
       </c>
       <c r="F9">
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
+        <v>0.275</v>
+      </c>
+      <c r="G9" t="s">
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -4003,7 +3984,7 @@
         <v>2.9</v>
       </c>
       <c r="M9">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
     </row>
   </sheetData>
@@ -4012,11 +3993,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:O1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4024,13 +4005,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="120">
   <si>
     <t>Marking type</t>
   </si>
@@ -63,138 +63,150 @@
     <t>Tile</t>
   </si>
   <si>
+    <t>TMP1S2d1</t>
+  </si>
+  <si>
+    <t>TMP1S2c4</t>
+  </si>
+  <si>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
     <t>TMP1S2c2</t>
   </si>
   <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
+    <t>TMP1S2b2</t>
+  </si>
+  <si>
+    <t>TMP1S2b1</t>
+  </si>
+  <si>
+    <t>TMP1S2a4</t>
+  </si>
+  <si>
+    <t>TMP1S2a3</t>
+  </si>
+  <si>
+    <t>TMP1S2a2</t>
+  </si>
+  <si>
+    <t>TMP1S2a1</t>
+  </si>
+  <si>
+    <t>TMP1S2d4</t>
+  </si>
+  <si>
+    <t>TMP1S2e1</t>
+  </si>
+  <si>
+    <t>TMP1S2e2</t>
+  </si>
+  <si>
+    <t>TMP1S2e3</t>
+  </si>
+  <si>
+    <t>TMP1S2e4</t>
+  </si>
+  <si>
+    <t>TMP1S2f1</t>
+  </si>
+  <si>
+    <t>TMP1S2f2</t>
+  </si>
+  <si>
+    <t>TMP1S2f3</t>
+  </si>
+  <si>
+    <t>TMP1S2f4</t>
+  </si>
+  <si>
+    <t>TMP1S2d2</t>
+  </si>
+  <si>
     <t>TMP1S2d3</t>
   </si>
   <si>
-    <t>TMP1S2d2</t>
-  </si>
-  <si>
-    <t>TMP1S2d1</t>
-  </si>
-  <si>
-    <t>TMP1S2c4</t>
-  </si>
-  <si>
-    <t>TMP1S2c3</t>
-  </si>
-  <si>
-    <t>TMP1S2e2</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2b3</t>
-  </si>
-  <si>
-    <t>TMP1S2b2</t>
-  </si>
-  <si>
-    <t>TMP1S2d4</t>
-  </si>
-  <si>
-    <t>TMP1S2b1</t>
-  </si>
-  <si>
-    <t>TMP1S2a3</t>
-  </si>
-  <si>
-    <t>TMP1S2a2</t>
-  </si>
-  <si>
-    <t>TMP1S2a1</t>
-  </si>
-  <si>
-    <t>TMP1S2e3</t>
-  </si>
-  <si>
-    <t>TMP1S2e4</t>
-  </si>
-  <si>
-    <t>TMP1S2f1</t>
-  </si>
-  <si>
-    <t>TMP1S2f2</t>
-  </si>
-  <si>
-    <t>TMP1S2f3</t>
-  </si>
-  <si>
-    <t>TMP1S2f4</t>
-  </si>
-  <si>
-    <t>TMP1S2a4</t>
-  </si>
-  <si>
-    <t>TMP1S2e1</t>
+    <t>TMP2S2a1</t>
+  </si>
+  <si>
+    <t>TMP2S2a2</t>
+  </si>
+  <si>
+    <t>TMP2S2b1</t>
+  </si>
+  <si>
+    <t>TMP2S2b2</t>
   </si>
   <si>
     <t>TMP2S2c1</t>
   </si>
   <si>
+    <t>TMP2S2c2</t>
+  </si>
+  <si>
     <t>TMP2S2c3</t>
   </si>
   <si>
-    <t>TMP2S2c2</t>
-  </si>
-  <si>
     <t>TMP2S2c4</t>
   </si>
   <si>
+    <t>TMP3S2a3</t>
+  </si>
+  <si>
+    <t>TMP3S2a4</t>
+  </si>
+  <si>
+    <t>TMP3S2b1</t>
+  </si>
+  <si>
+    <t>TMP3S2b2</t>
+  </si>
+  <si>
+    <t>TMP3S2b3</t>
+  </si>
+  <si>
+    <t>TMP3S2b4</t>
+  </si>
+  <si>
+    <t>TMP3S2a2</t>
+  </si>
+  <si>
     <t>TMP3S2a1</t>
   </si>
   <si>
-    <t>TMP3S2a2</t>
-  </si>
-  <si>
-    <t>TMP3S2a3</t>
-  </si>
-  <si>
-    <t>TMP3S2a4</t>
-  </si>
-  <si>
-    <t>TMP3S2b1</t>
-  </si>
-  <si>
-    <t>TMP3S2b3</t>
-  </si>
-  <si>
-    <t>TMP3S2b4</t>
-  </si>
-  <si>
-    <t>TMP3S2b2</t>
+    <t>TMP4S2a3</t>
+  </si>
+  <si>
+    <t>TMP4S2a4</t>
+  </si>
+  <si>
+    <t>TMP4S2b1</t>
+  </si>
+  <si>
+    <t>TMP4S2b2</t>
+  </si>
+  <si>
+    <t>TMP4S2b3</t>
+  </si>
+  <si>
+    <t>TMP4S2a2</t>
+  </si>
+  <si>
+    <t>TMP4S2a1</t>
   </si>
   <si>
     <t>TMP4S2b4</t>
   </si>
   <si>
-    <t>TMP4S2b3</t>
-  </si>
-  <si>
-    <t>TMP4S2a1</t>
-  </si>
-  <si>
-    <t>TMP4S2a2</t>
-  </si>
-  <si>
-    <t>TMP4S2a3</t>
-  </si>
-  <si>
-    <t>TMP4S2a4</t>
-  </si>
-  <si>
-    <t>TMP4S2b1</t>
-  </si>
-  <si>
-    <t>TMP4S2b2</t>
-  </si>
-  <si>
     <t>TMP5S2a4</t>
   </si>
   <si>
@@ -207,87 +219,87 @@
     <t>TMP5S2a1</t>
   </si>
   <si>
+    <t>TMP6S2b4</t>
+  </si>
+  <si>
+    <t>TMP6S2b3</t>
+  </si>
+  <si>
+    <t>TMP6S2b2</t>
+  </si>
+  <si>
     <t>TMP6S2b1</t>
   </si>
   <si>
+    <t>TMP6S2a3</t>
+  </si>
+  <si>
+    <t>TMP6S2a2</t>
+  </si>
+  <si>
     <t>TMP6S2a1</t>
   </si>
   <si>
-    <t>TMP6S2a2</t>
-  </si>
-  <si>
-    <t>TMP6S2a3</t>
-  </si>
-  <si>
     <t>TMP6S2a4</t>
   </si>
   <si>
-    <t>TMP6S2b4</t>
-  </si>
-  <si>
-    <t>TMP6S2b2</t>
-  </si>
-  <si>
-    <t>TMP6S2b3</t>
+    <t>TMP7S2e1</t>
+  </si>
+  <si>
+    <t>TMP7S2d2</t>
+  </si>
+  <si>
+    <t>TMP7S2d1</t>
+  </si>
+  <si>
+    <t>TMP7S2c2</t>
+  </si>
+  <si>
+    <t>TMP7S2c1</t>
+  </si>
+  <si>
+    <t>TMP7S2b7</t>
+  </si>
+  <si>
+    <t>TMP7S2b6</t>
+  </si>
+  <si>
+    <t>TMP7S2b5</t>
+  </si>
+  <si>
+    <t>TMP7S2b4</t>
+  </si>
+  <si>
+    <t>TMP7S2b1</t>
+  </si>
+  <si>
+    <t>TMP7S2b2</t>
+  </si>
+  <si>
+    <t>TMP7S2a7</t>
+  </si>
+  <si>
+    <t>TMP7S2a6</t>
+  </si>
+  <si>
+    <t>TMP7S2a5</t>
+  </si>
+  <si>
+    <t>TMP7S2a4</t>
+  </si>
+  <si>
+    <t>TMP7S2a3</t>
+  </si>
+  <si>
+    <t>TMP7S2a2</t>
+  </si>
+  <si>
+    <t>TMP7S2a1</t>
   </si>
   <si>
     <t>TMP7S2b3</t>
   </si>
   <si>
-    <t>TMP7S2b4</t>
-  </si>
-  <si>
-    <t>TMP7S2b5</t>
-  </si>
-  <si>
-    <t>TMP7S2b6</t>
-  </si>
-  <si>
-    <t>TMP7S2b7</t>
-  </si>
-  <si>
-    <t>TMP7S2c1</t>
-  </si>
-  <si>
-    <t>TMP7S2c2</t>
-  </si>
-  <si>
-    <t>TMP7S2d1</t>
-  </si>
-  <si>
-    <t>TMP7S2b2</t>
-  </si>
-  <si>
-    <t>TMP7S2d2</t>
-  </si>
-  <si>
-    <t>TMP7S2b1</t>
-  </si>
-  <si>
-    <t>TMP7S2a6</t>
-  </si>
-  <si>
-    <t>TMP7S2a5</t>
-  </si>
-  <si>
-    <t>TMP7S2a4</t>
-  </si>
-  <si>
-    <t>TMP7S2a3</t>
-  </si>
-  <si>
-    <t>TMP7S2a2</t>
-  </si>
-  <si>
-    <t>TMP7S2a1</t>
-  </si>
-  <si>
-    <t>TMP7S2e1</t>
-  </si>
-  <si>
-    <t>TMP7S2a7</t>
-  </si>
-  <si>
     <t>TMP7S2e2</t>
   </si>
   <si>
@@ -303,28 +315,55 @@
     <t>Fitting</t>
   </si>
   <si>
+    <t>BSS.GOMGO.TR.GG-6108-600:Chrome 000:1090991</t>
+  </si>
+  <si>
     <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
   </si>
   <si>
     <t>BSS.GESSI.SM.49079:29046000:1090989</t>
   </si>
   <si>
+    <t>BSS.GOMGO.PH.GG-6106:Chrome 000:1090992</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
+  </si>
+  <si>
     <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
   </si>
   <si>
+    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+  </si>
+  <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+  </si>
+  <si>
+    <t>BSS.GESSI,BM.49001:Default:1090988</t>
+  </si>
+  <si>
+    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+  </si>
+  <si>
+    <t>BSS.TECE.CONCEALED CISTERN.9370224:BSS.TECE.CONCEALED CISTERN.9370224:1090923</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
+  </si>
+  <si>
     <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
-  </si>
-  <si>
-    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
-  </si>
-  <si>
-    <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
   </si>
   <si>
     <t>6</t>
@@ -694,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -743,7 +782,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -755,10 +794,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F2">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -767,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -781,7 +820,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -793,10 +832,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F3">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -805,7 +844,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -819,7 +858,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -831,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F4">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -843,7 +882,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -857,7 +896,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -869,10 +908,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F5">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -881,7 +920,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -895,7 +934,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -910,7 +949,7 @@
         <v>0.47</v>
       </c>
       <c r="F6">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -919,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -933,7 +972,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -945,10 +984,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F7">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -957,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -971,7 +1010,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -983,10 +1022,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F8">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -995,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1009,7 +1048,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1021,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F9">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1033,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1047,7 +1086,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1062,7 +1101,7 @@
         <v>0.49</v>
       </c>
       <c r="F10">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1071,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1085,7 +1124,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1097,10 +1136,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.49</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F11">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1109,7 +1148,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1123,7 +1162,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1135,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.49</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F12">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1147,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1161,7 +1200,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1173,10 +1212,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-0.03</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F13">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1185,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1199,7 +1238,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1211,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.49</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F14">
         <v>-0.775</v>
@@ -1223,7 +1262,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1237,7 +1276,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1249,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F15">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1261,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1275,7 +1314,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1287,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.9350000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="F16">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1299,7 +1338,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1313,7 +1352,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1325,10 +1364,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.9350000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="F17">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1337,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1375,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1413,7 +1452,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1451,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1489,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1527,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1565,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1579,7 +1618,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1591,10 +1630,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.9350000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="F24">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1603,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1617,7 +1656,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1629,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>-0.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F25">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1641,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1667,10 +1706,10 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="F26">
-        <v>-0.775</v>
+        <v>-0.75</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1679,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1693,7 +1732,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1705,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="F27">
-        <v>0.425</v>
+        <v>-0.15</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1717,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1731,7 +1770,7 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1743,10 +1782,10 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F28">
-        <v>-0.175</v>
+        <v>-0.75</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1755,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1781,10 +1820,10 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F29">
-        <v>1.025</v>
+        <v>-0.15</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1793,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1816,28 +1855,28 @@
         <v>43</v>
       </c>
       <c r="D30">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="F30">
-        <v>-0.775</v>
+        <v>-0.75</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="L30">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="M30">
         <v>2.655</v>
@@ -1854,28 +1893,28 @@
         <v>44</v>
       </c>
       <c r="D31">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="F31">
-        <v>-0.175</v>
+        <v>-0.15</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="L31">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="M31">
         <v>2.655</v>
@@ -1892,28 +1931,28 @@
         <v>45</v>
       </c>
       <c r="D32">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="F32">
-        <v>0.425</v>
+        <v>0.45</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="L32">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="M32">
         <v>2.655</v>
@@ -1930,28 +1969,28 @@
         <v>46</v>
       </c>
       <c r="D33">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="F33">
-        <v>1.025</v>
+        <v>1.05</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="L33">
-        <v>0.96</v>
+        <v>1.34</v>
       </c>
       <c r="M33">
         <v>2.655</v>
@@ -1959,7 +1998,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -1971,10 +2010,10 @@
         <v>0.6</v>
       </c>
       <c r="E34">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -1983,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1997,7 +2036,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2009,10 +2048,10 @@
         <v>0.6</v>
       </c>
       <c r="E35">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2021,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2035,7 +2074,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2050,7 +2089,7 @@
         <v>0.445</v>
       </c>
       <c r="F36">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -2059,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2073,7 +2112,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2097,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2111,7 +2150,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2120,28 +2159,28 @@
         <v>51</v>
       </c>
       <c r="D38">
+        <v>0.6</v>
+      </c>
+      <c r="E38">
+        <v>0.445</v>
+      </c>
+      <c r="F38">
+        <v>0.425</v>
+      </c>
+      <c r="G38">
+        <v>3</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>97</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="L38">
         <v>0.96</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>1.025</v>
-      </c>
-      <c r="G38">
-        <v>4</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>93</v>
-      </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
-      <c r="L38">
-        <v>0.592</v>
       </c>
       <c r="M38">
         <v>2.655</v>
@@ -2149,7 +2188,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2158,28 +2197,28 @@
         <v>52</v>
       </c>
       <c r="D39">
+        <v>0.6</v>
+      </c>
+      <c r="E39">
+        <v>0.445</v>
+      </c>
+      <c r="F39">
+        <v>1.025</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>97</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="L39">
         <v>0.96</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>0.425</v>
-      </c>
-      <c r="G39">
-        <v>4</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>93</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="L39">
-        <v>0.592</v>
       </c>
       <c r="M39">
         <v>2.655</v>
@@ -2187,7 +2226,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2196,28 +2235,28 @@
         <v>53</v>
       </c>
       <c r="D40">
+        <v>0.6</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>-0.175</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>97</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="L40">
         <v>0.96</v>
-      </c>
-      <c r="E40">
-        <v>-0.3</v>
-      </c>
-      <c r="F40">
-        <v>-0.775</v>
-      </c>
-      <c r="G40">
-        <v>4</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40" t="s">
-        <v>93</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="L40">
-        <v>0.592</v>
       </c>
       <c r="M40">
         <v>2.655</v>
@@ -2225,7 +2264,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2234,28 +2273,28 @@
         <v>54</v>
       </c>
       <c r="D41">
+        <v>0.6</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>-0.775</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>97</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="L41">
         <v>0.96</v>
-      </c>
-      <c r="E41">
-        <v>-0.3</v>
-      </c>
-      <c r="F41">
-        <v>-0.175</v>
-      </c>
-      <c r="G41">
-        <v>4</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>93</v>
-      </c>
-      <c r="J41">
-        <v>1</v>
-      </c>
-      <c r="L41">
-        <v>0.592</v>
       </c>
       <c r="M41">
         <v>2.655</v>
@@ -2263,7 +2302,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2287,7 +2326,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2301,7 +2340,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2325,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2339,7 +2378,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2363,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2377,7 +2416,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2401,7 +2440,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2415,7 +2454,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2424,28 +2463,28 @@
         <v>59</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E46">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M46">
         <v>2.655</v>
@@ -2453,7 +2492,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2462,28 +2501,28 @@
         <v>60</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E47">
-        <v>0.45</v>
+        <v>-0.3</v>
       </c>
       <c r="F47">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M47">
         <v>2.655</v>
@@ -2491,7 +2530,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2500,28 +2539,28 @@
         <v>61</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F48">
         <v>-0.775</v>
       </c>
       <c r="G48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J48">
         <v>1</v>
       </c>
       <c r="L48">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M48">
         <v>2.655</v>
@@ -2529,7 +2568,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2538,28 +2577,28 @@
         <v>62</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E49">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="L49">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M49">
         <v>2.655</v>
@@ -2567,7 +2606,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2579,25 +2618,25 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>-0.3</v>
+        <v>0.9</v>
       </c>
       <c r="F50">
-        <v>-0.75</v>
+        <v>-0.775</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="L50">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M50">
         <v>2.655</v>
@@ -2605,7 +2644,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2617,25 +2656,25 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F51">
-        <v>-0.75</v>
+        <v>-0.775</v>
       </c>
       <c r="G51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="L51">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M51">
         <v>2.655</v>
@@ -2655,25 +2694,25 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>-0.15</v>
+        <v>-0.775</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M52">
         <v>2.655</v>
@@ -2681,7 +2720,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2693,25 +2732,25 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>0.3</v>
+        <v>-0.45</v>
       </c>
       <c r="F53">
-        <v>0.45</v>
+        <v>-0.775</v>
       </c>
       <c r="G53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M53">
         <v>2.655</v>
@@ -2719,7 +2758,7 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2731,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F54">
-        <v>1.05</v>
+        <v>1.025</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -2743,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2757,7 +2796,7 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2772,7 +2811,7 @@
         <v>-0.3</v>
       </c>
       <c r="F55">
-        <v>1.05</v>
+        <v>0.425</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -2781,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2795,7 +2834,7 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2810,7 +2849,7 @@
         <v>-0.3</v>
       </c>
       <c r="F56">
-        <v>-0.15</v>
+        <v>-0.175</v>
       </c>
       <c r="G56">
         <v>6</v>
@@ -2819,7 +2858,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2833,7 +2872,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2848,7 +2887,7 @@
         <v>-0.3</v>
       </c>
       <c r="F57">
-        <v>0.45</v>
+        <v>-0.775</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -2857,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2871,7 +2910,7 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -2880,36 +2919,36 @@
         <v>71</v>
       </c>
       <c r="D58">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58" t="s">
-        <v>91</v>
+        <v>0.425</v>
+      </c>
+      <c r="G58">
+        <v>6</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="L58">
-        <v>2.9</v>
+        <v>1.932</v>
       </c>
       <c r="M58">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -2918,36 +2957,36 @@
         <v>72</v>
       </c>
       <c r="D59">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59" t="s">
-        <v>91</v>
+        <v>-0.175</v>
+      </c>
+      <c r="G59">
+        <v>6</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="L59">
-        <v>2.9</v>
+        <v>1.932</v>
       </c>
       <c r="M59">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -2956,36 +2995,36 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60" t="s">
-        <v>91</v>
+        <v>-0.775</v>
+      </c>
+      <c r="G60">
+        <v>6</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
       <c r="L60">
-        <v>2.9</v>
+        <v>1.932</v>
       </c>
       <c r="M60">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -2994,36 +3033,36 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61" t="s">
-        <v>91</v>
+        <v>1.025</v>
+      </c>
+      <c r="G61">
+        <v>6</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="L61">
-        <v>2.9</v>
+        <v>1.932</v>
       </c>
       <c r="M61">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3032,22 +3071,22 @@
         <v>75</v>
       </c>
       <c r="D62">
-        <v>0.72</v>
+        <v>2.61</v>
       </c>
       <c r="E62">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3061,7 +3100,7 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3070,22 +3109,22 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="E63">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3099,7 +3138,7 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3108,22 +3147,22 @@
         <v>77</v>
       </c>
       <c r="D64">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="E64">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3137,7 +3176,7 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3146,22 +3185,22 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>2.01</v>
+        <v>1.41</v>
       </c>
       <c r="E65">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3175,7 +3214,7 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3184,22 +3223,22 @@
         <v>79</v>
       </c>
       <c r="D66">
-        <v>0.72</v>
+        <v>1.41</v>
       </c>
       <c r="E66">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3222,22 +3261,22 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>2.01</v>
+        <v>0.72</v>
       </c>
       <c r="E67">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3251,7 +3290,7 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="1">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3263,19 +3302,19 @@
         <v>0.72</v>
       </c>
       <c r="E68">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3289,7 +3328,7 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="1">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
@@ -3298,22 +3337,22 @@
         <v>82</v>
       </c>
       <c r="D69">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E69">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3327,7 +3366,7 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="1">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
@@ -3336,22 +3375,22 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E70">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3365,7 +3404,7 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="1">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -3374,22 +3413,22 @@
         <v>84</v>
       </c>
       <c r="D71">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E71">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3403,7 +3442,7 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="1">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -3412,22 +3451,22 @@
         <v>85</v>
       </c>
       <c r="D72">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E72">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F72">
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3441,7 +3480,7 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="1">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B73" t="s">
         <v>14</v>
@@ -3453,19 +3492,19 @@
         <v>0.12</v>
       </c>
       <c r="E73">
-        <v>0.3</v>
+        <v>1.05</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -3479,7 +3518,7 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="1">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B74" t="s">
         <v>14</v>
@@ -3491,19 +3530,19 @@
         <v>0.12</v>
       </c>
       <c r="E74">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3517,7 +3556,7 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="1">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B75" t="s">
         <v>14</v>
@@ -3526,22 +3565,22 @@
         <v>88</v>
       </c>
       <c r="D75">
-        <v>2.61</v>
+        <v>0.12</v>
       </c>
       <c r="E75">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -3555,7 +3594,7 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="1">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B76" t="s">
         <v>14</v>
@@ -3567,19 +3606,19 @@
         <v>0.12</v>
       </c>
       <c r="E76">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -3593,7 +3632,7 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="1">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="B77" t="s">
         <v>14</v>
@@ -3602,22 +3641,22 @@
         <v>90</v>
       </c>
       <c r="D77">
-        <v>2.61</v>
+        <v>0.12</v>
       </c>
       <c r="E77">
-        <v>1.2</v>
+        <v>0.45</v>
       </c>
       <c r="F77">
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -3626,6 +3665,158 @@
         <v>2.9</v>
       </c>
       <c r="M77">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="A78" s="1">
+        <v>226</v>
+      </c>
+      <c r="B78" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" t="s">
+        <v>91</v>
+      </c>
+      <c r="D78">
+        <v>0.12</v>
+      </c>
+      <c r="E78">
+        <v>0.3</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
+        <v>95</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78" t="s">
+        <v>97</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>2.9</v>
+      </c>
+      <c r="M78">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
+      <c r="A79" s="1">
+        <v>225</v>
+      </c>
+      <c r="B79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79" t="s">
+        <v>92</v>
+      </c>
+      <c r="D79">
+        <v>0.12</v>
+      </c>
+      <c r="E79">
+        <v>0.15</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
+        <v>95</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>97</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>2.9</v>
+      </c>
+      <c r="M79">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
+      <c r="A80" s="1">
+        <v>234</v>
+      </c>
+      <c r="B80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80" t="s">
+        <v>93</v>
+      </c>
+      <c r="D80">
+        <v>0.72</v>
+      </c>
+      <c r="E80">
+        <v>0.45</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
+        <v>95</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80" t="s">
+        <v>97</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="L80">
+        <v>2.9</v>
+      </c>
+      <c r="M80">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" s="1">
+        <v>244</v>
+      </c>
+      <c r="B81" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81" t="s">
+        <v>94</v>
+      </c>
+      <c r="D81">
+        <v>2.61</v>
+      </c>
+      <c r="E81">
+        <v>1.2</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81" t="s">
+        <v>95</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81" t="s">
+        <v>97</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>2.9</v>
+      </c>
+      <c r="M81">
         <v>1.932</v>
       </c>
     </row>
@@ -3636,7 +3827,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -3685,37 +3876,37 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>163</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D2">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0.023</v>
+        <v>0.06</v>
       </c>
       <c r="F2">
-        <v>0.387</v>
+        <v>0.175</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>0.96</v>
+        <v>2.9</v>
       </c>
       <c r="M2">
         <v>2.655</v>
@@ -3723,31 +3914,31 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>94</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>0.6</v>
       </c>
       <c r="E3">
-        <v>0.21</v>
+        <v>0.023</v>
       </c>
       <c r="F3">
-        <v>-0.05</v>
+        <v>0.387</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3761,37 +3952,37 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="F4">
-        <v>0.125</v>
+        <v>-0.05</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M4">
         <v>2.655</v>
@@ -3799,192 +3990,534 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D5">
-        <v>2.31</v>
+        <v>0.96</v>
       </c>
       <c r="E5">
-        <v>1.505</v>
+        <v>-0.17</v>
       </c>
       <c r="F5">
-        <v>0.547</v>
-      </c>
-      <c r="G5" t="s">
-        <v>91</v>
+        <v>-0.375</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>2.9</v>
+        <v>0.592</v>
       </c>
       <c r="M5">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>161</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D6">
-        <v>1.285</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E6">
-        <v>1.592</v>
+        <v>0.243</v>
       </c>
       <c r="F6">
-        <v>-0.024</v>
-      </c>
-      <c r="G6" t="s">
-        <v>91</v>
+        <v>-0.8</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2.9</v>
+        <v>0.592</v>
       </c>
       <c r="M6">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D7">
-        <v>1.41</v>
+        <v>0.86</v>
       </c>
       <c r="E7">
-        <v>1.692</v>
+        <v>0.508</v>
       </c>
       <c r="F7">
-        <v>0.825</v>
-      </c>
-      <c r="G7" t="s">
-        <v>91</v>
+        <v>1.468</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>2.9</v>
+        <v>0.592</v>
       </c>
       <c r="M7">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D8">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0.825</v>
-      </c>
-      <c r="G8" t="s">
-        <v>91</v>
+        <v>0.125</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M8">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
+        <v>161</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9">
+        <v>0.208</v>
+      </c>
+      <c r="E9">
+        <v>-0.575</v>
+      </c>
+      <c r="F9">
+        <v>-1.024</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1.94</v>
+      </c>
+      <c r="M9">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="1">
+        <v>159</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10">
+        <v>0.108</v>
+      </c>
+      <c r="E10">
+        <v>-0.45</v>
+      </c>
+      <c r="F10">
+        <v>-0.175</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1.94</v>
+      </c>
+      <c r="M10">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="1">
+        <v>157</v>
+      </c>
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11">
+        <v>0.06</v>
+      </c>
+      <c r="E11">
+        <v>0.45</v>
+      </c>
+      <c r="F11">
+        <v>-0.175</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1.94</v>
+      </c>
+      <c r="M11">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="1">
         <v>156</v>
       </c>
-      <c r="B9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9">
-        <v>1.06</v>
-      </c>
-      <c r="E9">
-        <v>1.58</v>
-      </c>
-      <c r="F9">
-        <v>0.275</v>
-      </c>
-      <c r="G9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>2.9</v>
-      </c>
-      <c r="M9">
-        <v>1.932</v>
+      <c r="B12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12">
+        <v>0.22</v>
+      </c>
+      <c r="E12">
+        <v>-0.8</v>
+      </c>
+      <c r="F12">
+        <v>-0.725</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1.94</v>
+      </c>
+      <c r="M12">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="1">
+        <v>155</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E13">
+        <v>-0.705</v>
+      </c>
+      <c r="F13">
+        <v>-1.2</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1.94</v>
+      </c>
+      <c r="M13">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="1">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14">
+        <v>0.435</v>
+      </c>
+      <c r="E14">
+        <v>-1.28</v>
+      </c>
+      <c r="F14">
+        <v>-0.79</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1.94</v>
+      </c>
+      <c r="M14">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="1">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15">
+        <v>-0.037</v>
+      </c>
+      <c r="E15">
+        <v>-0.8</v>
+      </c>
+      <c r="F15">
+        <v>-0.365</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I15" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1.94</v>
+      </c>
+      <c r="M15">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="1">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16">
+        <v>0.09</v>
+      </c>
+      <c r="E16">
+        <v>0.525</v>
+      </c>
+      <c r="F16">
+        <v>-0.825</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" t="s">
+        <v>97</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1.94</v>
+      </c>
+      <c r="M16">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="1">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17">
+        <v>0.15</v>
+      </c>
+      <c r="E17">
+        <v>0.375</v>
+      </c>
+      <c r="F17">
+        <v>-0.9</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="s">
+        <v>116</v>
+      </c>
+      <c r="I17" t="s">
+        <v>97</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1.94</v>
+      </c>
+      <c r="M17">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="1">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18">
+        <v>0.295</v>
+      </c>
+      <c r="E18">
+        <v>0.45</v>
+      </c>
+      <c r="F18">
+        <v>-0.453</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" t="s">
+        <v>97</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1.94</v>
+      </c>
+      <c r="M18">
+        <v>2.655</v>
       </c>
     </row>
   </sheetData>
@@ -4005,13 +4538,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D38385C-AFBF-4ACB-8C65-ED99160E463E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
     <sheet name="Stage 3" sheetId="2" r:id="rId2"/>
     <sheet name="Obstacles" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="119">
   <si>
     <t>Marking type</t>
   </si>
@@ -304,9 +310,6 @@
   </si>
   <si>
     <t>F</t>
-  </si>
-  <si>
-    <t>+</t>
   </si>
   <si>
     <t>blank</t>
@@ -381,8 +384,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,13 +448,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -489,7 +500,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -523,6 +534,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -557,9 +569,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -732,11 +745,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O81"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -780,7 +804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>177</v>
       </c>
@@ -797,7 +821,7 @@
         <v>-0.03</v>
       </c>
       <c r="F2">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -806,7 +830,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -815,10 +839,10 @@
         <v>2.9</v>
       </c>
       <c r="M2">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>176</v>
       </c>
@@ -835,7 +859,7 @@
         <v>0.47</v>
       </c>
       <c r="F3">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -844,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -853,10 +877,10 @@
         <v>2.9</v>
       </c>
       <c r="M3">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>175</v>
       </c>
@@ -873,7 +897,7 @@
         <v>0.47</v>
       </c>
       <c r="F4">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -882,7 +906,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -891,10 +915,10 @@
         <v>2.9</v>
       </c>
       <c r="M4">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>174</v>
       </c>
@@ -911,7 +935,7 @@
         <v>0.47</v>
       </c>
       <c r="F5">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -920,7 +944,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -929,10 +953,10 @@
         <v>2.9</v>
       </c>
       <c r="M5">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>173</v>
       </c>
@@ -949,7 +973,7 @@
         <v>0.47</v>
       </c>
       <c r="F6">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -958,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -967,10 +991,10 @@
         <v>2.9</v>
       </c>
       <c r="M6">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>172</v>
       </c>
@@ -987,7 +1011,7 @@
         <v>0.49</v>
       </c>
       <c r="F7">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -996,7 +1020,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1005,10 +1029,10 @@
         <v>2.9</v>
       </c>
       <c r="M7">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>171</v>
       </c>
@@ -1025,7 +1049,7 @@
         <v>0.49</v>
       </c>
       <c r="F8">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1034,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1043,10 +1067,10 @@
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>170</v>
       </c>
@@ -1063,7 +1087,7 @@
         <v>0.49</v>
       </c>
       <c r="F9">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1072,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1081,10 +1105,10 @@
         <v>2.9</v>
       </c>
       <c r="M9">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>169</v>
       </c>
@@ -1101,7 +1125,7 @@
         <v>0.49</v>
       </c>
       <c r="F10">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1110,7 +1134,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1119,10 +1143,10 @@
         <v>2.9</v>
       </c>
       <c r="M10">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>168</v>
       </c>
@@ -1136,10 +1160,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F11">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1148,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1157,10 +1181,10 @@
         <v>2.9</v>
       </c>
       <c r="M11">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>167</v>
       </c>
@@ -1174,10 +1198,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F12">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1186,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1195,10 +1219,10 @@
         <v>2.9</v>
       </c>
       <c r="M12">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>166</v>
       </c>
@@ -1212,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F13">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1224,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1233,10 +1257,10 @@
         <v>2.9</v>
       </c>
       <c r="M13">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>165</v>
       </c>
@@ -1250,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F14">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1262,7 +1286,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1271,10 +1295,10 @@
         <v>2.9</v>
       </c>
       <c r="M14">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>180</v>
       </c>
@@ -1291,7 +1315,7 @@
         <v>-0.03</v>
       </c>
       <c r="F15">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1300,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1309,10 +1333,10 @@
         <v>2.9</v>
       </c>
       <c r="M15">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>181</v>
       </c>
@@ -1329,7 +1353,7 @@
         <v>-0.35</v>
       </c>
       <c r="F16">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1338,7 +1362,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1347,10 +1371,10 @@
         <v>2.9</v>
       </c>
       <c r="M16">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>182</v>
       </c>
@@ -1367,7 +1391,7 @@
         <v>-0.35</v>
       </c>
       <c r="F17">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1376,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1385,10 +1409,10 @@
         <v>2.9</v>
       </c>
       <c r="M17">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>183</v>
       </c>
@@ -1405,7 +1429,7 @@
         <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1414,7 +1438,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1423,10 +1447,10 @@
         <v>2.9</v>
       </c>
       <c r="M18">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>184</v>
       </c>
@@ -1443,7 +1467,7 @@
         <v>-0.35</v>
       </c>
       <c r="F19">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1452,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1461,10 +1485,10 @@
         <v>2.9</v>
       </c>
       <c r="M19">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>185</v>
       </c>
@@ -1481,7 +1505,7 @@
         <v>-1.35</v>
       </c>
       <c r="F20">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1490,7 +1514,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1499,10 +1523,10 @@
         <v>2.9</v>
       </c>
       <c r="M20">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>186</v>
       </c>
@@ -1519,7 +1543,7 @@
         <v>-1.35</v>
       </c>
       <c r="F21">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1528,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1537,10 +1561,10 @@
         <v>2.9</v>
       </c>
       <c r="M21">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>187</v>
       </c>
@@ -1557,7 +1581,7 @@
         <v>-1.35</v>
       </c>
       <c r="F22">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1566,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1575,10 +1599,10 @@
         <v>2.9</v>
       </c>
       <c r="M22">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>188</v>
       </c>
@@ -1595,7 +1619,7 @@
         <v>-1.35</v>
       </c>
       <c r="F23">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1604,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1613,10 +1637,10 @@
         <v>2.9</v>
       </c>
       <c r="M23">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>178</v>
       </c>
@@ -1633,7 +1657,7 @@
         <v>-0.03</v>
       </c>
       <c r="F24">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1642,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1651,10 +1675,10 @@
         <v>2.9</v>
       </c>
       <c r="M24">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>179</v>
       </c>
@@ -1671,7 +1695,7 @@
         <v>-0.03</v>
       </c>
       <c r="F25">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1680,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1689,10 +1713,10 @@
         <v>2.9</v>
       </c>
       <c r="M25">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>189</v>
       </c>
@@ -1718,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1727,10 +1751,10 @@
         <v>1.34</v>
       </c>
       <c r="M26">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>190</v>
       </c>
@@ -1756,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1765,10 +1789,10 @@
         <v>1.34</v>
       </c>
       <c r="M27">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>191</v>
       </c>
@@ -1794,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1803,10 +1827,10 @@
         <v>1.34</v>
       </c>
       <c r="M28">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>192</v>
       </c>
@@ -1832,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1841,10 +1865,10 @@
         <v>1.34</v>
       </c>
       <c r="M29">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>193</v>
       </c>
@@ -1870,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1879,10 +1903,10 @@
         <v>1.34</v>
       </c>
       <c r="M30">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>194</v>
       </c>
@@ -1908,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1917,10 +1941,10 @@
         <v>1.34</v>
       </c>
       <c r="M31">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>195</v>
       </c>
@@ -1946,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1955,10 +1979,10 @@
         <v>1.34</v>
       </c>
       <c r="M32">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>196</v>
       </c>
@@ -1984,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -1993,10 +2017,10 @@
         <v>1.34</v>
       </c>
       <c r="M33">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>199</v>
       </c>
@@ -2013,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -2022,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2031,10 +2055,10 @@
         <v>0.96</v>
       </c>
       <c r="M34">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>200</v>
       </c>
@@ -2051,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2060,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2069,10 +2093,10 @@
         <v>0.96</v>
       </c>
       <c r="M35">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>201</v>
       </c>
@@ -2086,10 +2110,10 @@
         <v>0.6</v>
       </c>
       <c r="E36">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F36">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -2098,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2107,10 +2131,10 @@
         <v>0.96</v>
       </c>
       <c r="M36">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>202</v>
       </c>
@@ -2124,10 +2148,10 @@
         <v>0.6</v>
       </c>
       <c r="E37">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F37">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -2136,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2145,10 +2169,10 @@
         <v>0.96</v>
       </c>
       <c r="M37">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>203</v>
       </c>
@@ -2162,10 +2186,10 @@
         <v>0.6</v>
       </c>
       <c r="E38">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F38">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G38">
         <v>3</v>
@@ -2174,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2183,10 +2207,10 @@
         <v>0.96</v>
       </c>
       <c r="M38">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>204</v>
       </c>
@@ -2200,10 +2224,10 @@
         <v>0.6</v>
       </c>
       <c r="E39">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F39">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -2212,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2221,10 +2245,10 @@
         <v>0.96</v>
       </c>
       <c r="M39">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>198</v>
       </c>
@@ -2241,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -2250,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2259,10 +2283,10 @@
         <v>0.96</v>
       </c>
       <c r="M40">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>197</v>
       </c>
@@ -2279,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G41">
         <v>3</v>
@@ -2288,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -2297,10 +2321,10 @@
         <v>0.96</v>
       </c>
       <c r="M41">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>207</v>
       </c>
@@ -2317,7 +2341,7 @@
         <v>-0.3</v>
       </c>
       <c r="F42">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -2326,19 +2350,19 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M42">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>208</v>
       </c>
@@ -2355,7 +2379,7 @@
         <v>-0.3</v>
       </c>
       <c r="F43">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -2364,19 +2388,19 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M43">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>209</v>
       </c>
@@ -2393,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -2402,19 +2426,19 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M44">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>210</v>
       </c>
@@ -2431,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -2440,19 +2464,19 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M45">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>211</v>
       </c>
@@ -2469,7 +2493,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -2478,19 +2502,19 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M46">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>206</v>
       </c>
@@ -2507,7 +2531,7 @@
         <v>-0.3</v>
       </c>
       <c r="F47">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -2516,19 +2540,19 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M47">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>205</v>
       </c>
@@ -2545,7 +2569,7 @@
         <v>-0.3</v>
       </c>
       <c r="F48">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G48">
         <v>4</v>
@@ -2554,19 +2578,19 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J48">
         <v>1</v>
       </c>
       <c r="L48">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M48">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>212</v>
       </c>
@@ -2583,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -2592,19 +2616,19 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="L49">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M49">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>216</v>
       </c>
@@ -2621,7 +2645,7 @@
         <v>0.9</v>
       </c>
       <c r="F50">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G50">
         <v>5</v>
@@ -2630,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2639,10 +2663,10 @@
         <v>1.94</v>
       </c>
       <c r="M50">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>215</v>
       </c>
@@ -2659,7 +2683,7 @@
         <v>0.45</v>
       </c>
       <c r="F51">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -2668,7 +2692,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -2677,10 +2701,10 @@
         <v>1.94</v>
       </c>
       <c r="M51">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>214</v>
       </c>
@@ -2697,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -2706,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2715,10 +2739,10 @@
         <v>1.94</v>
       </c>
       <c r="M52">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>213</v>
       </c>
@@ -2735,7 +2759,7 @@
         <v>-0.45</v>
       </c>
       <c r="F53">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -2744,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2753,10 +2777,10 @@
         <v>1.94</v>
       </c>
       <c r="M53">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>224</v>
       </c>
@@ -2773,7 +2797,7 @@
         <v>-0.3</v>
       </c>
       <c r="F54">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -2782,19 +2806,19 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J54">
         <v>1</v>
       </c>
       <c r="L54">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M54">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>223</v>
       </c>
@@ -2811,7 +2835,7 @@
         <v>-0.3</v>
       </c>
       <c r="F55">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -2820,19 +2844,19 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J55">
         <v>1</v>
       </c>
       <c r="L55">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M55">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>222</v>
       </c>
@@ -2849,7 +2873,7 @@
         <v>-0.3</v>
       </c>
       <c r="F56">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G56">
         <v>6</v>
@@ -2858,19 +2882,19 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J56">
         <v>1</v>
       </c>
       <c r="L56">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M56">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>221</v>
       </c>
@@ -2887,7 +2911,7 @@
         <v>-0.3</v>
       </c>
       <c r="F57">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -2896,19 +2920,19 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J57">
         <v>1</v>
       </c>
       <c r="L57">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M57">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>219</v>
       </c>
@@ -2925,7 +2949,7 @@
         <v>0.3</v>
       </c>
       <c r="F58">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -2934,19 +2958,19 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="L58">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M58">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>218</v>
       </c>
@@ -2963,7 +2987,7 @@
         <v>0.3</v>
       </c>
       <c r="F59">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G59">
         <v>6</v>
@@ -2972,19 +2996,19 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="L59">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M59">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>217</v>
       </c>
@@ -3001,7 +3025,7 @@
         <v>0.3</v>
       </c>
       <c r="F60">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G60">
         <v>6</v>
@@ -3010,19 +3034,19 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
       <c r="L60">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M60">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>220</v>
       </c>
@@ -3039,7 +3063,7 @@
         <v>0.3</v>
       </c>
       <c r="F61">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G61">
         <v>6</v>
@@ -3048,19 +3072,19 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="L61">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M61">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>243</v>
       </c>
@@ -3086,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3095,10 +3119,10 @@
         <v>2.9</v>
       </c>
       <c r="M62">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>242</v>
       </c>
@@ -3109,7 +3133,7 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E63">
         <v>1.2</v>
@@ -3124,7 +3148,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3133,10 +3157,10 @@
         <v>2.9</v>
       </c>
       <c r="M63">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>241</v>
       </c>
@@ -3147,7 +3171,7 @@
         <v>77</v>
       </c>
       <c r="D64">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E64">
         <v>0.6</v>
@@ -3162,7 +3186,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3171,10 +3195,10 @@
         <v>2.9</v>
       </c>
       <c r="M64">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>240</v>
       </c>
@@ -3200,7 +3224,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3209,10 +3233,10 @@
         <v>2.9</v>
       </c>
       <c r="M65">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>239</v>
       </c>
@@ -3238,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3247,10 +3271,10 @@
         <v>2.9</v>
       </c>
       <c r="M66">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>238</v>
       </c>
@@ -3276,7 +3300,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3285,10 +3309,10 @@
         <v>2.9</v>
       </c>
       <c r="M67">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>237</v>
       </c>
@@ -3314,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3323,10 +3347,10 @@
         <v>2.9</v>
       </c>
       <c r="M68">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>236</v>
       </c>
@@ -3352,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3361,10 +3385,10 @@
         <v>2.9</v>
       </c>
       <c r="M69">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>235</v>
       </c>
@@ -3390,7 +3414,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3399,10 +3423,10 @@
         <v>2.9</v>
       </c>
       <c r="M70">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>232</v>
       </c>
@@ -3428,7 +3452,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3437,10 +3461,10 @@
         <v>2.9</v>
       </c>
       <c r="M71">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>233</v>
       </c>
@@ -3466,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3475,10 +3499,10 @@
         <v>2.9</v>
       </c>
       <c r="M72">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>231</v>
       </c>
@@ -3504,7 +3528,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -3513,10 +3537,10 @@
         <v>2.9</v>
       </c>
       <c r="M73">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>230</v>
       </c>
@@ -3542,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3551,10 +3575,10 @@
         <v>2.9</v>
       </c>
       <c r="M74">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>229</v>
       </c>
@@ -3580,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -3589,10 +3613,10 @@
         <v>2.9</v>
       </c>
       <c r="M75">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>228</v>
       </c>
@@ -3618,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -3627,10 +3651,10 @@
         <v>2.9</v>
       </c>
       <c r="M76">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>227</v>
       </c>
@@ -3656,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -3665,10 +3689,10 @@
         <v>2.9</v>
       </c>
       <c r="M77">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>226</v>
       </c>
@@ -3694,7 +3718,7 @@
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -3703,10 +3727,10 @@
         <v>2.9</v>
       </c>
       <c r="M78">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>225</v>
       </c>
@@ -3732,7 +3756,7 @@
         <v>1</v>
       </c>
       <c r="I79" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -3741,10 +3765,10 @@
         <v>2.9</v>
       </c>
       <c r="M79">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>234</v>
       </c>
@@ -3770,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="I80" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -3779,10 +3803,10 @@
         <v>2.9</v>
       </c>
       <c r="M80">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>244</v>
       </c>
@@ -3808,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J81">
         <v>1</v>
@@ -3817,7 +3841,7 @@
         <v>2.9</v>
       </c>
       <c r="M81">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3826,11 +3850,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3874,15 +3907,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" t="s">
         <v>98</v>
-      </c>
-      <c r="C2" t="s">
-        <v>99</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3891,16 +3924,16 @@
         <v>0.06</v>
       </c>
       <c r="F2">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -3909,36 +3942,36 @@
         <v>2.9</v>
       </c>
       <c r="M2">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>163</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D3">
         <v>0.6</v>
       </c>
       <c r="E3">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="F3">
-        <v>0.387</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3947,18 +3980,18 @@
         <v>0.96</v>
       </c>
       <c r="M3">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>0.6</v>
@@ -3973,10 +4006,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -3985,18 +4018,18 @@
         <v>0.96</v>
       </c>
       <c r="M4">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5">
         <v>0.96</v>
@@ -4011,36 +4044,36 @@
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M5">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6">
-        <v>0.9370000000000001</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="E6">
-        <v>0.243</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="F6">
         <v>-0.8</v>
@@ -4049,36 +4082,36 @@
         <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M6">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7">
         <v>0.86</v>
       </c>
       <c r="E7">
-        <v>0.508</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="F7">
         <v>1.468</v>
@@ -4087,30 +4120,30 @@
         <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M7">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>164</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -4125,10 +4158,10 @@
         <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -4137,24 +4170,24 @@
         <v>1.94</v>
       </c>
       <c r="M8">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>161</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9">
-        <v>0.208</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="E9">
-        <v>-0.575</v>
+        <v>-0.57499999999999996</v>
       </c>
       <c r="F9">
         <v>-1.024</v>
@@ -4163,10 +4196,10 @@
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -4175,18 +4208,18 @@
         <v>1.94</v>
       </c>
       <c r="M9">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10">
         <v>0.108</v>
@@ -4195,16 +4228,16 @@
         <v>-0.45</v>
       </c>
       <c r="F10">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -4213,18 +4246,18 @@
         <v>1.94</v>
       </c>
       <c r="M10">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>157</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11">
         <v>0.06</v>
@@ -4233,16 +4266,16 @@
         <v>0.45</v>
       </c>
       <c r="F11">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -4251,18 +4284,18 @@
         <v>1.94</v>
       </c>
       <c r="M11">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>156</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D12">
         <v>0.22</v>
@@ -4271,16 +4304,16 @@
         <v>-0.8</v>
       </c>
       <c r="F12">
-        <v>-0.725</v>
+        <v>-0.72499999999999998</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -4289,24 +4322,24 @@
         <v>1.94</v>
       </c>
       <c r="M12">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>155</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13">
-        <v>0.08799999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E13">
-        <v>-0.705</v>
+        <v>-0.70499999999999996</v>
       </c>
       <c r="F13">
         <v>-1.2</v>
@@ -4315,10 +4348,10 @@
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -4327,18 +4360,18 @@
         <v>1.94</v>
       </c>
       <c r="M13">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D14">
         <v>0.435</v>
@@ -4353,10 +4386,10 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -4365,36 +4398,36 @@
         <v>1.94</v>
       </c>
       <c r="M14">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D15">
-        <v>-0.037</v>
+        <v>-3.6999999999999998E-2</v>
       </c>
       <c r="E15">
         <v>-0.8</v>
       </c>
       <c r="F15">
-        <v>-0.365</v>
+        <v>-0.36499999999999999</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -4403,36 +4436,36 @@
         <v>1.94</v>
       </c>
       <c r="M15">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D16">
         <v>0.09</v>
       </c>
       <c r="E16">
-        <v>0.525</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="F16">
-        <v>-0.825</v>
+        <v>-0.82499999999999996</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -4441,18 +4474,18 @@
         <v>1.94</v>
       </c>
       <c r="M16">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D17">
         <v>0.15</v>
@@ -4467,10 +4500,10 @@
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -4479,36 +4512,36 @@
         <v>1.94</v>
       </c>
       <c r="M17">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D18">
-        <v>0.295</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="E18">
         <v>0.45</v>
       </c>
       <c r="F18">
-        <v>-0.453</v>
+        <v>-0.45300000000000001</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -4517,7 +4550,7 @@
         <v>1.94</v>
       </c>
       <c r="M18">
-        <v>2.655</v>
+        <v>2.6549999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -4526,11 +4559,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:O1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:15">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4538,13 +4571,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D38385C-AFBF-4ACB-8C65-ED99160E463E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
     <sheet name="Stage 3" sheetId="2" r:id="rId2"/>
     <sheet name="Obstacles" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="153">
   <si>
     <t>Marking type</t>
   </si>
@@ -69,304 +63,406 @@
     <t>Tile</t>
   </si>
   <si>
+    <t>TMP1S2d2</t>
+  </si>
+  <si>
+    <t>TMP1S2b2</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2c2</t>
+  </si>
+  <si>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
+    <t>TMP1S2b1</t>
+  </si>
+  <si>
+    <t>TMP1S2c4</t>
+  </si>
+  <si>
+    <t>TMP1S2f2</t>
+  </si>
+  <si>
+    <t>TMP1S2d3</t>
+  </si>
+  <si>
+    <t>TMP1S2d4</t>
+  </si>
+  <si>
+    <t>TMP1S2e1</t>
+  </si>
+  <si>
+    <t>TMP1S2e2</t>
+  </si>
+  <si>
+    <t>TMP1S2e3</t>
+  </si>
+  <si>
     <t>TMP1S2d1</t>
   </si>
   <si>
-    <t>TMP1S2c4</t>
-  </si>
-  <si>
-    <t>TMP1S2c3</t>
-  </si>
-  <si>
-    <t>TMP1S2c2</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2b3</t>
-  </si>
-  <si>
-    <t>TMP1S2b2</t>
-  </si>
-  <si>
-    <t>TMP1S2b1</t>
+    <t>TMP1S2e4</t>
   </si>
   <si>
     <t>TMP1S2a4</t>
   </si>
   <si>
+    <t>TMP1S2a2</t>
+  </si>
+  <si>
     <t>TMP1S2a3</t>
   </si>
   <si>
-    <t>TMP1S2a2</t>
+    <t>TMP1S2f1</t>
+  </si>
+  <si>
+    <t>TMP1S2f4</t>
+  </si>
+  <si>
+    <t>TMP1S2f3</t>
   </si>
   <si>
     <t>TMP1S2a1</t>
   </si>
   <si>
-    <t>TMP1S2d4</t>
-  </si>
-  <si>
-    <t>TMP1S2e1</t>
-  </si>
-  <si>
-    <t>TMP1S2e2</t>
-  </si>
-  <si>
-    <t>TMP1S2e3</t>
-  </si>
-  <si>
-    <t>TMP1S2e4</t>
-  </si>
-  <si>
-    <t>TMP1S2f1</t>
-  </si>
-  <si>
-    <t>TMP1S2f2</t>
-  </si>
-  <si>
-    <t>TMP1S2f3</t>
-  </si>
-  <si>
-    <t>TMP1S2f4</t>
-  </si>
-  <si>
-    <t>TMP1S2d2</t>
-  </si>
-  <si>
-    <t>TMP1S2d3</t>
+    <t>TMP2S2c1</t>
+  </si>
+  <si>
+    <t>TMP2S2b1</t>
+  </si>
+  <si>
+    <t>TMP2S2c3</t>
+  </si>
+  <si>
+    <t>TMP2S2c4</t>
+  </si>
+  <si>
+    <t>TMP2S2a2</t>
+  </si>
+  <si>
+    <t>TMP2S2b2</t>
+  </si>
+  <si>
+    <t>TMP2S2c2</t>
   </si>
   <si>
     <t>TMP2S2a1</t>
   </si>
   <si>
-    <t>TMP2S2a2</t>
-  </si>
-  <si>
-    <t>TMP2S2b1</t>
-  </si>
-  <si>
-    <t>TMP2S2b2</t>
-  </si>
-  <si>
-    <t>TMP2S2c1</t>
-  </si>
-  <si>
-    <t>TMP2S2c2</t>
-  </si>
-  <si>
-    <t>TMP2S2c3</t>
-  </si>
-  <si>
-    <t>TMP2S2c4</t>
+    <t>TMP3S2b3</t>
+  </si>
+  <si>
+    <t>TMP3S2b2</t>
+  </si>
+  <si>
+    <t>TMP3S2b1</t>
+  </si>
+  <si>
+    <t>TMP3S2a4</t>
+  </si>
+  <si>
+    <t>TMP3S2b4</t>
+  </si>
+  <si>
+    <t>TMP3S2a1</t>
+  </si>
+  <si>
+    <t>TMP3S2a2</t>
   </si>
   <si>
     <t>TMP3S2a3</t>
   </si>
   <si>
-    <t>TMP3S2a4</t>
-  </si>
-  <si>
-    <t>TMP3S2b1</t>
-  </si>
-  <si>
-    <t>TMP3S2b2</t>
-  </si>
-  <si>
-    <t>TMP3S2b3</t>
-  </si>
-  <si>
-    <t>TMP3S2b4</t>
-  </si>
-  <si>
-    <t>TMP3S2a2</t>
-  </si>
-  <si>
-    <t>TMP3S2a1</t>
+    <t>TMP4S2a4</t>
+  </si>
+  <si>
+    <t>TMP4S2b3</t>
+  </si>
+  <si>
+    <t>TMP4S2b2</t>
+  </si>
+  <si>
+    <t>TMP4S2b1</t>
+  </si>
+  <si>
+    <t>TMP4S2b4</t>
+  </si>
+  <si>
+    <t>TMP4S2a2</t>
   </si>
   <si>
     <t>TMP4S2a3</t>
   </si>
   <si>
-    <t>TMP4S2a4</t>
-  </si>
-  <si>
-    <t>TMP4S2b1</t>
-  </si>
-  <si>
-    <t>TMP4S2b2</t>
-  </si>
-  <si>
-    <t>TMP4S2b3</t>
-  </si>
-  <si>
-    <t>TMP4S2a2</t>
-  </si>
-  <si>
     <t>TMP4S2a1</t>
   </si>
   <si>
-    <t>TMP4S2b4</t>
+    <t>TMP5S2a1</t>
+  </si>
+  <si>
+    <t>TMP5S2a2</t>
+  </si>
+  <si>
+    <t>TMP5S2a3</t>
   </si>
   <si>
     <t>TMP5S2a4</t>
   </si>
   <si>
-    <t>TMP5S2a3</t>
-  </si>
-  <si>
-    <t>TMP5S2a2</t>
-  </si>
-  <si>
-    <t>TMP5S2a1</t>
+    <t>TMP6S2a2</t>
+  </si>
+  <si>
+    <t>TMP6S2a1</t>
+  </si>
+  <si>
+    <t>TMP6S2a3</t>
+  </si>
+  <si>
+    <t>TMP6S2a4</t>
+  </si>
+  <si>
+    <t>TMP6S2b1</t>
+  </si>
+  <si>
+    <t>TMP6S2b2</t>
+  </si>
+  <si>
+    <t>TMP6S2b3</t>
   </si>
   <si>
     <t>TMP6S2b4</t>
   </si>
   <si>
-    <t>TMP6S2b3</t>
-  </si>
-  <si>
-    <t>TMP6S2b2</t>
-  </si>
-  <si>
-    <t>TMP6S2b1</t>
-  </si>
-  <si>
-    <t>TMP6S2a3</t>
-  </si>
-  <si>
-    <t>TMP6S2a2</t>
-  </si>
-  <si>
-    <t>TMP6S2a1</t>
-  </si>
-  <si>
-    <t>TMP6S2a4</t>
-  </si>
-  <si>
     <t>TMP7S2e1</t>
   </si>
   <si>
+    <t>TMP7S2a1</t>
+  </si>
+  <si>
+    <t>TMP7S2a2</t>
+  </si>
+  <si>
+    <t>TMP7S2a3</t>
+  </si>
+  <si>
+    <t>TMP7S2a4</t>
+  </si>
+  <si>
+    <t>TMP7S2a5</t>
+  </si>
+  <si>
+    <t>TMP7S2a6</t>
+  </si>
+  <si>
+    <t>TMP7S2a7</t>
+  </si>
+  <si>
+    <t>TMP7S2e2</t>
+  </si>
+  <si>
+    <t>TMP7S2b1</t>
+  </si>
+  <si>
+    <t>TMP7S2b3</t>
+  </si>
+  <si>
+    <t>TMP7S2b4</t>
+  </si>
+  <si>
+    <t>TMP7S2b5</t>
+  </si>
+  <si>
+    <t>TMP7S2b6</t>
+  </si>
+  <si>
+    <t>TMP7S2b7</t>
+  </si>
+  <si>
+    <t>TMP7S2c1</t>
+  </si>
+  <si>
+    <t>TMP7S2c2</t>
+  </si>
+  <si>
+    <t>TMP7S2d1</t>
+  </si>
+  <si>
     <t>TMP7S2d2</t>
   </si>
   <si>
-    <t>TMP7S2d1</t>
-  </si>
-  <si>
-    <t>TMP7S2c2</t>
-  </si>
-  <si>
-    <t>TMP7S2c1</t>
-  </si>
-  <si>
-    <t>TMP7S2b7</t>
-  </si>
-  <si>
-    <t>TMP7S2b6</t>
-  </si>
-  <si>
-    <t>TMP7S2b5</t>
-  </si>
-  <si>
-    <t>TMP7S2b4</t>
-  </si>
-  <si>
-    <t>TMP7S2b1</t>
-  </si>
-  <si>
     <t>TMP7S2b2</t>
   </si>
   <si>
-    <t>TMP7S2a7</t>
-  </si>
-  <si>
-    <t>TMP7S2a6</t>
-  </si>
-  <si>
-    <t>TMP7S2a5</t>
-  </si>
-  <si>
-    <t>TMP7S2a4</t>
-  </si>
-  <si>
-    <t>TMP7S2a3</t>
-  </si>
-  <si>
-    <t>TMP7S2a2</t>
-  </si>
-  <si>
-    <t>TMP7S2a1</t>
-  </si>
-  <si>
-    <t>TMP7S2b3</t>
-  </si>
-  <si>
-    <t>TMP7S2e2</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
+    <t>+</t>
+  </si>
+  <si>
     <t>blank</t>
   </si>
   <si>
     <t>Fitting</t>
   </si>
   <si>
-    <t>BSS.GOMGO.TR.GG-6108-600:Chrome 000:1090991</t>
-  </si>
-  <si>
-    <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
+    <t>LP1S3a1</t>
+  </si>
+  <si>
+    <t>LP1S3a2</t>
+  </si>
+  <si>
+    <t>LP1S3a3</t>
+  </si>
+  <si>
+    <t>LP1S3a4</t>
+  </si>
+  <si>
+    <t>LP3S3a1</t>
+  </si>
+  <si>
+    <t>LP3S3a4</t>
   </si>
   <si>
     <t>BSS.GESSI.SM.49079:29046000:1090989</t>
   </si>
   <si>
-    <t>BSS.GOMGO.PH.GG-6106:Chrome 000:1090992</t>
+    <t>LP3S3a3</t>
+  </si>
+  <si>
+    <t>LP3S3a2</t>
   </si>
   <si>
     <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
   </si>
   <si>
+    <t>LP4S3a1</t>
+  </si>
+  <si>
+    <t>LP4S3a2</t>
+  </si>
+  <si>
     <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
   </si>
   <si>
-    <t>BSS.MIRROR CABINET.C5-MASTER BATH:BSS.MIRROR CABINET.C5-MASTER BATH:1090945</t>
+    <t>LP5S3d2</t>
+  </si>
+  <si>
+    <t>LP5S3d1</t>
+  </si>
+  <si>
+    <t>LP5S3c4</t>
+  </si>
+  <si>
+    <t>LP5S3c3</t>
+  </si>
+  <si>
+    <t>LP5S3c2</t>
+  </si>
+  <si>
+    <t>LP5S3c1</t>
+  </si>
+  <si>
+    <t>LP5S3b3</t>
+  </si>
+  <si>
+    <t>LP5S3d3</t>
+  </si>
+  <si>
+    <t>LP5S3b1</t>
+  </si>
+  <si>
+    <t>LP5S3a5</t>
+  </si>
+  <si>
+    <t>LP5S3a4</t>
+  </si>
+  <si>
+    <t>LP5S3a3</t>
+  </si>
+  <si>
+    <t>LP5S3a2</t>
+  </si>
+  <si>
+    <t>LP5S3a1</t>
+  </si>
+  <si>
+    <t>LP5S3b2</t>
+  </si>
+  <si>
+    <t>LP5S3d4</t>
+  </si>
+  <si>
+    <t>LP5S3b5</t>
+  </si>
+  <si>
+    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
+  </si>
+  <si>
+    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+  </si>
+  <si>
+    <t>BSS.GESSI,BM.49001:Default:1090988</t>
+  </si>
+  <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
   </si>
   <si>
     <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
   </si>
   <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
-  </si>
-  <si>
-    <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
-  </si>
-  <si>
-    <t>BSS.TECE.CONCEALED CISTERN.9370224:BSS.TECE.CONCEALED CISTERN.9370224:1090923</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
-  </si>
-  <si>
-    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+    <t>LP5S3b4</t>
+  </si>
+  <si>
+    <t>LP7S3a1</t>
+  </si>
+  <si>
+    <t>LP7S3b2</t>
+  </si>
+  <si>
+    <t>LP7S3b3</t>
+  </si>
+  <si>
+    <t>LP7S3b1</t>
+  </si>
+  <si>
+    <t>LP7S3a4</t>
+  </si>
+  <si>
+    <t>LP7S3a2</t>
+  </si>
+  <si>
+    <t>LP7S3a3</t>
+  </si>
+  <si>
+    <t>LP7S3b4</t>
+  </si>
+  <si>
+    <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
+  </si>
+  <si>
+    <t>BSS.Shallow_FW:BSS.Shallow_FW:1038276</t>
   </si>
   <si>
     <t>6</t>
@@ -384,8 +480,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,21 +544,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -500,7 +588,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -534,7 +622,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -569,10 +656,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -745,22 +831,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,9 +879,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -821,7 +896,7 @@
         <v>-0.03</v>
       </c>
       <c r="F2">
-        <v>-0.77500000000000002</v>
+        <v>-0.175</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -830,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -839,12 +914,12 @@
         <v>2.9</v>
       </c>
       <c r="M2">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -856,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F3">
-        <v>1.0249999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -868,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -877,12 +952,12 @@
         <v>2.9</v>
       </c>
       <c r="M3">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -894,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F4">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -906,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -915,12 +990,12 @@
         <v>2.9</v>
       </c>
       <c r="M4">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -932,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F5">
-        <v>-0.17499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -944,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -953,12 +1028,12 @@
         <v>2.9</v>
       </c>
       <c r="M5">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -973,7 +1048,7 @@
         <v>0.47</v>
       </c>
       <c r="F6">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -982,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -991,12 +1066,12 @@
         <v>2.9</v>
       </c>
       <c r="M6">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1008,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F7">
-        <v>1.0249999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1020,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1029,12 +1104,12 @@
         <v>2.9</v>
       </c>
       <c r="M7">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1046,10 +1121,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F8">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1058,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1067,12 +1142,12 @@
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1087,7 +1162,7 @@
         <v>0.49</v>
       </c>
       <c r="F9">
-        <v>-0.17499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1096,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1105,12 +1180,12 @@
         <v>2.9</v>
       </c>
       <c r="M9">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1122,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F10">
-        <v>-0.77500000000000002</v>
+        <v>1.025</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1134,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1143,12 +1218,12 @@
         <v>2.9</v>
       </c>
       <c r="M10">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1160,10 +1235,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.93500000000000005</v>
+        <v>-1.35</v>
       </c>
       <c r="F11">
-        <v>1.0249999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1172,7 +1247,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1181,12 +1256,12 @@
         <v>2.9</v>
       </c>
       <c r="M11">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1198,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.93500000000000005</v>
+        <v>-0.03</v>
       </c>
       <c r="F12">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1210,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1219,12 +1294,12 @@
         <v>2.9</v>
       </c>
       <c r="M12">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1236,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.93500000000000005</v>
+        <v>-0.03</v>
       </c>
       <c r="F13">
-        <v>-0.17499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1248,7 +1323,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1257,12 +1332,12 @@
         <v>2.9</v>
       </c>
       <c r="M13">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1274,10 +1349,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.93500000000000005</v>
+        <v>-0.35</v>
       </c>
       <c r="F14">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1286,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1295,12 +1370,12 @@
         <v>2.9</v>
       </c>
       <c r="M14">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1312,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F15">
-        <v>1.0249999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1324,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1333,12 +1408,12 @@
         <v>2.9</v>
       </c>
       <c r="M15">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1353,7 +1428,7 @@
         <v>-0.35</v>
       </c>
       <c r="F16">
-        <v>-0.77500000000000002</v>
+        <v>0.425</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1362,7 +1437,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1371,12 +1446,12 @@
         <v>2.9</v>
       </c>
       <c r="M16">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1388,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>-0.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F17">
-        <v>-0.17499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1400,7 +1475,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1409,12 +1484,12 @@
         <v>2.9</v>
       </c>
       <c r="M17">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1429,7 +1504,7 @@
         <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>0.42499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1438,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1447,12 +1522,12 @@
         <v>2.9</v>
       </c>
       <c r="M18">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1464,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-0.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F19">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1476,7 +1551,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1485,12 +1560,12 @@
         <v>2.9</v>
       </c>
       <c r="M19">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1502,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F20">
-        <v>-0.77500000000000002</v>
+        <v>-0.175</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1514,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1523,12 +1598,12 @@
         <v>2.9</v>
       </c>
       <c r="M20">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1540,10 +1615,10 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F21">
-        <v>-0.17499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1552,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1561,12 +1636,12 @@
         <v>2.9</v>
       </c>
       <c r="M21">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1581,7 +1656,7 @@
         <v>-1.35</v>
       </c>
       <c r="F22">
-        <v>0.42499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1590,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1599,12 +1674,12 @@
         <v>2.9</v>
       </c>
       <c r="M22">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1619,7 +1694,7 @@
         <v>-1.35</v>
       </c>
       <c r="F23">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1628,7 +1703,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1637,10 +1712,10 @@
         <v>2.9</v>
       </c>
       <c r="M23">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>178</v>
       </c>
@@ -1654,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F24">
-        <v>-0.17499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1666,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1675,12 +1750,12 @@
         <v>2.9</v>
       </c>
       <c r="M24">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1692,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>-0.03</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F25">
-        <v>0.42499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1704,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1713,12 +1788,12 @@
         <v>2.9</v>
       </c>
       <c r="M25">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1730,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>-0.5</v>
+        <v>0.22</v>
       </c>
       <c r="F26">
         <v>-0.75</v>
@@ -1742,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1751,12 +1826,12 @@
         <v>1.34</v>
       </c>
       <c r="M26">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1768,10 +1843,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F27">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1780,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1789,12 +1864,12 @@
         <v>1.34</v>
       </c>
       <c r="M27">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1806,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="F28">
-        <v>-0.75</v>
+        <v>0.45</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1818,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1827,12 +1902,12 @@
         <v>1.34</v>
       </c>
       <c r="M28">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -1844,10 +1919,10 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="F29">
-        <v>-0.15</v>
+        <v>1.05</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1856,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1865,12 +1940,12 @@
         <v>1.34</v>
       </c>
       <c r="M29">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1882,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0.22</v>
+        <v>-0.5</v>
       </c>
       <c r="F30">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1894,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1903,12 +1978,12 @@
         <v>1.34</v>
       </c>
       <c r="M30">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1920,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="F31">
         <v>-0.15</v>
@@ -1932,7 +2007,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1941,12 +2016,12 @@
         <v>1.34</v>
       </c>
       <c r="M31">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -1961,7 +2036,7 @@
         <v>0.22</v>
       </c>
       <c r="F32">
-        <v>0.45</v>
+        <v>-0.15</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -1970,7 +2045,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -1979,12 +2054,12 @@
         <v>1.34</v>
       </c>
       <c r="M32">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -1996,10 +2071,10 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0.22</v>
+        <v>-0.5</v>
       </c>
       <c r="F33">
-        <v>1.05</v>
+        <v>-0.75</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2008,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2017,12 +2092,12 @@
         <v>1.34</v>
       </c>
       <c r="M33">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -2034,10 +2109,10 @@
         <v>0.6</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>0.445</v>
       </c>
       <c r="F34">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -2046,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2055,12 +2130,12 @@
         <v>0.96</v>
       </c>
       <c r="M34">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2072,10 +2147,10 @@
         <v>0.6</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>0.445</v>
       </c>
       <c r="F35">
-        <v>1.0249999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2084,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2093,12 +2168,12 @@
         <v>0.96</v>
       </c>
       <c r="M35">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2110,10 +2185,10 @@
         <v>0.6</v>
       </c>
       <c r="E36">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="F36">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -2122,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2131,12 +2206,12 @@
         <v>0.96</v>
       </c>
       <c r="M36">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2148,10 +2223,10 @@
         <v>0.6</v>
       </c>
       <c r="E37">
-        <v>0.44500000000000001</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>-0.17499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -2160,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2169,12 +2244,12 @@
         <v>0.96</v>
       </c>
       <c r="M37">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2186,10 +2261,10 @@
         <v>0.6</v>
       </c>
       <c r="E38">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="F38">
-        <v>0.42499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G38">
         <v>3</v>
@@ -2198,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2207,12 +2282,12 @@
         <v>0.96</v>
       </c>
       <c r="M38">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2224,10 +2299,10 @@
         <v>0.6</v>
       </c>
       <c r="E39">
-        <v>0.44500000000000001</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>1.0249999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G39">
         <v>3</v>
@@ -2236,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2245,12 +2320,12 @@
         <v>0.96</v>
       </c>
       <c r="M39">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2265,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -2274,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2283,12 +2358,12 @@
         <v>0.96</v>
       </c>
       <c r="M40">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2303,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>-0.77500000000000002</v>
+        <v>0.425</v>
       </c>
       <c r="G41">
         <v>3</v>
@@ -2312,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -2321,12 +2396,12 @@
         <v>0.96</v>
       </c>
       <c r="M41">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2341,7 +2416,7 @@
         <v>-0.3</v>
       </c>
       <c r="F42">
-        <v>0.42499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -2350,21 +2425,21 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M42">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2376,10 +2451,10 @@
         <v>0.96</v>
       </c>
       <c r="E43">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>1.0249999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -2388,21 +2463,21 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M43">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2417,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>-0.77500000000000002</v>
+        <v>-0.175</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -2426,21 +2501,21 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M44">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2455,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>-0.17499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -2464,21 +2539,21 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M45">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2493,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>0.42499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -2502,21 +2577,21 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M46">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2531,7 +2606,7 @@
         <v>-0.3</v>
       </c>
       <c r="F47">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -2540,21 +2615,21 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M47">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2569,7 +2644,7 @@
         <v>-0.3</v>
       </c>
       <c r="F48">
-        <v>-0.77500000000000002</v>
+        <v>0.425</v>
       </c>
       <c r="G48">
         <v>4</v>
@@ -2578,21 +2653,21 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J48">
         <v>1</v>
       </c>
       <c r="L48">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M48">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2604,10 +2679,10 @@
         <v>0.96</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F49">
-        <v>1.0249999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -2616,21 +2691,21 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="L49">
-        <v>0.59199999999999997</v>
+        <v>0.592</v>
       </c>
       <c r="M49">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2642,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="F50">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G50">
         <v>5</v>
@@ -2654,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2663,12 +2738,12 @@
         <v>1.94</v>
       </c>
       <c r="M50">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2680,10 +2755,10 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -2692,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -2701,12 +2776,12 @@
         <v>1.94</v>
       </c>
       <c r="M51">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2718,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="F52">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -2730,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2739,12 +2814,12 @@
         <v>1.94</v>
       </c>
       <c r="M52">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2756,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>-0.45</v>
+        <v>0.9</v>
       </c>
       <c r="F53">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -2768,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2777,12 +2852,12 @@
         <v>1.94</v>
       </c>
       <c r="M53">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2794,10 +2869,10 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F54">
-        <v>1.0249999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -2806,21 +2881,21 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J54">
         <v>1</v>
       </c>
       <c r="L54">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M54">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2832,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F55">
-        <v>0.42499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -2844,21 +2919,21 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J55">
         <v>1</v>
       </c>
       <c r="L55">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M55">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="1">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2870,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F56">
-        <v>-0.17499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G56">
         <v>6</v>
@@ -2882,21 +2957,21 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J56">
         <v>1</v>
       </c>
       <c r="L56">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M56">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="1">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2908,10 +2983,10 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F57">
-        <v>-0.77500000000000002</v>
+        <v>1.025</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -2920,21 +2995,21 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J57">
         <v>1</v>
       </c>
       <c r="L57">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M57">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -2946,10 +3021,10 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F58">
-        <v>0.42499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -2958,21 +3033,21 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="L58">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M58">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -2984,10 +3059,10 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F59">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G59">
         <v>6</v>
@@ -2996,21 +3071,21 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="L59">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M59">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -3022,10 +3097,10 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F60">
-        <v>-0.77500000000000002</v>
+        <v>0.425</v>
       </c>
       <c r="G60">
         <v>6</v>
@@ -3034,21 +3109,21 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
       <c r="L60">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M60">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -3060,10 +3135,10 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F61">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G61">
         <v>6</v>
@@ -3072,21 +3147,21 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="L61">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
       <c r="M61">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3110,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3119,12 +3194,12 @@
         <v>2.9</v>
       </c>
       <c r="M62">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="1">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3133,10 +3208,10 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>2.0099999999999998</v>
+        <v>0.12</v>
       </c>
       <c r="E63">
-        <v>1.2</v>
+        <v>0.15</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3148,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3157,12 +3232,12 @@
         <v>2.9</v>
       </c>
       <c r="M63">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="1">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3171,10 +3246,10 @@
         <v>77</v>
       </c>
       <c r="D64">
-        <v>2.0099999999999998</v>
+        <v>0.12</v>
       </c>
       <c r="E64">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3186,7 +3261,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3195,12 +3270,12 @@
         <v>2.9</v>
       </c>
       <c r="M64">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="1">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3209,10 +3284,10 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>1.41</v>
+        <v>0.12</v>
       </c>
       <c r="E65">
-        <v>1.2</v>
+        <v>0.45</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3224,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3233,12 +3308,12 @@
         <v>2.9</v>
       </c>
       <c r="M65">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="1">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3247,7 +3322,7 @@
         <v>79</v>
       </c>
       <c r="D66">
-        <v>1.41</v>
+        <v>0.12</v>
       </c>
       <c r="E66">
         <v>0.6</v>
@@ -3262,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3271,12 +3346,12 @@
         <v>2.9</v>
       </c>
       <c r="M66">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="1">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
@@ -3285,10 +3360,10 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E67">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3300,7 +3375,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3309,12 +3384,12 @@
         <v>2.9</v>
       </c>
       <c r="M67">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="1">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3323,7 +3398,7 @@
         <v>81</v>
       </c>
       <c r="D68">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E68">
         <v>0.9</v>
@@ -3338,7 +3413,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3347,12 +3422,12 @@
         <v>2.9</v>
       </c>
       <c r="M68">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="1">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
@@ -3361,10 +3436,10 @@
         <v>82</v>
       </c>
       <c r="D69">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E69">
-        <v>0.75</v>
+        <v>1.05</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -3376,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3385,10 +3460,10 @@
         <v>2.9</v>
       </c>
       <c r="M69">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="1">
         <v>235</v>
       </c>
@@ -3399,10 +3474,10 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>0.72</v>
+        <v>2.61</v>
       </c>
       <c r="E70">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -3414,7 +3489,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3423,12 +3498,12 @@
         <v>2.9</v>
       </c>
       <c r="M70">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="1">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -3452,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3461,12 +3536,12 @@
         <v>2.9</v>
       </c>
       <c r="M71">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="1">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -3478,7 +3553,7 @@
         <v>0.72</v>
       </c>
       <c r="E72">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3490,7 +3565,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3499,12 +3574,12 @@
         <v>2.9</v>
       </c>
       <c r="M72">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="1">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B73" t="s">
         <v>14</v>
@@ -3513,10 +3588,10 @@
         <v>86</v>
       </c>
       <c r="D73">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E73">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -3528,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="I73" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -3537,12 +3612,12 @@
         <v>2.9</v>
       </c>
       <c r="M73">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="1">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B74" t="s">
         <v>14</v>
@@ -3551,10 +3626,10 @@
         <v>87</v>
       </c>
       <c r="D74">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E74">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3566,7 +3641,7 @@
         <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3575,12 +3650,12 @@
         <v>2.9</v>
       </c>
       <c r="M74">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="1">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B75" t="s">
         <v>14</v>
@@ -3589,10 +3664,10 @@
         <v>88</v>
       </c>
       <c r="D75">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E75">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -3604,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -3613,12 +3688,12 @@
         <v>2.9</v>
       </c>
       <c r="M75">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="1">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B76" t="s">
         <v>14</v>
@@ -3627,10 +3702,10 @@
         <v>89</v>
       </c>
       <c r="D76">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E76">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -3642,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -3651,12 +3726,12 @@
         <v>2.9</v>
       </c>
       <c r="M76">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="1">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B77" t="s">
         <v>14</v>
@@ -3665,10 +3740,10 @@
         <v>90</v>
       </c>
       <c r="D77">
-        <v>0.12</v>
+        <v>1.41</v>
       </c>
       <c r="E77">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -3680,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -3689,12 +3764,12 @@
         <v>2.9</v>
       </c>
       <c r="M77">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78" s="1">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B78" t="s">
         <v>14</v>
@@ -3703,10 +3778,10 @@
         <v>91</v>
       </c>
       <c r="D78">
-        <v>0.12</v>
+        <v>1.41</v>
       </c>
       <c r="E78">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3718,7 +3793,7 @@
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -3727,12 +3802,12 @@
         <v>2.9</v>
       </c>
       <c r="M78">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79" s="1">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B79" t="s">
         <v>14</v>
@@ -3741,10 +3816,10 @@
         <v>92</v>
       </c>
       <c r="D79">
-        <v>0.12</v>
+        <v>2.01</v>
       </c>
       <c r="E79">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3756,7 +3831,7 @@
         <v>1</v>
       </c>
       <c r="I79" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -3765,12 +3840,12 @@
         <v>2.9</v>
       </c>
       <c r="M79">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80" s="1">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B80" t="s">
         <v>14</v>
@@ -3779,10 +3854,10 @@
         <v>93</v>
       </c>
       <c r="D80">
-        <v>0.72</v>
+        <v>2.01</v>
       </c>
       <c r="E80">
-        <v>0.45</v>
+        <v>1.2</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3794,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="I80" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -3803,12 +3878,12 @@
         <v>2.9</v>
       </c>
       <c r="M80">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
       <c r="A81" s="1">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="B81" t="s">
         <v>14</v>
@@ -3817,10 +3892,10 @@
         <v>94</v>
       </c>
       <c r="D81">
-        <v>2.61</v>
+        <v>0.72</v>
       </c>
       <c r="E81">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -3832,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J81">
         <v>1</v>
@@ -3841,7 +3916,7 @@
         <v>2.9</v>
       </c>
       <c r="M81">
-        <v>1.9319999999999999</v>
+        <v>1.932</v>
       </c>
     </row>
   </sheetData>
@@ -3850,20 +3925,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O59"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3907,527 +3973,527 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>6</v>
+        <v>236</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0.375</v>
+      </c>
+      <c r="F2">
+        <v>0.213</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2.9</v>
+      </c>
+      <c r="M2">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="1">
+        <v>237</v>
+      </c>
+      <c r="B3" t="s">
         <v>98</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0.06</v>
-      </c>
-      <c r="F2">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I2" t="s">
-        <v>96</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2.9</v>
-      </c>
-      <c r="M2">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>163</v>
-      </c>
-      <c r="B3" t="s">
-        <v>97</v>
-      </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>-0.255</v>
+      </c>
+      <c r="F3">
+        <v>0.213</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2.9</v>
+      </c>
+      <c r="M3">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="1">
+        <v>238</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.375</v>
+      </c>
+      <c r="F4">
+        <v>0.137</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>2.9</v>
+      </c>
+      <c r="M4">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="1">
+        <v>239</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>-0.255</v>
+      </c>
+      <c r="F5">
+        <v>0.137</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>149</v>
+      </c>
+      <c r="I5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>2.9</v>
+      </c>
+      <c r="M5">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="1">
+        <v>240</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6">
         <v>0.6</v>
       </c>
-      <c r="E3">
-        <v>2.3E-2</v>
-      </c>
-      <c r="F3">
-        <v>0.38700000000000001</v>
-      </c>
-      <c r="G3">
+      <c r="E6">
+        <v>-0.077</v>
+      </c>
+      <c r="F6">
+        <v>0.962</v>
+      </c>
+      <c r="G6">
         <v>3</v>
       </c>
-      <c r="H3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
+      <c r="H6" t="s">
+        <v>149</v>
+      </c>
+      <c r="I6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
         <v>0.96</v>
       </c>
-      <c r="M3">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>94</v>
-      </c>
-      <c r="B4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4">
+      <c r="M6">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="1">
+        <v>243</v>
+      </c>
+      <c r="B7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7">
         <v>0.6</v>
       </c>
-      <c r="E4">
+      <c r="E7">
+        <v>0.123</v>
+      </c>
+      <c r="F7">
+        <v>-0.188</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I7" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0.96</v>
+      </c>
+      <c r="M7">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="1">
+        <v>90</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8">
+        <v>0.6</v>
+      </c>
+      <c r="E8">
         <v>0.21</v>
       </c>
-      <c r="F4">
+      <c r="F8">
         <v>-0.05</v>
       </c>
-      <c r="G4">
+      <c r="G8">
         <v>3</v>
       </c>
-      <c r="H4" t="s">
-        <v>115</v>
-      </c>
-      <c r="I4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="H8" t="s">
+        <v>149</v>
+      </c>
+      <c r="I8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="L8">
         <v>0.96</v>
       </c>
-      <c r="M4">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5">
+      <c r="M8">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="1">
+        <v>242</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9">
+        <v>0.6</v>
+      </c>
+      <c r="E9">
+        <v>-0.077</v>
+      </c>
+      <c r="F9">
+        <v>-0.188</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9" t="s">
+        <v>149</v>
+      </c>
+      <c r="I9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="L9">
         <v>0.96</v>
       </c>
-      <c r="E5">
-        <v>-0.17</v>
-      </c>
-      <c r="F5">
+      <c r="M9">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="1">
+        <v>241</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10">
+        <v>0.6</v>
+      </c>
+      <c r="E10">
+        <v>0.123</v>
+      </c>
+      <c r="F10">
+        <v>0.962</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10" t="s">
+        <v>149</v>
+      </c>
+      <c r="I10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0.96</v>
+      </c>
+      <c r="M10">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="E11">
+        <v>0.243</v>
+      </c>
+      <c r="F11">
+        <v>-0.8</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0.592</v>
+      </c>
+      <c r="M11">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="1">
+        <v>244</v>
+      </c>
+      <c r="B12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12">
+        <v>0.96</v>
+      </c>
+      <c r="E12">
+        <v>-0.195</v>
+      </c>
+      <c r="F12">
         <v>-0.375</v>
       </c>
-      <c r="G5">
+      <c r="G12">
         <v>4</v>
       </c>
-      <c r="H5" t="s">
-        <v>115</v>
-      </c>
-      <c r="I5" t="s">
-        <v>96</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>0.59199999999999997</v>
-      </c>
-      <c r="M5">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>44</v>
-      </c>
-      <c r="B6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6">
-        <v>0.93700000000000006</v>
-      </c>
-      <c r="E6">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="F6">
-        <v>-0.8</v>
-      </c>
-      <c r="G6">
+      <c r="H12" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0.592</v>
+      </c>
+      <c r="M12">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="1">
+        <v>245</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13">
+        <v>0.96</v>
+      </c>
+      <c r="E13">
+        <v>-0.145</v>
+      </c>
+      <c r="F13">
+        <v>-0.375</v>
+      </c>
+      <c r="G13">
         <v>4</v>
       </c>
-      <c r="H6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I6" t="s">
-        <v>96</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>0.59199999999999997</v>
-      </c>
-      <c r="M6">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>93</v>
-      </c>
-      <c r="B7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7">
+      <c r="H13" t="s">
+        <v>149</v>
+      </c>
+      <c r="I13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0.592</v>
+      </c>
+      <c r="M13">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="1">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14">
         <v>0.86</v>
       </c>
-      <c r="E7">
-        <v>0.50800000000000001</v>
-      </c>
-      <c r="F7">
+      <c r="E14">
+        <v>0.508</v>
+      </c>
+      <c r="F14">
         <v>1.468</v>
       </c>
-      <c r="G7">
+      <c r="G14">
         <v>4</v>
       </c>
-      <c r="H7" t="s">
-        <v>115</v>
-      </c>
-      <c r="I7" t="s">
-        <v>96</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>0.59199999999999997</v>
-      </c>
-      <c r="M7">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>164</v>
-      </c>
-      <c r="B8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0.125</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8" t="s">
-        <v>115</v>
-      </c>
-      <c r="I8" t="s">
-        <v>96</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1.94</v>
-      </c>
-      <c r="M8">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>161</v>
-      </c>
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="E9">
-        <v>-0.57499999999999996</v>
-      </c>
-      <c r="F9">
-        <v>-1.024</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9" t="s">
-        <v>115</v>
-      </c>
-      <c r="I9" t="s">
-        <v>96</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1.94</v>
-      </c>
-      <c r="M9">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>159</v>
-      </c>
-      <c r="B10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10">
-        <v>0.108</v>
-      </c>
-      <c r="E10">
-        <v>-0.45</v>
-      </c>
-      <c r="F10">
-        <v>-0.17499999999999999</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-      <c r="H10" t="s">
-        <v>115</v>
-      </c>
-      <c r="I10" t="s">
-        <v>96</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>1.94</v>
-      </c>
-      <c r="M10">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>157</v>
-      </c>
-      <c r="B11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11">
-        <v>0.06</v>
-      </c>
-      <c r="E11">
-        <v>0.45</v>
-      </c>
-      <c r="F11">
-        <v>-0.17499999999999999</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-      <c r="H11" t="s">
-        <v>115</v>
-      </c>
-      <c r="I11" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1.94</v>
-      </c>
-      <c r="M11">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>156</v>
-      </c>
-      <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12">
-        <v>0.22</v>
-      </c>
-      <c r="E12">
-        <v>-0.8</v>
-      </c>
-      <c r="F12">
-        <v>-0.72499999999999998</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-      <c r="H12" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" t="s">
-        <v>96</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1.94</v>
-      </c>
-      <c r="M12">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>155</v>
-      </c>
-      <c r="B13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13">
-        <v>8.7999999999999995E-2</v>
-      </c>
-      <c r="E13">
-        <v>-0.70499999999999996</v>
-      </c>
-      <c r="F13">
-        <v>-1.2</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-      <c r="H13" t="s">
-        <v>115</v>
-      </c>
-      <c r="I13" t="s">
-        <v>96</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>1.94</v>
-      </c>
-      <c r="M13">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>84</v>
-      </c>
-      <c r="B14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14">
-        <v>0.435</v>
-      </c>
-      <c r="E14">
-        <v>-1.28</v>
-      </c>
-      <c r="F14">
-        <v>-0.79</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
       <c r="H14" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="L14">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M14">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>67</v>
+        <v>261</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D15">
-        <v>-3.6999999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>-0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F15">
-        <v>-0.36499999999999999</v>
+        <v>-0.15</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="I15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -4436,36 +4502,36 @@
         <v>1.94</v>
       </c>
       <c r="M15">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>61</v>
+        <v>260</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D16">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.52500000000000002</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>-0.82499999999999996</v>
+        <v>-0.15</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -4474,36 +4540,36 @@
         <v>1.94</v>
       </c>
       <c r="M16">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>59</v>
+        <v>259</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D17">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0.375</v>
+        <v>0.9</v>
       </c>
       <c r="F17">
-        <v>-0.9</v>
+        <v>1.4</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="I17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -4512,36 +4578,36 @@
         <v>1.94</v>
       </c>
       <c r="M17">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>40</v>
+        <v>258</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D18">
-        <v>0.29499999999999998</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0.45</v>
+        <v>-0.9</v>
       </c>
       <c r="F18">
-        <v>-0.45300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="I18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -4550,7 +4616,1565 @@
         <v>1.94</v>
       </c>
       <c r="M18">
-        <v>2.6549999999999998</v>
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="1">
+        <v>257</v>
+      </c>
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0.9</v>
+      </c>
+      <c r="F19">
+        <v>1.4</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19" t="s">
+        <v>149</v>
+      </c>
+      <c r="I19" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1.94</v>
+      </c>
+      <c r="M19">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="1">
+        <v>256</v>
+      </c>
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>-0.9</v>
+      </c>
+      <c r="F20">
+        <v>1.4</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" t="s">
+        <v>97</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1.94</v>
+      </c>
+      <c r="M20">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="1">
+        <v>253</v>
+      </c>
+      <c r="B21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21">
+        <v>0.183</v>
+      </c>
+      <c r="E21">
+        <v>-0.63</v>
+      </c>
+      <c r="F21">
+        <v>-0.83</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1.94</v>
+      </c>
+      <c r="M21">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="1">
+        <v>262</v>
+      </c>
+      <c r="B22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>-0.75</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22" t="s">
+        <v>149</v>
+      </c>
+      <c r="I22" t="s">
+        <v>97</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1.94</v>
+      </c>
+      <c r="M22">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="1">
+        <v>251</v>
+      </c>
+      <c r="B23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23">
+        <v>0.183</v>
+      </c>
+      <c r="E23">
+        <v>-0.63</v>
+      </c>
+      <c r="F23">
+        <v>-0.402</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+      <c r="H23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I23" t="s">
+        <v>97</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1.94</v>
+      </c>
+      <c r="M23">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="1">
+        <v>250</v>
+      </c>
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E24">
+        <v>-0.455</v>
+      </c>
+      <c r="F24">
+        <v>-0.22</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24" t="s">
+        <v>149</v>
+      </c>
+      <c r="I24" t="s">
+        <v>97</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1.94</v>
+      </c>
+      <c r="M24">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="1">
+        <v>249</v>
+      </c>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E25">
+        <v>-0.205</v>
+      </c>
+      <c r="F25">
+        <v>-0.466</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25" t="s">
+        <v>149</v>
+      </c>
+      <c r="I25" t="s">
+        <v>97</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1.94</v>
+      </c>
+      <c r="M25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="1">
+        <v>248</v>
+      </c>
+      <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E26">
+        <v>-0.705</v>
+      </c>
+      <c r="F26">
+        <v>-0.466</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26" t="s">
+        <v>149</v>
+      </c>
+      <c r="I26" t="s">
+        <v>97</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1.94</v>
+      </c>
+      <c r="M26">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="1">
+        <v>247</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E27">
+        <v>-0.205</v>
+      </c>
+      <c r="F27">
+        <v>0.026</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="H27" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" t="s">
+        <v>97</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1.94</v>
+      </c>
+      <c r="M27">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="1">
+        <v>246</v>
+      </c>
+      <c r="B28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E28">
+        <v>-0.705</v>
+      </c>
+      <c r="F28">
+        <v>0.026</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>149</v>
+      </c>
+      <c r="I28" t="s">
+        <v>97</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1.94</v>
+      </c>
+      <c r="M28">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="1">
+        <v>252</v>
+      </c>
+      <c r="B29" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29">
+        <v>0.183</v>
+      </c>
+      <c r="E29">
+        <v>-0.27</v>
+      </c>
+      <c r="F29">
+        <v>-0.402</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I29" t="s">
+        <v>97</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>1.94</v>
+      </c>
+      <c r="M29">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="1">
+        <v>263</v>
+      </c>
+      <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0.9</v>
+      </c>
+      <c r="F30">
+        <v>-0.75</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30" t="s">
+        <v>149</v>
+      </c>
+      <c r="I30" t="s">
+        <v>97</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>1.94</v>
+      </c>
+      <c r="M30">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="1">
+        <v>255</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31">
+        <v>0.183</v>
+      </c>
+      <c r="E31">
+        <v>-0.45</v>
+      </c>
+      <c r="F31">
+        <v>-0.616</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="H31" t="s">
+        <v>149</v>
+      </c>
+      <c r="I31" t="s">
+        <v>97</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>1.94</v>
+      </c>
+      <c r="M31">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="1">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32">
+        <v>0.295</v>
+      </c>
+      <c r="E32">
+        <v>0.45</v>
+      </c>
+      <c r="F32">
+        <v>-0.453</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+      <c r="H32" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" t="s">
+        <v>97</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>1.94</v>
+      </c>
+      <c r="M32">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="1">
+        <v>55</v>
+      </c>
+      <c r="B33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33">
+        <v>0.15</v>
+      </c>
+      <c r="E33">
+        <v>0.375</v>
+      </c>
+      <c r="F33">
+        <v>-0.9</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" t="s">
+        <v>97</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>1.94</v>
+      </c>
+      <c r="M33">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="1">
+        <v>57</v>
+      </c>
+      <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
+        <v>131</v>
+      </c>
+      <c r="D34">
+        <v>0.09</v>
+      </c>
+      <c r="E34">
+        <v>0.525</v>
+      </c>
+      <c r="F34">
+        <v>-0.825</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="H34" t="s">
+        <v>149</v>
+      </c>
+      <c r="I34" t="s">
+        <v>97</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>1.94</v>
+      </c>
+      <c r="M34">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="1">
+        <v>63</v>
+      </c>
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
+        <v>132</v>
+      </c>
+      <c r="D35">
+        <v>-0.037</v>
+      </c>
+      <c r="E35">
+        <v>-0.8</v>
+      </c>
+      <c r="F35">
+        <v>-0.365</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
+      </c>
+      <c r="H35" t="s">
+        <v>149</v>
+      </c>
+      <c r="I35" t="s">
+        <v>97</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>1.94</v>
+      </c>
+      <c r="M35">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="1">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36">
+        <v>0.435</v>
+      </c>
+      <c r="E36">
+        <v>-1.28</v>
+      </c>
+      <c r="F36">
+        <v>-0.79</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36" t="s">
+        <v>149</v>
+      </c>
+      <c r="I36" t="s">
+        <v>97</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>1.94</v>
+      </c>
+      <c r="M36">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="1">
+        <v>151</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37">
+        <v>0.22</v>
+      </c>
+      <c r="E37">
+        <v>-0.8</v>
+      </c>
+      <c r="F37">
+        <v>-0.725</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+      <c r="H37" t="s">
+        <v>149</v>
+      </c>
+      <c r="I37" t="s">
+        <v>97</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>1.94</v>
+      </c>
+      <c r="M37">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="1">
+        <v>152</v>
+      </c>
+      <c r="B38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38">
+        <v>0.06</v>
+      </c>
+      <c r="E38">
+        <v>0.45</v>
+      </c>
+      <c r="F38">
+        <v>-0.175</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+      <c r="H38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I38" t="s">
+        <v>97</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>1.94</v>
+      </c>
+      <c r="M38">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="1">
+        <v>154</v>
+      </c>
+      <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39">
+        <v>0.108</v>
+      </c>
+      <c r="E39">
+        <v>-0.45</v>
+      </c>
+      <c r="F39">
+        <v>-0.175</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39" t="s">
+        <v>149</v>
+      </c>
+      <c r="I39" t="s">
+        <v>97</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>1.94</v>
+      </c>
+      <c r="M39">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="1">
+        <v>155</v>
+      </c>
+      <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40">
+        <v>0.208</v>
+      </c>
+      <c r="E40">
+        <v>-0.575</v>
+      </c>
+      <c r="F40">
+        <v>-1.024</v>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+      <c r="H40" t="s">
+        <v>149</v>
+      </c>
+      <c r="I40" t="s">
+        <v>97</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <v>1.94</v>
+      </c>
+      <c r="M40">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="1">
+        <v>254</v>
+      </c>
+      <c r="B41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41">
+        <v>0.183</v>
+      </c>
+      <c r="E41">
+        <v>-0.27</v>
+      </c>
+      <c r="F41">
+        <v>-0.83</v>
+      </c>
+      <c r="G41">
+        <v>5</v>
+      </c>
+      <c r="H41" t="s">
+        <v>149</v>
+      </c>
+      <c r="I41" t="s">
+        <v>97</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>1.94</v>
+      </c>
+      <c r="M41">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="1">
+        <v>272</v>
+      </c>
+      <c r="B42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42">
+        <v>0.57</v>
+      </c>
+      <c r="E42">
+        <v>1.075</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42" t="s">
+        <v>95</v>
+      </c>
+      <c r="H42" t="s">
+        <v>149</v>
+      </c>
+      <c r="I42" t="s">
+        <v>97</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>2.9</v>
+      </c>
+      <c r="M42">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="1">
+        <v>277</v>
+      </c>
+      <c r="B43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43">
+        <v>1.06</v>
+      </c>
+      <c r="E43">
+        <v>1.535</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" t="s">
+        <v>95</v>
+      </c>
+      <c r="H43" t="s">
+        <v>149</v>
+      </c>
+      <c r="I43" t="s">
+        <v>97</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>2.9</v>
+      </c>
+      <c r="M43">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="1">
+        <v>270</v>
+      </c>
+      <c r="B44" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44">
+        <v>0.96</v>
+      </c>
+      <c r="E44">
+        <v>1.535</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44" t="s">
+        <v>95</v>
+      </c>
+      <c r="H44" t="s">
+        <v>149</v>
+      </c>
+      <c r="I44" t="s">
+        <v>97</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="L44">
+        <v>2.9</v>
+      </c>
+      <c r="M44">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="1">
+        <v>269</v>
+      </c>
+      <c r="B45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45">
+        <v>1.06</v>
+      </c>
+      <c r="E45">
+        <v>1.535</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>95</v>
+      </c>
+      <c r="H45" t="s">
+        <v>149</v>
+      </c>
+      <c r="I45" t="s">
+        <v>97</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>2.9</v>
+      </c>
+      <c r="M45">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="1">
+        <v>268</v>
+      </c>
+      <c r="B46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" t="s">
+        <v>142</v>
+      </c>
+      <c r="D46">
+        <v>0.96</v>
+      </c>
+      <c r="E46">
+        <v>1.535</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
+        <v>95</v>
+      </c>
+      <c r="H46" t="s">
+        <v>149</v>
+      </c>
+      <c r="I46" t="s">
+        <v>97</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>2.9</v>
+      </c>
+      <c r="M46">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="1">
+        <v>267</v>
+      </c>
+      <c r="B47" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" t="s">
+        <v>143</v>
+      </c>
+      <c r="D47">
+        <v>0.72</v>
+      </c>
+      <c r="E47">
+        <v>1.075</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47" t="s">
+        <v>149</v>
+      </c>
+      <c r="I47" t="s">
+        <v>97</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>2.9</v>
+      </c>
+      <c r="M47">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="1">
+        <v>264</v>
+      </c>
+      <c r="B48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48">
+        <v>0.57</v>
+      </c>
+      <c r="E48">
+        <v>1.075</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48" t="s">
+        <v>95</v>
+      </c>
+      <c r="H48" t="s">
+        <v>149</v>
+      </c>
+      <c r="I48" t="s">
+        <v>97</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <v>2.9</v>
+      </c>
+      <c r="M48">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="1">
+        <v>265</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" t="s">
+        <v>144</v>
+      </c>
+      <c r="D49">
+        <v>0.72</v>
+      </c>
+      <c r="E49">
+        <v>1.075</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>95</v>
+      </c>
+      <c r="H49" t="s">
+        <v>149</v>
+      </c>
+      <c r="I49" t="s">
+        <v>97</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <v>2.9</v>
+      </c>
+      <c r="M49">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="1">
+        <v>276</v>
+      </c>
+      <c r="B50" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" t="s">
+        <v>142</v>
+      </c>
+      <c r="D50">
+        <v>0.96</v>
+      </c>
+      <c r="E50">
+        <v>1.535</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>95</v>
+      </c>
+      <c r="H50" t="s">
+        <v>149</v>
+      </c>
+      <c r="I50" t="s">
+        <v>97</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="L50">
+        <v>2.9</v>
+      </c>
+      <c r="M50">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="1">
+        <v>273</v>
+      </c>
+      <c r="B51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D51">
+        <v>0.72</v>
+      </c>
+      <c r="E51">
+        <v>1.075</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51" t="s">
+        <v>95</v>
+      </c>
+      <c r="H51" t="s">
+        <v>149</v>
+      </c>
+      <c r="I51" t="s">
+        <v>97</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <v>2.9</v>
+      </c>
+      <c r="M51">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="1">
+        <v>274</v>
+      </c>
+      <c r="B52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" t="s">
+        <v>145</v>
+      </c>
+      <c r="D52">
+        <v>0.57</v>
+      </c>
+      <c r="E52">
+        <v>1.075</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52" t="s">
+        <v>95</v>
+      </c>
+      <c r="H52" t="s">
+        <v>149</v>
+      </c>
+      <c r="I52" t="s">
+        <v>97</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <v>2.9</v>
+      </c>
+      <c r="M52">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="1">
+        <v>275</v>
+      </c>
+      <c r="B53" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" t="s">
+        <v>143</v>
+      </c>
+      <c r="D53">
+        <v>0.72</v>
+      </c>
+      <c r="E53">
+        <v>1.075</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53" t="s">
+        <v>95</v>
+      </c>
+      <c r="H53" t="s">
+        <v>149</v>
+      </c>
+      <c r="I53" t="s">
+        <v>97</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>2.9</v>
+      </c>
+      <c r="M53">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="1">
+        <v>266</v>
+      </c>
+      <c r="B54" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54">
+        <v>0.57</v>
+      </c>
+      <c r="E54">
+        <v>1.075</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54" t="s">
+        <v>95</v>
+      </c>
+      <c r="H54" t="s">
+        <v>149</v>
+      </c>
+      <c r="I54" t="s">
+        <v>97</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="L54">
+        <v>2.9</v>
+      </c>
+      <c r="M54">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="1">
+        <v>271</v>
+      </c>
+      <c r="B55" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55">
+        <v>1.06</v>
+      </c>
+      <c r="E55">
+        <v>1.535</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55" t="s">
+        <v>95</v>
+      </c>
+      <c r="H55" t="s">
+        <v>149</v>
+      </c>
+      <c r="I55" t="s">
+        <v>97</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="L55">
+        <v>2.9</v>
+      </c>
+      <c r="M55">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="1">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" t="s">
+        <v>147</v>
+      </c>
+      <c r="D56">
+        <v>0.645</v>
+      </c>
+      <c r="E56">
+        <v>1.112</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56" t="s">
+        <v>95</v>
+      </c>
+      <c r="H56" t="s">
+        <v>149</v>
+      </c>
+      <c r="I56" t="s">
+        <v>97</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>2.9</v>
+      </c>
+      <c r="M56">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" s="1">
+        <v>1</v>
+      </c>
+      <c r="B57" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57">
+        <v>1.01</v>
+      </c>
+      <c r="E57">
+        <v>1.535</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57" t="s">
+        <v>95</v>
+      </c>
+      <c r="H57" t="s">
+        <v>149</v>
+      </c>
+      <c r="I57" t="s">
+        <v>97</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="L57">
+        <v>2.9</v>
+      </c>
+      <c r="M57">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="1">
+        <v>278</v>
+      </c>
+      <c r="B58" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" t="s">
+        <v>141</v>
+      </c>
+      <c r="D58">
+        <v>0.96</v>
+      </c>
+      <c r="E58">
+        <v>1.535</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
+        <v>95</v>
+      </c>
+      <c r="H58" t="s">
+        <v>149</v>
+      </c>
+      <c r="I58" t="s">
+        <v>97</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <v>2.9</v>
+      </c>
+      <c r="M58">
+        <v>1.932</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="1">
+        <v>279</v>
+      </c>
+      <c r="B59" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59">
+        <v>1.06</v>
+      </c>
+      <c r="E59">
+        <v>1.535</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
+        <v>95</v>
+      </c>
+      <c r="H59" t="s">
+        <v>149</v>
+      </c>
+      <c r="I59" t="s">
+        <v>97</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="L59">
+        <v>2.9</v>
+      </c>
+      <c r="M59">
+        <v>1.932</v>
       </c>
     </row>
   </sheetData>
@@ -4559,11 +6183,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:O1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4571,13 +6195,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="144">
   <si>
     <t>Marking type</t>
   </si>
@@ -63,150 +63,126 @@
     <t>Tile</t>
   </si>
   <si>
+    <t>TMP1S2f1</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
+    <t>TMP1S2c4</t>
+  </si>
+  <si>
+    <t>TMP1S2d1</t>
+  </si>
+  <si>
     <t>TMP1S2d2</t>
   </si>
   <si>
+    <t>TMP1S2d3</t>
+  </si>
+  <si>
+    <t>TMP1S2d4</t>
+  </si>
+  <si>
+    <t>TMP1S2e1</t>
+  </si>
+  <si>
+    <t>TMP1S2e2</t>
+  </si>
+  <si>
+    <t>TMP1S2e3</t>
+  </si>
+  <si>
+    <t>TMP1S2e4</t>
+  </si>
+  <si>
+    <t>TMP1S2f2</t>
+  </si>
+  <si>
+    <t>TMP1S2f3</t>
+  </si>
+  <si>
+    <t>TMP1S2f4</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
     <t>TMP1S2b2</t>
   </si>
   <si>
-    <t>TMP1S2b3</t>
-  </si>
-  <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
     <t>TMP1S2c2</t>
   </si>
   <si>
-    <t>TMP1S2c3</t>
+    <t>TMP1S2a4</t>
   </si>
   <si>
     <t>TMP1S2b1</t>
   </si>
   <si>
-    <t>TMP1S2c4</t>
-  </si>
-  <si>
-    <t>TMP1S2f2</t>
-  </si>
-  <si>
-    <t>TMP1S2d3</t>
-  </si>
-  <si>
-    <t>TMP1S2d4</t>
-  </si>
-  <si>
-    <t>TMP1S2e1</t>
-  </si>
-  <si>
-    <t>TMP1S2e2</t>
-  </si>
-  <si>
-    <t>TMP1S2e3</t>
-  </si>
-  <si>
-    <t>TMP1S2d1</t>
-  </si>
-  <si>
-    <t>TMP1S2e4</t>
-  </si>
-  <si>
-    <t>TMP1S2a4</t>
-  </si>
-  <si>
     <t>TMP1S2a2</t>
   </si>
   <si>
     <t>TMP1S2a3</t>
   </si>
   <si>
-    <t>TMP1S2f1</t>
-  </si>
-  <si>
-    <t>TMP1S2f4</t>
-  </si>
-  <si>
-    <t>TMP1S2f3</t>
-  </si>
-  <si>
     <t>TMP1S2a1</t>
   </si>
   <si>
+    <t>TMP2S2c4</t>
+  </si>
+  <si>
+    <t>TMP2S2c3</t>
+  </si>
+  <si>
+    <t>TMP2S2c2</t>
+  </si>
+  <si>
     <t>TMP2S2c1</t>
   </si>
   <si>
+    <t>TMP2S2b2</t>
+  </si>
+  <si>
     <t>TMP2S2b1</t>
   </si>
   <si>
-    <t>TMP2S2c3</t>
-  </si>
-  <si>
-    <t>TMP2S2c4</t>
-  </si>
-  <si>
     <t>TMP2S2a2</t>
   </si>
   <si>
-    <t>TMP2S2b2</t>
-  </si>
-  <si>
-    <t>TMP2S2c2</t>
-  </si>
-  <si>
     <t>TMP2S2a1</t>
   </si>
   <si>
-    <t>TMP3S2b3</t>
-  </si>
-  <si>
-    <t>TMP3S2b2</t>
-  </si>
-  <si>
-    <t>TMP3S2b1</t>
+    <t>TMP3S2a2</t>
+  </si>
+  <si>
+    <t>TMP3S2a3</t>
+  </si>
+  <si>
+    <t>TMP3S2a1</t>
   </si>
   <si>
     <t>TMP3S2a4</t>
   </si>
   <si>
-    <t>TMP3S2b4</t>
-  </si>
-  <si>
-    <t>TMP3S2a1</t>
-  </si>
-  <si>
-    <t>TMP3S2a2</t>
-  </si>
-  <si>
-    <t>TMP3S2a3</t>
-  </si>
-  <si>
     <t>TMP4S2a4</t>
   </si>
   <si>
-    <t>TMP4S2b3</t>
-  </si>
-  <si>
-    <t>TMP4S2b2</t>
-  </si>
-  <si>
-    <t>TMP4S2b1</t>
-  </si>
-  <si>
-    <t>TMP4S2b4</t>
-  </si>
-  <si>
     <t>TMP4S2a2</t>
   </si>
   <si>
+    <t>TMP4S2a1</t>
+  </si>
+  <si>
     <t>TMP4S2a3</t>
   </si>
   <si>
-    <t>TMP4S2a1</t>
-  </si>
-  <si>
     <t>TMP5S2a1</t>
   </si>
   <si>
@@ -216,9 +192,6 @@
     <t>TMP5S2a3</t>
   </si>
   <si>
-    <t>TMP5S2a4</t>
-  </si>
-  <si>
     <t>TMP6S2a2</t>
   </si>
   <si>
@@ -228,21 +201,21 @@
     <t>TMP6S2a3</t>
   </si>
   <si>
+    <t>TMP6S2b4</t>
+  </si>
+  <si>
+    <t>TMP6S2b1</t>
+  </si>
+  <si>
+    <t>TMP6S2b2</t>
+  </si>
+  <si>
+    <t>TMP6S2b3</t>
+  </si>
+  <si>
     <t>TMP6S2a4</t>
   </si>
   <si>
-    <t>TMP6S2b1</t>
-  </si>
-  <si>
-    <t>TMP6S2b2</t>
-  </si>
-  <si>
-    <t>TMP6S2b3</t>
-  </si>
-  <si>
-    <t>TMP6S2b4</t>
-  </si>
-  <si>
     <t>TMP7S2e1</t>
   </si>
   <si>
@@ -330,28 +303,31 @@
     <t>LP3S3a1</t>
   </si>
   <si>
+    <t>LP3S3a2</t>
+  </si>
+  <si>
+    <t>LP3S3a3</t>
+  </si>
+  <si>
+    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
+  </si>
+  <si>
     <t>LP3S3a4</t>
   </si>
   <si>
-    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
-  </si>
-  <si>
-    <t>LP3S3a3</t>
-  </si>
-  <si>
-    <t>LP3S3a2</t>
+    <t>LP4S3a1</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
   </si>
   <si>
     <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
   </si>
   <si>
-    <t>LP4S3a1</t>
-  </si>
-  <si>
     <t>LP4S3a2</t>
   </si>
   <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
+    <t>LP5S3a2</t>
   </si>
   <si>
     <t>LP5S3d2</t>
@@ -375,6 +351,9 @@
     <t>LP5S3b3</t>
   </si>
   <si>
+    <t>LP5S3b2</t>
+  </si>
+  <si>
     <t>LP5S3d3</t>
   </si>
   <si>
@@ -390,15 +369,9 @@
     <t>LP5S3a3</t>
   </si>
   <si>
-    <t>LP5S3a2</t>
-  </si>
-  <si>
     <t>LP5S3a1</t>
   </si>
   <si>
-    <t>LP5S3b2</t>
-  </si>
-  <si>
     <t>LP5S3d4</t>
   </si>
   <si>
@@ -435,28 +408,28 @@
     <t>LP5S3b4</t>
   </si>
   <si>
+    <t>LP7S3b4</t>
+  </si>
+  <si>
+    <t>LP7S3b2</t>
+  </si>
+  <si>
+    <t>LP7S3b1</t>
+  </si>
+  <si>
+    <t>LP7S3a4</t>
+  </si>
+  <si>
+    <t>LP7S3a3</t>
+  </si>
+  <si>
     <t>LP7S3a1</t>
   </si>
   <si>
-    <t>LP7S3b2</t>
+    <t>LP7S3a2</t>
   </si>
   <si>
     <t>LP7S3b3</t>
-  </si>
-  <si>
-    <t>LP7S3b1</t>
-  </si>
-  <si>
-    <t>LP7S3a4</t>
-  </si>
-  <si>
-    <t>LP7S3a2</t>
-  </si>
-  <si>
-    <t>LP7S3a3</t>
-  </si>
-  <si>
-    <t>LP7S3b4</t>
   </si>
   <si>
     <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
@@ -832,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -881,7 +854,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -893,10 +866,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F2">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -905,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -919,7 +892,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -934,7 +907,7 @@
         <v>0.49</v>
       </c>
       <c r="F3">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -943,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -957,7 +930,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -969,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F4">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -981,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -995,7 +968,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -1007,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F5">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1019,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1033,7 +1006,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1048,7 +1021,7 @@
         <v>0.47</v>
       </c>
       <c r="F6">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1057,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1071,7 +1044,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1083,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F7">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1095,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1109,7 +1082,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1121,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F8">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1133,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1147,7 +1120,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1159,10 +1132,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
       <c r="F9">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1171,7 +1144,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1185,7 +1158,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1197,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F10">
         <v>1.025</v>
@@ -1209,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1223,7 +1196,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1235,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>-1.35</v>
+        <v>-0.35</v>
       </c>
       <c r="F11">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1247,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1261,7 +1234,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1273,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F12">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1285,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1299,7 +1272,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1311,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F13">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1323,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1337,7 +1310,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1352,7 +1325,7 @@
         <v>-0.35</v>
       </c>
       <c r="F14">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1361,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1375,7 +1348,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1387,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-0.35</v>
+        <v>-1.35</v>
       </c>
       <c r="F15">
         <v>-0.175</v>
@@ -1399,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1413,7 +1386,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1425,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-0.35</v>
+        <v>-1.35</v>
       </c>
       <c r="F16">
         <v>0.425</v>
@@ -1437,7 +1410,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1451,7 +1424,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1463,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F17">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1475,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1489,7 +1462,7 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1501,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F18">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1513,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1527,7 +1500,7 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1539,10 +1512,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0.9350000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="F19">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1551,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1565,7 +1538,7 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1577,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.9350000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="F20">
         <v>-0.175</v>
@@ -1589,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1603,7 +1576,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1618,7 +1591,7 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="F21">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1627,7 +1600,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1641,7 +1614,7 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1653,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>-1.35</v>
+        <v>0.49</v>
       </c>
       <c r="F22">
         <v>-0.775</v>
@@ -1665,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1679,7 +1652,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1691,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F23">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1703,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1717,7 +1690,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1729,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>-1.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F24">
         <v>0.425</v>
@@ -1741,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1779,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1793,7 +1766,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1805,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="F26">
-        <v>-0.75</v>
+        <v>1.05</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1817,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1831,7 +1804,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1843,10 +1816,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="F27">
-        <v>-0.75</v>
+        <v>0.45</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1855,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1869,7 +1842,7 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1881,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="F28">
-        <v>0.45</v>
+        <v>-0.15</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1893,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1907,7 +1880,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -1919,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="F29">
-        <v>1.05</v>
+        <v>-0.75</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1931,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1945,7 +1918,7 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1957,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F30">
         <v>-0.15</v>
@@ -1969,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1983,7 +1956,7 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1998,7 +1971,7 @@
         <v>0.1</v>
       </c>
       <c r="F31">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2007,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2021,7 +1994,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -2033,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0.22</v>
+        <v>-0.5</v>
       </c>
       <c r="F32">
         <v>-0.15</v>
@@ -2045,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2083,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2097,7 +2070,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -2109,10 +2082,10 @@
         <v>0.6</v>
       </c>
       <c r="E34">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -2121,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2135,7 +2108,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2147,10 +2120,10 @@
         <v>0.6</v>
       </c>
       <c r="E35">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G35">
         <v>3</v>
@@ -2159,7 +2132,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2173,7 +2146,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2185,7 +2158,7 @@
         <v>0.6</v>
       </c>
       <c r="E36">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>-0.775</v>
@@ -2197,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2235,7 +2208,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2258,28 +2231,28 @@
         <v>51</v>
       </c>
       <c r="D38">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E38">
-        <v>0.445</v>
+        <v>-0.3</v>
       </c>
       <c r="F38">
         <v>1.025</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="L38">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M38">
         <v>2.655</v>
@@ -2287,7 +2260,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2296,28 +2269,28 @@
         <v>52</v>
       </c>
       <c r="D39">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F39">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M39">
         <v>2.655</v>
@@ -2325,7 +2298,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2334,28 +2307,28 @@
         <v>53</v>
       </c>
       <c r="D40">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F40">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M40">
         <v>2.655</v>
@@ -2363,7 +2336,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2372,28 +2345,28 @@
         <v>54</v>
       </c>
       <c r="D41">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F41">
         <v>0.425</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="L41">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M41">
         <v>2.655</v>
@@ -2401,7 +2374,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2410,28 +2383,28 @@
         <v>55</v>
       </c>
       <c r="D42">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>-0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F42">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M42">
         <v>2.655</v>
@@ -2439,7 +2412,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2448,28 +2421,28 @@
         <v>56</v>
       </c>
       <c r="D43">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M43">
         <v>2.655</v>
@@ -2477,7 +2450,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2486,28 +2459,28 @@
         <v>57</v>
       </c>
       <c r="D44">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="F44">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M44">
         <v>2.655</v>
@@ -2524,28 +2497,28 @@
         <v>58</v>
       </c>
       <c r="D45">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F45">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M45">
         <v>2.655</v>
@@ -2553,7 +2526,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2562,28 +2535,28 @@
         <v>59</v>
       </c>
       <c r="D46">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F46">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M46">
         <v>2.655</v>
@@ -2591,7 +2564,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2600,28 +2573,28 @@
         <v>60</v>
       </c>
       <c r="D47">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F47">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M47">
         <v>2.655</v>
@@ -2629,7 +2602,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2638,28 +2611,28 @@
         <v>61</v>
       </c>
       <c r="D48">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>-0.3</v>
       </c>
       <c r="F48">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J48">
         <v>1</v>
       </c>
       <c r="L48">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M48">
         <v>2.655</v>
@@ -2667,7 +2640,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2676,7 +2649,7 @@
         <v>62</v>
       </c>
       <c r="D49">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>-0.3</v>
@@ -2685,19 +2658,19 @@
         <v>-0.775</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="L49">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M49">
         <v>2.655</v>
@@ -2717,25 +2690,25 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>-0.45</v>
+        <v>-0.3</v>
       </c>
       <c r="F50">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="L50">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M50">
         <v>2.655</v>
@@ -2755,25 +2728,25 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F51">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="L51">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M51">
         <v>2.655</v>
@@ -2781,7 +2754,7 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2793,25 +2766,25 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F52">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M52">
         <v>2.655</v>
@@ -2819,7 +2792,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2828,36 +2801,36 @@
         <v>66</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="E53">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F53">
-        <v>-0.775</v>
-      </c>
-      <c r="G53">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="G53" t="s">
+        <v>86</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M53">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2866,31 +2839,31 @@
         <v>67</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E54">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F54">
-        <v>-0.175</v>
-      </c>
-      <c r="G54">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G54" t="s">
+        <v>86</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J54">
         <v>1</v>
       </c>
       <c r="L54">
+        <v>2.9</v>
+      </c>
+      <c r="M54">
         <v>1.932</v>
-      </c>
-      <c r="M54">
-        <v>2.655</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -2904,36 +2877,36 @@
         <v>68</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E55">
         <v>0.3</v>
       </c>
       <c r="F55">
-        <v>-0.775</v>
-      </c>
-      <c r="G55">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G55" t="s">
+        <v>86</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J55">
         <v>1</v>
       </c>
       <c r="L55">
+        <v>2.9</v>
+      </c>
+      <c r="M55">
         <v>1.932</v>
-      </c>
-      <c r="M55">
-        <v>2.655</v>
       </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2942,36 +2915,36 @@
         <v>69</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E56">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F56">
-        <v>0.425</v>
-      </c>
-      <c r="G56">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G56" t="s">
+        <v>86</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J56">
         <v>1</v>
       </c>
       <c r="L56">
+        <v>2.9</v>
+      </c>
+      <c r="M56">
         <v>1.932</v>
-      </c>
-      <c r="M56">
-        <v>2.655</v>
       </c>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2980,36 +2953,36 @@
         <v>70</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E57">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F57">
-        <v>1.025</v>
-      </c>
-      <c r="G57">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G57" t="s">
+        <v>86</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J57">
         <v>1</v>
       </c>
       <c r="L57">
+        <v>2.9</v>
+      </c>
+      <c r="M57">
         <v>1.932</v>
-      </c>
-      <c r="M57">
-        <v>2.655</v>
       </c>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -3018,36 +2991,36 @@
         <v>71</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E58">
-        <v>-0.3</v>
+        <v>0.75</v>
       </c>
       <c r="F58">
-        <v>-0.775</v>
-      </c>
-      <c r="G58">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
+        <v>86</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="L58">
+        <v>2.9</v>
+      </c>
+      <c r="M58">
         <v>1.932</v>
-      </c>
-      <c r="M58">
-        <v>2.655</v>
       </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -3056,36 +3029,36 @@
         <v>72</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E59">
-        <v>-0.3</v>
+        <v>0.9</v>
       </c>
       <c r="F59">
-        <v>-0.175</v>
-      </c>
-      <c r="G59">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
+        <v>86</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="L59">
+        <v>2.9</v>
+      </c>
+      <c r="M59">
         <v>1.932</v>
-      </c>
-      <c r="M59">
-        <v>2.655</v>
       </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -3094,36 +3067,36 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E60">
-        <v>-0.3</v>
+        <v>1.05</v>
       </c>
       <c r="F60">
-        <v>0.425</v>
-      </c>
-      <c r="G60">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
+        <v>86</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J60">
         <v>1</v>
       </c>
       <c r="L60">
+        <v>2.9</v>
+      </c>
+      <c r="M60">
         <v>1.932</v>
-      </c>
-      <c r="M60">
-        <v>2.655</v>
       </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -3132,36 +3105,36 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="E61">
-        <v>-0.3</v>
+        <v>1.2</v>
       </c>
       <c r="F61">
-        <v>1.025</v>
-      </c>
-      <c r="G61">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>86</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="L61">
+        <v>2.9</v>
+      </c>
+      <c r="M61">
         <v>1.932</v>
-      </c>
-      <c r="M61">
-        <v>2.655</v>
       </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3170,22 +3143,22 @@
         <v>75</v>
       </c>
       <c r="D62">
-        <v>2.61</v>
+        <v>0.72</v>
       </c>
       <c r="E62">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3208,22 +3181,22 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E63">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3246,22 +3219,22 @@
         <v>77</v>
       </c>
       <c r="D64">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E64">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3284,22 +3257,22 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E65">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3322,22 +3295,22 @@
         <v>79</v>
       </c>
       <c r="D66">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E66">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3360,22 +3333,22 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E67">
-        <v>0.75</v>
+        <v>1.05</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3398,22 +3371,22 @@
         <v>81</v>
       </c>
       <c r="D68">
-        <v>0.12</v>
+        <v>1.41</v>
       </c>
       <c r="E68">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3436,22 +3409,22 @@
         <v>82</v>
       </c>
       <c r="D69">
-        <v>0.12</v>
+        <v>1.41</v>
       </c>
       <c r="E69">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3465,7 +3438,7 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="1">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
@@ -3474,22 +3447,22 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>2.61</v>
+        <v>2.01</v>
       </c>
       <c r="E70">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3503,7 +3476,7 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="1">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -3512,22 +3485,22 @@
         <v>84</v>
       </c>
       <c r="D71">
-        <v>0.72</v>
+        <v>2.01</v>
       </c>
       <c r="E71">
-        <v>0.15</v>
+        <v>1.2</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3541,7 +3514,7 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="1">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -3553,19 +3526,19 @@
         <v>0.72</v>
       </c>
       <c r="E72">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F72">
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3574,348 +3547,6 @@
         <v>2.9</v>
       </c>
       <c r="M72">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13">
-      <c r="A73" s="1">
-        <v>226</v>
-      </c>
-      <c r="B73" t="s">
-        <v>14</v>
-      </c>
-      <c r="C73" t="s">
-        <v>86</v>
-      </c>
-      <c r="D73">
-        <v>0.72</v>
-      </c>
-      <c r="E73">
-        <v>0.6</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73" t="s">
-        <v>95</v>
-      </c>
-      <c r="H73">
-        <v>1</v>
-      </c>
-      <c r="I73" t="s">
-        <v>97</v>
-      </c>
-      <c r="J73">
-        <v>1</v>
-      </c>
-      <c r="L73">
-        <v>2.9</v>
-      </c>
-      <c r="M73">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13">
-      <c r="A74" s="1">
-        <v>227</v>
-      </c>
-      <c r="B74" t="s">
-        <v>14</v>
-      </c>
-      <c r="C74" t="s">
-        <v>87</v>
-      </c>
-      <c r="D74">
-        <v>0.72</v>
-      </c>
-      <c r="E74">
-        <v>0.75</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74" t="s">
-        <v>95</v>
-      </c>
-      <c r="H74">
-        <v>1</v>
-      </c>
-      <c r="I74" t="s">
-        <v>97</v>
-      </c>
-      <c r="J74">
-        <v>1</v>
-      </c>
-      <c r="L74">
-        <v>2.9</v>
-      </c>
-      <c r="M74">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13">
-      <c r="A75" s="1">
-        <v>228</v>
-      </c>
-      <c r="B75" t="s">
-        <v>14</v>
-      </c>
-      <c r="C75" t="s">
-        <v>88</v>
-      </c>
-      <c r="D75">
-        <v>0.72</v>
-      </c>
-      <c r="E75">
-        <v>0.9</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-      <c r="G75" t="s">
-        <v>95</v>
-      </c>
-      <c r="H75">
-        <v>1</v>
-      </c>
-      <c r="I75" t="s">
-        <v>97</v>
-      </c>
-      <c r="J75">
-        <v>1</v>
-      </c>
-      <c r="L75">
-        <v>2.9</v>
-      </c>
-      <c r="M75">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13">
-      <c r="A76" s="1">
-        <v>229</v>
-      </c>
-      <c r="B76" t="s">
-        <v>14</v>
-      </c>
-      <c r="C76" t="s">
-        <v>89</v>
-      </c>
-      <c r="D76">
-        <v>0.72</v>
-      </c>
-      <c r="E76">
-        <v>1.05</v>
-      </c>
-      <c r="F76">
-        <v>0</v>
-      </c>
-      <c r="G76" t="s">
-        <v>95</v>
-      </c>
-      <c r="H76">
-        <v>1</v>
-      </c>
-      <c r="I76" t="s">
-        <v>97</v>
-      </c>
-      <c r="J76">
-        <v>1</v>
-      </c>
-      <c r="L76">
-        <v>2.9</v>
-      </c>
-      <c r="M76">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13">
-      <c r="A77" s="1">
-        <v>230</v>
-      </c>
-      <c r="B77" t="s">
-        <v>14</v>
-      </c>
-      <c r="C77" t="s">
-        <v>90</v>
-      </c>
-      <c r="D77">
-        <v>1.41</v>
-      </c>
-      <c r="E77">
-        <v>0.6</v>
-      </c>
-      <c r="F77">
-        <v>0</v>
-      </c>
-      <c r="G77" t="s">
-        <v>95</v>
-      </c>
-      <c r="H77">
-        <v>1</v>
-      </c>
-      <c r="I77" t="s">
-        <v>97</v>
-      </c>
-      <c r="J77">
-        <v>1</v>
-      </c>
-      <c r="L77">
-        <v>2.9</v>
-      </c>
-      <c r="M77">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13">
-      <c r="A78" s="1">
-        <v>231</v>
-      </c>
-      <c r="B78" t="s">
-        <v>14</v>
-      </c>
-      <c r="C78" t="s">
-        <v>91</v>
-      </c>
-      <c r="D78">
-        <v>1.41</v>
-      </c>
-      <c r="E78">
-        <v>1.2</v>
-      </c>
-      <c r="F78">
-        <v>0</v>
-      </c>
-      <c r="G78" t="s">
-        <v>95</v>
-      </c>
-      <c r="H78">
-        <v>1</v>
-      </c>
-      <c r="I78" t="s">
-        <v>97</v>
-      </c>
-      <c r="J78">
-        <v>1</v>
-      </c>
-      <c r="L78">
-        <v>2.9</v>
-      </c>
-      <c r="M78">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13">
-      <c r="A79" s="1">
-        <v>232</v>
-      </c>
-      <c r="B79" t="s">
-        <v>14</v>
-      </c>
-      <c r="C79" t="s">
-        <v>92</v>
-      </c>
-      <c r="D79">
-        <v>2.01</v>
-      </c>
-      <c r="E79">
-        <v>0.6</v>
-      </c>
-      <c r="F79">
-        <v>0</v>
-      </c>
-      <c r="G79" t="s">
-        <v>95</v>
-      </c>
-      <c r="H79">
-        <v>1</v>
-      </c>
-      <c r="I79" t="s">
-        <v>97</v>
-      </c>
-      <c r="J79">
-        <v>1</v>
-      </c>
-      <c r="L79">
-        <v>2.9</v>
-      </c>
-      <c r="M79">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13">
-      <c r="A80" s="1">
-        <v>233</v>
-      </c>
-      <c r="B80" t="s">
-        <v>14</v>
-      </c>
-      <c r="C80" t="s">
-        <v>93</v>
-      </c>
-      <c r="D80">
-        <v>2.01</v>
-      </c>
-      <c r="E80">
-        <v>1.2</v>
-      </c>
-      <c r="F80">
-        <v>0</v>
-      </c>
-      <c r="G80" t="s">
-        <v>95</v>
-      </c>
-      <c r="H80">
-        <v>1</v>
-      </c>
-      <c r="I80" t="s">
-        <v>97</v>
-      </c>
-      <c r="J80">
-        <v>1</v>
-      </c>
-      <c r="L80">
-        <v>2.9</v>
-      </c>
-      <c r="M80">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13">
-      <c r="A81" s="1">
-        <v>224</v>
-      </c>
-      <c r="B81" t="s">
-        <v>14</v>
-      </c>
-      <c r="C81" t="s">
-        <v>94</v>
-      </c>
-      <c r="D81">
-        <v>0.72</v>
-      </c>
-      <c r="E81">
-        <v>0.3</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
-      </c>
-      <c r="G81" t="s">
-        <v>95</v>
-      </c>
-      <c r="H81">
-        <v>1</v>
-      </c>
-      <c r="I81" t="s">
-        <v>97</v>
-      </c>
-      <c r="J81">
-        <v>1</v>
-      </c>
-      <c r="L81">
-        <v>2.9</v>
-      </c>
-      <c r="M81">
         <v>1.932</v>
       </c>
     </row>
@@ -3975,13 +3606,13 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3996,10 +3627,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -4013,13 +3644,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -4034,10 +3665,10 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -4051,13 +3682,13 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -4072,10 +3703,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I4" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -4089,13 +3720,13 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -4110,10 +3741,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -4127,13 +3758,13 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D6">
         <v>0.6</v>
@@ -4148,10 +3779,10 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -4165,13 +3796,13 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D7">
         <v>0.6</v>
@@ -4180,16 +3811,16 @@
         <v>0.123</v>
       </c>
       <c r="F7">
-        <v>-0.188</v>
+        <v>0.962</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I7" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -4203,31 +3834,31 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>90</v>
+        <v>233</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D8">
         <v>0.6</v>
       </c>
       <c r="E8">
-        <v>0.21</v>
+        <v>-0.077</v>
       </c>
       <c r="F8">
-        <v>-0.05</v>
+        <v>-0.188</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I8" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -4241,31 +3872,31 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>242</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D9">
         <v>0.6</v>
       </c>
       <c r="E9">
-        <v>-0.077</v>
+        <v>0.21</v>
       </c>
       <c r="F9">
-        <v>-0.188</v>
+        <v>-0.05</v>
       </c>
       <c r="G9">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -4279,13 +3910,13 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" t="s">
         <v>98</v>
-      </c>
-      <c r="C10" t="s">
-        <v>107</v>
       </c>
       <c r="D10">
         <v>0.6</v>
@@ -4294,16 +3925,16 @@
         <v>0.123</v>
       </c>
       <c r="F10">
-        <v>0.962</v>
+        <v>-0.188</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I10" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -4317,31 +3948,31 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>40</v>
+        <v>235</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D11">
-        <v>0.9370000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E11">
-        <v>0.243</v>
+        <v>-0.195</v>
       </c>
       <c r="F11">
-        <v>-0.8</v>
+        <v>-0.375</v>
       </c>
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I11" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -4355,31 +3986,31 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>244</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D12">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="E12">
-        <v>-0.195</v>
+        <v>0.508</v>
       </c>
       <c r="F12">
-        <v>-0.375</v>
+        <v>1.468</v>
       </c>
       <c r="G12">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -4393,31 +4024,31 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>245</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D13">
-        <v>0.96</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E13">
-        <v>-0.145</v>
+        <v>0.243</v>
       </c>
       <c r="F13">
-        <v>-0.375</v>
+        <v>-0.8</v>
       </c>
       <c r="G13">
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I13" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -4431,31 +4062,31 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
+        <v>236</v>
+      </c>
+      <c r="B14" t="s">
         <v>89</v>
       </c>
-      <c r="B14" t="s">
-        <v>98</v>
-      </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D14">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="E14">
-        <v>0.508</v>
+        <v>-0.145</v>
       </c>
       <c r="F14">
-        <v>1.468</v>
+        <v>-0.375</v>
       </c>
       <c r="G14">
         <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -4469,31 +4100,31 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E15">
-        <v>0.9</v>
+        <v>-0.205</v>
       </c>
       <c r="F15">
-        <v>-0.15</v>
+        <v>0.026</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I15" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -4507,19 +4138,19 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F16">
         <v>-0.15</v>
@@ -4528,10 +4159,10 @@
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -4545,31 +4176,31 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>1.4</v>
+        <v>-0.15</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -4583,19 +4214,19 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-0.9</v>
+        <v>0.9</v>
       </c>
       <c r="F18">
         <v>1.4</v>
@@ -4604,10 +4235,10 @@
         <v>5</v>
       </c>
       <c r="H18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I18" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -4621,19 +4252,19 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0.9</v>
+        <v>-0.9</v>
       </c>
       <c r="F19">
         <v>1.4</v>
@@ -4642,10 +4273,10 @@
         <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I19" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -4659,19 +4290,19 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.9</v>
+        <v>0.9</v>
       </c>
       <c r="F20">
         <v>1.4</v>
@@ -4680,10 +4311,10 @@
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I20" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -4697,31 +4328,31 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D21">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>-0.63</v>
+        <v>-0.9</v>
       </c>
       <c r="F21">
-        <v>-0.83</v>
+        <v>1.4</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I21" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -4735,31 +4366,31 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="F22">
-        <v>-0.75</v>
+        <v>-0.83</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I22" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -4773,19 +4404,19 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D23">
         <v>0.183</v>
       </c>
       <c r="E23">
-        <v>-0.63</v>
+        <v>-0.27</v>
       </c>
       <c r="F23">
         <v>-0.402</v>
@@ -4794,10 +4425,10 @@
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I23" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -4811,31 +4442,31 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D24">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>-0.455</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>-0.22</v>
+        <v>-0.75</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I24" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -4849,31 +4480,31 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D25">
-        <v>0.08799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E25">
-        <v>-0.205</v>
+        <v>-0.63</v>
       </c>
       <c r="F25">
-        <v>-0.466</v>
+        <v>-0.402</v>
       </c>
       <c r="G25">
         <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I25" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -4887,31 +4518,31 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D26">
         <v>0.08799999999999999</v>
       </c>
       <c r="E26">
-        <v>-0.705</v>
+        <v>-0.455</v>
       </c>
       <c r="F26">
-        <v>-0.466</v>
+        <v>-0.22</v>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
       <c r="H26" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -4925,13 +4556,13 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D27">
         <v>0.08799999999999999</v>
@@ -4940,16 +4571,16 @@
         <v>-0.205</v>
       </c>
       <c r="F27">
-        <v>0.026</v>
+        <v>-0.466</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I27" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -4963,13 +4594,13 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D28">
         <v>0.08799999999999999</v>
@@ -4978,16 +4609,16 @@
         <v>-0.705</v>
       </c>
       <c r="F28">
-        <v>0.026</v>
+        <v>-0.466</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I28" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -5001,31 +4632,31 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D29">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E29">
-        <v>-0.27</v>
+        <v>-0.705</v>
       </c>
       <c r="F29">
-        <v>-0.402</v>
+        <v>0.026</v>
       </c>
       <c r="G29">
         <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I29" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -5039,13 +4670,13 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -5060,10 +4691,10 @@
         <v>5</v>
       </c>
       <c r="H30" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I30" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -5077,13 +4708,13 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D31">
         <v>0.183</v>
@@ -5098,10 +4729,10 @@
         <v>5</v>
       </c>
       <c r="H31" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I31" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -5118,10 +4749,10 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D32">
         <v>0.295</v>
@@ -5136,10 +4767,10 @@
         <v>5</v>
       </c>
       <c r="H32" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I32" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -5156,10 +4787,10 @@
         <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D33">
         <v>0.15</v>
@@ -5174,10 +4805,10 @@
         <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I33" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -5194,10 +4825,10 @@
         <v>57</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D34">
         <v>0.09</v>
@@ -5212,10 +4843,10 @@
         <v>5</v>
       </c>
       <c r="H34" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I34" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -5232,10 +4863,10 @@
         <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D35">
         <v>-0.037</v>
@@ -5250,10 +4881,10 @@
         <v>5</v>
       </c>
       <c r="H35" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I35" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -5270,10 +4901,10 @@
         <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D36">
         <v>0.435</v>
@@ -5288,10 +4919,10 @@
         <v>5</v>
       </c>
       <c r="H36" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I36" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -5308,10 +4939,10 @@
         <v>151</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D37">
         <v>0.22</v>
@@ -5326,10 +4957,10 @@
         <v>5</v>
       </c>
       <c r="H37" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I37" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -5346,10 +4977,10 @@
         <v>152</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D38">
         <v>0.06</v>
@@ -5364,10 +4995,10 @@
         <v>5</v>
       </c>
       <c r="H38" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I38" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -5384,10 +5015,10 @@
         <v>154</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D39">
         <v>0.108</v>
@@ -5402,10 +5033,10 @@
         <v>5</v>
       </c>
       <c r="H39" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I39" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -5422,10 +5053,10 @@
         <v>155</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D40">
         <v>0.208</v>
@@ -5440,10 +5071,10 @@
         <v>5</v>
       </c>
       <c r="H40" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -5457,13 +5088,13 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D41">
         <v>0.183</v>
@@ -5478,10 +5109,10 @@
         <v>5</v>
       </c>
       <c r="H41" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I41" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -5495,31 +5126,31 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D42">
-        <v>0.57</v>
+        <v>1.06</v>
       </c>
       <c r="E42">
-        <v>1.075</v>
+        <v>1.535</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I42" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -5533,13 +5164,13 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D43">
         <v>1.06</v>
@@ -5551,13 +5182,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I43" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -5571,16 +5202,16 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D44">
-        <v>0.96</v>
+        <v>1.06</v>
       </c>
       <c r="E44">
         <v>1.535</v>
@@ -5589,13 +5220,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I44" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -5609,16 +5240,16 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D45">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="E45">
         <v>1.535</v>
@@ -5627,13 +5258,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I45" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -5647,31 +5278,31 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D46">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="E46">
-        <v>1.535</v>
+        <v>1.075</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I46" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -5685,16 +5316,16 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D47">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="E47">
         <v>1.075</v>
@@ -5703,13 +5334,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I47" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -5723,13 +5354,13 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C48" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D48">
         <v>0.57</v>
@@ -5741,13 +5372,13 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I48" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -5761,16 +5392,16 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D49">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="E49">
         <v>1.075</v>
@@ -5779,13 +5410,13 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H49" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I49" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -5799,31 +5430,31 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C50" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D50">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="E50">
-        <v>1.535</v>
+        <v>1.075</v>
       </c>
       <c r="F50">
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I50" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -5837,16 +5468,16 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C51" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D51">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="E51">
         <v>1.075</v>
@@ -5855,13 +5486,13 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H51" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I51" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -5875,16 +5506,16 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D52">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="E52">
         <v>1.075</v>
@@ -5893,13 +5524,13 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H52" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I52" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -5913,31 +5544,31 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C53" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D53">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="E53">
-        <v>1.075</v>
+        <v>1.535</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I53" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -5951,16 +5582,16 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C54" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D54">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="E54">
         <v>1.075</v>
@@ -5969,13 +5600,13 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I54" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -5989,16 +5620,16 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C55" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D55">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="E55">
         <v>1.535</v>
@@ -6007,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I55" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -6030,10 +5661,10 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D56">
         <v>0.645</v>
@@ -6045,13 +5676,13 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I56" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -6068,10 +5699,10 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C57" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D57">
         <v>1.01</v>
@@ -6083,13 +5714,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I57" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -6103,13 +5734,13 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C58" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D58">
         <v>0.96</v>
@@ -6121,13 +5752,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I58" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -6141,13 +5772,13 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C59" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="D59">
         <v>1.06</v>
@@ -6159,13 +5790,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H59" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I59" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -6195,13 +5826,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="140">
   <si>
     <t>Marking type</t>
   </si>
@@ -63,88 +63,79 @@
     <t>Tile</t>
   </si>
   <si>
+    <t>TMP1S2e3</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2c2</t>
+  </si>
+  <si>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
+    <t>TMP1S2c4</t>
+  </si>
+  <si>
+    <t>TMP1S2d2</t>
+  </si>
+  <si>
+    <t>TMP1S2d3</t>
+  </si>
+  <si>
+    <t>TMP1S2d4</t>
+  </si>
+  <si>
+    <t>TMP1S2e1</t>
+  </si>
+  <si>
+    <t>TMP1S2e2</t>
+  </si>
+  <si>
+    <t>TMP1S2e4</t>
+  </si>
+  <si>
     <t>TMP1S2f1</t>
   </si>
   <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
-    <t>TMP1S2c3</t>
-  </si>
-  <si>
-    <t>TMP1S2c4</t>
+    <t>TMP1S2f2</t>
+  </si>
+  <si>
+    <t>TMP1S2f3</t>
+  </si>
+  <si>
+    <t>TMP1S2f4</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
+    <t>TMP1S2b2</t>
   </si>
   <si>
     <t>TMP1S2d1</t>
   </si>
   <si>
-    <t>TMP1S2d2</t>
-  </si>
-  <si>
-    <t>TMP1S2d3</t>
-  </si>
-  <si>
-    <t>TMP1S2d4</t>
-  </si>
-  <si>
-    <t>TMP1S2e1</t>
-  </si>
-  <si>
-    <t>TMP1S2e2</t>
-  </si>
-  <si>
-    <t>TMP1S2e3</t>
-  </si>
-  <si>
-    <t>TMP1S2e4</t>
-  </si>
-  <si>
-    <t>TMP1S2f2</t>
-  </si>
-  <si>
-    <t>TMP1S2f3</t>
-  </si>
-  <si>
-    <t>TMP1S2f4</t>
-  </si>
-  <si>
-    <t>TMP1S2b3</t>
-  </si>
-  <si>
-    <t>TMP1S2b2</t>
-  </si>
-  <si>
-    <t>TMP1S2c2</t>
-  </si>
-  <si>
     <t>TMP1S2a4</t>
   </si>
   <si>
+    <t>TMP1S2a1</t>
+  </si>
+  <si>
+    <t>TMP1S2a2</t>
+  </si>
+  <si>
+    <t>TMP1S2a3</t>
+  </si>
+  <si>
     <t>TMP1S2b1</t>
   </si>
   <si>
-    <t>TMP1S2a2</t>
-  </si>
-  <si>
-    <t>TMP1S2a3</t>
-  </si>
-  <si>
-    <t>TMP1S2a1</t>
-  </si>
-  <si>
-    <t>TMP2S2c4</t>
-  </si>
-  <si>
-    <t>TMP2S2c3</t>
-  </si>
-  <si>
-    <t>TMP2S2c2</t>
-  </si>
-  <si>
-    <t>TMP2S2c1</t>
+    <t>TMP2S2a1</t>
   </si>
   <si>
     <t>TMP2S2b2</t>
@@ -156,33 +147,30 @@
     <t>TMP2S2a2</t>
   </si>
   <si>
-    <t>TMP2S2a1</t>
+    <t>TMP3S2a4</t>
+  </si>
+  <si>
+    <t>TMP3S2a3</t>
   </si>
   <si>
     <t>TMP3S2a2</t>
   </si>
   <si>
-    <t>TMP3S2a3</t>
-  </si>
-  <si>
     <t>TMP3S2a1</t>
   </si>
   <si>
-    <t>TMP3S2a4</t>
+    <t>TMP4S2a1</t>
+  </si>
+  <si>
+    <t>TMP4S2a2</t>
+  </si>
+  <si>
+    <t>TMP4S2a3</t>
   </si>
   <si>
     <t>TMP4S2a4</t>
   </si>
   <si>
-    <t>TMP4S2a2</t>
-  </si>
-  <si>
-    <t>TMP4S2a1</t>
-  </si>
-  <si>
-    <t>TMP4S2a3</t>
-  </si>
-  <si>
     <t>TMP5S2a1</t>
   </si>
   <si>
@@ -192,28 +180,31 @@
     <t>TMP5S2a3</t>
   </si>
   <si>
+    <t>TMP6S2a1</t>
+  </si>
+  <si>
+    <t>TMP6S2b4</t>
+  </si>
+  <si>
+    <t>TMP6S2b3</t>
+  </si>
+  <si>
+    <t>TMP6S2b2</t>
+  </si>
+  <si>
+    <t>TMP6S2b1</t>
+  </si>
+  <si>
+    <t>TMP6S2a4</t>
+  </si>
+  <si>
     <t>TMP6S2a2</t>
   </si>
   <si>
-    <t>TMP6S2a1</t>
-  </si>
-  <si>
     <t>TMP6S2a3</t>
   </si>
   <si>
-    <t>TMP6S2b4</t>
-  </si>
-  <si>
-    <t>TMP6S2b1</t>
-  </si>
-  <si>
-    <t>TMP6S2b2</t>
-  </si>
-  <si>
-    <t>TMP6S2b3</t>
-  </si>
-  <si>
-    <t>TMP6S2a4</t>
+    <t>TMP7S2a2</t>
   </si>
   <si>
     <t>TMP7S2e1</t>
@@ -222,9 +213,6 @@
     <t>TMP7S2a1</t>
   </si>
   <si>
-    <t>TMP7S2a2</t>
-  </si>
-  <si>
     <t>TMP7S2a3</t>
   </si>
   <si>
@@ -240,42 +228,42 @@
     <t>TMP7S2a7</t>
   </si>
   <si>
+    <t>TMP7S2b1</t>
+  </si>
+  <si>
+    <t>TMP7S2b2</t>
+  </si>
+  <si>
+    <t>TMP7S2b3</t>
+  </si>
+  <si>
+    <t>TMP7S2b4</t>
+  </si>
+  <si>
+    <t>TMP7S2b5</t>
+  </si>
+  <si>
+    <t>TMP7S2b6</t>
+  </si>
+  <si>
+    <t>TMP7S2b7</t>
+  </si>
+  <si>
+    <t>TMP7S2c1</t>
+  </si>
+  <si>
+    <t>TMP7S2c2</t>
+  </si>
+  <si>
+    <t>TMP7S2d1</t>
+  </si>
+  <si>
+    <t>TMP7S2d2</t>
+  </si>
+  <si>
     <t>TMP7S2e2</t>
   </si>
   <si>
-    <t>TMP7S2b1</t>
-  </si>
-  <si>
-    <t>TMP7S2b3</t>
-  </si>
-  <si>
-    <t>TMP7S2b4</t>
-  </si>
-  <si>
-    <t>TMP7S2b5</t>
-  </si>
-  <si>
-    <t>TMP7S2b6</t>
-  </si>
-  <si>
-    <t>TMP7S2b7</t>
-  </si>
-  <si>
-    <t>TMP7S2c1</t>
-  </si>
-  <si>
-    <t>TMP7S2c2</t>
-  </si>
-  <si>
-    <t>TMP7S2d1</t>
-  </si>
-  <si>
-    <t>TMP7S2d2</t>
-  </si>
-  <si>
-    <t>TMP7S2b2</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -291,145 +279,145 @@
     <t>LP1S3a1</t>
   </si>
   <si>
+    <t>LP1S3a3</t>
+  </si>
+  <si>
+    <t>LP1S3a4</t>
+  </si>
+  <si>
     <t>LP1S3a2</t>
   </si>
   <si>
-    <t>LP1S3a3</t>
-  </si>
-  <si>
-    <t>LP1S3a4</t>
+    <t>LP3S3a4</t>
+  </si>
+  <si>
+    <t>LP3S3a2</t>
   </si>
   <si>
     <t>LP3S3a1</t>
   </si>
   <si>
-    <t>LP3S3a2</t>
+    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
   </si>
   <si>
     <t>LP3S3a3</t>
   </si>
   <si>
-    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
-  </si>
-  <si>
-    <t>LP3S3a4</t>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
   </si>
   <si>
     <t>LP4S3a1</t>
   </si>
   <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
-  </si>
-  <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
-  </si>
-  <si>
     <t>LP4S3a2</t>
   </si>
   <si>
+    <t>LP5S3c4</t>
+  </si>
+  <si>
+    <t>LP5S3c3</t>
+  </si>
+  <si>
+    <t>LP5S3c2</t>
+  </si>
+  <si>
+    <t>LP5S3d2</t>
+  </si>
+  <si>
+    <t>LP5S3d1</t>
+  </si>
+  <si>
+    <t>LP5S3a1</t>
+  </si>
+  <si>
     <t>LP5S3a2</t>
   </si>
   <si>
-    <t>LP5S3d2</t>
-  </si>
-  <si>
-    <t>LP5S3d1</t>
-  </si>
-  <si>
-    <t>LP5S3c4</t>
-  </si>
-  <si>
-    <t>LP5S3c3</t>
-  </si>
-  <si>
-    <t>LP5S3c2</t>
+    <t>LP5S3a3</t>
+  </si>
+  <si>
+    <t>LP5S3a4</t>
+  </si>
+  <si>
+    <t>LP5S3a5</t>
+  </si>
+  <si>
+    <t>LP5S3b1</t>
+  </si>
+  <si>
+    <t>LP5S3b2</t>
+  </si>
+  <si>
+    <t>LP5S3b3</t>
+  </si>
+  <si>
+    <t>LP5S3b4</t>
+  </si>
+  <si>
+    <t>LP5S3d3</t>
+  </si>
+  <si>
+    <t>LP5S3d4</t>
   </si>
   <si>
     <t>LP5S3c1</t>
   </si>
   <si>
-    <t>LP5S3b3</t>
-  </si>
-  <si>
-    <t>LP5S3b2</t>
-  </si>
-  <si>
-    <t>LP5S3d3</t>
-  </si>
-  <si>
-    <t>LP5S3b1</t>
-  </si>
-  <si>
-    <t>LP5S3a5</t>
-  </si>
-  <si>
-    <t>LP5S3a4</t>
-  </si>
-  <si>
-    <t>LP5S3a3</t>
-  </si>
-  <si>
-    <t>LP5S3a1</t>
-  </si>
-  <si>
-    <t>LP5S3d4</t>
+    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
   </si>
   <si>
     <t>LP5S3b5</t>
   </si>
   <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+  </si>
+  <si>
+    <t>BSS.GESSI,BM.49001:Default:1090988</t>
+  </si>
+  <si>
+    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
+  </si>
+  <si>
     <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
   </si>
   <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
-  </si>
-  <si>
     <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
   </si>
   <si>
-    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
-  </si>
-  <si>
-    <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
-  </si>
-  <si>
-    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
-  </si>
-  <si>
-    <t>LP5S3b4</t>
+    <t>LP7S3b2</t>
+  </si>
+  <si>
+    <t>LP7S3b3</t>
+  </si>
+  <si>
+    <t>LP7S3b1</t>
+  </si>
+  <si>
+    <t>LP7S3a4</t>
+  </si>
+  <si>
+    <t>LP7S3a3</t>
+  </si>
+  <si>
+    <t>LP7S3a2</t>
+  </si>
+  <si>
+    <t>LP7S3a1</t>
   </si>
   <si>
     <t>LP7S3b4</t>
-  </si>
-  <si>
-    <t>LP7S3b2</t>
-  </si>
-  <si>
-    <t>LP7S3b1</t>
-  </si>
-  <si>
-    <t>LP7S3a4</t>
-  </si>
-  <si>
-    <t>LP7S3a3</t>
-  </si>
-  <si>
-    <t>LP7S3a1</t>
-  </si>
-  <si>
-    <t>LP7S3a2</t>
-  </si>
-  <si>
-    <t>LP7S3b3</t>
   </si>
   <si>
     <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
@@ -805,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -854,7 +842,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -866,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-1.35</v>
+        <v>-0.35</v>
       </c>
       <c r="F2">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -878,7 +866,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -916,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -954,7 +942,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -968,7 +956,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -983,7 +971,7 @@
         <v>0.47</v>
       </c>
       <c r="F5">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -992,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1006,7 +994,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1021,7 +1009,7 @@
         <v>0.47</v>
       </c>
       <c r="F6">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1030,7 +1018,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1044,7 +1032,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1056,10 +1044,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F7">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1068,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1106,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1144,7 +1132,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1182,7 +1170,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1220,7 +1208,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1258,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1272,7 +1260,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1287,7 +1275,7 @@
         <v>-0.35</v>
       </c>
       <c r="F13">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1296,7 +1284,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1310,7 +1298,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1322,10 +1310,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-0.35</v>
+        <v>-1.35</v>
       </c>
       <c r="F14">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1334,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1372,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1410,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1448,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1486,7 +1474,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1524,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1538,7 +1526,7 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1550,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F20">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1562,7 +1550,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1600,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1614,7 +1602,7 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1626,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.49</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F22">
         <v>-0.775</v>
@@ -1638,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1676,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1714,7 +1702,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1728,7 +1716,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1740,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0.9350000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="F25">
         <v>-0.775</v>
@@ -1752,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1766,7 +1754,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1778,10 +1766,10 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="F26">
-        <v>1.05</v>
+        <v>-0.75</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1790,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1804,7 +1792,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1816,10 +1804,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="F27">
-        <v>0.45</v>
+        <v>-0.15</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1828,7 +1816,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1842,7 +1830,7 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1854,10 +1842,10 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="F28">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1866,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1880,7 +1868,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -1892,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="F29">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1904,7 +1892,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1918,7 +1906,7 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1927,28 +1915,28 @@
         <v>43</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E30">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>-0.15</v>
+        <v>1.025</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="L30">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="M30">
         <v>2.655</v>
@@ -1956,7 +1944,7 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1965,28 +1953,28 @@
         <v>44</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E31">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>-0.75</v>
+        <v>0.425</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="L31">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="M31">
         <v>2.655</v>
@@ -1994,7 +1982,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -2003,28 +1991,28 @@
         <v>45</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E32">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>-0.15</v>
+        <v>-0.175</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="L32">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="M32">
         <v>2.655</v>
@@ -2032,7 +2020,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -2041,28 +2029,28 @@
         <v>46</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E33">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>-0.75</v>
+        <v>-0.775</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="L33">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="M33">
         <v>2.655</v>
@@ -2070,7 +2058,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -2079,28 +2067,28 @@
         <v>47</v>
       </c>
       <c r="D34">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F34">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="L34">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M34">
         <v>2.655</v>
@@ -2108,7 +2096,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2117,28 +2105,28 @@
         <v>48</v>
       </c>
       <c r="D35">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F35">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="L35">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M35">
         <v>2.655</v>
@@ -2146,7 +2134,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2155,28 +2143,28 @@
         <v>49</v>
       </c>
       <c r="D36">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F36">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="L36">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M36">
         <v>2.655</v>
@@ -2193,28 +2181,28 @@
         <v>50</v>
       </c>
       <c r="D37">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F37">
         <v>1.025</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="L37">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M37">
         <v>2.655</v>
@@ -2222,7 +2210,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2231,28 +2219,28 @@
         <v>51</v>
       </c>
       <c r="D38">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>-0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F38">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="L38">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M38">
         <v>2.655</v>
@@ -2269,28 +2257,28 @@
         <v>52</v>
       </c>
       <c r="D39">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M39">
         <v>2.655</v>
@@ -2298,7 +2286,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2307,28 +2295,28 @@
         <v>53</v>
       </c>
       <c r="D40">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>-0.3</v>
+        <v>-0.45</v>
       </c>
       <c r="F40">
         <v>-0.775</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M40">
         <v>2.655</v>
@@ -2336,7 +2324,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2345,28 +2333,28 @@
         <v>54</v>
       </c>
       <c r="D41">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F41">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="L41">
-        <v>0.592</v>
+        <v>1.932</v>
       </c>
       <c r="M41">
         <v>2.655</v>
@@ -2374,7 +2362,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2386,25 +2374,25 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0.45</v>
+        <v>-0.3</v>
       </c>
       <c r="F42">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M42">
         <v>2.655</v>
@@ -2412,7 +2400,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2424,25 +2412,25 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F43">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M43">
         <v>2.655</v>
@@ -2450,7 +2438,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2462,25 +2450,25 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>-0.45</v>
+        <v>-0.3</v>
       </c>
       <c r="F44">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>1.94</v>
+        <v>1.932</v>
       </c>
       <c r="M44">
         <v>2.655</v>
@@ -2488,7 +2476,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2500,10 +2488,10 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F45">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -2512,7 +2500,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2526,7 +2514,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2541,7 +2529,7 @@
         <v>0.3</v>
       </c>
       <c r="F46">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G46">
         <v>6</v>
@@ -2550,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -2564,7 +2552,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2579,7 +2567,7 @@
         <v>0.3</v>
       </c>
       <c r="F47">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G47">
         <v>6</v>
@@ -2588,7 +2576,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2602,7 +2590,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2614,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F48">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -2626,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2640,7 +2628,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2649,36 +2637,36 @@
         <v>62</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E49">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F49">
-        <v>-0.775</v>
-      </c>
-      <c r="G49">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>82</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="L49">
+        <v>2.9</v>
+      </c>
+      <c r="M49">
         <v>1.932</v>
-      </c>
-      <c r="M49">
-        <v>2.655</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2687,36 +2675,36 @@
         <v>63</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="E50">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F50">
-        <v>-0.175</v>
-      </c>
-      <c r="G50">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>82</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="L50">
+        <v>2.9</v>
+      </c>
+      <c r="M50">
         <v>1.932</v>
-      </c>
-      <c r="M50">
-        <v>2.655</v>
       </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2725,36 +2713,36 @@
         <v>64</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E51">
-        <v>-0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F51">
-        <v>0.425</v>
-      </c>
-      <c r="G51">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G51" t="s">
+        <v>82</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="L51">
+        <v>2.9</v>
+      </c>
+      <c r="M51">
         <v>1.932</v>
-      </c>
-      <c r="M51">
-        <v>2.655</v>
       </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2763,36 +2751,36 @@
         <v>65</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E52">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F52">
-        <v>1.025</v>
-      </c>
-      <c r="G52">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="G52" t="s">
+        <v>82</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="L52">
+        <v>2.9</v>
+      </c>
+      <c r="M52">
         <v>1.932</v>
-      </c>
-      <c r="M52">
-        <v>2.655</v>
       </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2801,7 +2789,7 @@
         <v>66</v>
       </c>
       <c r="D53">
-        <v>2.61</v>
+        <v>0.12</v>
       </c>
       <c r="E53">
         <v>0.6</v>
@@ -2810,13 +2798,13 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2842,19 +2830,19 @@
         <v>0.12</v>
       </c>
       <c r="E54">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2880,19 +2868,19 @@
         <v>0.12</v>
       </c>
       <c r="E55">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2918,19 +2906,19 @@
         <v>0.12</v>
       </c>
       <c r="E56">
-        <v>0.45</v>
+        <v>1.05</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2953,22 +2941,22 @@
         <v>70</v>
       </c>
       <c r="D57">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E57">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2991,22 +2979,22 @@
         <v>71</v>
       </c>
       <c r="D58">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E58">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="F58">
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -3029,22 +3017,22 @@
         <v>72</v>
       </c>
       <c r="D59">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E59">
-        <v>0.9</v>
+        <v>0.45</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -3067,22 +3055,22 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E60">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -3096,7 +3084,7 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -3105,22 +3093,22 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>2.61</v>
+        <v>0.72</v>
       </c>
       <c r="E61">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -3134,7 +3122,7 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3146,19 +3134,19 @@
         <v>0.72</v>
       </c>
       <c r="E62">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3184,19 +3172,19 @@
         <v>0.72</v>
       </c>
       <c r="E63">
-        <v>0.45</v>
+        <v>1.05</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3219,7 +3207,7 @@
         <v>77</v>
       </c>
       <c r="D64">
-        <v>0.72</v>
+        <v>1.41</v>
       </c>
       <c r="E64">
         <v>0.6</v>
@@ -3228,13 +3216,13 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3257,22 +3245,22 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>0.72</v>
+        <v>1.41</v>
       </c>
       <c r="E65">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3295,22 +3283,22 @@
         <v>79</v>
       </c>
       <c r="D66">
-        <v>0.72</v>
+        <v>2.01</v>
       </c>
       <c r="E66">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3333,22 +3321,22 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>0.72</v>
+        <v>2.01</v>
       </c>
       <c r="E67">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3362,7 +3350,7 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="1">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3371,22 +3359,22 @@
         <v>81</v>
       </c>
       <c r="D68">
-        <v>1.41</v>
+        <v>2.61</v>
       </c>
       <c r="E68">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3395,158 +3383,6 @@
         <v>2.9</v>
       </c>
       <c r="M68">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13">
-      <c r="A69" s="1">
-        <v>222</v>
-      </c>
-      <c r="B69" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" t="s">
-        <v>82</v>
-      </c>
-      <c r="D69">
-        <v>1.41</v>
-      </c>
-      <c r="E69">
-        <v>1.2</v>
-      </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
-      <c r="G69" t="s">
-        <v>86</v>
-      </c>
-      <c r="H69">
-        <v>1</v>
-      </c>
-      <c r="I69" t="s">
-        <v>88</v>
-      </c>
-      <c r="J69">
-        <v>1</v>
-      </c>
-      <c r="L69">
-        <v>2.9</v>
-      </c>
-      <c r="M69">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13">
-      <c r="A70" s="1">
-        <v>223</v>
-      </c>
-      <c r="B70" t="s">
-        <v>14</v>
-      </c>
-      <c r="C70" t="s">
-        <v>83</v>
-      </c>
-      <c r="D70">
-        <v>2.01</v>
-      </c>
-      <c r="E70">
-        <v>0.6</v>
-      </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
-      <c r="G70" t="s">
-        <v>86</v>
-      </c>
-      <c r="H70">
-        <v>1</v>
-      </c>
-      <c r="I70" t="s">
-        <v>88</v>
-      </c>
-      <c r="J70">
-        <v>1</v>
-      </c>
-      <c r="L70">
-        <v>2.9</v>
-      </c>
-      <c r="M70">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13">
-      <c r="A71" s="1">
-        <v>224</v>
-      </c>
-      <c r="B71" t="s">
-        <v>14</v>
-      </c>
-      <c r="C71" t="s">
-        <v>84</v>
-      </c>
-      <c r="D71">
-        <v>2.01</v>
-      </c>
-      <c r="E71">
-        <v>1.2</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71" t="s">
-        <v>86</v>
-      </c>
-      <c r="H71">
-        <v>1</v>
-      </c>
-      <c r="I71" t="s">
-        <v>88</v>
-      </c>
-      <c r="J71">
-        <v>1</v>
-      </c>
-      <c r="L71">
-        <v>2.9</v>
-      </c>
-      <c r="M71">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13">
-      <c r="A72" s="1">
-        <v>215</v>
-      </c>
-      <c r="B72" t="s">
-        <v>14</v>
-      </c>
-      <c r="C72" t="s">
-        <v>85</v>
-      </c>
-      <c r="D72">
-        <v>0.72</v>
-      </c>
-      <c r="E72">
-        <v>0.3</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="G72" t="s">
-        <v>86</v>
-      </c>
-      <c r="H72">
-        <v>1</v>
-      </c>
-      <c r="I72" t="s">
-        <v>88</v>
-      </c>
-      <c r="J72">
-        <v>1</v>
-      </c>
-      <c r="L72">
-        <v>2.9</v>
-      </c>
-      <c r="M72">
         <v>1.932</v>
       </c>
     </row>
@@ -3606,13 +3442,13 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3627,10 +3463,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -3644,31 +3480,31 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>-0.255</v>
+        <v>0.375</v>
       </c>
       <c r="F3">
-        <v>0.213</v>
+        <v>0.137</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3682,19 +3518,19 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.375</v>
+        <v>-0.255</v>
       </c>
       <c r="F4">
         <v>0.137</v>
@@ -3703,10 +3539,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -3720,13 +3556,13 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
         <v>89</v>
-      </c>
-      <c r="C5" t="s">
-        <v>93</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -3735,16 +3571,16 @@
         <v>-0.255</v>
       </c>
       <c r="F5">
-        <v>0.137</v>
+        <v>0.213</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -3758,31 +3594,31 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D6">
         <v>0.6</v>
       </c>
       <c r="E6">
-        <v>-0.077</v>
+        <v>0.123</v>
       </c>
       <c r="F6">
-        <v>0.962</v>
+        <v>-0.188</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -3796,13 +3632,13 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D7">
         <v>0.6</v>
@@ -3817,10 +3653,10 @@
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -3834,13 +3670,13 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D8">
         <v>0.6</v>
@@ -3849,16 +3685,16 @@
         <v>-0.077</v>
       </c>
       <c r="F8">
-        <v>-0.188</v>
+        <v>0.962</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -3875,10 +3711,10 @@
         <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D9">
         <v>0.6</v>
@@ -3893,10 +3729,10 @@
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -3910,19 +3746,19 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D10">
         <v>0.6</v>
       </c>
       <c r="E10">
-        <v>0.123</v>
+        <v>-0.077</v>
       </c>
       <c r="F10">
         <v>-0.188</v>
@@ -3931,10 +3767,10 @@
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -3948,31 +3784,31 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>235</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D11">
-        <v>0.96</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E11">
-        <v>-0.195</v>
+        <v>0.243</v>
       </c>
       <c r="F11">
-        <v>-0.375</v>
+        <v>-0.8</v>
       </c>
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -3989,10 +3825,10 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D12">
         <v>0.86</v>
@@ -4007,10 +3843,10 @@
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -4024,31 +3860,31 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>40</v>
+        <v>231</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D13">
-        <v>0.9370000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E13">
-        <v>0.243</v>
+        <v>-0.195</v>
       </c>
       <c r="F13">
-        <v>-0.8</v>
+        <v>-0.375</v>
       </c>
       <c r="G13">
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -4062,13 +3898,13 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D14">
         <v>0.96</v>
@@ -4083,10 +3919,10 @@
         <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -4100,31 +3936,31 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D15">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>-0.205</v>
+        <v>0.9</v>
       </c>
       <c r="F15">
-        <v>0.026</v>
+        <v>1.4</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -4138,31 +3974,31 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.9</v>
+        <v>-0.9</v>
       </c>
       <c r="F16">
-        <v>-0.15</v>
+        <v>1.4</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -4176,31 +4012,31 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F17">
-        <v>-0.15</v>
+        <v>1.4</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -4214,13 +4050,13 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -4229,16 +4065,16 @@
         <v>0.9</v>
       </c>
       <c r="F18">
-        <v>1.4</v>
+        <v>-0.15</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -4252,31 +4088,31 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1.4</v>
+        <v>-0.15</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -4290,31 +4126,31 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E20">
-        <v>0.9</v>
+        <v>-0.705</v>
       </c>
       <c r="F20">
-        <v>1.4</v>
+        <v>0.026</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I20" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -4328,31 +4164,31 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E21">
-        <v>-0.9</v>
+        <v>-0.205</v>
       </c>
       <c r="F21">
-        <v>1.4</v>
+        <v>0.026</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -4366,31 +4202,31 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D22">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E22">
-        <v>-0.63</v>
+        <v>-0.705</v>
       </c>
       <c r="F22">
-        <v>-0.83</v>
+        <v>-0.466</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -4404,31 +4240,31 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D23">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E23">
-        <v>-0.27</v>
+        <v>-0.205</v>
       </c>
       <c r="F23">
-        <v>-0.402</v>
+        <v>-0.466</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -4442,31 +4278,31 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>-0.455</v>
       </c>
       <c r="F24">
-        <v>-0.75</v>
+        <v>-0.22</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I24" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -4480,13 +4316,13 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D25">
         <v>0.183</v>
@@ -4501,10 +4337,10 @@
         <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I25" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -4518,31 +4354,31 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D26">
-        <v>0.08799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E26">
-        <v>-0.455</v>
+        <v>-0.27</v>
       </c>
       <c r="F26">
-        <v>-0.22</v>
+        <v>-0.402</v>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
       <c r="H26" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I26" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -4559,28 +4395,28 @@
         <v>240</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D27">
-        <v>0.08799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E27">
-        <v>-0.205</v>
+        <v>-0.63</v>
       </c>
       <c r="F27">
-        <v>-0.466</v>
+        <v>-0.83</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I27" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -4594,31 +4430,31 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D28">
-        <v>0.08799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E28">
-        <v>-0.705</v>
+        <v>-0.27</v>
       </c>
       <c r="F28">
-        <v>-0.466</v>
+        <v>-0.83</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I28" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -4632,31 +4468,31 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D29">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>-0.705</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>0.026</v>
+        <v>-0.75</v>
       </c>
       <c r="G29">
         <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I29" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -4670,13 +4506,13 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -4691,10 +4527,10 @@
         <v>5</v>
       </c>
       <c r="H30" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -4708,31 +4544,31 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D31">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>-0.45</v>
+        <v>-0.9</v>
       </c>
       <c r="F31">
-        <v>-0.616</v>
+        <v>1.4</v>
       </c>
       <c r="G31">
         <v>5</v>
       </c>
       <c r="H31" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -4746,31 +4582,31 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D32">
-        <v>0.295</v>
+        <v>0.208</v>
       </c>
       <c r="E32">
-        <v>0.45</v>
+        <v>-0.575</v>
       </c>
       <c r="F32">
-        <v>-0.453</v>
+        <v>-1.024</v>
       </c>
       <c r="G32">
         <v>5</v>
       </c>
       <c r="H32" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I32" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -4784,31 +4620,31 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>55</v>
+        <v>242</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D33">
-        <v>0.15</v>
+        <v>0.183</v>
       </c>
       <c r="E33">
-        <v>0.375</v>
+        <v>-0.45</v>
       </c>
       <c r="F33">
-        <v>-0.9</v>
+        <v>-0.616</v>
       </c>
       <c r="G33">
         <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I33" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -4822,31 +4658,31 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D34">
-        <v>0.09</v>
+        <v>0.108</v>
       </c>
       <c r="E34">
-        <v>0.525</v>
+        <v>-0.45</v>
       </c>
       <c r="F34">
-        <v>-0.825</v>
+        <v>-0.175</v>
       </c>
       <c r="G34">
         <v>5</v>
       </c>
       <c r="H34" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I34" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -4860,31 +4696,31 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D35">
-        <v>-0.037</v>
+        <v>0.06</v>
       </c>
       <c r="E35">
-        <v>-0.8</v>
+        <v>0.45</v>
       </c>
       <c r="F35">
-        <v>-0.365</v>
+        <v>-0.175</v>
       </c>
       <c r="G35">
         <v>5</v>
       </c>
       <c r="H35" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I35" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -4898,31 +4734,31 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D36">
-        <v>0.435</v>
+        <v>0.22</v>
       </c>
       <c r="E36">
-        <v>-1.28</v>
+        <v>-0.8</v>
       </c>
       <c r="F36">
-        <v>-0.79</v>
+        <v>-0.725</v>
       </c>
       <c r="G36">
         <v>5</v>
       </c>
       <c r="H36" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I36" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -4936,31 +4772,31 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D37">
-        <v>0.22</v>
+        <v>-0.037</v>
       </c>
       <c r="E37">
         <v>-0.8</v>
       </c>
       <c r="F37">
-        <v>-0.725</v>
+        <v>-0.365</v>
       </c>
       <c r="G37">
         <v>5</v>
       </c>
       <c r="H37" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I37" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -4974,31 +4810,31 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D38">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E38">
-        <v>0.45</v>
+        <v>0.525</v>
       </c>
       <c r="F38">
-        <v>-0.175</v>
+        <v>-0.825</v>
       </c>
       <c r="G38">
         <v>5</v>
       </c>
       <c r="H38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I38" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -5012,31 +4848,31 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D39">
-        <v>0.108</v>
+        <v>0.15</v>
       </c>
       <c r="E39">
-        <v>-0.45</v>
+        <v>0.375</v>
       </c>
       <c r="F39">
-        <v>-0.175</v>
+        <v>-0.9</v>
       </c>
       <c r="G39">
         <v>5</v>
       </c>
       <c r="H39" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I39" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -5050,31 +4886,31 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>155</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D40">
-        <v>0.208</v>
+        <v>0.295</v>
       </c>
       <c r="E40">
-        <v>-0.575</v>
+        <v>0.45</v>
       </c>
       <c r="F40">
-        <v>-1.024</v>
+        <v>-0.453</v>
       </c>
       <c r="G40">
         <v>5</v>
       </c>
       <c r="H40" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I40" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -5088,31 +4924,31 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D41">
-        <v>0.183</v>
+        <v>0.435</v>
       </c>
       <c r="E41">
-        <v>-0.27</v>
+        <v>-1.28</v>
       </c>
       <c r="F41">
-        <v>-0.83</v>
+        <v>-0.79</v>
       </c>
       <c r="G41">
         <v>5</v>
       </c>
       <c r="H41" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I41" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -5126,13 +4962,13 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D42">
         <v>1.06</v>
@@ -5144,13 +4980,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I42" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -5164,16 +5000,16 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D43">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="E43">
         <v>1.535</v>
@@ -5182,13 +5018,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I43" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -5202,16 +5038,16 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D44">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="E44">
         <v>1.535</v>
@@ -5220,13 +5056,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I44" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -5240,31 +5076,31 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D45">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="E45">
-        <v>1.535</v>
+        <v>1.075</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I45" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -5278,16 +5114,16 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D46">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="E46">
         <v>1.075</v>
@@ -5296,13 +5132,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I46" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -5316,16 +5152,16 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D47">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="E47">
         <v>1.075</v>
@@ -5334,13 +5170,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I47" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -5354,13 +5190,13 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D48">
         <v>0.57</v>
@@ -5372,13 +5208,13 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I48" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -5392,13 +5228,13 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D49">
         <v>0.57</v>
@@ -5410,13 +5246,13 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I49" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -5430,13 +5266,13 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C50" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D50">
         <v>0.72</v>
@@ -5448,13 +5284,13 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I50" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -5468,13 +5304,13 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D51">
         <v>0.57</v>
@@ -5486,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I51" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -5506,13 +5342,13 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B52" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C52" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D52">
         <v>0.72</v>
@@ -5524,13 +5360,13 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I52" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -5544,13 +5380,13 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B53" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D53">
         <v>0.96</v>
@@ -5562,13 +5398,13 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I53" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -5585,28 +5421,28 @@
         <v>256</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C54" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54">
+        <v>1.06</v>
+      </c>
+      <c r="E54">
+        <v>1.535</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54" t="s">
+        <v>82</v>
+      </c>
+      <c r="H54" t="s">
         <v>136</v>
       </c>
-      <c r="D54">
-        <v>0.72</v>
-      </c>
-      <c r="E54">
-        <v>1.075</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54" t="s">
-        <v>86</v>
-      </c>
-      <c r="H54" t="s">
-        <v>140</v>
-      </c>
       <c r="I54" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -5620,16 +5456,16 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B55" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C55" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D55">
-        <v>0.96</v>
+        <v>1.06</v>
       </c>
       <c r="E55">
         <v>1.535</v>
@@ -5638,13 +5474,13 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I55" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -5661,10 +5497,10 @@
         <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D56">
         <v>0.645</v>
@@ -5676,13 +5512,13 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I56" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -5699,10 +5535,10 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C57" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D57">
         <v>1.01</v>
@@ -5714,13 +5550,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I57" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -5734,13 +5570,13 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C58" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D58">
         <v>0.96</v>
@@ -5752,13 +5588,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I58" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -5772,13 +5608,13 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B59" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D59">
         <v>1.06</v>
@@ -5790,13 +5626,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I59" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -5826,13 +5662,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -3462,8 +3462,8 @@
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" t="s">
-        <v>136</v>
+      <c r="H2">
+        <v>6</v>
       </c>
       <c r="I2" t="s">
         <v>84</v>
@@ -3500,8 +3500,8 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" t="s">
-        <v>136</v>
+      <c r="H3">
+        <v>6</v>
       </c>
       <c r="I3" t="s">
         <v>84</v>
@@ -3538,8 +3538,8 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>136</v>
+      <c r="H4">
+        <v>6</v>
       </c>
       <c r="I4" t="s">
         <v>84</v>
@@ -3576,8 +3576,8 @@
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5" t="s">
-        <v>136</v>
+      <c r="H5">
+        <v>6</v>
       </c>
       <c r="I5" t="s">
         <v>84</v>
@@ -3614,8 +3614,8 @@
       <c r="G6">
         <v>3</v>
       </c>
-      <c r="H6" t="s">
-        <v>136</v>
+      <c r="H6">
+        <v>6</v>
       </c>
       <c r="I6" t="s">
         <v>84</v>
@@ -3652,8 +3652,8 @@
       <c r="G7">
         <v>3</v>
       </c>
-      <c r="H7" t="s">
-        <v>136</v>
+      <c r="H7">
+        <v>6</v>
       </c>
       <c r="I7" t="s">
         <v>84</v>
@@ -3690,8 +3690,8 @@
       <c r="G8">
         <v>3</v>
       </c>
-      <c r="H8" t="s">
-        <v>136</v>
+      <c r="H8">
+        <v>6</v>
       </c>
       <c r="I8" t="s">
         <v>84</v>
@@ -3728,8 +3728,8 @@
       <c r="G9">
         <v>3</v>
       </c>
-      <c r="H9" t="s">
-        <v>136</v>
+      <c r="H9">
+        <v>6</v>
       </c>
       <c r="I9" t="s">
         <v>84</v>
@@ -3766,8 +3766,8 @@
       <c r="G10">
         <v>3</v>
       </c>
-      <c r="H10" t="s">
-        <v>136</v>
+      <c r="H10">
+        <v>6</v>
       </c>
       <c r="I10" t="s">
         <v>84</v>
@@ -3804,8 +3804,8 @@
       <c r="G11">
         <v>4</v>
       </c>
-      <c r="H11" t="s">
-        <v>136</v>
+      <c r="H11">
+        <v>6</v>
       </c>
       <c r="I11" t="s">
         <v>84</v>
@@ -3842,8 +3842,8 @@
       <c r="G12">
         <v>4</v>
       </c>
-      <c r="H12" t="s">
-        <v>136</v>
+      <c r="H12">
+        <v>6</v>
       </c>
       <c r="I12" t="s">
         <v>84</v>
@@ -3880,8 +3880,8 @@
       <c r="G13">
         <v>4</v>
       </c>
-      <c r="H13" t="s">
-        <v>136</v>
+      <c r="H13">
+        <v>6</v>
       </c>
       <c r="I13" t="s">
         <v>84</v>
@@ -3918,8 +3918,8 @@
       <c r="G14">
         <v>4</v>
       </c>
-      <c r="H14" t="s">
-        <v>136</v>
+      <c r="H14">
+        <v>6</v>
       </c>
       <c r="I14" t="s">
         <v>84</v>
@@ -3956,8 +3956,8 @@
       <c r="G15">
         <v>5</v>
       </c>
-      <c r="H15" t="s">
-        <v>136</v>
+      <c r="H15">
+        <v>6</v>
       </c>
       <c r="I15" t="s">
         <v>84</v>
@@ -3994,8 +3994,8 @@
       <c r="G16">
         <v>5</v>
       </c>
-      <c r="H16" t="s">
-        <v>136</v>
+      <c r="H16">
+        <v>6</v>
       </c>
       <c r="I16" t="s">
         <v>84</v>
@@ -4032,8 +4032,8 @@
       <c r="G17">
         <v>5</v>
       </c>
-      <c r="H17" t="s">
-        <v>136</v>
+      <c r="H17">
+        <v>6</v>
       </c>
       <c r="I17" t="s">
         <v>84</v>
@@ -4070,8 +4070,8 @@
       <c r="G18">
         <v>5</v>
       </c>
-      <c r="H18" t="s">
-        <v>136</v>
+      <c r="H18">
+        <v>6</v>
       </c>
       <c r="I18" t="s">
         <v>84</v>
@@ -4108,8 +4108,8 @@
       <c r="G19">
         <v>5</v>
       </c>
-      <c r="H19" t="s">
-        <v>136</v>
+      <c r="H19">
+        <v>6</v>
       </c>
       <c r="I19" t="s">
         <v>84</v>
@@ -4146,8 +4146,8 @@
       <c r="G20">
         <v>5</v>
       </c>
-      <c r="H20" t="s">
-        <v>136</v>
+      <c r="H20">
+        <v>6</v>
       </c>
       <c r="I20" t="s">
         <v>84</v>
@@ -4184,8 +4184,8 @@
       <c r="G21">
         <v>5</v>
       </c>
-      <c r="H21" t="s">
-        <v>136</v>
+      <c r="H21">
+        <v>6</v>
       </c>
       <c r="I21" t="s">
         <v>84</v>
@@ -4222,8 +4222,8 @@
       <c r="G22">
         <v>5</v>
       </c>
-      <c r="H22" t="s">
-        <v>136</v>
+      <c r="H22">
+        <v>6</v>
       </c>
       <c r="I22" t="s">
         <v>84</v>
@@ -4260,8 +4260,8 @@
       <c r="G23">
         <v>5</v>
       </c>
-      <c r="H23" t="s">
-        <v>136</v>
+      <c r="H23">
+        <v>6</v>
       </c>
       <c r="I23" t="s">
         <v>84</v>
@@ -4298,8 +4298,8 @@
       <c r="G24">
         <v>5</v>
       </c>
-      <c r="H24" t="s">
-        <v>136</v>
+      <c r="H24">
+        <v>6</v>
       </c>
       <c r="I24" t="s">
         <v>84</v>
@@ -4336,8 +4336,8 @@
       <c r="G25">
         <v>5</v>
       </c>
-      <c r="H25" t="s">
-        <v>136</v>
+      <c r="H25">
+        <v>6</v>
       </c>
       <c r="I25" t="s">
         <v>84</v>
@@ -4374,8 +4374,8 @@
       <c r="G26">
         <v>5</v>
       </c>
-      <c r="H26" t="s">
-        <v>136</v>
+      <c r="H26">
+        <v>6</v>
       </c>
       <c r="I26" t="s">
         <v>84</v>
@@ -4412,8 +4412,8 @@
       <c r="G27">
         <v>5</v>
       </c>
-      <c r="H27" t="s">
-        <v>136</v>
+      <c r="H27">
+        <v>6</v>
       </c>
       <c r="I27" t="s">
         <v>84</v>
@@ -4450,8 +4450,8 @@
       <c r="G28">
         <v>5</v>
       </c>
-      <c r="H28" t="s">
-        <v>136</v>
+      <c r="H28">
+        <v>6</v>
       </c>
       <c r="I28" t="s">
         <v>84</v>
@@ -4488,8 +4488,8 @@
       <c r="G29">
         <v>5</v>
       </c>
-      <c r="H29" t="s">
-        <v>136</v>
+      <c r="H29">
+        <v>6</v>
       </c>
       <c r="I29" t="s">
         <v>84</v>
@@ -4526,8 +4526,8 @@
       <c r="G30">
         <v>5</v>
       </c>
-      <c r="H30" t="s">
-        <v>136</v>
+      <c r="H30">
+        <v>6</v>
       </c>
       <c r="I30" t="s">
         <v>84</v>
@@ -4564,8 +4564,8 @@
       <c r="G31">
         <v>5</v>
       </c>
-      <c r="H31" t="s">
-        <v>136</v>
+      <c r="H31">
+        <v>6</v>
       </c>
       <c r="I31" t="s">
         <v>84</v>
@@ -4602,8 +4602,8 @@
       <c r="G32">
         <v>5</v>
       </c>
-      <c r="H32" t="s">
-        <v>136</v>
+      <c r="H32">
+        <v>6</v>
       </c>
       <c r="I32" t="s">
         <v>84</v>
@@ -4640,8 +4640,8 @@
       <c r="G33">
         <v>5</v>
       </c>
-      <c r="H33" t="s">
-        <v>136</v>
+      <c r="H33">
+        <v>6</v>
       </c>
       <c r="I33" t="s">
         <v>84</v>
@@ -4678,8 +4678,8 @@
       <c r="G34">
         <v>5</v>
       </c>
-      <c r="H34" t="s">
-        <v>136</v>
+      <c r="H34">
+        <v>6</v>
       </c>
       <c r="I34" t="s">
         <v>84</v>
@@ -4716,8 +4716,8 @@
       <c r="G35">
         <v>5</v>
       </c>
-      <c r="H35" t="s">
-        <v>136</v>
+      <c r="H35">
+        <v>6</v>
       </c>
       <c r="I35" t="s">
         <v>84</v>
@@ -4754,8 +4754,8 @@
       <c r="G36">
         <v>5</v>
       </c>
-      <c r="H36" t="s">
-        <v>136</v>
+      <c r="H36">
+        <v>6</v>
       </c>
       <c r="I36" t="s">
         <v>84</v>
@@ -4792,8 +4792,8 @@
       <c r="G37">
         <v>5</v>
       </c>
-      <c r="H37" t="s">
-        <v>136</v>
+      <c r="H37">
+        <v>6</v>
       </c>
       <c r="I37" t="s">
         <v>84</v>
@@ -4830,8 +4830,8 @@
       <c r="G38">
         <v>5</v>
       </c>
-      <c r="H38" t="s">
-        <v>136</v>
+      <c r="H38">
+        <v>6</v>
       </c>
       <c r="I38" t="s">
         <v>84</v>
@@ -4868,8 +4868,8 @@
       <c r="G39">
         <v>5</v>
       </c>
-      <c r="H39" t="s">
-        <v>136</v>
+      <c r="H39">
+        <v>6</v>
       </c>
       <c r="I39" t="s">
         <v>84</v>
@@ -4906,8 +4906,8 @@
       <c r="G40">
         <v>5</v>
       </c>
-      <c r="H40" t="s">
-        <v>136</v>
+      <c r="H40">
+        <v>6</v>
       </c>
       <c r="I40" t="s">
         <v>84</v>
@@ -4944,8 +4944,8 @@
       <c r="G41">
         <v>5</v>
       </c>
-      <c r="H41" t="s">
-        <v>136</v>
+      <c r="H41">
+        <v>6</v>
       </c>
       <c r="I41" t="s">
         <v>84</v>
@@ -4982,8 +4982,8 @@
       <c r="G42" t="s">
         <v>82</v>
       </c>
-      <c r="H42" t="s">
-        <v>136</v>
+      <c r="H42">
+        <v>6</v>
       </c>
       <c r="I42" t="s">
         <v>84</v>
@@ -5020,8 +5020,8 @@
       <c r="G43" t="s">
         <v>82</v>
       </c>
-      <c r="H43" t="s">
-        <v>136</v>
+      <c r="H43">
+        <v>6</v>
       </c>
       <c r="I43" t="s">
         <v>84</v>
@@ -5058,8 +5058,8 @@
       <c r="G44" t="s">
         <v>82</v>
       </c>
-      <c r="H44" t="s">
-        <v>136</v>
+      <c r="H44">
+        <v>6</v>
       </c>
       <c r="I44" t="s">
         <v>84</v>
@@ -5096,8 +5096,8 @@
       <c r="G45" t="s">
         <v>82</v>
       </c>
-      <c r="H45" t="s">
-        <v>136</v>
+      <c r="H45">
+        <v>6</v>
       </c>
       <c r="I45" t="s">
         <v>84</v>
@@ -5134,8 +5134,8 @@
       <c r="G46" t="s">
         <v>82</v>
       </c>
-      <c r="H46" t="s">
-        <v>136</v>
+      <c r="H46">
+        <v>6</v>
       </c>
       <c r="I46" t="s">
         <v>84</v>
@@ -5172,8 +5172,8 @@
       <c r="G47" t="s">
         <v>82</v>
       </c>
-      <c r="H47" t="s">
-        <v>136</v>
+      <c r="H47">
+        <v>6</v>
       </c>
       <c r="I47" t="s">
         <v>84</v>
@@ -5210,8 +5210,8 @@
       <c r="G48" t="s">
         <v>82</v>
       </c>
-      <c r="H48" t="s">
-        <v>136</v>
+      <c r="H48">
+        <v>6</v>
       </c>
       <c r="I48" t="s">
         <v>84</v>
@@ -5248,8 +5248,8 @@
       <c r="G49" t="s">
         <v>82</v>
       </c>
-      <c r="H49" t="s">
-        <v>136</v>
+      <c r="H49">
+        <v>6</v>
       </c>
       <c r="I49" t="s">
         <v>84</v>
@@ -5286,8 +5286,8 @@
       <c r="G50" t="s">
         <v>82</v>
       </c>
-      <c r="H50" t="s">
-        <v>136</v>
+      <c r="H50">
+        <v>6</v>
       </c>
       <c r="I50" t="s">
         <v>84</v>
@@ -5324,8 +5324,8 @@
       <c r="G51" t="s">
         <v>82</v>
       </c>
-      <c r="H51" t="s">
-        <v>136</v>
+      <c r="H51">
+        <v>6</v>
       </c>
       <c r="I51" t="s">
         <v>84</v>
@@ -5362,8 +5362,8 @@
       <c r="G52" t="s">
         <v>82</v>
       </c>
-      <c r="H52" t="s">
-        <v>136</v>
+      <c r="H52">
+        <v>6</v>
       </c>
       <c r="I52" t="s">
         <v>84</v>
@@ -5400,8 +5400,8 @@
       <c r="G53" t="s">
         <v>82</v>
       </c>
-      <c r="H53" t="s">
-        <v>136</v>
+      <c r="H53">
+        <v>6</v>
       </c>
       <c r="I53" t="s">
         <v>84</v>
@@ -5438,8 +5438,8 @@
       <c r="G54" t="s">
         <v>82</v>
       </c>
-      <c r="H54" t="s">
-        <v>136</v>
+      <c r="H54">
+        <v>6</v>
       </c>
       <c r="I54" t="s">
         <v>84</v>
@@ -5476,8 +5476,8 @@
       <c r="G55" t="s">
         <v>82</v>
       </c>
-      <c r="H55" t="s">
-        <v>136</v>
+      <c r="H55">
+        <v>6</v>
       </c>
       <c r="I55" t="s">
         <v>84</v>
@@ -5514,8 +5514,8 @@
       <c r="G56" t="s">
         <v>82</v>
       </c>
-      <c r="H56" t="s">
-        <v>136</v>
+      <c r="H56">
+        <v>6</v>
       </c>
       <c r="I56" t="s">
         <v>84</v>
@@ -5552,8 +5552,8 @@
       <c r="G57" t="s">
         <v>82</v>
       </c>
-      <c r="H57" t="s">
-        <v>136</v>
+      <c r="H57">
+        <v>6</v>
       </c>
       <c r="I57" t="s">
         <v>84</v>
@@ -5590,8 +5590,8 @@
       <c r="G58" t="s">
         <v>82</v>
       </c>
-      <c r="H58" t="s">
-        <v>136</v>
+      <c r="H58">
+        <v>6</v>
       </c>
       <c r="I58" t="s">
         <v>84</v>
@@ -5628,8 +5628,8 @@
       <c r="G59" t="s">
         <v>82</v>
       </c>
-      <c r="H59" t="s">
-        <v>136</v>
+      <c r="H59">
+        <v>6</v>
       </c>
       <c r="I59" t="s">
         <v>84</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="142">
   <si>
     <t>Marking type</t>
   </si>
@@ -63,76 +63,79 @@
     <t>Tile</t>
   </si>
   <si>
+    <t>TMP1S2e1</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2c2</t>
+  </si>
+  <si>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
+    <t>TMP1S2c4</t>
+  </si>
+  <si>
+    <t>TMP1S2d1</t>
+  </si>
+  <si>
+    <t>TMP1S2d2</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
+    <t>TMP1S2d3</t>
+  </si>
+  <si>
+    <t>TMP1S2e2</t>
+  </si>
+  <si>
     <t>TMP1S2e3</t>
   </si>
   <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
-    <t>TMP1S2c2</t>
-  </si>
-  <si>
-    <t>TMP1S2c3</t>
-  </si>
-  <si>
-    <t>TMP1S2c4</t>
-  </si>
-  <si>
-    <t>TMP1S2d2</t>
-  </si>
-  <si>
-    <t>TMP1S2d3</t>
+    <t>TMP1S2e4</t>
+  </si>
+  <si>
+    <t>TMP1S2f1</t>
+  </si>
+  <si>
+    <t>TMP1S2f2</t>
+  </si>
+  <si>
+    <t>TMP1S2f3</t>
+  </si>
+  <si>
+    <t>TMP1S2f4</t>
   </si>
   <si>
     <t>TMP1S2d4</t>
   </si>
   <si>
-    <t>TMP1S2e1</t>
-  </si>
-  <si>
-    <t>TMP1S2e2</t>
-  </si>
-  <si>
-    <t>TMP1S2e4</t>
-  </si>
-  <si>
-    <t>TMP1S2f1</t>
-  </si>
-  <si>
-    <t>TMP1S2f2</t>
-  </si>
-  <si>
-    <t>TMP1S2f3</t>
-  </si>
-  <si>
-    <t>TMP1S2f4</t>
-  </si>
-  <si>
-    <t>TMP1S2b3</t>
+    <t>TMP1S2b1</t>
   </si>
   <si>
     <t>TMP1S2b2</t>
   </si>
   <si>
-    <t>TMP1S2d1</t>
+    <t>TMP1S2a3</t>
+  </si>
+  <si>
+    <t>TMP1S2a2</t>
+  </si>
+  <si>
+    <t>TMP1S2a1</t>
   </si>
   <si>
     <t>TMP1S2a4</t>
   </si>
   <si>
-    <t>TMP1S2a1</t>
-  </si>
-  <si>
-    <t>TMP1S2a2</t>
-  </si>
-  <si>
-    <t>TMP1S2a3</t>
-  </si>
-  <si>
-    <t>TMP1S2b1</t>
+    <t>TMP2S2a2</t>
   </si>
   <si>
     <t>TMP2S2a1</t>
@@ -144,33 +147,30 @@
     <t>TMP2S2b1</t>
   </si>
   <si>
-    <t>TMP2S2a2</t>
-  </si>
-  <si>
     <t>TMP3S2a4</t>
   </si>
   <si>
+    <t>TMP3S2a1</t>
+  </si>
+  <si>
     <t>TMP3S2a3</t>
   </si>
   <si>
     <t>TMP3S2a2</t>
   </si>
   <si>
-    <t>TMP3S2a1</t>
+    <t>TMP4S2a2</t>
+  </si>
+  <si>
+    <t>TMP4S2a4</t>
   </si>
   <si>
     <t>TMP4S2a1</t>
   </si>
   <si>
-    <t>TMP4S2a2</t>
-  </si>
-  <si>
     <t>TMP4S2a3</t>
   </si>
   <si>
-    <t>TMP4S2a4</t>
-  </si>
-  <si>
     <t>TMP5S2a1</t>
   </si>
   <si>
@@ -180,39 +180,39 @@
     <t>TMP5S2a3</t>
   </si>
   <si>
+    <t>TMP6S2a2</t>
+  </si>
+  <si>
+    <t>TMP6S2a3</t>
+  </si>
+  <si>
     <t>TMP6S2a1</t>
   </si>
   <si>
+    <t>TMP6S2b1</t>
+  </si>
+  <si>
+    <t>TMP6S2b2</t>
+  </si>
+  <si>
     <t>TMP6S2b4</t>
   </si>
   <si>
+    <t>TMP6S2a4</t>
+  </si>
+  <si>
     <t>TMP6S2b3</t>
   </si>
   <si>
-    <t>TMP6S2b2</t>
-  </si>
-  <si>
-    <t>TMP6S2b1</t>
-  </si>
-  <si>
-    <t>TMP6S2a4</t>
-  </si>
-  <si>
-    <t>TMP6S2a2</t>
-  </si>
-  <si>
-    <t>TMP6S2a3</t>
+    <t>TMP7S2a1</t>
+  </si>
+  <si>
+    <t>TMP7S2e1</t>
   </si>
   <si>
     <t>TMP7S2a2</t>
   </si>
   <si>
-    <t>TMP7S2e1</t>
-  </si>
-  <si>
-    <t>TMP7S2a1</t>
-  </si>
-  <si>
     <t>TMP7S2a3</t>
   </si>
   <si>
@@ -279,40 +279,46 @@
     <t>LP1S3a1</t>
   </si>
   <si>
+    <t>LP1S3a2</t>
+  </si>
+  <si>
     <t>LP1S3a3</t>
   </si>
   <si>
     <t>LP1S3a4</t>
   </si>
   <si>
-    <t>LP1S3a2</t>
+    <t>LP3S3a1</t>
   </si>
   <si>
     <t>LP3S3a4</t>
   </si>
   <si>
+    <t>LP3S3a3</t>
+  </si>
+  <si>
     <t>LP3S3a2</t>
   </si>
   <si>
-    <t>LP3S3a1</t>
-  </si>
-  <si>
     <t>BSS.GESSI.SM.49079:29046000:1090989</t>
   </si>
   <si>
-    <t>LP3S3a3</t>
+    <t>LP4S3a1</t>
+  </si>
+  <si>
+    <t>LP4S3a2</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
   </si>
   <si>
     <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
   </si>
   <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
-  </si>
-  <si>
-    <t>LP4S3a1</t>
-  </si>
-  <si>
-    <t>LP4S3a2</t>
+    <t>LP5S3d2</t>
+  </si>
+  <si>
+    <t>LP5S3d1</t>
   </si>
   <si>
     <t>LP5S3c4</t>
@@ -324,106 +330,106 @@
     <t>LP5S3c2</t>
   </si>
   <si>
-    <t>LP5S3d2</t>
-  </si>
-  <si>
-    <t>LP5S3d1</t>
+    <t>LP5S3c1</t>
+  </si>
+  <si>
+    <t>LP5S3b5</t>
+  </si>
+  <si>
+    <t>LP5S3b1</t>
+  </si>
+  <si>
+    <t>LP5S3d3</t>
+  </si>
+  <si>
+    <t>LP5S3a5</t>
+  </si>
+  <si>
+    <t>LP5S3a4</t>
+  </si>
+  <si>
+    <t>LP5S3a3</t>
+  </si>
+  <si>
+    <t>LP5S3a2</t>
   </si>
   <si>
     <t>LP5S3a1</t>
   </si>
   <si>
-    <t>LP5S3a2</t>
-  </si>
-  <si>
-    <t>LP5S3a3</t>
-  </si>
-  <si>
-    <t>LP5S3a4</t>
-  </si>
-  <si>
-    <t>LP5S3a5</t>
-  </si>
-  <si>
-    <t>LP5S3b1</t>
-  </si>
-  <si>
     <t>LP5S3b2</t>
   </si>
   <si>
+    <t>LP5S3d4</t>
+  </si>
+  <si>
+    <t>LP5S3b4</t>
+  </si>
+  <si>
+    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+  </si>
+  <si>
+    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
+  </si>
+  <si>
+    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+  </si>
+  <si>
+    <t>BSS.GESSI,BM.49001:Default:1090988</t>
+  </si>
+  <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+  </si>
+  <si>
     <t>LP5S3b3</t>
   </si>
   <si>
-    <t>LP5S3b4</t>
-  </si>
-  <si>
-    <t>LP5S3d3</t>
-  </si>
-  <si>
-    <t>LP5S3d4</t>
-  </si>
-  <si>
-    <t>LP5S3c1</t>
-  </si>
-  <si>
-    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
-  </si>
-  <si>
-    <t>LP5S3b5</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
-  </si>
-  <si>
-    <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
-  </si>
-  <si>
-    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
+    <t>LP7S3b1</t>
   </si>
   <si>
     <t>LP7S3b2</t>
   </si>
   <si>
+    <t>LP7S3b4</t>
+  </si>
+  <si>
+    <t>LP7S3a1</t>
+  </si>
+  <si>
+    <t>LP7S3a3</t>
+  </si>
+  <si>
+    <t>LP7S3a2</t>
+  </si>
+  <si>
+    <t>LP7S3a4</t>
+  </si>
+  <si>
     <t>LP7S3b3</t>
   </si>
   <si>
-    <t>LP7S3b1</t>
-  </si>
-  <si>
-    <t>LP7S3a4</t>
-  </si>
-  <si>
-    <t>LP7S3a3</t>
-  </si>
-  <si>
-    <t>LP7S3a2</t>
-  </si>
-  <si>
-    <t>LP7S3a1</t>
-  </si>
-  <si>
-    <t>LP7S3b4</t>
-  </si>
-  <si>
     <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
   </si>
   <si>
     <t>BSS.Shallow_FW:BSS.Shallow_FW:1038276</t>
+  </si>
+  <si>
+    <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
+  </si>
+  <si>
+    <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
   </si>
   <si>
     <t>6</t>
@@ -857,7 +863,7 @@
         <v>-0.35</v>
       </c>
       <c r="F2">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -880,7 +886,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -918,7 +924,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -956,7 +962,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -994,7 +1000,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1032,7 +1038,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1070,7 +1076,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1085,7 +1091,7 @@
         <v>-0.03</v>
       </c>
       <c r="F8">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1108,7 +1114,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1123,7 +1129,7 @@
         <v>-0.03</v>
       </c>
       <c r="F9">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1146,7 +1152,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1158,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>-0.03</v>
+        <v>0.49</v>
       </c>
       <c r="F10">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1196,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>-0.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F11">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1222,7 +1228,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1260,7 +1266,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1275,7 +1281,7 @@
         <v>-0.35</v>
       </c>
       <c r="F13">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1298,7 +1304,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1310,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-1.35</v>
+        <v>-0.35</v>
       </c>
       <c r="F14">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1336,7 +1342,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1351,7 +1357,7 @@
         <v>-1.35</v>
       </c>
       <c r="F15">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1374,7 +1380,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1389,7 +1395,7 @@
         <v>-1.35</v>
       </c>
       <c r="F16">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1412,7 +1418,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1427,7 +1433,7 @@
         <v>-1.35</v>
       </c>
       <c r="F17">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1450,7 +1456,7 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1462,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.49</v>
+        <v>-1.35</v>
       </c>
       <c r="F18">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1488,7 +1494,7 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1500,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
       <c r="F19">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1526,7 +1532,7 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1538,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.03</v>
+        <v>0.49</v>
       </c>
       <c r="F20">
         <v>-0.775</v>
@@ -1564,7 +1570,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1576,10 +1582,10 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0.9350000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="F21">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1602,7 +1608,7 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1617,7 +1623,7 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="F22">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1640,7 +1646,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1693,7 +1699,7 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="F24">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1716,7 +1722,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1728,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0.49</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F25">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1754,7 +1760,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1769,7 +1775,7 @@
         <v>-0.5</v>
       </c>
       <c r="F26">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1792,7 +1798,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1804,10 +1810,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="F27">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1830,7 +1836,7 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1845,7 +1851,7 @@
         <v>0.1</v>
       </c>
       <c r="F28">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1868,7 +1874,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -1880,10 +1886,10 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F29">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1906,7 +1912,7 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1959,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -1982,7 +1988,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -1997,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -2020,7 +2026,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -2035,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -2058,7 +2064,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -2073,7 +2079,7 @@
         <v>-0.3</v>
       </c>
       <c r="F34">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -2096,7 +2102,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2111,7 +2117,7 @@
         <v>-0.3</v>
       </c>
       <c r="F35">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G35">
         <v>4</v>
@@ -2149,7 +2155,7 @@
         <v>-0.3</v>
       </c>
       <c r="F36">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -2172,7 +2178,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2187,7 +2193,7 @@
         <v>-0.3</v>
       </c>
       <c r="F37">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -2210,7 +2216,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2248,7 +2254,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2286,7 +2292,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2324,7 +2330,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2339,7 +2345,7 @@
         <v>0.3</v>
       </c>
       <c r="F41">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G41">
         <v>6</v>
@@ -2362,7 +2368,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2374,10 +2380,10 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F42">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G42">
         <v>6</v>
@@ -2400,7 +2406,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2412,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F43">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G43">
         <v>6</v>
@@ -2438,7 +2444,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2453,7 +2459,7 @@
         <v>-0.3</v>
       </c>
       <c r="F44">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G44">
         <v>6</v>
@@ -2476,7 +2482,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2491,7 +2497,7 @@
         <v>-0.3</v>
       </c>
       <c r="F45">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -2514,7 +2520,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2526,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F46">
         <v>1.025</v>
@@ -2552,7 +2558,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2567,7 +2573,7 @@
         <v>0.3</v>
       </c>
       <c r="F47">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G47">
         <v>6</v>
@@ -2590,7 +2596,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2602,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F48">
         <v>0.425</v>
@@ -2628,7 +2634,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2640,7 +2646,7 @@
         <v>0.12</v>
       </c>
       <c r="E49">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2666,7 +2672,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2704,7 +2710,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2716,7 +2722,7 @@
         <v>0.12</v>
       </c>
       <c r="E51">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2742,7 +2748,7 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2780,7 +2786,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2818,7 +2824,7 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2856,7 +2862,7 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2894,7 +2900,7 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2932,7 +2938,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2970,7 +2976,7 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -3008,7 +3014,7 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -3046,7 +3052,7 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -3084,7 +3090,7 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -3122,7 +3128,7 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3160,7 +3166,7 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3198,7 +3204,7 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3236,7 +3242,7 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3274,7 +3280,7 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3312,7 +3318,7 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="1">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
@@ -3350,7 +3356,7 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="1">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3393,7 +3399,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -3442,7 +3448,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B2" t="s">
         <v>85</v>
@@ -3480,7 +3486,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B3" t="s">
         <v>85</v>
@@ -3492,10 +3498,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.375</v>
+        <v>-0.255</v>
       </c>
       <c r="F3">
-        <v>0.137</v>
+        <v>0.213</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -3518,7 +3524,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
         <v>85</v>
@@ -3530,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>-0.255</v>
+        <v>0.375</v>
       </c>
       <c r="F4">
         <v>0.137</v>
@@ -3556,7 +3562,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B5" t="s">
         <v>85</v>
@@ -3571,7 +3577,7 @@
         <v>-0.255</v>
       </c>
       <c r="F5">
-        <v>0.213</v>
+        <v>0.137</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3594,7 +3600,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B6" t="s">
         <v>85</v>
@@ -3606,10 +3612,10 @@
         <v>0.6</v>
       </c>
       <c r="E6">
-        <v>0.123</v>
+        <v>-0.077</v>
       </c>
       <c r="F6">
-        <v>-0.188</v>
+        <v>0.962</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -3632,7 +3638,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
         <v>85</v>
@@ -3647,7 +3653,7 @@
         <v>0.123</v>
       </c>
       <c r="F7">
-        <v>0.962</v>
+        <v>-0.188</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -3670,7 +3676,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B8" t="s">
         <v>85</v>
@@ -3685,7 +3691,7 @@
         <v>-0.077</v>
       </c>
       <c r="F8">
-        <v>0.962</v>
+        <v>-0.188</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -3708,7 +3714,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="B9" t="s">
         <v>85</v>
@@ -3720,10 +3726,10 @@
         <v>0.6</v>
       </c>
       <c r="E9">
-        <v>0.21</v>
+        <v>0.123</v>
       </c>
       <c r="F9">
-        <v>-0.05</v>
+        <v>0.962</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -3746,7 +3752,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>229</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
         <v>85</v>
@@ -3758,10 +3764,10 @@
         <v>0.6</v>
       </c>
       <c r="E10">
-        <v>-0.077</v>
+        <v>0.21</v>
       </c>
       <c r="F10">
-        <v>-0.188</v>
+        <v>-0.05</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -3784,7 +3790,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>40</v>
+        <v>233</v>
       </c>
       <c r="B11" t="s">
         <v>85</v>
@@ -3793,13 +3799,13 @@
         <v>95</v>
       </c>
       <c r="D11">
-        <v>0.9370000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E11">
-        <v>0.243</v>
+        <v>-0.195</v>
       </c>
       <c r="F11">
-        <v>-0.8</v>
+        <v>-0.375</v>
       </c>
       <c r="G11">
         <v>4</v>
@@ -3822,7 +3828,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>89</v>
+        <v>234</v>
       </c>
       <c r="B12" t="s">
         <v>85</v>
@@ -3831,13 +3837,13 @@
         <v>96</v>
       </c>
       <c r="D12">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="E12">
-        <v>0.508</v>
+        <v>-0.145</v>
       </c>
       <c r="F12">
-        <v>1.468</v>
+        <v>-0.375</v>
       </c>
       <c r="G12">
         <v>4</v>
@@ -3860,7 +3866,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>231</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
         <v>85</v>
@@ -3869,13 +3875,13 @@
         <v>97</v>
       </c>
       <c r="D13">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="E13">
-        <v>-0.195</v>
+        <v>0.508</v>
       </c>
       <c r="F13">
-        <v>-0.375</v>
+        <v>1.468</v>
       </c>
       <c r="G13">
         <v>4</v>
@@ -3898,7 +3904,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>85</v>
@@ -3907,13 +3913,13 @@
         <v>98</v>
       </c>
       <c r="D14">
-        <v>0.96</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E14">
-        <v>-0.145</v>
+        <v>0.243</v>
       </c>
       <c r="F14">
-        <v>-0.375</v>
+        <v>-0.8</v>
       </c>
       <c r="G14">
         <v>4</v>
@@ -3936,7 +3942,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B15" t="s">
         <v>85</v>
@@ -3951,7 +3957,7 @@
         <v>0.9</v>
       </c>
       <c r="F15">
-        <v>1.4</v>
+        <v>-0.15</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -3974,7 +3980,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B16" t="s">
         <v>85</v>
@@ -3986,10 +3992,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>1.4</v>
+        <v>-0.15</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -4012,7 +4018,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B17" t="s">
         <v>85</v>
@@ -4050,7 +4056,7 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B18" t="s">
         <v>85</v>
@@ -4062,10 +4068,10 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.9</v>
+        <v>-0.9</v>
       </c>
       <c r="F18">
-        <v>-0.15</v>
+        <v>1.4</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -4088,7 +4094,7 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B19" t="s">
         <v>85</v>
@@ -4100,10 +4106,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F19">
-        <v>-0.15</v>
+        <v>1.4</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -4126,7 +4132,7 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s">
         <v>85</v>
@@ -4135,13 +4141,13 @@
         <v>104</v>
       </c>
       <c r="D20">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.705</v>
+        <v>-0.9</v>
       </c>
       <c r="F20">
-        <v>0.026</v>
+        <v>1.4</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -4164,7 +4170,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B21" t="s">
         <v>85</v>
@@ -4173,13 +4179,13 @@
         <v>105</v>
       </c>
       <c r="D21">
-        <v>0.08799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E21">
-        <v>-0.205</v>
+        <v>-0.45</v>
       </c>
       <c r="F21">
-        <v>0.026</v>
+        <v>-0.616</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -4202,7 +4208,7 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s">
         <v>85</v>
@@ -4211,13 +4217,13 @@
         <v>106</v>
       </c>
       <c r="D22">
-        <v>0.08799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E22">
-        <v>-0.705</v>
+        <v>-0.63</v>
       </c>
       <c r="F22">
-        <v>-0.466</v>
+        <v>-0.402</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -4240,7 +4246,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s">
         <v>85</v>
@@ -4249,13 +4255,13 @@
         <v>107</v>
       </c>
       <c r="D23">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>-0.205</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>-0.466</v>
+        <v>-0.75</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -4278,7 +4284,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s">
         <v>85</v>
@@ -4325,13 +4331,13 @@
         <v>109</v>
       </c>
       <c r="D25">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E25">
-        <v>-0.63</v>
+        <v>-0.205</v>
       </c>
       <c r="F25">
-        <v>-0.402</v>
+        <v>-0.466</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -4354,7 +4360,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s">
         <v>85</v>
@@ -4363,13 +4369,13 @@
         <v>110</v>
       </c>
       <c r="D26">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E26">
-        <v>-0.27</v>
+        <v>-0.705</v>
       </c>
       <c r="F26">
-        <v>-0.402</v>
+        <v>-0.466</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -4392,7 +4398,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s">
         <v>85</v>
@@ -4401,13 +4407,13 @@
         <v>111</v>
       </c>
       <c r="D27">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E27">
-        <v>-0.63</v>
+        <v>-0.205</v>
       </c>
       <c r="F27">
-        <v>-0.83</v>
+        <v>0.026</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -4430,7 +4436,7 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B28" t="s">
         <v>85</v>
@@ -4439,13 +4445,13 @@
         <v>112</v>
       </c>
       <c r="D28">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E28">
-        <v>-0.27</v>
+        <v>-0.705</v>
       </c>
       <c r="F28">
-        <v>-0.83</v>
+        <v>0.026</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -4468,7 +4474,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s">
         <v>85</v>
@@ -4477,13 +4483,13 @@
         <v>113</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="F29">
-        <v>-0.75</v>
+        <v>-0.402</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -4506,7 +4512,7 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s">
         <v>85</v>
@@ -4553,13 +4559,13 @@
         <v>115</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="E31">
-        <v>-0.9</v>
+        <v>-0.27</v>
       </c>
       <c r="F31">
-        <v>1.4</v>
+        <v>-0.83</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -4582,7 +4588,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B32" t="s">
         <v>85</v>
@@ -4620,7 +4626,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>242</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>85</v>
@@ -4629,13 +4635,13 @@
         <v>117</v>
       </c>
       <c r="D33">
-        <v>0.183</v>
+        <v>0.295</v>
       </c>
       <c r="E33">
-        <v>-0.45</v>
+        <v>0.45</v>
       </c>
       <c r="F33">
-        <v>-0.616</v>
+        <v>-0.453</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -4658,7 +4664,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="B34" t="s">
         <v>85</v>
@@ -4667,13 +4673,13 @@
         <v>118</v>
       </c>
       <c r="D34">
-        <v>0.108</v>
+        <v>0.15</v>
       </c>
       <c r="E34">
-        <v>-0.45</v>
+        <v>0.375</v>
       </c>
       <c r="F34">
-        <v>-0.175</v>
+        <v>-0.9</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -4696,7 +4702,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
         <v>85</v>
@@ -4705,13 +4711,13 @@
         <v>119</v>
       </c>
       <c r="D35">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E35">
-        <v>0.45</v>
+        <v>0.525</v>
       </c>
       <c r="F35">
-        <v>-0.175</v>
+        <v>-0.825</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -4734,7 +4740,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
         <v>85</v>
@@ -4743,13 +4749,13 @@
         <v>120</v>
       </c>
       <c r="D36">
-        <v>0.22</v>
+        <v>-0.037</v>
       </c>
       <c r="E36">
         <v>-0.8</v>
       </c>
       <c r="F36">
-        <v>-0.725</v>
+        <v>-0.365</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -4772,7 +4778,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B37" t="s">
         <v>85</v>
@@ -4781,13 +4787,13 @@
         <v>121</v>
       </c>
       <c r="D37">
-        <v>-0.037</v>
+        <v>0.435</v>
       </c>
       <c r="E37">
-        <v>-0.8</v>
+        <v>-1.28</v>
       </c>
       <c r="F37">
-        <v>-0.365</v>
+        <v>-0.79</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -4810,7 +4816,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="B38" t="s">
         <v>85</v>
@@ -4819,13 +4825,13 @@
         <v>122</v>
       </c>
       <c r="D38">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="E38">
-        <v>0.525</v>
+        <v>-0.8</v>
       </c>
       <c r="F38">
-        <v>-0.825</v>
+        <v>-0.725</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -4848,7 +4854,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="B39" t="s">
         <v>85</v>
@@ -4857,13 +4863,13 @@
         <v>123</v>
       </c>
       <c r="D39">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="E39">
-        <v>0.375</v>
+        <v>0.45</v>
       </c>
       <c r="F39">
-        <v>-0.9</v>
+        <v>-0.175</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -4886,7 +4892,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>36</v>
+        <v>154</v>
       </c>
       <c r="B40" t="s">
         <v>85</v>
@@ -4895,13 +4901,13 @@
         <v>124</v>
       </c>
       <c r="D40">
-        <v>0.295</v>
+        <v>0.108</v>
       </c>
       <c r="E40">
-        <v>0.45</v>
+        <v>-0.45</v>
       </c>
       <c r="F40">
-        <v>-0.453</v>
+        <v>-0.175</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -4924,7 +4930,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="B41" t="s">
         <v>85</v>
@@ -4933,13 +4939,13 @@
         <v>125</v>
       </c>
       <c r="D41">
-        <v>0.435</v>
+        <v>0.183</v>
       </c>
       <c r="E41">
-        <v>-1.28</v>
+        <v>-0.63</v>
       </c>
       <c r="F41">
-        <v>-0.79</v>
+        <v>-0.83</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -4962,7 +4968,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B42" t="s">
         <v>85</v>
@@ -4971,7 +4977,7 @@
         <v>126</v>
       </c>
       <c r="D42">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="E42">
         <v>1.535</v>
@@ -5000,7 +5006,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B43" t="s">
         <v>85</v>
@@ -5009,7 +5015,7 @@
         <v>127</v>
       </c>
       <c r="D43">
-        <v>0.96</v>
+        <v>1.06</v>
       </c>
       <c r="E43">
         <v>1.535</v>
@@ -5038,7 +5044,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s">
         <v>85</v>
@@ -5047,7 +5053,7 @@
         <v>128</v>
       </c>
       <c r="D44">
-        <v>0.96</v>
+        <v>1.06</v>
       </c>
       <c r="E44">
         <v>1.535</v>
@@ -5076,7 +5082,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B45" t="s">
         <v>85</v>
@@ -5085,7 +5091,7 @@
         <v>129</v>
       </c>
       <c r="D45">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="E45">
         <v>1.075</v>
@@ -5114,7 +5120,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B46" t="s">
         <v>85</v>
@@ -5152,7 +5158,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B47" t="s">
         <v>85</v>
@@ -5190,7 +5196,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B48" t="s">
         <v>85</v>
@@ -5199,7 +5205,7 @@
         <v>132</v>
       </c>
       <c r="D48">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="E48">
         <v>1.075</v>
@@ -5228,19 +5234,19 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B49" t="s">
         <v>85</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D49">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="E49">
-        <v>1.075</v>
+        <v>1.535</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -5266,19 +5272,19 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="B50" t="s">
         <v>85</v>
       </c>
       <c r="C50" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D50">
-        <v>0.72</v>
+        <v>0.645</v>
       </c>
       <c r="E50">
-        <v>1.075</v>
+        <v>1.112</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -5304,19 +5310,19 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>253</v>
+        <v>1</v>
       </c>
       <c r="B51" t="s">
         <v>85</v>
       </c>
       <c r="C51" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D51">
-        <v>0.57</v>
+        <v>1.01</v>
       </c>
       <c r="E51">
-        <v>1.075</v>
+        <v>1.535</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -5342,19 +5348,19 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>254</v>
+        <v>155</v>
       </c>
       <c r="B52" t="s">
         <v>85</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D52">
-        <v>0.72</v>
+        <v>1.01</v>
       </c>
       <c r="E52">
-        <v>1.075</v>
+        <v>1.535</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -5380,19 +5386,19 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>255</v>
+        <v>157</v>
       </c>
       <c r="B53" t="s">
         <v>85</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D53">
-        <v>0.96</v>
+        <v>0.645</v>
       </c>
       <c r="E53">
-        <v>1.535</v>
+        <v>1.075</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -5413,234 +5419,6 @@
         <v>2.9</v>
       </c>
       <c r="M53">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
-      <c r="A54" s="1">
-        <v>256</v>
-      </c>
-      <c r="B54" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" t="s">
-        <v>126</v>
-      </c>
-      <c r="D54">
-        <v>1.06</v>
-      </c>
-      <c r="E54">
-        <v>1.535</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54" t="s">
-        <v>82</v>
-      </c>
-      <c r="H54">
-        <v>6</v>
-      </c>
-      <c r="I54" t="s">
-        <v>84</v>
-      </c>
-      <c r="J54">
-        <v>1</v>
-      </c>
-      <c r="L54">
-        <v>2.9</v>
-      </c>
-      <c r="M54">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
-      <c r="A55" s="1">
-        <v>258</v>
-      </c>
-      <c r="B55" t="s">
-        <v>85</v>
-      </c>
-      <c r="C55" t="s">
-        <v>133</v>
-      </c>
-      <c r="D55">
-        <v>1.06</v>
-      </c>
-      <c r="E55">
-        <v>1.535</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55" t="s">
-        <v>82</v>
-      </c>
-      <c r="H55">
-        <v>6</v>
-      </c>
-      <c r="I55" t="s">
-        <v>84</v>
-      </c>
-      <c r="J55">
-        <v>1</v>
-      </c>
-      <c r="L55">
-        <v>2.9</v>
-      </c>
-      <c r="M55">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
-      <c r="A56" s="1">
-        <v>0</v>
-      </c>
-      <c r="B56" t="s">
-        <v>85</v>
-      </c>
-      <c r="C56" t="s">
-        <v>134</v>
-      </c>
-      <c r="D56">
-        <v>0.645</v>
-      </c>
-      <c r="E56">
-        <v>1.112</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56" t="s">
-        <v>82</v>
-      </c>
-      <c r="H56">
-        <v>6</v>
-      </c>
-      <c r="I56" t="s">
-        <v>84</v>
-      </c>
-      <c r="J56">
-        <v>1</v>
-      </c>
-      <c r="L56">
-        <v>2.9</v>
-      </c>
-      <c r="M56">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
-      <c r="A57" s="1">
-        <v>1</v>
-      </c>
-      <c r="B57" t="s">
-        <v>85</v>
-      </c>
-      <c r="C57" t="s">
-        <v>135</v>
-      </c>
-      <c r="D57">
-        <v>1.01</v>
-      </c>
-      <c r="E57">
-        <v>1.535</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57" t="s">
-        <v>82</v>
-      </c>
-      <c r="H57">
-        <v>6</v>
-      </c>
-      <c r="I57" t="s">
-        <v>84</v>
-      </c>
-      <c r="J57">
-        <v>1</v>
-      </c>
-      <c r="L57">
-        <v>2.9</v>
-      </c>
-      <c r="M57">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
-      <c r="A58" s="1">
-        <v>265</v>
-      </c>
-      <c r="B58" t="s">
-        <v>85</v>
-      </c>
-      <c r="C58" t="s">
-        <v>127</v>
-      </c>
-      <c r="D58">
-        <v>0.96</v>
-      </c>
-      <c r="E58">
-        <v>1.535</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58" t="s">
-        <v>82</v>
-      </c>
-      <c r="H58">
-        <v>6</v>
-      </c>
-      <c r="I58" t="s">
-        <v>84</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
-      </c>
-      <c r="L58">
-        <v>2.9</v>
-      </c>
-      <c r="M58">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
-      <c r="A59" s="1">
-        <v>266</v>
-      </c>
-      <c r="B59" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" t="s">
-        <v>133</v>
-      </c>
-      <c r="D59">
-        <v>1.06</v>
-      </c>
-      <c r="E59">
-        <v>1.535</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59" t="s">
-        <v>82</v>
-      </c>
-      <c r="H59">
-        <v>6</v>
-      </c>
-      <c r="I59" t="s">
-        <v>84</v>
-      </c>
-      <c r="J59">
-        <v>1</v>
-      </c>
-      <c r="L59">
-        <v>2.9</v>
-      </c>
-      <c r="M59">
         <v>1.932</v>
       </c>
     </row>
@@ -5662,13 +5440,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -63,36 +63,57 @@
     <t>Tile</t>
   </si>
   <si>
+    <t>TMP1S2a1</t>
+  </si>
+  <si>
+    <t>TMP1S2a2</t>
+  </si>
+  <si>
+    <t>TMP1S2a3</t>
+  </si>
+  <si>
+    <t>TMP1S2a4</t>
+  </si>
+  <si>
+    <t>TMP1S2b1</t>
+  </si>
+  <si>
+    <t>TMP1S2b2</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2c2</t>
+  </si>
+  <si>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
+    <t>TMP1S2c4</t>
+  </si>
+  <si>
+    <t>TMP1S2d1</t>
+  </si>
+  <si>
+    <t>TMP1S2d2</t>
+  </si>
+  <si>
+    <t>TMP1S2d3</t>
+  </si>
+  <si>
+    <t>TMP1S2d4</t>
+  </si>
+  <si>
     <t>TMP1S2e1</t>
   </si>
   <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
-    <t>TMP1S2c2</t>
-  </si>
-  <si>
-    <t>TMP1S2c3</t>
-  </si>
-  <si>
-    <t>TMP1S2c4</t>
-  </si>
-  <si>
-    <t>TMP1S2d1</t>
-  </si>
-  <si>
-    <t>TMP1S2d2</t>
-  </si>
-  <si>
-    <t>TMP1S2b3</t>
-  </si>
-  <si>
-    <t>TMP1S2d3</t>
-  </si>
-  <si>
     <t>TMP1S2e2</t>
   </si>
   <si>
@@ -114,63 +135,42 @@
     <t>TMP1S2f4</t>
   </si>
   <si>
-    <t>TMP1S2d4</t>
-  </si>
-  <si>
-    <t>TMP1S2b1</t>
-  </si>
-  <si>
-    <t>TMP1S2b2</t>
-  </si>
-  <si>
-    <t>TMP1S2a3</t>
-  </si>
-  <si>
-    <t>TMP1S2a2</t>
-  </si>
-  <si>
-    <t>TMP1S2a1</t>
-  </si>
-  <si>
-    <t>TMP1S2a4</t>
+    <t>TMP2S2a1</t>
   </si>
   <si>
     <t>TMP2S2a2</t>
   </si>
   <si>
-    <t>TMP2S2a1</t>
+    <t>TMP2S2b1</t>
   </si>
   <si>
     <t>TMP2S2b2</t>
   </si>
   <si>
-    <t>TMP2S2b1</t>
+    <t>TMP3S2a1</t>
+  </si>
+  <si>
+    <t>TMP3S2a2</t>
+  </si>
+  <si>
+    <t>TMP3S2a3</t>
   </si>
   <si>
     <t>TMP3S2a4</t>
   </si>
   <si>
-    <t>TMP3S2a1</t>
-  </si>
-  <si>
-    <t>TMP3S2a3</t>
-  </si>
-  <si>
-    <t>TMP3S2a2</t>
+    <t>TMP4S2a1</t>
   </si>
   <si>
     <t>TMP4S2a2</t>
   </si>
   <si>
+    <t>TMP4S2a3</t>
+  </si>
+  <si>
     <t>TMP4S2a4</t>
   </si>
   <si>
-    <t>TMP4S2a1</t>
-  </si>
-  <si>
-    <t>TMP4S2a3</t>
-  </si>
-  <si>
     <t>TMP5S2a1</t>
   </si>
   <si>
@@ -180,13 +180,16 @@
     <t>TMP5S2a3</t>
   </si>
   <si>
+    <t>TMP6S2a1</t>
+  </si>
+  <si>
     <t>TMP6S2a2</t>
   </si>
   <si>
     <t>TMP6S2a3</t>
   </si>
   <si>
-    <t>TMP6S2a1</t>
+    <t>TMP6S2a4</t>
   </si>
   <si>
     <t>TMP6S2b1</t>
@@ -195,72 +198,69 @@
     <t>TMP6S2b2</t>
   </si>
   <si>
+    <t>TMP6S2b3</t>
+  </si>
+  <si>
     <t>TMP6S2b4</t>
   </si>
   <si>
-    <t>TMP6S2a4</t>
-  </si>
-  <si>
-    <t>TMP6S2b3</t>
-  </si>
-  <si>
     <t>TMP7S2a1</t>
   </si>
   <si>
+    <t>TMP7S2a2</t>
+  </si>
+  <si>
+    <t>TMP7S2a3</t>
+  </si>
+  <si>
+    <t>TMP7S2a4</t>
+  </si>
+  <si>
+    <t>TMP7S2a5</t>
+  </si>
+  <si>
+    <t>TMP7S2a6</t>
+  </si>
+  <si>
+    <t>TMP7S2a7</t>
+  </si>
+  <si>
+    <t>TMP7S2b1</t>
+  </si>
+  <si>
+    <t>TMP7S2b2</t>
+  </si>
+  <si>
+    <t>TMP7S2b3</t>
+  </si>
+  <si>
+    <t>TMP7S2b4</t>
+  </si>
+  <si>
+    <t>TMP7S2b5</t>
+  </si>
+  <si>
+    <t>TMP7S2b6</t>
+  </si>
+  <si>
+    <t>TMP7S2b7</t>
+  </si>
+  <si>
+    <t>TMP7S2c1</t>
+  </si>
+  <si>
+    <t>TMP7S2c2</t>
+  </si>
+  <si>
+    <t>TMP7S2d1</t>
+  </si>
+  <si>
+    <t>TMP7S2d2</t>
+  </si>
+  <si>
     <t>TMP7S2e1</t>
   </si>
   <si>
-    <t>TMP7S2a2</t>
-  </si>
-  <si>
-    <t>TMP7S2a3</t>
-  </si>
-  <si>
-    <t>TMP7S2a4</t>
-  </si>
-  <si>
-    <t>TMP7S2a5</t>
-  </si>
-  <si>
-    <t>TMP7S2a6</t>
-  </si>
-  <si>
-    <t>TMP7S2a7</t>
-  </si>
-  <si>
-    <t>TMP7S2b1</t>
-  </si>
-  <si>
-    <t>TMP7S2b2</t>
-  </si>
-  <si>
-    <t>TMP7S2b3</t>
-  </si>
-  <si>
-    <t>TMP7S2b4</t>
-  </si>
-  <si>
-    <t>TMP7S2b5</t>
-  </si>
-  <si>
-    <t>TMP7S2b6</t>
-  </si>
-  <si>
-    <t>TMP7S2b7</t>
-  </si>
-  <si>
-    <t>TMP7S2c1</t>
-  </si>
-  <si>
-    <t>TMP7S2c2</t>
-  </si>
-  <si>
-    <t>TMP7S2d1</t>
-  </si>
-  <si>
-    <t>TMP7S2d2</t>
-  </si>
-  <si>
     <t>TMP7S2e2</t>
   </si>
   <si>
@@ -276,6 +276,54 @@
     <t>Fitting</t>
   </si>
   <si>
+    <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
+  </si>
+  <si>
+    <t>BSS.Shallow_FW:BSS.Shallow_FW:1038276</t>
+  </si>
+  <si>
+    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
+  </si>
+  <si>
+    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
+  </si>
+  <si>
+    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+  </si>
+  <si>
+    <t>BSS.GESSI,BM.49001:Default:1090988</t>
+  </si>
+  <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+  </si>
+  <si>
+    <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
+  </si>
+  <si>
+    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+  </si>
+  <si>
+    <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
+  </si>
+  <si>
     <t>LP1S3a1</t>
   </si>
   <si>
@@ -291,109 +339,85 @@
     <t>LP3S3a1</t>
   </si>
   <si>
+    <t>LP3S3a2</t>
+  </si>
+  <si>
+    <t>LP3S3a3</t>
+  </si>
+  <si>
     <t>LP3S3a4</t>
   </si>
   <si>
-    <t>LP3S3a3</t>
-  </si>
-  <si>
-    <t>LP3S3a2</t>
-  </si>
-  <si>
-    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
-  </si>
-  <si>
     <t>LP4S3a1</t>
   </si>
   <si>
     <t>LP4S3a2</t>
   </si>
   <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
-  </si>
-  <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
+    <t>LP5S3a1</t>
+  </si>
+  <si>
+    <t>LP5S3a2</t>
+  </si>
+  <si>
+    <t>LP5S3a3</t>
+  </si>
+  <si>
+    <t>LP5S3a4</t>
+  </si>
+  <si>
+    <t>LP5S3a5</t>
+  </si>
+  <si>
+    <t>LP5S3b1</t>
+  </si>
+  <si>
+    <t>LP5S3b2</t>
+  </si>
+  <si>
+    <t>LP5S3b3</t>
+  </si>
+  <si>
+    <t>LP5S3b4</t>
+  </si>
+  <si>
+    <t>LP5S3b5</t>
+  </si>
+  <si>
+    <t>LP5S3c1</t>
+  </si>
+  <si>
+    <t>LP5S3c2</t>
+  </si>
+  <si>
+    <t>LP5S3c3</t>
+  </si>
+  <si>
+    <t>LP5S3c4</t>
+  </si>
+  <si>
+    <t>LP5S3d1</t>
   </si>
   <si>
     <t>LP5S3d2</t>
   </si>
   <si>
-    <t>LP5S3d1</t>
-  </si>
-  <si>
-    <t>LP5S3c4</t>
-  </si>
-  <si>
-    <t>LP5S3c3</t>
-  </si>
-  <si>
-    <t>LP5S3c2</t>
-  </si>
-  <si>
-    <t>LP5S3c1</t>
-  </si>
-  <si>
-    <t>LP5S3b5</t>
-  </si>
-  <si>
-    <t>LP5S3b1</t>
-  </si>
-  <si>
     <t>LP5S3d3</t>
   </si>
   <si>
-    <t>LP5S3a5</t>
-  </si>
-  <si>
-    <t>LP5S3a4</t>
-  </si>
-  <si>
-    <t>LP5S3a3</t>
-  </si>
-  <si>
-    <t>LP5S3a2</t>
-  </si>
-  <si>
-    <t>LP5S3a1</t>
-  </si>
-  <si>
-    <t>LP5S3b2</t>
-  </si>
-  <si>
     <t>LP5S3d4</t>
   </si>
   <si>
-    <t>LP5S3b4</t>
-  </si>
-  <si>
-    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
-  </si>
-  <si>
-    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
-  </si>
-  <si>
-    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
-  </si>
-  <si>
-    <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
-  </si>
-  <si>
-    <t>LP5S3b3</t>
+    <t>LP7S3a1</t>
+  </si>
+  <si>
+    <t>LP7S3a2</t>
+  </si>
+  <si>
+    <t>LP7S3a3</t>
+  </si>
+  <si>
+    <t>LP7S3a4</t>
   </si>
   <si>
     <t>LP7S3b1</t>
@@ -402,34 +426,10 @@
     <t>LP7S3b2</t>
   </si>
   <si>
+    <t>LP7S3b3</t>
+  </si>
+  <si>
     <t>LP7S3b4</t>
-  </si>
-  <si>
-    <t>LP7S3a1</t>
-  </si>
-  <si>
-    <t>LP7S3a3</t>
-  </si>
-  <si>
-    <t>LP7S3a2</t>
-  </si>
-  <si>
-    <t>LP7S3a4</t>
-  </si>
-  <si>
-    <t>LP7S3b3</t>
-  </si>
-  <si>
-    <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
-  </si>
-  <si>
-    <t>BSS.Shallow_FW:BSS.Shallow_FW:1038276</t>
-  </si>
-  <si>
-    <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
-  </si>
-  <si>
-    <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
   </si>
   <si>
     <t>6</t>
@@ -848,7 +848,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-0.35</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F2">
         <v>-0.775</v>
@@ -886,7 +886,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -898,10 +898,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.49</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F3">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -924,7 +924,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.47</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F4">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -974,10 +974,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.47</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F5">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1012,10 +1012,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F6">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1050,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F7">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-0.03</v>
+        <v>0.49</v>
       </c>
       <c r="F8">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1126,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>-0.03</v>
+        <v>0.49</v>
       </c>
       <c r="F9">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F10">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F11">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>-0.35</v>
+        <v>0.47</v>
       </c>
       <c r="F12">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1278,10 +1278,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-0.35</v>
+        <v>0.47</v>
       </c>
       <c r="F13">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1304,7 +1304,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-0.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F14">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1354,10 +1354,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-1.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F15">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1380,7 +1380,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-1.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F16">
-        <v>-0.175</v>
+        <v>0.425</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1418,7 +1418,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1430,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>-1.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F17">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1468,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-1.35</v>
+        <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F19">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1544,10 +1544,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="F20">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1582,10 +1582,10 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="F21">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.9350000000000001</v>
+        <v>-1.35</v>
       </c>
       <c r="F22">
-        <v>0.425</v>
+        <v>-0.775</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0.9350000000000001</v>
+        <v>-1.35</v>
       </c>
       <c r="F23">
         <v>-0.175</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1696,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.9350000000000001</v>
+        <v>-1.35</v>
       </c>
       <c r="F24">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1734,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0.9350000000000001</v>
+        <v>-1.35</v>
       </c>
       <c r="F25">
         <v>1.025</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1775,7 +1775,7 @@
         <v>-0.5</v>
       </c>
       <c r="F26">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1813,7 +1813,7 @@
         <v>-0.5</v>
       </c>
       <c r="F27">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1851,7 +1851,7 @@
         <v>0.1</v>
       </c>
       <c r="F28">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -1889,7 +1889,7 @@
         <v>0.1</v>
       </c>
       <c r="F29">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1912,7 +1912,7 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>1.025</v>
+        <v>-0.775</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>-0.775</v>
+        <v>-0.175</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>-0.175</v>
+        <v>1.025</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -2079,7 +2079,7 @@
         <v>-0.3</v>
       </c>
       <c r="F34">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -2102,7 +2102,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2117,7 +2117,7 @@
         <v>-0.3</v>
       </c>
       <c r="F35">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G35">
         <v>4</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2155,7 +2155,7 @@
         <v>-0.3</v>
       </c>
       <c r="F36">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -2178,7 +2178,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2193,7 +2193,7 @@
         <v>-0.3</v>
       </c>
       <c r="F37">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2345,7 +2345,7 @@
         <v>0.3</v>
       </c>
       <c r="F41">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G41">
         <v>6</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2383,7 +2383,7 @@
         <v>0.3</v>
       </c>
       <c r="F42">
-        <v>0.425</v>
+        <v>-0.175</v>
       </c>
       <c r="G42">
         <v>6</v>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2421,7 +2421,7 @@
         <v>0.3</v>
       </c>
       <c r="F43">
-        <v>-0.775</v>
+        <v>0.425</v>
       </c>
       <c r="G43">
         <v>6</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2456,10 +2456,10 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F44">
-        <v>-0.775</v>
+        <v>1.025</v>
       </c>
       <c r="G44">
         <v>6</v>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2497,7 +2497,7 @@
         <v>-0.3</v>
       </c>
       <c r="F45">
-        <v>-0.175</v>
+        <v>-0.775</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2535,7 +2535,7 @@
         <v>-0.3</v>
       </c>
       <c r="F46">
-        <v>1.025</v>
+        <v>-0.175</v>
       </c>
       <c r="G46">
         <v>6</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F47">
-        <v>1.025</v>
+        <v>0.425</v>
       </c>
       <c r="G47">
         <v>6</v>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2611,7 +2611,7 @@
         <v>-0.3</v>
       </c>
       <c r="F48">
-        <v>0.425</v>
+        <v>1.025</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2681,10 +2681,10 @@
         <v>63</v>
       </c>
       <c r="D50">
-        <v>2.61</v>
+        <v>0.12</v>
       </c>
       <c r="E50">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2722,7 +2722,7 @@
         <v>0.12</v>
       </c>
       <c r="E51">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2760,7 +2760,7 @@
         <v>0.12</v>
       </c>
       <c r="E52">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2798,7 +2798,7 @@
         <v>0.12</v>
       </c>
       <c r="E53">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2836,7 +2836,7 @@
         <v>0.12</v>
       </c>
       <c r="E54">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2874,7 +2874,7 @@
         <v>0.12</v>
       </c>
       <c r="E55">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2909,10 +2909,10 @@
         <v>69</v>
       </c>
       <c r="D56">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E56">
-        <v>1.05</v>
+        <v>0.15</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2938,7 +2938,7 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2950,7 +2950,7 @@
         <v>0.72</v>
       </c>
       <c r="E57">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2976,7 +2976,7 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -2988,7 +2988,7 @@
         <v>0.72</v>
       </c>
       <c r="E58">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -3026,7 +3026,7 @@
         <v>0.72</v>
       </c>
       <c r="E59">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -3052,7 +3052,7 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -3064,7 +3064,7 @@
         <v>0.72</v>
       </c>
       <c r="E60">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -3102,7 +3102,7 @@
         <v>0.72</v>
       </c>
       <c r="E61">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3140,7 +3140,7 @@
         <v>0.72</v>
       </c>
       <c r="E62">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="1">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3175,10 +3175,10 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>0.72</v>
+        <v>1.41</v>
       </c>
       <c r="E63">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="1">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3216,7 +3216,7 @@
         <v>1.41</v>
       </c>
       <c r="E64">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3242,7 +3242,7 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="1">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3251,10 +3251,10 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="E65">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="1">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3292,7 +3292,7 @@
         <v>2.01</v>
       </c>
       <c r="E66">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="1">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
@@ -3327,10 +3327,10 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>2.01</v>
+        <v>2.61</v>
       </c>
       <c r="E67">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3448,7 +3448,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>85</v>
@@ -3457,16 +3457,16 @@
         <v>86</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.645</v>
       </c>
       <c r="E2">
-        <v>0.375</v>
+        <v>1.112</v>
       </c>
       <c r="F2">
-        <v>0.213</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>82</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -3481,12 +3481,12 @@
         <v>2.9</v>
       </c>
       <c r="M2">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>226</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>85</v>
@@ -3495,16 +3495,16 @@
         <v>87</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="E3">
-        <v>-0.255</v>
+        <v>1.535</v>
       </c>
       <c r="F3">
-        <v>0.213</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>82</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -3519,12 +3519,12 @@
         <v>2.9</v>
       </c>
       <c r="M3">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>227</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
         <v>85</v>
@@ -3533,16 +3533,16 @@
         <v>88</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="E4">
-        <v>0.375</v>
+        <v>0.45</v>
       </c>
       <c r="F4">
-        <v>0.137</v>
+        <v>-0.453</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -3554,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M4">
         <v>2.655</v>
@@ -3562,7 +3562,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>228</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
         <v>85</v>
@@ -3571,16 +3571,16 @@
         <v>89</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E5">
-        <v>-0.255</v>
+        <v>0.243</v>
       </c>
       <c r="F5">
-        <v>0.137</v>
+        <v>-0.8</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -3592,7 +3592,7 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>2.9</v>
+        <v>0.592</v>
       </c>
       <c r="M5">
         <v>2.655</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>229</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
         <v>85</v>
@@ -3609,16 +3609,16 @@
         <v>90</v>
       </c>
       <c r="D6">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="E6">
-        <v>-0.077</v>
+        <v>0.375</v>
       </c>
       <c r="F6">
-        <v>0.962</v>
+        <v>-0.9</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>6</v>
@@ -3630,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M6">
         <v>2.655</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>232</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
         <v>85</v>
@@ -3647,16 +3647,16 @@
         <v>91</v>
       </c>
       <c r="D7">
-        <v>0.6</v>
+        <v>0.09</v>
       </c>
       <c r="E7">
-        <v>0.123</v>
+        <v>0.525</v>
       </c>
       <c r="F7">
-        <v>-0.188</v>
+        <v>-0.825</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -3668,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M7">
         <v>2.655</v>
@@ -3676,7 +3676,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
         <v>85</v>
@@ -3685,16 +3685,16 @@
         <v>92</v>
       </c>
       <c r="D8">
-        <v>0.6</v>
+        <v>-0.037</v>
       </c>
       <c r="E8">
-        <v>-0.077</v>
+        <v>-0.8</v>
       </c>
       <c r="F8">
-        <v>-0.188</v>
+        <v>-0.365</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -3706,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M8">
         <v>2.655</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
         <v>85</v>
@@ -3723,16 +3723,16 @@
         <v>93</v>
       </c>
       <c r="D9">
-        <v>0.6</v>
+        <v>0.435</v>
       </c>
       <c r="E9">
-        <v>0.123</v>
+        <v>-1.28</v>
       </c>
       <c r="F9">
-        <v>0.962</v>
+        <v>-0.79</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>6</v>
@@ -3744,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M9">
         <v>2.655</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
         <v>85</v>
@@ -3761,16 +3761,16 @@
         <v>94</v>
       </c>
       <c r="D10">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="E10">
-        <v>0.21</v>
+        <v>0.508</v>
       </c>
       <c r="F10">
-        <v>-0.05</v>
+        <v>1.468</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10">
         <v>6</v>
@@ -3782,7 +3782,7 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>0.96</v>
+        <v>0.592</v>
       </c>
       <c r="M10">
         <v>2.655</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>233</v>
+        <v>90</v>
       </c>
       <c r="B11" t="s">
         <v>85</v>
@@ -3799,28 +3799,28 @@
         <v>95</v>
       </c>
       <c r="D11">
+        <v>0.6</v>
+      </c>
+      <c r="E11">
+        <v>0.21</v>
+      </c>
+      <c r="F11">
+        <v>-0.05</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="L11">
         <v>0.96</v>
-      </c>
-      <c r="E11">
-        <v>-0.195</v>
-      </c>
-      <c r="F11">
-        <v>-0.375</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-      <c r="H11">
-        <v>6</v>
-      </c>
-      <c r="I11" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>0.592</v>
       </c>
       <c r="M11">
         <v>2.655</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>234</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s">
         <v>85</v>
@@ -3837,16 +3837,16 @@
         <v>96</v>
       </c>
       <c r="D12">
-        <v>0.96</v>
+        <v>0.22</v>
       </c>
       <c r="E12">
-        <v>-0.145</v>
+        <v>-0.8</v>
       </c>
       <c r="F12">
-        <v>-0.375</v>
+        <v>-0.725</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>6</v>
@@ -3858,7 +3858,7 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M12">
         <v>2.655</v>
@@ -3866,7 +3866,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
         <v>85</v>
@@ -3875,16 +3875,16 @@
         <v>97</v>
       </c>
       <c r="D13">
-        <v>0.86</v>
+        <v>0.06</v>
       </c>
       <c r="E13">
-        <v>0.508</v>
+        <v>0.45</v>
       </c>
       <c r="F13">
-        <v>1.468</v>
+        <v>-0.175</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>6</v>
@@ -3896,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="L13">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M13">
         <v>2.655</v>
@@ -3904,7 +3904,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
         <v>85</v>
@@ -3913,16 +3913,16 @@
         <v>98</v>
       </c>
       <c r="D14">
-        <v>0.9370000000000001</v>
+        <v>0.108</v>
       </c>
       <c r="E14">
-        <v>0.243</v>
+        <v>-0.45</v>
       </c>
       <c r="F14">
-        <v>-0.8</v>
+        <v>-0.175</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>6</v>
@@ -3934,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="L14">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M14">
         <v>2.655</v>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="B15" t="s">
         <v>85</v>
@@ -3951,16 +3951,16 @@
         <v>99</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="E15">
-        <v>0.9</v>
+        <v>1.535</v>
       </c>
       <c r="F15">
-        <v>-0.15</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>82</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -3972,15 +3972,15 @@
         <v>1</v>
       </c>
       <c r="L15">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M15">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>249</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s">
         <v>85</v>
@@ -3989,13 +3989,13 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>-0.575</v>
       </c>
       <c r="F16">
-        <v>-0.15</v>
+        <v>-1.024</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>248</v>
+        <v>157</v>
       </c>
       <c r="B17" t="s">
         <v>85</v>
@@ -4027,16 +4027,16 @@
         <v>101</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>0.645</v>
       </c>
       <c r="E17">
-        <v>0.9</v>
+        <v>1.075</v>
       </c>
       <c r="F17">
-        <v>1.4</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>82</v>
       </c>
       <c r="H17">
         <v>6</v>
@@ -4048,15 +4048,15 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M17">
-        <v>2.655</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="B18" t="s">
         <v>85</v>
@@ -4068,13 +4068,13 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-0.9</v>
+        <v>0.375</v>
       </c>
       <c r="F18">
-        <v>1.4</v>
+        <v>0.213</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>6</v>
@@ -4086,7 +4086,7 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M18">
         <v>2.655</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="B19" t="s">
         <v>85</v>
@@ -4106,13 +4106,13 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0.9</v>
+        <v>-0.255</v>
       </c>
       <c r="F19">
-        <v>1.4</v>
+        <v>0.213</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>6</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="L19">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M19">
         <v>2.655</v>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s">
         <v>85</v>
@@ -4144,13 +4144,13 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.9</v>
+        <v>0.375</v>
       </c>
       <c r="F20">
-        <v>1.4</v>
+        <v>0.137</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>6</v>
@@ -4162,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="L20">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M20">
         <v>2.655</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s">
         <v>85</v>
@@ -4179,16 +4179,16 @@
         <v>105</v>
       </c>
       <c r="D21">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>-0.45</v>
+        <v>-0.255</v>
       </c>
       <c r="F21">
-        <v>-0.616</v>
+        <v>0.137</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -4200,7 +4200,7 @@
         <v>1</v>
       </c>
       <c r="L21">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M21">
         <v>2.655</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s">
         <v>85</v>
@@ -4217,16 +4217,16 @@
         <v>106</v>
       </c>
       <c r="D22">
-        <v>0.183</v>
+        <v>0.6</v>
       </c>
       <c r="E22">
-        <v>-0.63</v>
+        <v>-0.077</v>
       </c>
       <c r="F22">
-        <v>-0.402</v>
+        <v>0.962</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <v>6</v>
@@ -4238,7 +4238,7 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M22">
         <v>2.655</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s">
         <v>85</v>
@@ -4255,16 +4255,16 @@
         <v>107</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="F23">
-        <v>-0.75</v>
+        <v>0.962</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H23">
         <v>6</v>
@@ -4276,7 +4276,7 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M23">
         <v>2.655</v>
@@ -4284,7 +4284,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
         <v>85</v>
@@ -4293,16 +4293,16 @@
         <v>108</v>
       </c>
       <c r="D24">
-        <v>0.08799999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="E24">
-        <v>-0.455</v>
+        <v>-0.077</v>
       </c>
       <c r="F24">
-        <v>-0.22</v>
+        <v>-0.188</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -4314,7 +4314,7 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M24">
         <v>2.655</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s">
         <v>85</v>
@@ -4331,16 +4331,16 @@
         <v>109</v>
       </c>
       <c r="D25">
-        <v>0.08799999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="E25">
-        <v>-0.205</v>
+        <v>0.123</v>
       </c>
       <c r="F25">
-        <v>-0.466</v>
+        <v>-0.188</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H25">
         <v>6</v>
@@ -4352,7 +4352,7 @@
         <v>1</v>
       </c>
       <c r="L25">
-        <v>1.94</v>
+        <v>0.96</v>
       </c>
       <c r="M25">
         <v>2.655</v>
@@ -4360,7 +4360,7 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s">
         <v>85</v>
@@ -4369,16 +4369,16 @@
         <v>110</v>
       </c>
       <c r="D26">
-        <v>0.08799999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="E26">
-        <v>-0.705</v>
+        <v>-0.195</v>
       </c>
       <c r="F26">
-        <v>-0.466</v>
+        <v>-0.375</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H26">
         <v>6</v>
@@ -4390,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M26">
         <v>2.655</v>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s">
         <v>85</v>
@@ -4407,16 +4407,16 @@
         <v>111</v>
       </c>
       <c r="D27">
-        <v>0.08799999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="E27">
-        <v>-0.205</v>
+        <v>-0.145</v>
       </c>
       <c r="F27">
-        <v>0.026</v>
+        <v>-0.375</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27">
         <v>6</v>
@@ -4428,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <v>1.94</v>
+        <v>0.592</v>
       </c>
       <c r="M27">
         <v>2.655</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B29" t="s">
         <v>85</v>
@@ -4483,13 +4483,13 @@
         <v>113</v>
       </c>
       <c r="D29">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E29">
-        <v>-0.27</v>
+        <v>-0.205</v>
       </c>
       <c r="F29">
-        <v>-0.402</v>
+        <v>0.026</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -4512,7 +4512,7 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B30" t="s">
         <v>85</v>
@@ -4521,13 +4521,13 @@
         <v>114</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E30">
-        <v>0.9</v>
+        <v>-0.705</v>
       </c>
       <c r="F30">
-        <v>-0.75</v>
+        <v>-0.466</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B31" t="s">
         <v>85</v>
@@ -4559,13 +4559,13 @@
         <v>115</v>
       </c>
       <c r="D31">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E31">
-        <v>-0.27</v>
+        <v>-0.205</v>
       </c>
       <c r="F31">
-        <v>-0.83</v>
+        <v>-0.466</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="B32" t="s">
         <v>85</v>
@@ -4597,13 +4597,13 @@
         <v>116</v>
       </c>
       <c r="D32">
-        <v>0.208</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E32">
-        <v>-0.575</v>
+        <v>-0.455</v>
       </c>
       <c r="F32">
-        <v>-1.024</v>
+        <v>-0.22</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="B33" t="s">
         <v>85</v>
@@ -4635,13 +4635,13 @@
         <v>117</v>
       </c>
       <c r="D33">
-        <v>0.295</v>
+        <v>0.183</v>
       </c>
       <c r="E33">
-        <v>0.45</v>
+        <v>-0.63</v>
       </c>
       <c r="F33">
-        <v>-0.453</v>
+        <v>-0.402</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>55</v>
+        <v>241</v>
       </c>
       <c r="B34" t="s">
         <v>85</v>
@@ -4673,13 +4673,13 @@
         <v>118</v>
       </c>
       <c r="D34">
-        <v>0.15</v>
+        <v>0.183</v>
       </c>
       <c r="E34">
-        <v>0.375</v>
+        <v>-0.27</v>
       </c>
       <c r="F34">
-        <v>-0.9</v>
+        <v>-0.402</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -4702,7 +4702,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>57</v>
+        <v>242</v>
       </c>
       <c r="B35" t="s">
         <v>85</v>
@@ -4711,13 +4711,13 @@
         <v>119</v>
       </c>
       <c r="D35">
-        <v>0.09</v>
+        <v>0.183</v>
       </c>
       <c r="E35">
-        <v>0.525</v>
+        <v>-0.63</v>
       </c>
       <c r="F35">
-        <v>-0.825</v>
+        <v>-0.83</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -4740,7 +4740,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>63</v>
+        <v>243</v>
       </c>
       <c r="B36" t="s">
         <v>85</v>
@@ -4749,13 +4749,13 @@
         <v>120</v>
       </c>
       <c r="D36">
-        <v>-0.037</v>
+        <v>0.183</v>
       </c>
       <c r="E36">
-        <v>-0.8</v>
+        <v>-0.27</v>
       </c>
       <c r="F36">
-        <v>-0.365</v>
+        <v>-0.83</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -4778,7 +4778,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>80</v>
+        <v>244</v>
       </c>
       <c r="B37" t="s">
         <v>85</v>
@@ -4787,13 +4787,13 @@
         <v>121</v>
       </c>
       <c r="D37">
-        <v>0.435</v>
+        <v>0.183</v>
       </c>
       <c r="E37">
-        <v>-1.28</v>
+        <v>-0.45</v>
       </c>
       <c r="F37">
-        <v>-0.79</v>
+        <v>-0.616</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -4816,7 +4816,7 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="B38" t="s">
         <v>85</v>
@@ -4825,13 +4825,13 @@
         <v>122</v>
       </c>
       <c r="D38">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="F38">
-        <v>-0.725</v>
+        <v>1.4</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>152</v>
+        <v>246</v>
       </c>
       <c r="B39" t="s">
         <v>85</v>
@@ -4863,13 +4863,13 @@
         <v>123</v>
       </c>
       <c r="D39">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0.45</v>
+        <v>0.9</v>
       </c>
       <c r="F39">
-        <v>-0.175</v>
+        <v>1.4</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -4892,7 +4892,7 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>154</v>
+        <v>247</v>
       </c>
       <c r="B40" t="s">
         <v>85</v>
@@ -4901,13 +4901,13 @@
         <v>124</v>
       </c>
       <c r="D40">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>-0.45</v>
+        <v>-0.9</v>
       </c>
       <c r="F40">
-        <v>-0.175</v>
+        <v>1.4</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B41" t="s">
         <v>85</v>
@@ -4939,13 +4939,13 @@
         <v>125</v>
       </c>
       <c r="D41">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>-0.63</v>
+        <v>0.9</v>
       </c>
       <c r="F41">
-        <v>-0.83</v>
+        <v>1.4</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="B42" t="s">
         <v>85</v>
@@ -4977,16 +4977,16 @@
         <v>126</v>
       </c>
       <c r="D42">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>1.535</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42" t="s">
-        <v>82</v>
+        <v>-0.15</v>
+      </c>
+      <c r="G42">
+        <v>5</v>
       </c>
       <c r="H42">
         <v>6</v>
@@ -4998,15 +4998,15 @@
         <v>1</v>
       </c>
       <c r="L42">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M42">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B43" t="s">
         <v>85</v>
@@ -5015,16 +5015,16 @@
         <v>127</v>
       </c>
       <c r="D43">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>1.535</v>
+        <v>0.9</v>
       </c>
       <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43" t="s">
-        <v>82</v>
+        <v>-0.15</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
       </c>
       <c r="H43">
         <v>6</v>
@@ -5036,15 +5036,15 @@
         <v>1</v>
       </c>
       <c r="L43">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M43">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B44" t="s">
         <v>85</v>
@@ -5053,16 +5053,16 @@
         <v>128</v>
       </c>
       <c r="D44">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>1.535</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44" t="s">
-        <v>82</v>
+        <v>-0.75</v>
+      </c>
+      <c r="G44">
+        <v>5</v>
       </c>
       <c r="H44">
         <v>6</v>
@@ -5074,15 +5074,15 @@
         <v>1</v>
       </c>
       <c r="L44">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M44">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B45" t="s">
         <v>85</v>
@@ -5091,16 +5091,16 @@
         <v>129</v>
       </c>
       <c r="D45">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>1.075</v>
+        <v>0.9</v>
       </c>
       <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45" t="s">
-        <v>82</v>
+        <v>-0.75</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
       </c>
       <c r="H45">
         <v>6</v>
@@ -5112,15 +5112,15 @@
         <v>1</v>
       </c>
       <c r="L45">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M45">
-        <v>1.932</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B46" t="s">
         <v>85</v>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B47" t="s">
         <v>85</v>
@@ -5196,7 +5196,7 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B48" t="s">
         <v>85</v>
@@ -5205,7 +5205,7 @@
         <v>132</v>
       </c>
       <c r="D48">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="E48">
         <v>1.075</v>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B49" t="s">
         <v>85</v>
@@ -5243,10 +5243,10 @@
         <v>133</v>
       </c>
       <c r="D49">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="E49">
-        <v>1.535</v>
+        <v>1.075</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -5272,7 +5272,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="B50" t="s">
         <v>85</v>
@@ -5281,10 +5281,10 @@
         <v>134</v>
       </c>
       <c r="D50">
-        <v>0.645</v>
+        <v>0.96</v>
       </c>
       <c r="E50">
-        <v>1.112</v>
+        <v>1.535</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -5310,7 +5310,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>1</v>
+        <v>258</v>
       </c>
       <c r="B51" t="s">
         <v>85</v>
@@ -5319,7 +5319,7 @@
         <v>135</v>
       </c>
       <c r="D51">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="E51">
         <v>1.535</v>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>155</v>
+        <v>259</v>
       </c>
       <c r="B52" t="s">
         <v>85</v>
@@ -5357,7 +5357,7 @@
         <v>136</v>
       </c>
       <c r="D52">
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
       <c r="E52">
         <v>1.535</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="B53" t="s">
         <v>85</v>
@@ -5395,10 +5395,10 @@
         <v>137</v>
       </c>
       <c r="D53">
-        <v>0.645</v>
+        <v>1.06</v>
       </c>
       <c r="E53">
-        <v>1.075</v>
+        <v>1.535</v>
       </c>
       <c r="F53">
         <v>0</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD01C8E8-8E51-4F72-9073-45C8FC9E286C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="3120" yWindow="735" windowWidth="23235" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
     <sheet name="Stage 3" sheetId="2" r:id="rId2"/>
     <sheet name="Obstacles" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="144">
   <si>
     <t>Marking type</t>
   </si>
@@ -63,6 +69,69 @@
     <t>Tile</t>
   </si>
   <si>
+    <t>TMP1S2e1</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2c2</t>
+  </si>
+  <si>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
+    <t>TMP1S2d1</t>
+  </si>
+  <si>
+    <t>TMP1S2d2</t>
+  </si>
+  <si>
+    <t>TMP1S2d3</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
+    <t>TMP1S2d4</t>
+  </si>
+  <si>
+    <t>TMP1S2e3</t>
+  </si>
+  <si>
+    <t>TMP1S2e4</t>
+  </si>
+  <si>
+    <t>TMP1S2f1</t>
+  </si>
+  <si>
+    <t>TMP1S2f2</t>
+  </si>
+  <si>
+    <t>TMP1S2f3</t>
+  </si>
+  <si>
+    <t>TMP1S2f4</t>
+  </si>
+  <si>
+    <t>TMP1S2e2</t>
+  </si>
+  <si>
+    <t>TMP1S2b2</t>
+  </si>
+  <si>
+    <t>TMP1S2c4</t>
+  </si>
+  <si>
+    <t>TMP1S2a4</t>
+  </si>
+  <si>
+    <t>TMP1S2b1</t>
+  </si>
+  <si>
     <t>TMP1S2a1</t>
   </si>
   <si>
@@ -72,91 +141,31 @@
     <t>TMP1S2a3</t>
   </si>
   <si>
-    <t>TMP1S2a4</t>
-  </si>
-  <si>
-    <t>TMP1S2b1</t>
-  </si>
-  <si>
-    <t>TMP1S2b2</t>
-  </si>
-  <si>
-    <t>TMP1S2b3</t>
-  </si>
-  <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
-    <t>TMP1S2c2</t>
-  </si>
-  <si>
-    <t>TMP1S2c3</t>
-  </si>
-  <si>
-    <t>TMP1S2c4</t>
-  </si>
-  <si>
-    <t>TMP1S2d1</t>
-  </si>
-  <si>
-    <t>TMP1S2d2</t>
-  </si>
-  <si>
-    <t>TMP1S2d3</t>
-  </si>
-  <si>
-    <t>TMP1S2d4</t>
-  </si>
-  <si>
-    <t>TMP1S2e1</t>
-  </si>
-  <si>
-    <t>TMP1S2e2</t>
-  </si>
-  <si>
-    <t>TMP1S2e3</t>
-  </si>
-  <si>
-    <t>TMP1S2e4</t>
-  </si>
-  <si>
-    <t>TMP1S2f1</t>
-  </si>
-  <si>
-    <t>TMP1S2f2</t>
-  </si>
-  <si>
-    <t>TMP1S2f3</t>
-  </si>
-  <si>
-    <t>TMP1S2f4</t>
-  </si>
-  <si>
     <t>TMP2S2a1</t>
   </si>
   <si>
+    <t>TMP2S2b2</t>
+  </si>
+  <si>
+    <t>TMP2S2b1</t>
+  </si>
+  <si>
     <t>TMP2S2a2</t>
   </si>
   <si>
-    <t>TMP2S2b1</t>
-  </si>
-  <si>
-    <t>TMP2S2b2</t>
+    <t>TMP3S2a4</t>
+  </si>
+  <si>
+    <t>TMP3S2a3</t>
+  </si>
+  <si>
+    <t>TMP3S2a2</t>
   </si>
   <si>
     <t>TMP3S2a1</t>
   </si>
   <si>
-    <t>TMP3S2a2</t>
-  </si>
-  <si>
-    <t>TMP3S2a3</t>
-  </si>
-  <si>
-    <t>TMP3S2a4</t>
+    <t>TMP4S2a4</t>
   </si>
   <si>
     <t>TMP4S2a1</t>
@@ -168,40 +177,52 @@
     <t>TMP4S2a3</t>
   </si>
   <si>
-    <t>TMP4S2a4</t>
-  </si>
-  <si>
     <t>TMP5S2a1</t>
   </si>
   <si>
+    <t>TMP5S2b3</t>
+  </si>
+  <si>
+    <t>TMP5S2b2</t>
+  </si>
+  <si>
+    <t>TMP5S2b1</t>
+  </si>
+  <si>
+    <t>TMP5S2a3</t>
+  </si>
+  <si>
     <t>TMP5S2a2</t>
   </si>
   <si>
-    <t>TMP5S2a3</t>
+    <t>TMP5S2b4</t>
+  </si>
+  <si>
+    <t>TMP6S2b4</t>
+  </si>
+  <si>
+    <t>TMP6S2b3</t>
+  </si>
+  <si>
+    <t>TMP6S2a2</t>
+  </si>
+  <si>
+    <t>TMP6S2a3</t>
+  </si>
+  <si>
+    <t>TMP6S2a4</t>
+  </si>
+  <si>
+    <t>TMP6S2b1</t>
+  </si>
+  <si>
+    <t>TMP6S2b2</t>
   </si>
   <si>
     <t>TMP6S2a1</t>
   </si>
   <si>
-    <t>TMP6S2a2</t>
-  </si>
-  <si>
-    <t>TMP6S2a3</t>
-  </si>
-  <si>
-    <t>TMP6S2a4</t>
-  </si>
-  <si>
-    <t>TMP6S2b1</t>
-  </si>
-  <si>
-    <t>TMP6S2b2</t>
-  </si>
-  <si>
-    <t>TMP6S2b3</t>
-  </si>
-  <si>
-    <t>TMP6S2b4</t>
+    <t>TMP7S2e1</t>
   </si>
   <si>
     <t>TMP7S2a1</t>
@@ -222,217 +243,208 @@
     <t>TMP7S2a6</t>
   </si>
   <si>
+    <t>TMP7S2e2</t>
+  </si>
+  <si>
     <t>TMP7S2a7</t>
   </si>
   <si>
+    <t>TMP7S2b2</t>
+  </si>
+  <si>
+    <t>TMP7S2b3</t>
+  </si>
+  <si>
+    <t>TMP7S2b4</t>
+  </si>
+  <si>
+    <t>TMP7S2b5</t>
+  </si>
+  <si>
+    <t>TMP7S2b6</t>
+  </si>
+  <si>
+    <t>TMP7S2b7</t>
+  </si>
+  <si>
+    <t>TMP7S2c1</t>
+  </si>
+  <si>
+    <t>TMP7S2c2</t>
+  </si>
+  <si>
+    <t>TMP7S2d1</t>
+  </si>
+  <si>
+    <t>TMP7S2d2</t>
+  </si>
+  <si>
     <t>TMP7S2b1</t>
   </si>
   <si>
-    <t>TMP7S2b2</t>
-  </si>
-  <si>
-    <t>TMP7S2b3</t>
-  </si>
-  <si>
-    <t>TMP7S2b4</t>
-  </si>
-  <si>
-    <t>TMP7S2b5</t>
-  </si>
-  <si>
-    <t>TMP7S2b6</t>
-  </si>
-  <si>
-    <t>TMP7S2b7</t>
-  </si>
-  <si>
-    <t>TMP7S2c1</t>
-  </si>
-  <si>
-    <t>TMP7S2c2</t>
-  </si>
-  <si>
-    <t>TMP7S2d1</t>
-  </si>
-  <si>
-    <t>TMP7S2d2</t>
-  </si>
-  <si>
-    <t>TMP7S2e1</t>
-  </si>
-  <si>
-    <t>TMP7S2e2</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
-    <t>+</t>
-  </si>
-  <si>
     <t>blank</t>
   </si>
   <si>
     <t>Fitting</t>
   </si>
   <si>
+    <t>LP1S3a2</t>
+  </si>
+  <si>
+    <t>LP1S3a4</t>
+  </si>
+  <si>
+    <t>LP1S3a3</t>
+  </si>
+  <si>
+    <t>LP1S3a1</t>
+  </si>
+  <si>
+    <t>LP3S3a1</t>
+  </si>
+  <si>
+    <t>LP3S3a3</t>
+  </si>
+  <si>
+    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
+  </si>
+  <si>
+    <t>LP3S3a4</t>
+  </si>
+  <si>
+    <t>LP3S3a2</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
+  </si>
+  <si>
+    <t>LP4S3a2</t>
+  </si>
+  <si>
+    <t>LP4S3a1</t>
+  </si>
+  <si>
+    <t>LP5S3d2</t>
+  </si>
+  <si>
+    <t>LP5S3d1</t>
+  </si>
+  <si>
+    <t>LP5S3c3</t>
+  </si>
+  <si>
+    <t>LP5S3b5</t>
+  </si>
+  <si>
+    <t>LP5S3c1</t>
+  </si>
+  <si>
+    <t>LP5S3c2</t>
+  </si>
+  <si>
+    <t>LP5S3c4</t>
+  </si>
+  <si>
+    <t>LP5S3d3</t>
+  </si>
+  <si>
+    <t>LP5S3a1</t>
+  </si>
+  <si>
+    <t>LP5S3a2</t>
+  </si>
+  <si>
+    <t>LP5S3a3</t>
+  </si>
+  <si>
+    <t>LP5S3a4</t>
+  </si>
+  <si>
+    <t>LP5S3a5</t>
+  </si>
+  <si>
+    <t>LP5S3b1</t>
+  </si>
+  <si>
+    <t>LP5S3b4</t>
+  </si>
+  <si>
+    <t>LP5S3d4</t>
+  </si>
+  <si>
+    <t>LP5S3b3</t>
+  </si>
+  <si>
+    <t>LP5S3b2</t>
+  </si>
+  <si>
+    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+  </si>
+  <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+  </si>
+  <si>
+    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
+  </si>
+  <si>
+    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
+  </si>
+  <si>
+    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
+  </si>
+  <si>
+    <t>BSS.GESSI,BM.49001:Default:1090988</t>
+  </si>
+  <si>
+    <t>LP7S3b2</t>
+  </si>
+  <si>
+    <t>LP7S3a1</t>
+  </si>
+  <si>
+    <t>LP7S3b4</t>
+  </si>
+  <si>
+    <t>LP7S3b3</t>
+  </si>
+  <si>
+    <t>LP7S3b1</t>
+  </si>
+  <si>
+    <t>LP7S3a2</t>
+  </si>
+  <si>
+    <t>LP7S3a3</t>
+  </si>
+  <si>
+    <t>LP7S3a4</t>
+  </si>
+  <si>
     <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
   </si>
   <si>
     <t>BSS.Shallow_FW:BSS.Shallow_FW:1038276</t>
   </si>
   <si>
-    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
-  </si>
-  <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
-  </si>
-  <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
-  </si>
-  <si>
-    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
-  </si>
-  <si>
-    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
-  </si>
-  <si>
-    <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
-  </si>
-  <si>
     <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
   </si>
   <si>
-    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
-  </si>
-  <si>
     <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
-  </si>
-  <si>
-    <t>LP1S3a1</t>
-  </si>
-  <si>
-    <t>LP1S3a2</t>
-  </si>
-  <si>
-    <t>LP1S3a3</t>
-  </si>
-  <si>
-    <t>LP1S3a4</t>
-  </si>
-  <si>
-    <t>LP3S3a1</t>
-  </si>
-  <si>
-    <t>LP3S3a2</t>
-  </si>
-  <si>
-    <t>LP3S3a3</t>
-  </si>
-  <si>
-    <t>LP3S3a4</t>
-  </si>
-  <si>
-    <t>LP4S3a1</t>
-  </si>
-  <si>
-    <t>LP4S3a2</t>
-  </si>
-  <si>
-    <t>LP5S3a1</t>
-  </si>
-  <si>
-    <t>LP5S3a2</t>
-  </si>
-  <si>
-    <t>LP5S3a3</t>
-  </si>
-  <si>
-    <t>LP5S3a4</t>
-  </si>
-  <si>
-    <t>LP5S3a5</t>
-  </si>
-  <si>
-    <t>LP5S3b1</t>
-  </si>
-  <si>
-    <t>LP5S3b2</t>
-  </si>
-  <si>
-    <t>LP5S3b3</t>
-  </si>
-  <si>
-    <t>LP5S3b4</t>
-  </si>
-  <si>
-    <t>LP5S3b5</t>
-  </si>
-  <si>
-    <t>LP5S3c1</t>
-  </si>
-  <si>
-    <t>LP5S3c2</t>
-  </si>
-  <si>
-    <t>LP5S3c3</t>
-  </si>
-  <si>
-    <t>LP5S3c4</t>
-  </si>
-  <si>
-    <t>LP5S3d1</t>
-  </si>
-  <si>
-    <t>LP5S3d2</t>
-  </si>
-  <si>
-    <t>LP5S3d3</t>
-  </si>
-  <si>
-    <t>LP5S3d4</t>
-  </si>
-  <si>
-    <t>LP7S3a1</t>
-  </si>
-  <si>
-    <t>LP7S3a2</t>
-  </si>
-  <si>
-    <t>LP7S3a3</t>
-  </si>
-  <si>
-    <t>LP7S3a4</t>
-  </si>
-  <si>
-    <t>LP7S3b1</t>
-  </si>
-  <si>
-    <t>LP7S3b2</t>
-  </si>
-  <si>
-    <t>LP7S3b3</t>
-  </si>
-  <si>
-    <t>LP7S3b4</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
   <si>
     <t>Position X (mm)</t>
@@ -447,8 +459,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -511,13 +523,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -555,7 +575,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -589,6 +609,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -623,9 +644,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -798,11 +820,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O68"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O72"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -846,9 +877,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -860,10 +891,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.9350000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="F2">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -872,7 +903,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -881,12 +912,12 @@
         <v>2.9</v>
       </c>
       <c r="M2">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -898,10 +929,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.9350000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="F3">
-        <v>-0.175</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -910,7 +941,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -919,12 +950,12 @@
         <v>2.9</v>
       </c>
       <c r="M3">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -936,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.9350000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="F4">
-        <v>0.425</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -948,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -957,12 +988,12 @@
         <v>2.9</v>
       </c>
       <c r="M4">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -974,10 +1005,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.9350000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="F5">
-        <v>1.025</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -986,7 +1017,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -995,12 +1026,12 @@
         <v>2.9</v>
       </c>
       <c r="M5">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1012,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="F6">
-        <v>-0.775</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1024,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1033,12 +1064,12 @@
         <v>2.9</v>
       </c>
       <c r="M6">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1050,10 +1081,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
       <c r="F7">
-        <v>-0.175</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1062,7 +1093,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1071,12 +1102,12 @@
         <v>2.9</v>
       </c>
       <c r="M7">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1088,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
       <c r="F8">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1100,7 +1131,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1109,12 +1140,12 @@
         <v>2.9</v>
       </c>
       <c r="M8">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1126,10 +1157,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
       <c r="F9">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1138,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1147,12 +1178,12 @@
         <v>2.9</v>
       </c>
       <c r="M9">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1164,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F10">
-        <v>-0.775</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1176,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1185,12 +1216,12 @@
         <v>2.9</v>
       </c>
       <c r="M10">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1202,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F11">
-        <v>-0.175</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1214,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1223,12 +1254,12 @@
         <v>2.9</v>
       </c>
       <c r="M11">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1240,10 +1271,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.47</v>
+        <v>-0.35</v>
       </c>
       <c r="F12">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1252,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1261,12 +1292,12 @@
         <v>2.9</v>
       </c>
       <c r="M12">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1278,10 +1309,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.47</v>
+        <v>-0.35</v>
       </c>
       <c r="F13">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1290,7 +1321,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1299,12 +1330,12 @@
         <v>2.9</v>
       </c>
       <c r="M13">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1316,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F14">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1328,7 +1359,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1337,12 +1368,12 @@
         <v>2.9</v>
       </c>
       <c r="M14">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1354,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F15">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1366,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1375,12 +1406,12 @@
         <v>2.9</v>
       </c>
       <c r="M15">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1392,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F16">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1404,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1413,12 +1444,12 @@
         <v>2.9</v>
       </c>
       <c r="M16">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1430,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F17">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1442,7 +1473,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1451,12 +1482,12 @@
         <v>2.9</v>
       </c>
       <c r="M17">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1471,7 +1502,7 @@
         <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>-0.775</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1480,7 +1511,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1489,12 +1520,12 @@
         <v>2.9</v>
       </c>
       <c r="M18">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1506,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F19">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1518,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1527,12 +1558,12 @@
         <v>2.9</v>
       </c>
       <c r="M19">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1544,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.35</v>
+        <v>0.47</v>
       </c>
       <c r="F20">
-        <v>0.425</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1556,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1565,12 +1596,12 @@
         <v>2.9</v>
       </c>
       <c r="M20">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1582,10 +1613,10 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>-0.35</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F21">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1594,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1603,12 +1634,12 @@
         <v>2.9</v>
       </c>
       <c r="M21">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1620,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>-1.35</v>
+        <v>0.49</v>
       </c>
       <c r="F22">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1632,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1641,12 +1672,12 @@
         <v>2.9</v>
       </c>
       <c r="M22">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1658,10 +1689,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>-1.35</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F23">
-        <v>-0.175</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1670,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1679,12 +1710,12 @@
         <v>2.9</v>
       </c>
       <c r="M23">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1696,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>-1.35</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F24">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1708,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1717,12 +1748,12 @@
         <v>2.9</v>
       </c>
       <c r="M24">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1734,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>-1.35</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F25">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1746,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1755,10 +1786,10 @@
         <v>2.9</v>
       </c>
       <c r="M25">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>182</v>
       </c>
@@ -1772,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="F26">
         <v>-0.75</v>
@@ -1784,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1793,12 +1824,12 @@
         <v>1.34</v>
       </c>
       <c r="M26">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1810,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="F27">
         <v>-0.15</v>
@@ -1822,7 +1853,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1831,10 +1862,10 @@
         <v>1.34</v>
       </c>
       <c r="M27">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>184</v>
       </c>
@@ -1848,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F28">
         <v>-0.75</v>
@@ -1860,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1869,12 +1900,12 @@
         <v>1.34</v>
       </c>
       <c r="M28">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -1886,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="F29">
         <v>-0.15</v>
@@ -1898,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1907,12 +1938,12 @@
         <v>1.34</v>
       </c>
       <c r="M29">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1924,10 +1955,10 @@
         <v>0.6</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>-0.93500000000000005</v>
       </c>
       <c r="F30">
-        <v>-0.775</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -1936,7 +1967,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1945,12 +1976,12 @@
         <v>0.96</v>
       </c>
       <c r="M30">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1962,10 +1993,10 @@
         <v>0.6</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>-0.93500000000000005</v>
       </c>
       <c r="F31">
-        <v>-0.175</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -1974,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1983,12 +2014,12 @@
         <v>0.96</v>
       </c>
       <c r="M31">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -2000,10 +2031,10 @@
         <v>0.6</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>-0.93500000000000005</v>
       </c>
       <c r="F32">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -2012,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2021,12 +2052,12 @@
         <v>0.96</v>
       </c>
       <c r="M32">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -2038,10 +2069,10 @@
         <v>0.6</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>-0.93500000000000005</v>
       </c>
       <c r="F33">
-        <v>1.025</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -2050,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2059,12 +2090,12 @@
         <v>0.96</v>
       </c>
       <c r="M33">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -2076,10 +2107,10 @@
         <v>0.96</v>
       </c>
       <c r="E34">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F34">
-        <v>-0.775</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -2088,21 +2119,21 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="L34">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M34">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2114,10 +2145,10 @@
         <v>0.96</v>
       </c>
       <c r="E35">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F35">
-        <v>-0.175</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G35">
         <v>4</v>
@@ -2126,21 +2157,21 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="L35">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M35">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2152,10 +2183,10 @@
         <v>0.96</v>
       </c>
       <c r="E36">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F36">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -2164,21 +2195,21 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="L36">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M36">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2190,10 +2221,10 @@
         <v>0.96</v>
       </c>
       <c r="E37">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F37">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -2202,19 +2233,19 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="L37">
-        <v>0.592</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="M37">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>194</v>
       </c>
@@ -2228,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="F38">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -2240,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2249,12 +2280,12 @@
         <v>1.94</v>
       </c>
       <c r="M38">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2266,10 +2297,10 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1.155</v>
       </c>
       <c r="F39">
-        <v>-0.775</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -2278,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2287,12 +2318,12 @@
         <v>1.94</v>
       </c>
       <c r="M39">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2304,10 +2335,10 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>-0.45</v>
+        <v>1.155</v>
       </c>
       <c r="F40">
-        <v>-0.775</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -2316,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2325,10 +2356,10 @@
         <v>1.94</v>
       </c>
       <c r="M40">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>197</v>
       </c>
@@ -2342,33 +2373,33 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0.3</v>
+        <v>1.155</v>
       </c>
       <c r="F41">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="L41">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M41">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2380,33 +2411,33 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="F42">
-        <v>-0.175</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M42">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2418,31 +2449,31 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="F43">
-        <v>0.425</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M43">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>200</v>
       </c>
@@ -2456,33 +2487,33 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0.3</v>
+        <v>1.155</v>
       </c>
       <c r="F44">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>1.932</v>
+        <v>1.94</v>
       </c>
       <c r="M44">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2497,7 +2528,7 @@
         <v>-0.3</v>
       </c>
       <c r="F45">
-        <v>-0.775</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -2506,21 +2537,21 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M45">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2535,7 +2566,7 @@
         <v>-0.3</v>
       </c>
       <c r="F46">
-        <v>-0.175</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G46">
         <v>6</v>
@@ -2544,21 +2575,21 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M46">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2570,10 +2601,10 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F47">
-        <v>0.425</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G47">
         <v>6</v>
@@ -2582,21 +2613,21 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="L47">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M47">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2608,10 +2639,10 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F48">
-        <v>1.025</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -2620,21 +2651,21 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J48">
         <v>1</v>
       </c>
       <c r="L48">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M48">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2643,36 +2674,36 @@
         <v>62</v>
       </c>
       <c r="D49">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49" t="s">
-        <v>82</v>
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="L49">
-        <v>2.9</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M49">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2681,36 +2712,36 @@
         <v>63</v>
       </c>
       <c r="D50">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="G50" t="s">
-        <v>82</v>
+        <v>-0.77500000000000002</v>
+      </c>
+      <c r="G50">
+        <v>6</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="L50">
-        <v>2.9</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M50">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2719,36 +2750,36 @@
         <v>64</v>
       </c>
       <c r="D51">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>0.45</v>
+        <v>-0.3</v>
       </c>
       <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51" t="s">
-        <v>82</v>
+        <v>-0.17499999999999999</v>
+      </c>
+      <c r="G51">
+        <v>6</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="L51">
-        <v>2.9</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M51">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2757,36 +2788,36 @@
         <v>65</v>
       </c>
       <c r="D52">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52" t="s">
-        <v>82</v>
+        <v>-0.77500000000000002</v>
+      </c>
+      <c r="G52">
+        <v>6</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>2.9</v>
+        <v>1.9319999999999999</v>
       </c>
       <c r="M52">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2795,22 +2826,22 @@
         <v>66</v>
       </c>
       <c r="D53">
-        <v>0.12</v>
+        <v>2.61</v>
       </c>
       <c r="E53">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H53">
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2819,12 +2850,12 @@
         <v>2.9</v>
       </c>
       <c r="M53">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2836,19 +2867,19 @@
         <v>0.12</v>
       </c>
       <c r="E54">
-        <v>0.9</v>
+        <v>0.15</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2857,12 +2888,12 @@
         <v>2.9</v>
       </c>
       <c r="M54">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2874,19 +2905,19 @@
         <v>0.12</v>
       </c>
       <c r="E55">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2895,12 +2926,12 @@
         <v>2.9</v>
       </c>
       <c r="M55">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2909,22 +2940,22 @@
         <v>69</v>
       </c>
       <c r="D56">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E56">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2933,12 +2964,12 @@
         <v>2.9</v>
       </c>
       <c r="M56">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2947,22 +2978,22 @@
         <v>70</v>
       </c>
       <c r="D57">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E57">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2971,12 +3002,12 @@
         <v>2.9</v>
       </c>
       <c r="M57">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -2985,22 +3016,22 @@
         <v>71</v>
       </c>
       <c r="D58">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E58">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="F58">
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -3009,12 +3040,12 @@
         <v>2.9</v>
       </c>
       <c r="M58">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -3023,22 +3054,22 @@
         <v>72</v>
       </c>
       <c r="D59">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E59">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -3047,12 +3078,12 @@
         <v>2.9</v>
       </c>
       <c r="M59">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -3061,22 +3092,22 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>0.72</v>
+        <v>2.61</v>
       </c>
       <c r="E60">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -3085,12 +3116,12 @@
         <v>2.9</v>
       </c>
       <c r="M60">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -3099,22 +3130,22 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>0.72</v>
+        <v>0.12</v>
       </c>
       <c r="E61">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -3123,12 +3154,12 @@
         <v>2.9</v>
       </c>
       <c r="M61">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3140,19 +3171,19 @@
         <v>0.72</v>
       </c>
       <c r="E62">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3161,12 +3192,12 @@
         <v>2.9</v>
       </c>
       <c r="M62">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3175,22 +3206,22 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>1.41</v>
+        <v>0.72</v>
       </c>
       <c r="E63">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3199,12 +3230,12 @@
         <v>2.9</v>
       </c>
       <c r="M63">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3213,22 +3244,22 @@
         <v>77</v>
       </c>
       <c r="D64">
-        <v>1.41</v>
+        <v>0.72</v>
       </c>
       <c r="E64">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3237,12 +3268,12 @@
         <v>2.9</v>
       </c>
       <c r="M64">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3251,22 +3282,22 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>2.01</v>
+        <v>0.72</v>
       </c>
       <c r="E65">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3275,12 +3306,12 @@
         <v>2.9</v>
       </c>
       <c r="M65">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3289,22 +3320,22 @@
         <v>79</v>
       </c>
       <c r="D66">
-        <v>2.01</v>
+        <v>0.72</v>
       </c>
       <c r="E66">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3313,12 +3344,12 @@
         <v>2.9</v>
       </c>
       <c r="M66">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
@@ -3327,22 +3358,22 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>2.61</v>
+        <v>0.72</v>
       </c>
       <c r="E67">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3351,12 +3382,12 @@
         <v>2.9</v>
       </c>
       <c r="M67">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3365,31 +3396,183 @@
         <v>81</v>
       </c>
       <c r="D68">
-        <v>2.61</v>
+        <v>1.41</v>
       </c>
       <c r="E68">
+        <v>0.6</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68" t="s">
+        <v>86</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68" t="s">
+        <v>87</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>2.9</v>
+      </c>
+      <c r="M68">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>224</v>
+      </c>
+      <c r="B69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69">
+        <v>1.41</v>
+      </c>
+      <c r="E69">
         <v>1.2</v>
       </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68" t="s">
-        <v>82</v>
-      </c>
-      <c r="H68">
-        <v>1</v>
-      </c>
-      <c r="I68" t="s">
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69" t="s">
+        <v>86</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69" t="s">
+        <v>87</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <v>2.9</v>
+      </c>
+      <c r="M69">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>225</v>
+      </c>
+      <c r="B70" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" t="s">
+        <v>83</v>
+      </c>
+      <c r="D70">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="E70">
+        <v>0.6</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
+        <v>86</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70" t="s">
+        <v>87</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>2.9</v>
+      </c>
+      <c r="M70">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>226</v>
+      </c>
+      <c r="B71" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" t="s">
         <v>84</v>
       </c>
-      <c r="J68">
-        <v>1</v>
-      </c>
-      <c r="L68">
-        <v>2.9</v>
-      </c>
-      <c r="M68">
-        <v>1.932</v>
+      <c r="D71">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="E71">
+        <v>1.2</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
+        <v>86</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71" t="s">
+        <v>87</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="L71">
+        <v>2.9</v>
+      </c>
+      <c r="M71">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>216</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72">
+        <v>0.72</v>
+      </c>
+      <c r="E72">
+        <v>0.15</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
+        <v>86</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
+        <v>87</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="L72">
+        <v>2.9</v>
+      </c>
+      <c r="M72">
+        <v>1.9319999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3398,11 +3581,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3446,33 +3629,33 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D2">
-        <v>0.645</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1.112</v>
+        <v>-0.255</v>
       </c>
       <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>82</v>
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
       </c>
       <c r="H2">
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -3481,36 +3664,36 @@
         <v>2.9</v>
       </c>
       <c r="M2">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D3">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1.535</v>
+        <v>-0.255</v>
       </c>
       <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>82</v>
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="H3">
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3519,483 +3702,483 @@
         <v>2.9</v>
       </c>
       <c r="M3">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>36</v>
+        <v>231</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.375</v>
+      </c>
+      <c r="F4">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>2.9</v>
+      </c>
+      <c r="M4">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>229</v>
+      </c>
+      <c r="B5" t="s">
         <v>88</v>
       </c>
-      <c r="D4">
-        <v>0.295</v>
-      </c>
-      <c r="E4">
-        <v>0.45</v>
-      </c>
-      <c r="F4">
-        <v>-0.453</v>
-      </c>
-      <c r="G4">
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0.375</v>
+      </c>
+      <c r="F5">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>2.9</v>
+      </c>
+      <c r="M5">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>233</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6">
+        <v>0.6</v>
+      </c>
+      <c r="E6">
+        <v>-1.012</v>
+      </c>
+      <c r="F6">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0.96</v>
+      </c>
+      <c r="M6">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>235</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7">
+        <v>0.6</v>
+      </c>
+      <c r="E7">
+        <v>-1.012</v>
+      </c>
+      <c r="F7">
+        <v>-0.188</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0.96</v>
+      </c>
+      <c r="M7">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>90</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8">
+        <v>0.6</v>
+      </c>
+      <c r="E8">
+        <v>-0.72499999999999998</v>
+      </c>
+      <c r="F8">
+        <v>-0.05</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0.96</v>
+      </c>
+      <c r="M8">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>236</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9">
+        <v>0.6</v>
+      </c>
+      <c r="E9">
+        <v>-0.81200000000000006</v>
+      </c>
+      <c r="F9">
+        <v>-0.188</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0.96</v>
+      </c>
+      <c r="M9">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>234</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10">
+        <v>0.6</v>
+      </c>
+      <c r="E10">
+        <v>-0.81200000000000006</v>
+      </c>
+      <c r="F10">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0.96</v>
+      </c>
+      <c r="M10">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11">
+        <v>0.93700000000000006</v>
+      </c>
+      <c r="E11">
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="F11">
+        <v>-0.8</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="M11">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12">
+        <v>0.86</v>
+      </c>
+      <c r="E12">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="F12">
+        <v>1.468</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
+      </c>
+      <c r="I12" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="M12">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>238</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>0.96</v>
+      </c>
+      <c r="E13">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="F13">
+        <v>-0.375</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="M13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>237</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14">
+        <v>0.96</v>
+      </c>
+      <c r="E14">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="F14">
+        <v>-0.375</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+      <c r="I14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="M14">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>254</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>1.38</v>
+      </c>
+      <c r="F15">
+        <v>-0.15</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="L15">
         <v>1.94</v>
       </c>
-      <c r="M4">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="1">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5">
-        <v>0.9370000000000001</v>
-      </c>
-      <c r="E5">
-        <v>0.243</v>
-      </c>
-      <c r="F5">
-        <v>-0.8</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5" t="s">
-        <v>84</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>0.592</v>
-      </c>
-      <c r="M5">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="1">
-        <v>55</v>
-      </c>
-      <c r="B6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6">
-        <v>0.15</v>
-      </c>
-      <c r="E6">
-        <v>0.375</v>
-      </c>
-      <c r="F6">
-        <v>-0.9</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
-        <v>84</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1.94</v>
-      </c>
-      <c r="M6">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="1">
-        <v>57</v>
-      </c>
-      <c r="B7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7">
-        <v>0.09</v>
-      </c>
-      <c r="E7">
-        <v>0.525</v>
-      </c>
-      <c r="F7">
-        <v>-0.825</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7" t="s">
-        <v>84</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1.94</v>
-      </c>
-      <c r="M7">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="1">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8">
-        <v>-0.037</v>
-      </c>
-      <c r="E8">
-        <v>-0.8</v>
-      </c>
-      <c r="F8">
-        <v>-0.365</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-      <c r="I8" t="s">
-        <v>84</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1.94</v>
-      </c>
-      <c r="M8">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="1">
-        <v>80</v>
-      </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9">
-        <v>0.435</v>
-      </c>
-      <c r="E9">
-        <v>-1.28</v>
-      </c>
-      <c r="F9">
-        <v>-0.79</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9">
-        <v>6</v>
-      </c>
-      <c r="I9" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1.94</v>
-      </c>
-      <c r="M9">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="1">
-        <v>89</v>
-      </c>
-      <c r="B10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10">
-        <v>0.86</v>
-      </c>
-      <c r="E10">
-        <v>0.508</v>
-      </c>
-      <c r="F10">
-        <v>1.468</v>
-      </c>
-      <c r="G10">
-        <v>4</v>
-      </c>
-      <c r="H10">
-        <v>6</v>
-      </c>
-      <c r="I10" t="s">
-        <v>84</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>0.592</v>
-      </c>
-      <c r="M10">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="1">
-        <v>90</v>
-      </c>
-      <c r="B11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11">
-        <v>0.6</v>
-      </c>
-      <c r="E11">
-        <v>0.21</v>
-      </c>
-      <c r="F11">
-        <v>-0.05</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
-      <c r="H11">
-        <v>6</v>
-      </c>
-      <c r="I11" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>0.96</v>
-      </c>
-      <c r="M11">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="1">
-        <v>151</v>
-      </c>
-      <c r="B12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12">
-        <v>0.22</v>
-      </c>
-      <c r="E12">
-        <v>-0.8</v>
-      </c>
-      <c r="F12">
-        <v>-0.725</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-      <c r="H12">
-        <v>6</v>
-      </c>
-      <c r="I12" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>1.94</v>
-      </c>
-      <c r="M12">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="1">
-        <v>152</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13">
-        <v>0.06</v>
-      </c>
-      <c r="E13">
-        <v>0.45</v>
-      </c>
-      <c r="F13">
-        <v>-0.175</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-      <c r="H13">
-        <v>6</v>
-      </c>
-      <c r="I13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>1.94</v>
-      </c>
-      <c r="M13">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="1">
-        <v>154</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14">
-        <v>0.108</v>
-      </c>
-      <c r="E14">
-        <v>-0.45</v>
-      </c>
-      <c r="F14">
-        <v>-0.175</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-      <c r="H14">
-        <v>6</v>
-      </c>
-      <c r="I14" t="s">
-        <v>84</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <v>1.94</v>
-      </c>
-      <c r="M14">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="1">
-        <v>155</v>
-      </c>
-      <c r="B15" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15">
-        <v>1.01</v>
-      </c>
-      <c r="E15">
-        <v>1.535</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>82</v>
-      </c>
-      <c r="H15">
-        <v>6</v>
-      </c>
-      <c r="I15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>2.9</v>
-      </c>
       <c r="M15">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>156</v>
+        <v>253</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D16">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>-0.575</v>
+        <v>0.48</v>
       </c>
       <c r="F16">
-        <v>-1.024</v>
+        <v>-0.15</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -4004,7 +4187,7 @@
         <v>6</v>
       </c>
       <c r="I16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -4013,445 +4196,445 @@
         <v>1.94</v>
       </c>
       <c r="M16">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>157</v>
+        <v>251</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D17">
-        <v>0.645</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>1.075</v>
+        <v>-0.42</v>
       </c>
       <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17" t="s">
-        <v>82</v>
+        <v>1.4</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
       </c>
       <c r="H17">
         <v>6</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
       <c r="L17">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M17">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="E18">
-        <v>0.375</v>
+        <v>0.03</v>
       </c>
       <c r="F18">
-        <v>0.213</v>
+        <v>-0.61599999999999999</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>6</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="L18">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M18">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-0.255</v>
+        <v>-0.42</v>
       </c>
       <c r="F19">
-        <v>0.213</v>
+        <v>1.4</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>6</v>
       </c>
       <c r="I19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
       <c r="L19">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M19">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.375</v>
+        <v>1.38</v>
       </c>
       <c r="F20">
-        <v>0.137</v>
+        <v>1.4</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>6</v>
       </c>
       <c r="I20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="L20">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M20">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>-0.255</v>
+        <v>1.38</v>
       </c>
       <c r="F21">
-        <v>0.137</v>
+        <v>1.4</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>6</v>
       </c>
       <c r="I21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
       <c r="L21">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="M21">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D22">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>-0.077</v>
+        <v>0.48</v>
       </c>
       <c r="F22">
-        <v>0.962</v>
+        <v>-0.75</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>6</v>
       </c>
       <c r="I22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J22">
         <v>1</v>
       </c>
       <c r="L22">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M22">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D23">
-        <v>0.6</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E23">
-        <v>0.123</v>
+        <v>-0.22500000000000001</v>
       </c>
       <c r="F23">
-        <v>0.962</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>6</v>
       </c>
       <c r="I23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="L23">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M23">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D24">
-        <v>0.6</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E24">
-        <v>-0.077</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="F24">
-        <v>-0.188</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H24">
         <v>6</v>
       </c>
       <c r="I24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="L24">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M24">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D25">
-        <v>0.6</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E25">
-        <v>0.123</v>
+        <v>-0.22500000000000001</v>
       </c>
       <c r="F25">
-        <v>-0.188</v>
+        <v>-0.46600000000000003</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>6</v>
       </c>
       <c r="I25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="L25">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="M25">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D26">
-        <v>0.96</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E26">
-        <v>-0.195</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="F26">
-        <v>-0.375</v>
+        <v>-0.46600000000000003</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>6</v>
       </c>
       <c r="I26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="L26">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M26">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D27">
-        <v>0.96</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E27">
-        <v>-0.145</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F27">
-        <v>-0.375</v>
+        <v>-0.22</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>6</v>
       </c>
       <c r="I27" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J27">
         <v>1</v>
       </c>
       <c r="L27">
-        <v>0.592</v>
+        <v>1.94</v>
       </c>
       <c r="M27">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D28">
-        <v>0.08799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E28">
-        <v>-0.705</v>
+        <v>-0.15</v>
       </c>
       <c r="F28">
-        <v>0.026</v>
+        <v>-0.40200000000000002</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -4460,7 +4643,7 @@
         <v>6</v>
       </c>
       <c r="I28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -4469,27 +4652,27 @@
         <v>1.94</v>
       </c>
       <c r="M28">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D29">
-        <v>0.08799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E29">
-        <v>-0.205</v>
+        <v>0.21</v>
       </c>
       <c r="F29">
-        <v>0.026</v>
+        <v>-0.83</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -4498,7 +4681,7 @@
         <v>6</v>
       </c>
       <c r="I29" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -4507,27 +4690,27 @@
         <v>1.94</v>
       </c>
       <c r="M29">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D30">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>-0.705</v>
+        <v>1.38</v>
       </c>
       <c r="F30">
-        <v>-0.466</v>
+        <v>-0.75</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -4536,7 +4719,7 @@
         <v>6</v>
       </c>
       <c r="I30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -4545,27 +4728,27 @@
         <v>1.94</v>
       </c>
       <c r="M30">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D31">
-        <v>0.08799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E31">
-        <v>-0.205</v>
+        <v>-0.15</v>
       </c>
       <c r="F31">
-        <v>-0.466</v>
+        <v>-0.83</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -4574,7 +4757,7 @@
         <v>6</v>
       </c>
       <c r="I31" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -4583,27 +4766,27 @@
         <v>1.94</v>
       </c>
       <c r="M31">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D32">
-        <v>0.08799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E32">
-        <v>-0.455</v>
+        <v>0.21</v>
       </c>
       <c r="F32">
-        <v>-0.22</v>
+        <v>-0.40200000000000002</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -4612,7 +4795,7 @@
         <v>6</v>
       </c>
       <c r="I32" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -4621,27 +4804,27 @@
         <v>1.94</v>
       </c>
       <c r="M32">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>240</v>
+        <v>156</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D33">
-        <v>0.183</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="E33">
-        <v>-0.63</v>
+        <v>-9.5000000000000001E-2</v>
       </c>
       <c r="F33">
-        <v>-0.402</v>
+        <v>-1.024</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -4650,7 +4833,7 @@
         <v>6</v>
       </c>
       <c r="I33" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -4659,27 +4842,27 @@
         <v>1.94</v>
       </c>
       <c r="M33">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D34">
-        <v>0.183</v>
+        <v>0.108</v>
       </c>
       <c r="E34">
-        <v>-0.27</v>
+        <v>0.03</v>
       </c>
       <c r="F34">
-        <v>-0.402</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -4688,7 +4871,7 @@
         <v>6</v>
       </c>
       <c r="I34" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -4697,27 +4880,27 @@
         <v>1.94</v>
       </c>
       <c r="M34">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>242</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D35">
-        <v>0.183</v>
+        <v>0.22</v>
       </c>
       <c r="E35">
-        <v>-0.63</v>
+        <v>-0.32</v>
       </c>
       <c r="F35">
-        <v>-0.83</v>
+        <v>-0.72499999999999998</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -4726,7 +4909,7 @@
         <v>6</v>
       </c>
       <c r="I35" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -4735,27 +4918,27 @@
         <v>1.94</v>
       </c>
       <c r="M35">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D36">
-        <v>0.183</v>
+        <v>1.365</v>
       </c>
       <c r="E36">
-        <v>-0.27</v>
+        <v>1.28</v>
       </c>
       <c r="F36">
-        <v>-0.83</v>
+        <v>-0.79</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -4764,7 +4947,7 @@
         <v>6</v>
       </c>
       <c r="I36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -4773,27 +4956,27 @@
         <v>1.94</v>
       </c>
       <c r="M36">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D37">
-        <v>0.183</v>
+        <v>-3.6999999999999998E-2</v>
       </c>
       <c r="E37">
-        <v>-0.45</v>
+        <v>-0.32</v>
       </c>
       <c r="F37">
-        <v>-0.616</v>
+        <v>-0.36499999999999999</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -4802,7 +4985,7 @@
         <v>6</v>
       </c>
       <c r="I37" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -4811,27 +4994,27 @@
         <v>1.94</v>
       </c>
       <c r="M37">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>245</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="E38">
-        <v>-0.9</v>
+        <v>1.0049999999999999</v>
       </c>
       <c r="F38">
-        <v>1.4</v>
+        <v>-0.82499999999999996</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -4840,7 +5023,7 @@
         <v>6</v>
       </c>
       <c r="I38" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -4849,27 +5032,27 @@
         <v>1.94</v>
       </c>
       <c r="M38">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>246</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E39">
-        <v>0.9</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="F39">
-        <v>1.4</v>
+        <v>-0.9</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -4878,7 +5061,7 @@
         <v>6</v>
       </c>
       <c r="I39" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -4887,27 +5070,27 @@
         <v>1.94</v>
       </c>
       <c r="M39">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>247</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="E40">
-        <v>-0.9</v>
+        <v>0.93</v>
       </c>
       <c r="F40">
-        <v>1.4</v>
+        <v>-0.45300000000000001</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -4916,7 +5099,7 @@
         <v>6</v>
       </c>
       <c r="I40" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -4925,27 +5108,27 @@
         <v>1.94</v>
       </c>
       <c r="M40">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>248</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E41">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="F41">
-        <v>1.4</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -4954,7 +5137,7 @@
         <v>6</v>
       </c>
       <c r="I41" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -4963,188 +5146,188 @@
         <v>1.94</v>
       </c>
       <c r="M41">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1.5349999999999999</v>
       </c>
       <c r="F42">
-        <v>-0.15</v>
-      </c>
-      <c r="G42">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="G42" t="s">
+        <v>86</v>
       </c>
       <c r="H42">
         <v>6</v>
       </c>
       <c r="I42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M42">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E43">
-        <v>0.9</v>
+        <v>1.075</v>
       </c>
       <c r="F43">
-        <v>-0.15</v>
-      </c>
-      <c r="G43">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="G43" t="s">
+        <v>86</v>
       </c>
       <c r="H43">
         <v>6</v>
       </c>
       <c r="I43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="L43">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M43">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1.5349999999999999</v>
       </c>
       <c r="F44">
-        <v>-0.75</v>
-      </c>
-      <c r="G44">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="G44" t="s">
+        <v>86</v>
       </c>
       <c r="H44">
         <v>6</v>
       </c>
       <c r="I44" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M44">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E45">
-        <v>0.9</v>
+        <v>1.5349999999999999</v>
       </c>
       <c r="F45">
-        <v>-0.75</v>
-      </c>
-      <c r="G45">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>86</v>
       </c>
       <c r="H45">
         <v>6</v>
       </c>
       <c r="I45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="M45">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D46">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="E46">
-        <v>1.075</v>
+        <v>1.5349999999999999</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H46">
         <v>6</v>
       </c>
       <c r="I46" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -5153,18 +5336,18 @@
         <v>2.9</v>
       </c>
       <c r="M46">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D47">
         <v>0.72</v>
@@ -5176,13 +5359,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H47">
         <v>6</v>
       </c>
       <c r="I47" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -5191,21 +5374,21 @@
         <v>2.9</v>
       </c>
       <c r="M47">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B48" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D48">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E48">
         <v>1.075</v>
@@ -5214,13 +5397,13 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H48">
         <v>6</v>
       </c>
       <c r="I48" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -5229,18 +5412,18 @@
         <v>2.9</v>
       </c>
       <c r="M48">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D49">
         <v>0.72</v>
@@ -5252,13 +5435,13 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H49">
         <v>6</v>
       </c>
       <c r="I49" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -5267,36 +5450,36 @@
         <v>2.9</v>
       </c>
       <c r="M49">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D50">
-        <v>0.96</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="E50">
-        <v>1.535</v>
+        <v>1.1120000000000001</v>
       </c>
       <c r="F50">
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H50">
         <v>6</v>
       </c>
       <c r="I50" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -5305,36 +5488,36 @@
         <v>2.9</v>
       </c>
       <c r="M50">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>258</v>
+        <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D51">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="E51">
-        <v>1.535</v>
+        <v>1.5349999999999999</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H51">
         <v>6</v>
       </c>
       <c r="I51" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -5343,36 +5526,36 @@
         <v>2.9</v>
       </c>
       <c r="M51">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>259</v>
+        <v>155</v>
       </c>
       <c r="B52" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D52">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="E52">
-        <v>1.535</v>
+        <v>1.5349999999999999</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H52">
         <v>6</v>
       </c>
       <c r="I52" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -5381,36 +5564,36 @@
         <v>2.9</v>
       </c>
       <c r="M52">
-        <v>1.932</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>1.9319999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>260</v>
+        <v>157</v>
       </c>
       <c r="B53" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D53">
-        <v>1.06</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="E53">
-        <v>1.535</v>
+        <v>1.075</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H53">
         <v>6</v>
       </c>
       <c r="I53" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -5419,7 +5602,7 @@
         <v>2.9</v>
       </c>
       <c r="M53">
-        <v>1.932</v>
+        <v>1.9319999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5428,11 +5611,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:O1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:15">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5440,13 +5623,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD01C8E8-8E51-4F72-9073-45C8FC9E286C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0C6E3D-F991-41C6-95E3-CF439203FCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="735" windowWidth="23235" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="315" windowWidth="23235" windowHeight="15465" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
@@ -22,438 +22,432 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="142">
   <si>
     <t>Marking type</t>
   </si>
   <si>
+    <t>Point Name</t>
+  </si>
+  <si>
+    <t>Position X</t>
+  </si>
+  <si>
+    <t>Position Y</t>
+  </si>
+  <si>
+    <t>Position Z</t>
+  </si>
+  <si>
+    <t>Wall Number</t>
+  </si>
+  <si>
+    <t>Shape Type</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Quadrant</t>
+  </si>
+  <si>
+    <t>Unnamed : 9</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Orientation</t>
+  </si>
+  <si>
+    <t>Diameter</t>
+  </si>
+  <si>
+    <t>Tile</t>
+  </si>
+  <si>
+    <t>TMP1S2f2</t>
+  </si>
+  <si>
+    <t>TMP1S2d1</t>
+  </si>
+  <si>
+    <t>TMP1S2d2</t>
+  </si>
+  <si>
+    <t>TMP1S2d3</t>
+  </si>
+  <si>
+    <t>TMP1S2d4</t>
+  </si>
+  <si>
+    <t>TMP1S2e1</t>
+  </si>
+  <si>
+    <t>TMP1S2e2</t>
+  </si>
+  <si>
+    <t>TMP1S2c4</t>
+  </si>
+  <si>
+    <t>TMP1S2e3</t>
+  </si>
+  <si>
+    <t>TMP1S2f1</t>
+  </si>
+  <si>
+    <t>TMP1S2f3</t>
+  </si>
+  <si>
+    <t>TMP1S2f4</t>
+  </si>
+  <si>
+    <t>TMP1S2e4</t>
+  </si>
+  <si>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
+    <t>TMP1S2b2</t>
+  </si>
+  <si>
+    <t>TMP1S2b1</t>
+  </si>
+  <si>
+    <t>TMP1S2a4</t>
+  </si>
+  <si>
+    <t>TMP1S2a3</t>
+  </si>
+  <si>
+    <t>TMP1S2a2</t>
+  </si>
+  <si>
+    <t>TMP1S2a1</t>
+  </si>
+  <si>
+    <t>TMP1S2c2</t>
+  </si>
+  <si>
+    <t>TMP2S2b2</t>
+  </si>
+  <si>
+    <t>TMP2S2a2</t>
+  </si>
+  <si>
+    <t>TMP2S2a1</t>
+  </si>
+  <si>
+    <t>TMP2S2b1</t>
+  </si>
+  <si>
+    <t>TMP3S2a3</t>
+  </si>
+  <si>
+    <t>TMP3S2a1</t>
+  </si>
+  <si>
+    <t>TMP3S2a2</t>
+  </si>
+  <si>
+    <t>TMP3S2a4</t>
+  </si>
+  <si>
+    <t>TMP4S2a4</t>
+  </si>
+  <si>
+    <t>TMP4S2a3</t>
+  </si>
+  <si>
+    <t>TMP4S2a2</t>
+  </si>
+  <si>
+    <t>TMP4S2a1</t>
+  </si>
+  <si>
+    <t>TMP5S2b4</t>
+  </si>
+  <si>
+    <t>TMP5S2b1</t>
+  </si>
+  <si>
+    <t>TMP5S2b2</t>
+  </si>
+  <si>
+    <t>TMP5S2a3</t>
+  </si>
+  <si>
+    <t>TMP5S2a2</t>
+  </si>
+  <si>
+    <t>TMP5S2a1</t>
+  </si>
+  <si>
+    <t>TMP5S2b3</t>
+  </si>
+  <si>
+    <t>TMP6S2b4</t>
+  </si>
+  <si>
+    <t>TMP6S2b3</t>
+  </si>
+  <si>
+    <t>TMP6S2b2</t>
+  </si>
+  <si>
+    <t>TMP6S2b1</t>
+  </si>
+  <si>
+    <t>TMP6S2a4</t>
+  </si>
+  <si>
+    <t>TMP6S2a2</t>
+  </si>
+  <si>
+    <t>TMP6S2a1</t>
+  </si>
+  <si>
+    <t>TMP6S2a3</t>
+  </si>
+  <si>
+    <t>TMP7S2a5</t>
+  </si>
+  <si>
+    <t>TMP7S2e1</t>
+  </si>
+  <si>
+    <t>TMP7S2a1</t>
+  </si>
+  <si>
+    <t>TMP7S2a2</t>
+  </si>
+  <si>
+    <t>TMP7S2a3</t>
+  </si>
+  <si>
+    <t>TMP7S2a4</t>
+  </si>
+  <si>
+    <t>TMP7S2a6</t>
+  </si>
+  <si>
+    <t>TMP7S2a7</t>
+  </si>
+  <si>
+    <t>TMP7S2b1</t>
+  </si>
+  <si>
+    <t>TMP7S2b2</t>
+  </si>
+  <si>
+    <t>TMP7S2b3</t>
+  </si>
+  <si>
+    <t>TMP7S2b4</t>
+  </si>
+  <si>
+    <t>TMP7S2b5</t>
+  </si>
+  <si>
+    <t>TMP7S2b6</t>
+  </si>
+  <si>
+    <t>TMP7S2b7</t>
+  </si>
+  <si>
+    <t>TMP7S2c1</t>
+  </si>
+  <si>
+    <t>TMP7S2c2</t>
+  </si>
+  <si>
+    <t>TMP7S2d1</t>
+  </si>
+  <si>
+    <t>TMP7S2d2</t>
+  </si>
+  <si>
+    <t>TMP7S2e2</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>blank</t>
+  </si>
+  <si>
+    <t>Fitting</t>
+  </si>
+  <si>
+    <t>LP1S3a3</t>
+  </si>
+  <si>
+    <t>LP1S3a1</t>
+  </si>
+  <si>
+    <t>LP1S3a4</t>
+  </si>
+  <si>
+    <t>LP1S3a2</t>
+  </si>
+  <si>
+    <t>LP3S3a1</t>
+  </si>
+  <si>
+    <t>LP3S3a2</t>
+  </si>
+  <si>
+    <t>LP3S3a3</t>
+  </si>
+  <si>
+    <t>LP3S3a4</t>
+  </si>
+  <si>
+    <t>LP3S3b1</t>
+  </si>
+  <si>
+    <t>LP3S3b2</t>
+  </si>
+  <si>
+    <t>LP3S3b3</t>
+  </si>
+  <si>
+    <t>LP3S3b4</t>
+  </si>
+  <si>
+    <t>LP4S3a1</t>
+  </si>
+  <si>
+    <t>LP4S3a2</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
+  </si>
+  <si>
+    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
+  </si>
+  <si>
+    <t>LP5S3b5</t>
+  </si>
+  <si>
+    <t>LP5S3c2</t>
+  </si>
+  <si>
+    <t>LP5S3c3</t>
+  </si>
+  <si>
+    <t>LP5S3c1</t>
+  </si>
+  <si>
+    <t>LP5S3c4</t>
+  </si>
+  <si>
+    <t>LP5S3d2</t>
+  </si>
+  <si>
+    <t>LP5S3d1</t>
+  </si>
+  <si>
+    <t>LP5S3a2</t>
+  </si>
+  <si>
+    <t>LP5S3d3</t>
+  </si>
+  <si>
+    <t>LP5S3a3</t>
+  </si>
+  <si>
+    <t>LP5S3a4</t>
+  </si>
+  <si>
+    <t>LP5S3a5</t>
+  </si>
+  <si>
+    <t>LP5S3b1</t>
+  </si>
+  <si>
+    <t>LP5S3b2</t>
+  </si>
+  <si>
+    <t>LP5S3a1</t>
+  </si>
+  <si>
+    <t>LP5S3d4</t>
+  </si>
+  <si>
+    <t>LP5S3b4</t>
+  </si>
+  <si>
+    <t>LP5S3b3</t>
+  </si>
+  <si>
+    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
+  </si>
+  <si>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+  </si>
+  <si>
+    <t>LP7S3b1</t>
+  </si>
+  <si>
+    <t>LP7S3b2</t>
+  </si>
+  <si>
+    <t>LP7S3a4</t>
+  </si>
+  <si>
+    <t>LP7S3a2</t>
+  </si>
+  <si>
+    <t>LP7S3a3</t>
+  </si>
+  <si>
+    <t>LP7S3a1</t>
+  </si>
+  <si>
+    <t>LP7S3b4</t>
+  </si>
+  <si>
+    <t>LP7S3b3</t>
+  </si>
+  <si>
+    <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
+  </si>
+  <si>
+    <t>BSS.Shallow_FW:BSS.Shallow_FW:1038276</t>
+  </si>
+  <si>
+    <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
+  </si>
+  <si>
+    <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
+  </si>
+  <si>
     <t>Point number/name</t>
   </si>
   <si>
-    <t>Position X (m)</t>
-  </si>
-  <si>
-    <t>Position Y (m)</t>
-  </si>
-  <si>
-    <t>Position Z (m)</t>
-  </si>
-  <si>
-    <t>Wall Number</t>
+    <t>Position X (mm)</t>
+  </si>
+  <si>
+    <t>Position Y (mm)</t>
+  </si>
+  <si>
+    <t>Position Z (mm)</t>
   </si>
   <si>
     <t>Shape type</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Quadrant</t>
-  </si>
-  <si>
-    <t>Unnamed : 9</t>
-  </si>
-  <si>
-    <t>Width</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Orientation</t>
-  </si>
-  <si>
-    <t>Diameter</t>
-  </si>
-  <si>
-    <t>Tile</t>
-  </si>
-  <si>
-    <t>TMP1S2e1</t>
-  </si>
-  <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
-    <t>TMP1S2c2</t>
-  </si>
-  <si>
-    <t>TMP1S2c3</t>
-  </si>
-  <si>
-    <t>TMP1S2d1</t>
-  </si>
-  <si>
-    <t>TMP1S2d2</t>
-  </si>
-  <si>
-    <t>TMP1S2d3</t>
-  </si>
-  <si>
-    <t>TMP1S2b3</t>
-  </si>
-  <si>
-    <t>TMP1S2d4</t>
-  </si>
-  <si>
-    <t>TMP1S2e3</t>
-  </si>
-  <si>
-    <t>TMP1S2e4</t>
-  </si>
-  <si>
-    <t>TMP1S2f1</t>
-  </si>
-  <si>
-    <t>TMP1S2f2</t>
-  </si>
-  <si>
-    <t>TMP1S2f3</t>
-  </si>
-  <si>
-    <t>TMP1S2f4</t>
-  </si>
-  <si>
-    <t>TMP1S2e2</t>
-  </si>
-  <si>
-    <t>TMP1S2b2</t>
-  </si>
-  <si>
-    <t>TMP1S2c4</t>
-  </si>
-  <si>
-    <t>TMP1S2a4</t>
-  </si>
-  <si>
-    <t>TMP1S2b1</t>
-  </si>
-  <si>
-    <t>TMP1S2a1</t>
-  </si>
-  <si>
-    <t>TMP1S2a2</t>
-  </si>
-  <si>
-    <t>TMP1S2a3</t>
-  </si>
-  <si>
-    <t>TMP2S2a1</t>
-  </si>
-  <si>
-    <t>TMP2S2b2</t>
-  </si>
-  <si>
-    <t>TMP2S2b1</t>
-  </si>
-  <si>
-    <t>TMP2S2a2</t>
-  </si>
-  <si>
-    <t>TMP3S2a4</t>
-  </si>
-  <si>
-    <t>TMP3S2a3</t>
-  </si>
-  <si>
-    <t>TMP3S2a2</t>
-  </si>
-  <si>
-    <t>TMP3S2a1</t>
-  </si>
-  <si>
-    <t>TMP4S2a4</t>
-  </si>
-  <si>
-    <t>TMP4S2a1</t>
-  </si>
-  <si>
-    <t>TMP4S2a2</t>
-  </si>
-  <si>
-    <t>TMP4S2a3</t>
-  </si>
-  <si>
-    <t>TMP5S2a1</t>
-  </si>
-  <si>
-    <t>TMP5S2b3</t>
-  </si>
-  <si>
-    <t>TMP5S2b2</t>
-  </si>
-  <si>
-    <t>TMP5S2b1</t>
-  </si>
-  <si>
-    <t>TMP5S2a3</t>
-  </si>
-  <si>
-    <t>TMP5S2a2</t>
-  </si>
-  <si>
-    <t>TMP5S2b4</t>
-  </si>
-  <si>
-    <t>TMP6S2b4</t>
-  </si>
-  <si>
-    <t>TMP6S2b3</t>
-  </si>
-  <si>
-    <t>TMP6S2a2</t>
-  </si>
-  <si>
-    <t>TMP6S2a3</t>
-  </si>
-  <si>
-    <t>TMP6S2a4</t>
-  </si>
-  <si>
-    <t>TMP6S2b1</t>
-  </si>
-  <si>
-    <t>TMP6S2b2</t>
-  </si>
-  <si>
-    <t>TMP6S2a1</t>
-  </si>
-  <si>
-    <t>TMP7S2e1</t>
-  </si>
-  <si>
-    <t>TMP7S2a1</t>
-  </si>
-  <si>
-    <t>TMP7S2a2</t>
-  </si>
-  <si>
-    <t>TMP7S2a3</t>
-  </si>
-  <si>
-    <t>TMP7S2a4</t>
-  </si>
-  <si>
-    <t>TMP7S2a5</t>
-  </si>
-  <si>
-    <t>TMP7S2a6</t>
-  </si>
-  <si>
-    <t>TMP7S2e2</t>
-  </si>
-  <si>
-    <t>TMP7S2a7</t>
-  </si>
-  <si>
-    <t>TMP7S2b2</t>
-  </si>
-  <si>
-    <t>TMP7S2b3</t>
-  </si>
-  <si>
-    <t>TMP7S2b4</t>
-  </si>
-  <si>
-    <t>TMP7S2b5</t>
-  </si>
-  <si>
-    <t>TMP7S2b6</t>
-  </si>
-  <si>
-    <t>TMP7S2b7</t>
-  </si>
-  <si>
-    <t>TMP7S2c1</t>
-  </si>
-  <si>
-    <t>TMP7S2c2</t>
-  </si>
-  <si>
-    <t>TMP7S2d1</t>
-  </si>
-  <si>
-    <t>TMP7S2d2</t>
-  </si>
-  <si>
-    <t>TMP7S2b1</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>blank</t>
-  </si>
-  <si>
-    <t>Fitting</t>
-  </si>
-  <si>
-    <t>LP1S3a2</t>
-  </si>
-  <si>
-    <t>LP1S3a4</t>
-  </si>
-  <si>
-    <t>LP1S3a3</t>
-  </si>
-  <si>
-    <t>LP1S3a1</t>
-  </si>
-  <si>
-    <t>LP3S3a1</t>
-  </si>
-  <si>
-    <t>LP3S3a3</t>
-  </si>
-  <si>
-    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
-  </si>
-  <si>
-    <t>LP3S3a4</t>
-  </si>
-  <si>
-    <t>LP3S3a2</t>
-  </si>
-  <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
-  </si>
-  <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
-  </si>
-  <si>
-    <t>LP4S3a2</t>
-  </si>
-  <si>
-    <t>LP4S3a1</t>
-  </si>
-  <si>
-    <t>LP5S3d2</t>
-  </si>
-  <si>
-    <t>LP5S3d1</t>
-  </si>
-  <si>
-    <t>LP5S3c3</t>
-  </si>
-  <si>
-    <t>LP5S3b5</t>
-  </si>
-  <si>
-    <t>LP5S3c1</t>
-  </si>
-  <si>
-    <t>LP5S3c2</t>
-  </si>
-  <si>
-    <t>LP5S3c4</t>
-  </si>
-  <si>
-    <t>LP5S3d3</t>
-  </si>
-  <si>
-    <t>LP5S3a1</t>
-  </si>
-  <si>
-    <t>LP5S3a2</t>
-  </si>
-  <si>
-    <t>LP5S3a3</t>
-  </si>
-  <si>
-    <t>LP5S3a4</t>
-  </si>
-  <si>
-    <t>LP5S3a5</t>
-  </si>
-  <si>
-    <t>LP5S3b1</t>
-  </si>
-  <si>
-    <t>LP5S3b4</t>
-  </si>
-  <si>
-    <t>LP5S3d4</t>
-  </si>
-  <si>
-    <t>LP5S3b3</t>
-  </si>
-  <si>
-    <t>LP5S3b2</t>
-  </si>
-  <si>
-    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
-  </si>
-  <si>
-    <t>BSS.MONIC.BIB TAP.T-4L:BIB TAP:1090961</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1042747</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1035758</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1033022</t>
-  </si>
-  <si>
-    <t>BSS.Vesbo Tee Fiting:Standard:1032950</t>
-  </si>
-  <si>
-    <t>BSS.Bottle Trap:BSS.Bottle trap:1018126</t>
-  </si>
-  <si>
-    <t>BSS.GESSI,BM.49001:Default:1090988</t>
-  </si>
-  <si>
-    <t>LP7S3b2</t>
-  </si>
-  <si>
-    <t>LP7S3a1</t>
-  </si>
-  <si>
-    <t>LP7S3b4</t>
-  </si>
-  <si>
-    <t>LP7S3b3</t>
-  </si>
-  <si>
-    <t>LP7S3b1</t>
-  </si>
-  <si>
-    <t>LP7S3a2</t>
-  </si>
-  <si>
-    <t>LP7S3a3</t>
-  </si>
-  <si>
-    <t>LP7S3a4</t>
-  </si>
-  <si>
-    <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
-  </si>
-  <si>
-    <t>BSS.Shallow_FW:BSS.Shallow_FW:1038276</t>
-  </si>
-  <si>
-    <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
-  </si>
-  <si>
-    <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
-  </si>
-  <si>
-    <t>Position X (mm)</t>
-  </si>
-  <si>
-    <t>Position Y (mm)</t>
-  </si>
-  <si>
-    <t>Position Z (mm)</t>
   </si>
 </sst>
 </file>
@@ -823,15 +817,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
@@ -879,7 +864,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -891,10 +876,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-0.35</v>
+        <v>-1.35</v>
       </c>
       <c r="F2">
-        <v>-0.77500000000000002</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -909,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M2">
         <v>2.6549999999999998</v>
@@ -917,7 +902,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -929,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.49</v>
+        <v>-0.03</v>
       </c>
       <c r="F3">
-        <v>1.0249999999999999</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -947,7 +932,7 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M3">
         <v>2.6549999999999998</v>
@@ -955,7 +940,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -967,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F4">
-        <v>-0.77500000000000002</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -985,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M4">
         <v>2.6549999999999998</v>
@@ -993,7 +978,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -1005,10 +990,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F5">
-        <v>-0.17499999999999999</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1023,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M5">
         <v>2.6549999999999998</v>
@@ -1031,7 +1016,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1043,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F6">
-        <v>0.42499999999999999</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1061,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M6">
         <v>2.6549999999999998</v>
@@ -1069,7 +1054,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1081,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F7">
         <v>-0.77500000000000002</v>
@@ -1099,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M7">
         <v>2.6549999999999998</v>
@@ -1107,7 +1092,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1119,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F8">
         <v>-0.17499999999999999</v>
@@ -1137,7 +1122,7 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M8">
         <v>2.6549999999999998</v>
@@ -1145,7 +1130,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1157,10 +1142,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>-0.03</v>
+        <v>0.47</v>
       </c>
       <c r="F9">
-        <v>0.42499999999999999</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1175,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M9">
         <v>2.6549999999999998</v>
@@ -1183,7 +1168,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1195,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="F10">
         <v>0.42499999999999999</v>
@@ -1213,7 +1198,7 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M10">
         <v>2.6549999999999998</v>
@@ -1221,7 +1206,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1233,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F11">
-        <v>1.0249999999999999</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1251,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M11">
         <v>2.6549999999999998</v>
@@ -1259,7 +1244,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1271,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>-0.35</v>
+        <v>-1.35</v>
       </c>
       <c r="F12">
         <v>0.42499999999999999</v>
@@ -1289,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M12">
         <v>2.6549999999999998</v>
@@ -1297,7 +1282,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1309,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-0.35</v>
+        <v>-1.35</v>
       </c>
       <c r="F13">
         <v>1.0249999999999999</v>
@@ -1327,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="L13">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M13">
         <v>2.6549999999999998</v>
@@ -1335,7 +1320,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1347,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-1.35</v>
+        <v>-0.35</v>
       </c>
       <c r="F14">
-        <v>-0.77500000000000002</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1365,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="L14">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M14">
         <v>2.6549999999999998</v>
@@ -1373,7 +1358,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1385,10 +1370,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-1.35</v>
+        <v>0.47</v>
       </c>
       <c r="F15">
-        <v>-0.17499999999999999</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1403,7 +1388,7 @@
         <v>1</v>
       </c>
       <c r="L15">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M15">
         <v>2.6549999999999998</v>
@@ -1411,7 +1396,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1423,10 +1408,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-1.35</v>
+        <v>0.47</v>
       </c>
       <c r="F16">
-        <v>0.42499999999999999</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1441,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="L16">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M16">
         <v>2.6549999999999998</v>
@@ -1449,7 +1434,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1461,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>-1.35</v>
+        <v>0.49</v>
       </c>
       <c r="F17">
         <v>1.0249999999999999</v>
@@ -1479,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M17">
         <v>2.6549999999999998</v>
@@ -1487,7 +1472,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1499,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-0.35</v>
+        <v>0.49</v>
       </c>
       <c r="F18">
-        <v>-0.17499999999999999</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1517,7 +1502,7 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M18">
         <v>2.6549999999999998</v>
@@ -1525,7 +1510,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1555,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="L19">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M19">
         <v>2.6549999999999998</v>
@@ -1563,7 +1548,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1575,10 +1560,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F20">
-        <v>1.0249999999999999</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1593,7 +1578,7 @@
         <v>1</v>
       </c>
       <c r="L20">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M20">
         <v>2.6549999999999998</v>
@@ -1601,7 +1586,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1631,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="L21">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M21">
         <v>2.6549999999999998</v>
@@ -1639,7 +1624,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1651,10 +1636,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.49</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F22">
-        <v>-0.77500000000000002</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1669,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M22">
         <v>2.6549999999999998</v>
@@ -1692,7 +1677,7 @@
         <v>0.93500000000000005</v>
       </c>
       <c r="F23">
-        <v>-0.77500000000000002</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1707,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M23">
         <v>2.6549999999999998</v>
@@ -1715,7 +1700,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1730,7 +1715,7 @@
         <v>0.93500000000000005</v>
       </c>
       <c r="F24">
-        <v>-0.17499999999999999</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1745,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M24">
         <v>2.6549999999999998</v>
@@ -1753,7 +1738,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1765,10 +1750,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0.93500000000000005</v>
+        <v>0.47</v>
       </c>
       <c r="F25">
-        <v>0.42499999999999999</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1783,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="L25">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M25">
         <v>2.6549999999999998</v>
@@ -1791,7 +1776,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1803,10 +1788,10 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="F26">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1821,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="M26">
         <v>2.6549999999999998</v>
@@ -1829,7 +1814,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1841,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="F27">
         <v>-0.15</v>
@@ -1859,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="M27">
         <v>2.6549999999999998</v>
@@ -1867,7 +1852,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1879,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="F28">
         <v>-0.75</v>
@@ -1897,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="L28">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="M28">
         <v>2.6549999999999998</v>
@@ -1917,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="F29">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1935,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="M29">
         <v>2.6549999999999998</v>
@@ -1943,7 +1928,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1958,7 +1943,7 @@
         <v>-0.93500000000000005</v>
       </c>
       <c r="F30">
-        <v>1.0249999999999999</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -1981,7 +1966,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1996,7 +1981,7 @@
         <v>-0.93500000000000005</v>
       </c>
       <c r="F31">
-        <v>0.42499999999999999</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -2019,7 +2004,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -2057,7 +2042,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -2072,7 +2057,7 @@
         <v>-0.93500000000000005</v>
       </c>
       <c r="F33">
-        <v>-0.77500000000000002</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -2095,7 +2080,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -2125,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>0.59199999999999997</v>
+        <v>0.6</v>
       </c>
       <c r="M34">
         <v>2.6549999999999998</v>
@@ -2133,7 +2118,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2148,7 +2133,7 @@
         <v>0.3</v>
       </c>
       <c r="F35">
-        <v>-0.77500000000000002</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G35">
         <v>4</v>
@@ -2163,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>0.59199999999999997</v>
+        <v>0.6</v>
       </c>
       <c r="M35">
         <v>2.6549999999999998</v>
@@ -2171,7 +2156,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2201,7 +2186,7 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <v>0.59199999999999997</v>
+        <v>0.6</v>
       </c>
       <c r="M36">
         <v>2.6549999999999998</v>
@@ -2209,7 +2194,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2224,7 +2209,7 @@
         <v>0.3</v>
       </c>
       <c r="F37">
-        <v>0.42499999999999999</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -2239,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>0.59199999999999997</v>
+        <v>0.6</v>
       </c>
       <c r="M37">
         <v>2.6549999999999998</v>
@@ -2247,7 +2232,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2259,10 +2244,10 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.93</v>
+        <v>1.155</v>
       </c>
       <c r="F38">
-        <v>-0.77500000000000002</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -2277,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="L38">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M38">
         <v>2.6549999999999998</v>
@@ -2285,7 +2270,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2300,7 +2285,7 @@
         <v>1.155</v>
       </c>
       <c r="F39">
-        <v>0.42499999999999999</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -2315,7 +2300,7 @@
         <v>1</v>
       </c>
       <c r="L39">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M39">
         <v>2.6549999999999998</v>
@@ -2323,7 +2308,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2353,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="L40">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M40">
         <v>2.6549999999999998</v>
@@ -2361,7 +2346,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2373,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>1.155</v>
+        <v>0.03</v>
       </c>
       <c r="F41">
         <v>-0.77500000000000002</v>
@@ -2391,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="L41">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M41">
         <v>2.6549999999999998</v>
@@ -2399,7 +2384,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2411,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0.03</v>
+        <v>0.48</v>
       </c>
       <c r="F42">
         <v>-0.77500000000000002</v>
@@ -2429,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="L42">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M42">
         <v>2.6549999999999998</v>
@@ -2437,7 +2422,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2449,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0.48</v>
+        <v>0.93</v>
       </c>
       <c r="F43">
         <v>-0.77500000000000002</v>
@@ -2467,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="L43">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M43">
         <v>2.6549999999999998</v>
@@ -2475,7 +2460,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2490,7 +2475,7 @@
         <v>1.155</v>
       </c>
       <c r="F44">
-        <v>1.0249999999999999</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G44">
         <v>5</v>
@@ -2505,7 +2490,7 @@
         <v>1</v>
       </c>
       <c r="L44">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M44">
         <v>2.6549999999999998</v>
@@ -2513,7 +2498,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2543,7 +2528,7 @@
         <v>1</v>
       </c>
       <c r="L45">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M45">
         <v>2.6549999999999998</v>
@@ -2551,7 +2536,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2581,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="L46">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M46">
         <v>2.6549999999999998</v>
@@ -2589,7 +2574,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2601,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F47">
         <v>-0.17499999999999999</v>
@@ -2619,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="L47">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M47">
         <v>2.6549999999999998</v>
@@ -2627,7 +2612,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2639,10 +2624,10 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F48">
-        <v>0.42499999999999999</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -2657,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="L48">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M48">
         <v>2.6549999999999998</v>
@@ -2665,7 +2650,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2695,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="L49">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M49">
         <v>2.6549999999999998</v>
@@ -2703,7 +2688,7 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2715,10 +2700,10 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F50">
-        <v>-0.77500000000000002</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G50">
         <v>6</v>
@@ -2733,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="L50">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M50">
         <v>2.6549999999999998</v>
@@ -2741,7 +2726,7 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2753,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F51">
-        <v>-0.17499999999999999</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G51">
         <v>6</v>
@@ -2771,7 +2756,7 @@
         <v>1</v>
       </c>
       <c r="L51">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M51">
         <v>2.6549999999999998</v>
@@ -2779,7 +2764,7 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2794,7 +2779,7 @@
         <v>0.3</v>
       </c>
       <c r="F52">
-        <v>-0.77500000000000002</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G52">
         <v>6</v>
@@ -2809,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="L52">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M52">
         <v>2.6549999999999998</v>
@@ -2817,7 +2802,7 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2826,13 +2811,13 @@
         <v>66</v>
       </c>
       <c r="D53">
-        <v>2.61</v>
+        <v>0.12</v>
       </c>
       <c r="E53">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G53" t="s">
         <v>86</v>
@@ -2847,15 +2832,15 @@
         <v>1</v>
       </c>
       <c r="L53">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M53">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2864,13 +2849,13 @@
         <v>67</v>
       </c>
       <c r="D54">
-        <v>0.12</v>
+        <v>2.61</v>
       </c>
       <c r="E54">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G54" t="s">
         <v>86</v>
@@ -2885,15 +2870,15 @@
         <v>1</v>
       </c>
       <c r="L54">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M54">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2905,10 +2890,10 @@
         <v>0.12</v>
       </c>
       <c r="E55">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G55" t="s">
         <v>86</v>
@@ -2923,15 +2908,15 @@
         <v>1</v>
       </c>
       <c r="L55">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M55">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2943,10 +2928,10 @@
         <v>0.12</v>
       </c>
       <c r="E56">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G56" t="s">
         <v>86</v>
@@ -2961,15 +2946,15 @@
         <v>1</v>
       </c>
       <c r="L56">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M56">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2981,10 +2966,10 @@
         <v>0.12</v>
       </c>
       <c r="E57">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G57" t="s">
         <v>86</v>
@@ -2999,15 +2984,15 @@
         <v>1</v>
       </c>
       <c r="L57">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M57">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -3019,10 +3004,10 @@
         <v>0.12</v>
       </c>
       <c r="E58">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G58" t="s">
         <v>86</v>
@@ -3037,15 +3022,15 @@
         <v>1</v>
       </c>
       <c r="L58">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M58">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -3060,7 +3045,7 @@
         <v>0.9</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G59" t="s">
         <v>86</v>
@@ -3075,15 +3060,15 @@
         <v>1</v>
       </c>
       <c r="L59">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M59">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -3092,13 +3077,13 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>2.61</v>
+        <v>0.12</v>
       </c>
       <c r="E60">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G60" t="s">
         <v>86</v>
@@ -3113,10 +3098,10 @@
         <v>1</v>
       </c>
       <c r="L60">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M60">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -3130,13 +3115,13 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="E61">
-        <v>1.05</v>
+        <v>0.15</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G61" t="s">
         <v>86</v>
@@ -3151,15 +3136,15 @@
         <v>1</v>
       </c>
       <c r="L61">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M61">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3174,7 +3159,7 @@
         <v>0.3</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G62" t="s">
         <v>86</v>
@@ -3189,15 +3174,15 @@
         <v>1</v>
       </c>
       <c r="L62">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M62">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3212,7 +3197,7 @@
         <v>0.45</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G63" t="s">
         <v>86</v>
@@ -3227,15 +3212,15 @@
         <v>1</v>
       </c>
       <c r="L63">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M63">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3250,7 +3235,7 @@
         <v>0.6</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G64" t="s">
         <v>86</v>
@@ -3265,15 +3250,15 @@
         <v>1</v>
       </c>
       <c r="L64">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M64">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3288,7 +3273,7 @@
         <v>0.75</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G65" t="s">
         <v>86</v>
@@ -3303,15 +3288,15 @@
         <v>1</v>
       </c>
       <c r="L65">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M65">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3326,7 +3311,7 @@
         <v>0.9</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G66" t="s">
         <v>86</v>
@@ -3341,15 +3326,15 @@
         <v>1</v>
       </c>
       <c r="L66">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M66">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
@@ -3364,7 +3349,7 @@
         <v>1.05</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G67" t="s">
         <v>86</v>
@@ -3379,15 +3364,15 @@
         <v>1</v>
       </c>
       <c r="L67">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M67">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3402,7 +3387,7 @@
         <v>0.6</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G68" t="s">
         <v>86</v>
@@ -3417,15 +3402,15 @@
         <v>1</v>
       </c>
       <c r="L68">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M68">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
@@ -3440,7 +3425,7 @@
         <v>1.2</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G69" t="s">
         <v>86</v>
@@ -3455,15 +3440,15 @@
         <v>1</v>
       </c>
       <c r="L69">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M69">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
@@ -3478,7 +3463,7 @@
         <v>0.6</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G70" t="s">
         <v>86</v>
@@ -3493,15 +3478,15 @@
         <v>1</v>
       </c>
       <c r="L70">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M70">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -3516,7 +3501,7 @@
         <v>1.2</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G71" t="s">
         <v>86</v>
@@ -3531,15 +3516,15 @@
         <v>1</v>
       </c>
       <c r="L71">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M71">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -3548,13 +3533,13 @@
         <v>85</v>
       </c>
       <c r="D72">
-        <v>0.72</v>
+        <v>2.61</v>
       </c>
       <c r="E72">
-        <v>0.15</v>
+        <v>1.2</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G72" t="s">
         <v>86</v>
@@ -3569,10 +3554,10 @@
         <v>1</v>
       </c>
       <c r="L72">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M72">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -3582,8 +3567,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
@@ -3643,10 +3634,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>-0.255</v>
+        <v>0.375</v>
       </c>
       <c r="F2">
-        <v>0.21299999999999999</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -3661,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M2">
         <v>2.6549999999999998</v>
@@ -3669,7 +3660,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -3681,10 +3672,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>-0.255</v>
+        <v>0.375</v>
       </c>
       <c r="F3">
-        <v>0.13700000000000001</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -3699,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M3">
         <v>2.6549999999999998</v>
@@ -3719,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.375</v>
+        <v>-0.255</v>
       </c>
       <c r="F4">
         <v>0.13700000000000001</v>
@@ -3737,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M4">
         <v>2.6549999999999998</v>
@@ -3757,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.375</v>
+        <v>-0.255</v>
       </c>
       <c r="F5">
         <v>0.21299999999999999</v>
@@ -3775,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M5">
         <v>2.6549999999999998</v>
@@ -3783,7 +3774,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B6" t="s">
         <v>88</v>
@@ -3821,7 +3812,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B7" t="s">
         <v>88</v>
@@ -3833,10 +3824,10 @@
         <v>0.6</v>
       </c>
       <c r="E7">
-        <v>-1.012</v>
+        <v>-0.81200000000000006</v>
       </c>
       <c r="F7">
-        <v>-0.188</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -3859,7 +3850,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>90</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
         <v>88</v>
@@ -3871,10 +3862,10 @@
         <v>0.6</v>
       </c>
       <c r="E8">
-        <v>-0.72499999999999998</v>
+        <v>-1.012</v>
       </c>
       <c r="F8">
-        <v>-0.05</v>
+        <v>-0.188</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -3897,7 +3888,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B9" t="s">
         <v>88</v>
@@ -3935,7 +3926,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B10" t="s">
         <v>88</v>
@@ -3947,10 +3938,10 @@
         <v>0.6</v>
       </c>
       <c r="E10">
-        <v>-0.81200000000000006</v>
+        <v>-0.79500000000000004</v>
       </c>
       <c r="F10">
-        <v>0.96199999999999997</v>
+        <v>-1.4E-2</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -3973,7 +3964,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="B11" t="s">
         <v>88</v>
@@ -3982,16 +3973,16 @@
         <v>98</v>
       </c>
       <c r="D11">
-        <v>0.93700000000000006</v>
+        <v>0.6</v>
       </c>
       <c r="E11">
-        <v>0.84299999999999997</v>
+        <v>-0.65500000000000003</v>
       </c>
       <c r="F11">
-        <v>-0.8</v>
+        <v>-1.4E-2</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <v>6</v>
@@ -4003,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>0.59199999999999997</v>
+        <v>0.96</v>
       </c>
       <c r="M11">
         <v>2.6549999999999998</v>
@@ -4011,7 +4002,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>89</v>
+        <v>238</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
@@ -4020,16 +4011,16 @@
         <v>99</v>
       </c>
       <c r="D12">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="E12">
-        <v>0.39900000000000002</v>
+        <v>-0.79500000000000004</v>
       </c>
       <c r="F12">
-        <v>1.468</v>
+        <v>-8.5999999999999993E-2</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>6</v>
@@ -4041,7 +4032,7 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <v>0.59199999999999997</v>
+        <v>0.96</v>
       </c>
       <c r="M12">
         <v>2.6549999999999998</v>
@@ -4049,7 +4040,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B13" t="s">
         <v>88</v>
@@ -4058,28 +4049,28 @@
         <v>100</v>
       </c>
       <c r="D13">
+        <v>0.6</v>
+      </c>
+      <c r="E13">
+        <v>-0.65500000000000003</v>
+      </c>
+      <c r="F13">
+        <v>-8.5999999999999993E-2</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="L13">
         <v>0.96</v>
-      </c>
-      <c r="E13">
-        <v>0.45500000000000002</v>
-      </c>
-      <c r="F13">
-        <v>-0.375</v>
-      </c>
-      <c r="G13">
-        <v>4</v>
-      </c>
-      <c r="H13">
-        <v>6</v>
-      </c>
-      <c r="I13" t="s">
-        <v>87</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>0.59199999999999997</v>
       </c>
       <c r="M13">
         <v>2.6549999999999998</v>
@@ -4087,7 +4078,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
@@ -4117,7 +4108,7 @@
         <v>1</v>
       </c>
       <c r="L14">
-        <v>0.59199999999999997</v>
+        <v>0.6</v>
       </c>
       <c r="M14">
         <v>2.6549999999999998</v>
@@ -4125,7 +4116,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="B15" t="s">
         <v>88</v>
@@ -4134,16 +4125,16 @@
         <v>102</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E15">
-        <v>1.38</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="F15">
-        <v>-0.15</v>
+        <v>-0.375</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -4155,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="L15">
-        <v>1.94</v>
+        <v>0.6</v>
       </c>
       <c r="M15">
         <v>2.6549999999999998</v>
@@ -4163,7 +4154,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>253</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
         <v>88</v>
@@ -4172,16 +4163,16 @@
         <v>103</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>0.93700000000000006</v>
       </c>
       <c r="E16">
-        <v>0.48</v>
+        <v>0.84299999999999997</v>
       </c>
       <c r="F16">
-        <v>-0.15</v>
+        <v>-0.8</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16">
         <v>6</v>
@@ -4193,7 +4184,7 @@
         <v>1</v>
       </c>
       <c r="L16">
-        <v>1.94</v>
+        <v>0.6</v>
       </c>
       <c r="M16">
         <v>2.6549999999999998</v>
@@ -4201,7 +4192,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>251</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
         <v>88</v>
@@ -4210,16 +4201,16 @@
         <v>104</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="E17">
-        <v>-0.42</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="F17">
-        <v>1.4</v>
+        <v>1.468</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17">
         <v>6</v>
@@ -4231,7 +4222,7 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>1.94</v>
+        <v>0.6</v>
       </c>
       <c r="M17">
         <v>2.6549999999999998</v>
@@ -4239,7 +4230,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B18" t="s">
         <v>88</v>
@@ -4269,7 +4260,7 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M18">
         <v>2.6549999999999998</v>
@@ -4277,7 +4268,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B19" t="s">
         <v>88</v>
@@ -4289,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-0.42</v>
+        <v>1.38</v>
       </c>
       <c r="F19">
         <v>1.4</v>
@@ -4307,7 +4298,7 @@
         <v>1</v>
       </c>
       <c r="L19">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M19">
         <v>2.6549999999999998</v>
@@ -4315,7 +4306,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B20" t="s">
         <v>88</v>
@@ -4327,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>1.38</v>
+        <v>-0.42</v>
       </c>
       <c r="F20">
         <v>1.4</v>
@@ -4345,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="L20">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M20">
         <v>2.6549999999999998</v>
@@ -4365,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>1.38</v>
+        <v>-0.42</v>
       </c>
       <c r="F21">
         <v>1.4</v>
@@ -4383,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="L21">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M21">
         <v>2.6549999999999998</v>
@@ -4403,10 +4394,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.48</v>
+        <v>1.38</v>
       </c>
       <c r="F22">
-        <v>-0.75</v>
+        <v>1.4</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -4421,7 +4412,7 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M22">
         <v>2.6549999999999998</v>
@@ -4429,7 +4420,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s">
         <v>88</v>
@@ -4438,13 +4429,13 @@
         <v>110</v>
       </c>
       <c r="D23">
-        <v>8.7999999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>-0.22500000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="F23">
-        <v>2.5999999999999999E-2</v>
+        <v>-0.15</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -4459,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M23">
         <v>2.6549999999999998</v>
@@ -4467,7 +4458,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s">
         <v>88</v>
@@ -4476,13 +4467,13 @@
         <v>111</v>
       </c>
       <c r="D24">
-        <v>8.7999999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0.27500000000000002</v>
+        <v>-0.42</v>
       </c>
       <c r="F24">
-        <v>2.5999999999999999E-2</v>
+        <v>-0.15</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -4497,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M24">
         <v>2.6549999999999998</v>
@@ -4505,7 +4496,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s">
         <v>88</v>
@@ -4517,10 +4508,10 @@
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="E25">
-        <v>-0.22500000000000001</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="F25">
-        <v>-0.46600000000000003</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -4535,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="L25">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M25">
         <v>2.6549999999999998</v>
@@ -4543,7 +4534,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s">
         <v>88</v>
@@ -4552,13 +4543,13 @@
         <v>113</v>
       </c>
       <c r="D26">
-        <v>8.7999999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>0.27500000000000002</v>
+        <v>-0.42</v>
       </c>
       <c r="F26">
-        <v>-0.46600000000000003</v>
+        <v>-0.75</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -4573,7 +4564,7 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M26">
         <v>2.6549999999999998</v>
@@ -4581,7 +4572,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s">
         <v>88</v>
@@ -4593,10 +4584,10 @@
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="E27">
-        <v>2.5000000000000001E-2</v>
+        <v>-0.22500000000000001</v>
       </c>
       <c r="F27">
-        <v>-0.22</v>
+        <v>-0.46600000000000003</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -4611,7 +4602,7 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M27">
         <v>2.6549999999999998</v>
@@ -4619,7 +4610,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s">
         <v>88</v>
@@ -4628,13 +4619,13 @@
         <v>115</v>
       </c>
       <c r="D28">
-        <v>0.183</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E28">
-        <v>-0.15</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="F28">
-        <v>-0.40200000000000002</v>
+        <v>-0.46600000000000003</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -4649,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="L28">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M28">
         <v>2.6549999999999998</v>
@@ -4657,7 +4648,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s">
         <v>88</v>
@@ -4666,13 +4657,13 @@
         <v>116</v>
       </c>
       <c r="D29">
-        <v>0.183</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E29">
-        <v>0.21</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F29">
-        <v>-0.83</v>
+        <v>-0.22</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -4687,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M29">
         <v>2.6549999999999998</v>
@@ -4695,7 +4686,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s">
         <v>88</v>
@@ -4704,13 +4695,13 @@
         <v>117</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="E30">
-        <v>1.38</v>
+        <v>-0.15</v>
       </c>
       <c r="F30">
-        <v>-0.75</v>
+        <v>-0.40200000000000002</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -4725,7 +4716,7 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M30">
         <v>2.6549999999999998</v>
@@ -4733,7 +4724,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s">
         <v>88</v>
@@ -4745,10 +4736,10 @@
         <v>0.183</v>
       </c>
       <c r="E31">
-        <v>-0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F31">
-        <v>-0.83</v>
+        <v>-0.40200000000000002</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -4763,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M31">
         <v>2.6549999999999998</v>
@@ -4771,7 +4762,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B32" t="s">
         <v>88</v>
@@ -4780,13 +4771,13 @@
         <v>119</v>
       </c>
       <c r="D32">
-        <v>0.183</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E32">
-        <v>0.21</v>
+        <v>-0.22500000000000001</v>
       </c>
       <c r="F32">
-        <v>-0.40200000000000002</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -4801,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M32">
         <v>2.6549999999999998</v>
@@ -4809,7 +4800,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>156</v>
+        <v>259</v>
       </c>
       <c r="B33" t="s">
         <v>88</v>
@@ -4818,13 +4809,13 @@
         <v>120</v>
       </c>
       <c r="D33">
-        <v>0.20799999999999999</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>-9.5000000000000001E-2</v>
+        <v>1.38</v>
       </c>
       <c r="F33">
-        <v>-1.024</v>
+        <v>-0.75</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -4839,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M33">
         <v>2.6549999999999998</v>
@@ -4847,7 +4838,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>154</v>
+        <v>250</v>
       </c>
       <c r="B34" t="s">
         <v>88</v>
@@ -4856,13 +4847,13 @@
         <v>121</v>
       </c>
       <c r="D34">
-        <v>0.108</v>
+        <v>0.183</v>
       </c>
       <c r="E34">
-        <v>0.03</v>
+        <v>0.21</v>
       </c>
       <c r="F34">
-        <v>-0.17499999999999999</v>
+        <v>-0.83</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -4877,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M34">
         <v>2.6549999999999998</v>
@@ -4885,7 +4876,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>151</v>
+        <v>249</v>
       </c>
       <c r="B35" t="s">
         <v>88</v>
@@ -4894,13 +4885,13 @@
         <v>122</v>
       </c>
       <c r="D35">
-        <v>0.22</v>
+        <v>0.183</v>
       </c>
       <c r="E35">
-        <v>-0.32</v>
+        <v>-0.15</v>
       </c>
       <c r="F35">
-        <v>-0.72499999999999998</v>
+        <v>-0.83</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -4915,7 +4906,7 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M35">
         <v>2.6549999999999998</v>
@@ -4923,7 +4914,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="B36" t="s">
         <v>88</v>
@@ -4932,13 +4923,13 @@
         <v>123</v>
       </c>
       <c r="D36">
-        <v>1.365</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="E36">
-        <v>1.28</v>
+        <v>-9.5000000000000001E-2</v>
       </c>
       <c r="F36">
-        <v>-0.79</v>
+        <v>-1.024</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -4953,7 +4944,7 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M36">
         <v>2.6549999999999998</v>
@@ -4961,7 +4952,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="B37" t="s">
         <v>88</v>
@@ -4970,13 +4961,13 @@
         <v>124</v>
       </c>
       <c r="D37">
-        <v>-3.6999999999999998E-2</v>
+        <v>0.108</v>
       </c>
       <c r="E37">
-        <v>-0.32</v>
+        <v>0.03</v>
       </c>
       <c r="F37">
-        <v>-0.36499999999999999</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -4991,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="M37">
         <v>2.6549999999999998</v>
@@ -4999,7 +4990,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>57</v>
+        <v>272</v>
       </c>
       <c r="B38" t="s">
         <v>88</v>
@@ -5008,16 +4999,16 @@
         <v>125</v>
       </c>
       <c r="D38">
-        <v>0.09</v>
+        <v>0.96</v>
       </c>
       <c r="E38">
-        <v>1.0049999999999999</v>
+        <v>1.585</v>
       </c>
       <c r="F38">
-        <v>-0.82499999999999996</v>
-      </c>
-      <c r="G38">
-        <v>5</v>
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="G38" t="s">
+        <v>86</v>
       </c>
       <c r="H38">
         <v>6</v>
@@ -5029,15 +5020,15 @@
         <v>1</v>
       </c>
       <c r="L38">
-        <v>1.94</v>
+        <v>2.76</v>
       </c>
       <c r="M38">
-        <v>2.6549999999999998</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>55</v>
+        <v>273</v>
       </c>
       <c r="B39" t="s">
         <v>88</v>
@@ -5046,16 +5037,16 @@
         <v>126</v>
       </c>
       <c r="D39">
-        <v>0.15</v>
+        <v>1.06</v>
       </c>
       <c r="E39">
-        <v>0.85499999999999998</v>
+        <v>1.585</v>
       </c>
       <c r="F39">
-        <v>-0.9</v>
-      </c>
-      <c r="G39">
-        <v>5</v>
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="G39" t="s">
+        <v>86</v>
       </c>
       <c r="H39">
         <v>6</v>
@@ -5067,15 +5058,15 @@
         <v>1</v>
       </c>
       <c r="L39">
-        <v>1.94</v>
+        <v>2.76</v>
       </c>
       <c r="M39">
-        <v>2.6549999999999998</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="B40" t="s">
         <v>88</v>
@@ -5084,16 +5075,16 @@
         <v>127</v>
       </c>
       <c r="D40">
-        <v>0.29499999999999998</v>
+        <v>0.72</v>
       </c>
       <c r="E40">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>-0.45300000000000001</v>
-      </c>
-      <c r="G40">
-        <v>5</v>
+        <v>-0.05</v>
+      </c>
+      <c r="G40" t="s">
+        <v>86</v>
       </c>
       <c r="H40">
         <v>6</v>
@@ -5105,15 +5096,15 @@
         <v>1</v>
       </c>
       <c r="L40">
-        <v>1.94</v>
+        <v>2.76</v>
       </c>
       <c r="M40">
-        <v>2.6549999999999998</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>152</v>
+        <v>261</v>
       </c>
       <c r="B41" t="s">
         <v>88</v>
@@ -5122,16 +5113,16 @@
         <v>128</v>
       </c>
       <c r="D41">
-        <v>0.06</v>
+        <v>0.72</v>
       </c>
       <c r="E41">
-        <v>0.93</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F41">
-        <v>-0.17499999999999999</v>
-      </c>
-      <c r="G41">
-        <v>5</v>
+        <v>-0.05</v>
+      </c>
+      <c r="G41" t="s">
+        <v>86</v>
       </c>
       <c r="H41">
         <v>6</v>
@@ -5143,10 +5134,10 @@
         <v>1</v>
       </c>
       <c r="L41">
-        <v>1.94</v>
+        <v>2.76</v>
       </c>
       <c r="M41">
-        <v>2.6549999999999998</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -5160,13 +5151,13 @@
         <v>129</v>
       </c>
       <c r="D42">
-        <v>1.06</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E42">
-        <v>1.5349999999999999</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G42" t="s">
         <v>86</v>
@@ -5181,15 +5172,15 @@
         <v>1</v>
       </c>
       <c r="L42">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M42">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B43" t="s">
         <v>88</v>
@@ -5201,10 +5192,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="E43">
-        <v>1.075</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G43" t="s">
         <v>86</v>
@@ -5219,15 +5210,15 @@
         <v>1</v>
       </c>
       <c r="L43">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M43">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B44" t="s">
         <v>88</v>
@@ -5239,10 +5230,10 @@
         <v>1.06</v>
       </c>
       <c r="E44">
-        <v>1.5349999999999999</v>
+        <v>1.4850000000000001</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G44" t="s">
         <v>86</v>
@@ -5257,15 +5248,15 @@
         <v>1</v>
       </c>
       <c r="L44">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M44">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B45" t="s">
         <v>88</v>
@@ -5277,10 +5268,10 @@
         <v>0.96</v>
       </c>
       <c r="E45">
-        <v>1.5349999999999999</v>
+        <v>1.4850000000000001</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G45" t="s">
         <v>86</v>
@@ -5295,15 +5286,15 @@
         <v>1</v>
       </c>
       <c r="L45">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M45">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="B46" t="s">
         <v>88</v>
@@ -5312,13 +5303,13 @@
         <v>133</v>
       </c>
       <c r="D46">
-        <v>0.96</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="E46">
-        <v>1.5349999999999999</v>
+        <v>1.1120000000000001</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>-7.6999999999999999E-2</v>
       </c>
       <c r="G46" t="s">
         <v>86</v>
@@ -5333,15 +5324,15 @@
         <v>1</v>
       </c>
       <c r="L46">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M46">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>258</v>
+        <v>1</v>
       </c>
       <c r="B47" t="s">
         <v>88</v>
@@ -5350,13 +5341,13 @@
         <v>134</v>
       </c>
       <c r="D47">
-        <v>0.72</v>
+        <v>1.01</v>
       </c>
       <c r="E47">
-        <v>1.075</v>
+        <v>1.5349999999999999</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>-7.6999999999999999E-2</v>
       </c>
       <c r="G47" t="s">
         <v>86</v>
@@ -5371,15 +5362,15 @@
         <v>1</v>
       </c>
       <c r="L47">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M47">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>259</v>
+        <v>154</v>
       </c>
       <c r="B48" t="s">
         <v>88</v>
@@ -5388,13 +5379,13 @@
         <v>135</v>
       </c>
       <c r="D48">
-        <v>0.56999999999999995</v>
+        <v>1.01</v>
       </c>
       <c r="E48">
-        <v>1.075</v>
+        <v>1.5349999999999999</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G48" t="s">
         <v>86</v>
@@ -5409,15 +5400,15 @@
         <v>1</v>
       </c>
       <c r="L48">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M48">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>268</v>
+        <v>156</v>
       </c>
       <c r="B49" t="s">
         <v>88</v>
@@ -5426,13 +5417,13 @@
         <v>136</v>
       </c>
       <c r="D49">
-        <v>0.72</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="E49">
         <v>1.075</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G49" t="s">
         <v>86</v>
@@ -5447,162 +5438,10 @@
         <v>1</v>
       </c>
       <c r="L49">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M49">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>0</v>
-      </c>
-      <c r="B50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" t="s">
-        <v>137</v>
-      </c>
-      <c r="D50">
-        <v>0.64500000000000002</v>
-      </c>
-      <c r="E50">
-        <v>1.1120000000000001</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="G50" t="s">
-        <v>86</v>
-      </c>
-      <c r="H50">
-        <v>6</v>
-      </c>
-      <c r="I50" t="s">
-        <v>87</v>
-      </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
-      <c r="L50">
-        <v>2.9</v>
-      </c>
-      <c r="M50">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>1</v>
-      </c>
-      <c r="B51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" t="s">
-        <v>138</v>
-      </c>
-      <c r="D51">
-        <v>1.01</v>
-      </c>
-      <c r="E51">
-        <v>1.5349999999999999</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51" t="s">
-        <v>86</v>
-      </c>
-      <c r="H51">
-        <v>6</v>
-      </c>
-      <c r="I51" t="s">
-        <v>87</v>
-      </c>
-      <c r="J51">
-        <v>1</v>
-      </c>
-      <c r="L51">
-        <v>2.9</v>
-      </c>
-      <c r="M51">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>155</v>
-      </c>
-      <c r="B52" t="s">
-        <v>88</v>
-      </c>
-      <c r="C52" t="s">
-        <v>139</v>
-      </c>
-      <c r="D52">
-        <v>1.01</v>
-      </c>
-      <c r="E52">
-        <v>1.5349999999999999</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52" t="s">
-        <v>86</v>
-      </c>
-      <c r="H52">
-        <v>6</v>
-      </c>
-      <c r="I52" t="s">
-        <v>87</v>
-      </c>
-      <c r="J52">
-        <v>1</v>
-      </c>
-      <c r="L52">
-        <v>2.9</v>
-      </c>
-      <c r="M52">
-        <v>1.9319999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>157</v>
-      </c>
-      <c r="B53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" t="s">
-        <v>140</v>
-      </c>
-      <c r="D53">
-        <v>0.64500000000000002</v>
-      </c>
-      <c r="E53">
-        <v>1.075</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53" t="s">
-        <v>86</v>
-      </c>
-      <c r="H53">
-        <v>6</v>
-      </c>
-      <c r="I53" t="s">
-        <v>87</v>
-      </c>
-      <c r="J53">
-        <v>1</v>
-      </c>
-      <c r="L53">
-        <v>2.9</v>
-      </c>
-      <c r="M53">
-        <v>1.9319999999999999</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -5620,22 +5459,22 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>141</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0C6E3D-F991-41C6-95E3-CF439203FCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="315" windowWidth="23235" windowHeight="15465" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
     <sheet name="Stage 3" sheetId="2" r:id="rId2"/>
     <sheet name="Obstacles" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="144">
   <si>
     <t>Marking type</t>
   </si>
@@ -72,31 +66,67 @@
     <t>TMP1S2f2</t>
   </si>
   <si>
+    <t>TMP1S2f1</t>
+  </si>
+  <si>
+    <t>TMP1S2e4</t>
+  </si>
+  <si>
+    <t>TMP1S2e3</t>
+  </si>
+  <si>
+    <t>TMP1S2e2</t>
+  </si>
+  <si>
+    <t>TMP1S2e1</t>
+  </si>
+  <si>
+    <t>TMP1S2d4</t>
+  </si>
+  <si>
+    <t>TMP1S2d3</t>
+  </si>
+  <si>
+    <t>TMP1S2d2</t>
+  </si>
+  <si>
     <t>TMP1S2d1</t>
   </si>
   <si>
-    <t>TMP1S2d2</t>
-  </si>
-  <si>
-    <t>TMP1S2d3</t>
-  </si>
-  <si>
-    <t>TMP1S2d4</t>
-  </si>
-  <si>
-    <t>TMP1S2e1</t>
-  </si>
-  <si>
-    <t>TMP1S2e2</t>
-  </si>
-  <si>
     <t>TMP1S2c4</t>
   </si>
   <si>
-    <t>TMP1S2e3</t>
-  </si>
-  <si>
-    <t>TMP1S2f1</t>
+    <t>TMP1S2c3</t>
+  </si>
+  <si>
+    <t>TMP1S2c2</t>
+  </si>
+  <si>
+    <t>TMP1S2c1</t>
+  </si>
+  <si>
+    <t>TMP1S2b4</t>
+  </si>
+  <si>
+    <t>TMP1S2b3</t>
+  </si>
+  <si>
+    <t>TMP1S2b2</t>
+  </si>
+  <si>
+    <t>TMP1S2b1</t>
+  </si>
+  <si>
+    <t>TMP1S2a4</t>
+  </si>
+  <si>
+    <t>TMP1S2a3</t>
+  </si>
+  <si>
+    <t>TMP1S2a2</t>
+  </si>
+  <si>
+    <t>TMP1S2a1</t>
   </si>
   <si>
     <t>TMP1S2f3</t>
@@ -105,63 +135,27 @@
     <t>TMP1S2f4</t>
   </si>
   <si>
-    <t>TMP1S2e4</t>
-  </si>
-  <si>
-    <t>TMP1S2c3</t>
-  </si>
-  <si>
-    <t>TMP1S2c1</t>
-  </si>
-  <si>
-    <t>TMP1S2b4</t>
-  </si>
-  <si>
-    <t>TMP1S2b3</t>
-  </si>
-  <si>
-    <t>TMP1S2b2</t>
-  </si>
-  <si>
-    <t>TMP1S2b1</t>
-  </si>
-  <si>
-    <t>TMP1S2a4</t>
-  </si>
-  <si>
-    <t>TMP1S2a3</t>
-  </si>
-  <si>
-    <t>TMP1S2a2</t>
-  </si>
-  <si>
-    <t>TMP1S2a1</t>
-  </si>
-  <si>
-    <t>TMP1S2c2</t>
+    <t>TMP2S2a1</t>
+  </si>
+  <si>
+    <t>TMP2S2a2</t>
   </si>
   <si>
     <t>TMP2S2b2</t>
   </si>
   <si>
-    <t>TMP2S2a2</t>
-  </si>
-  <si>
-    <t>TMP2S2a1</t>
-  </si>
-  <si>
     <t>TMP2S2b1</t>
   </si>
   <si>
+    <t>TMP3S2a1</t>
+  </si>
+  <si>
+    <t>TMP3S2a2</t>
+  </si>
+  <si>
     <t>TMP3S2a3</t>
   </si>
   <si>
-    <t>TMP3S2a1</t>
-  </si>
-  <si>
-    <t>TMP3S2a2</t>
-  </si>
-  <si>
     <t>TMP3S2a4</t>
   </si>
   <si>
@@ -177,51 +171,51 @@
     <t>TMP4S2a1</t>
   </si>
   <si>
+    <t>TMP5S2a1</t>
+  </si>
+  <si>
+    <t>TMP5S2a2</t>
+  </si>
+  <si>
+    <t>TMP5S2a3</t>
+  </si>
+  <si>
+    <t>TMP5S2b1</t>
+  </si>
+  <si>
+    <t>TMP5S2b2</t>
+  </si>
+  <si>
+    <t>TMP5S2b3</t>
+  </si>
+  <si>
     <t>TMP5S2b4</t>
   </si>
   <si>
-    <t>TMP5S2b1</t>
-  </si>
-  <si>
-    <t>TMP5S2b2</t>
-  </si>
-  <si>
-    <t>TMP5S2a3</t>
-  </si>
-  <si>
-    <t>TMP5S2a2</t>
-  </si>
-  <si>
-    <t>TMP5S2a1</t>
-  </si>
-  <si>
-    <t>TMP5S2b3</t>
+    <t>TMP6S2a4</t>
+  </si>
+  <si>
+    <t>TMP6S2a2</t>
+  </si>
+  <si>
+    <t>TMP6S2a3</t>
+  </si>
+  <si>
+    <t>TMP6S2b1</t>
+  </si>
+  <si>
+    <t>TMP6S2a1</t>
+  </si>
+  <si>
+    <t>TMP6S2b3</t>
   </si>
   <si>
     <t>TMP6S2b4</t>
   </si>
   <si>
-    <t>TMP6S2b3</t>
-  </si>
-  <si>
     <t>TMP6S2b2</t>
   </si>
   <si>
-    <t>TMP6S2b1</t>
-  </si>
-  <si>
-    <t>TMP6S2a4</t>
-  </si>
-  <si>
-    <t>TMP6S2a2</t>
-  </si>
-  <si>
-    <t>TMP6S2a1</t>
-  </si>
-  <si>
-    <t>TMP6S2a3</t>
-  </si>
-  <si>
     <t>TMP7S2a5</t>
   </si>
   <si>
@@ -246,61 +240,70 @@
     <t>TMP7S2a7</t>
   </si>
   <si>
+    <t>TMP7S2e2</t>
+  </si>
+  <si>
     <t>TMP7S2b1</t>
   </si>
   <si>
+    <t>TMP7S2b3</t>
+  </si>
+  <si>
+    <t>TMP7S2b4</t>
+  </si>
+  <si>
+    <t>TMP7S2b5</t>
+  </si>
+  <si>
+    <t>TMP7S2b6</t>
+  </si>
+  <si>
+    <t>TMP7S2b7</t>
+  </si>
+  <si>
+    <t>TMP7S2c1</t>
+  </si>
+  <si>
+    <t>TMP7S2c2</t>
+  </si>
+  <si>
+    <t>TMP7S2d1</t>
+  </si>
+  <si>
+    <t>TMP7S2d2</t>
+  </si>
+  <si>
     <t>TMP7S2b2</t>
   </si>
   <si>
-    <t>TMP7S2b3</t>
-  </si>
-  <si>
-    <t>TMP7S2b4</t>
-  </si>
-  <si>
-    <t>TMP7S2b5</t>
-  </si>
-  <si>
-    <t>TMP7S2b6</t>
-  </si>
-  <si>
-    <t>TMP7S2b7</t>
-  </si>
-  <si>
-    <t>TMP7S2c1</t>
-  </si>
-  <si>
-    <t>TMP7S2c2</t>
-  </si>
-  <si>
-    <t>TMP7S2d1</t>
-  </si>
-  <si>
-    <t>TMP7S2d2</t>
-  </si>
-  <si>
-    <t>TMP7S2e2</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
+    <t>+</t>
+  </si>
+  <si>
     <t>blank</t>
   </si>
   <si>
     <t>Fitting</t>
   </si>
   <si>
+    <t>BSS.GOMGO.TR.GG-6108-600:Chrome 000:1090991</t>
+  </si>
+  <si>
+    <t>LP1S3a4</t>
+  </si>
+  <si>
     <t>LP1S3a3</t>
   </si>
   <si>
+    <t>LP1S3a2</t>
+  </si>
+  <si>
     <t>LP1S3a1</t>
   </si>
   <si>
-    <t>LP1S3a4</t>
-  </si>
-  <si>
-    <t>LP1S3a2</t>
+    <t>LP3S3b3</t>
   </si>
   <si>
     <t>LP3S3a1</t>
@@ -321,118 +324,115 @@
     <t>LP3S3b2</t>
   </si>
   <si>
-    <t>LP3S3b3</t>
+    <t>BSS.HAND SHOWER SET.MASTER BATH:BSS.HAND SHOWER SET.MASTER BATH:1091130</t>
   </si>
   <si>
     <t>LP3S3b4</t>
   </si>
   <si>
+    <t>BSS.GESSI.SM.49079:29046000:1090989</t>
+  </si>
+  <si>
+    <t>LP4S3a2</t>
+  </si>
+  <si>
+    <t>BSS.GOMGO.PH.GG-6106:Chrome 000:1090992</t>
+  </si>
+  <si>
     <t>LP4S3a1</t>
   </si>
   <si>
-    <t>LP4S3a2</t>
-  </si>
-  <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1018144</t>
-  </si>
-  <si>
-    <t>M_Coupling - Threaded - MI - Class 150:Standard:1044021</t>
+    <t>LP5S3c1</t>
+  </si>
+  <si>
+    <t>LP5S3c3</t>
+  </si>
+  <si>
+    <t>LP5S3c4</t>
+  </si>
+  <si>
+    <t>LP5S3d1</t>
+  </si>
+  <si>
+    <t>LP5S3d2</t>
+  </si>
+  <si>
+    <t>LP5S3c2</t>
+  </si>
+  <si>
+    <t>LP5S3a5</t>
+  </si>
+  <si>
+    <t>LP5S3b2</t>
+  </si>
+  <si>
+    <t>LP5S3a1</t>
+  </si>
+  <si>
+    <t>LP5S3a2</t>
+  </si>
+  <si>
+    <t>LP5S3a3</t>
+  </si>
+  <si>
+    <t>LP5S3a4</t>
+  </si>
+  <si>
+    <t>LP5S3b1</t>
+  </si>
+  <si>
+    <t>LP5S3d3</t>
+  </si>
+  <si>
+    <t>LP5S3b3</t>
+  </si>
+  <si>
+    <t>LP5S3d4</t>
   </si>
   <si>
     <t>LP5S3b5</t>
   </si>
   <si>
-    <t>LP5S3c2</t>
-  </si>
-  <si>
-    <t>LP5S3c3</t>
-  </si>
-  <si>
-    <t>LP5S3c1</t>
-  </si>
-  <si>
-    <t>LP5S3c4</t>
-  </si>
-  <si>
-    <t>LP5S3d2</t>
-  </si>
-  <si>
-    <t>LP5S3d1</t>
-  </si>
-  <si>
-    <t>LP5S3a2</t>
-  </si>
-  <si>
-    <t>LP5S3d3</t>
-  </si>
-  <si>
-    <t>LP5S3a3</t>
-  </si>
-  <si>
-    <t>LP5S3a4</t>
-  </si>
-  <si>
-    <t>LP5S3a5</t>
-  </si>
-  <si>
-    <t>LP5S3b1</t>
-  </si>
-  <si>
-    <t>LP5S3b2</t>
-  </si>
-  <si>
-    <t>LP5S3a1</t>
-  </si>
-  <si>
-    <t>LP5S3d4</t>
+    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+  </si>
+  <si>
+    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
   </si>
   <si>
     <t>LP5S3b4</t>
   </si>
   <si>
-    <t>LP5S3b3</t>
-  </si>
-  <si>
-    <t>BSS.LAUFEN.WC.820714:820959000 White:1091064</t>
-  </si>
-  <si>
-    <t>BSS.TECE.AP.9240402:Flush Plate:1091024</t>
+    <t>LP7S3a1</t>
+  </si>
+  <si>
+    <t>LP7S3a3</t>
+  </si>
+  <si>
+    <t>LP7S3b2</t>
+  </si>
+  <si>
+    <t>LP7S3a4</t>
   </si>
   <si>
     <t>LP7S3b1</t>
   </si>
   <si>
-    <t>LP7S3b2</t>
-  </si>
-  <si>
-    <t>LP7S3a4</t>
+    <t>LP7S3b3</t>
+  </si>
+  <si>
+    <t>LP7S3b4</t>
   </si>
   <si>
     <t>LP7S3a2</t>
   </si>
   <si>
-    <t>LP7S3a3</t>
-  </si>
-  <si>
-    <t>LP7S3a1</t>
-  </si>
-  <si>
-    <t>LP7S3b4</t>
-  </si>
-  <si>
-    <t>LP7S3b3</t>
-  </si>
-  <si>
-    <t>BSS.Shallow_FT:150 x 150MM:1018227</t>
-  </si>
-  <si>
-    <t>BSS.Shallow_FW:BSS.Shallow_FW:1038276</t>
-  </si>
-  <si>
     <t>BSS.FLOOR DRAIN_100:BSS.FLOOR DRAIN_100:1091045</t>
   </si>
   <si>
     <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>Point number/name</t>
@@ -453,8 +453,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -517,21 +517,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -569,7 +561,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -603,7 +595,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -638,10 +629,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -814,11 +804,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -862,9 +852,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -879,7 +869,7 @@
         <v>-1.35</v>
       </c>
       <c r="F2">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -888,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -897,12 +887,12 @@
         <v>2.76</v>
       </c>
       <c r="M2">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -914,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>-0.03</v>
+        <v>-1.35</v>
       </c>
       <c r="F3">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -926,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -935,12 +925,12 @@
         <v>2.76</v>
       </c>
       <c r="M3">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -952,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F4">
-        <v>-0.17499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -964,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -973,12 +963,12 @@
         <v>2.76</v>
       </c>
       <c r="M4">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -990,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F5">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1002,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1011,12 +1001,12 @@
         <v>2.76</v>
       </c>
       <c r="M5">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -1028,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F6">
-        <v>1.0249999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1040,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1049,12 +1039,12 @@
         <v>2.76</v>
       </c>
       <c r="M6">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -1069,7 +1059,7 @@
         <v>-0.35</v>
       </c>
       <c r="F7">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1078,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1087,12 +1077,12 @@
         <v>2.76</v>
       </c>
       <c r="M7">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1104,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-0.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F8">
-        <v>-0.17499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1116,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1125,12 +1115,12 @@
         <v>2.76</v>
       </c>
       <c r="M8">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1142,10 +1132,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.47</v>
+        <v>-0.03</v>
       </c>
       <c r="F9">
-        <v>1.0249999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1154,7 +1144,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1163,12 +1153,12 @@
         <v>2.76</v>
       </c>
       <c r="M9">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1180,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>-0.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F10">
-        <v>0.42499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1192,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1201,12 +1191,12 @@
         <v>2.76</v>
       </c>
       <c r="M10">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1218,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>-1.35</v>
+        <v>-0.03</v>
       </c>
       <c r="F11">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1230,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1239,12 +1229,12 @@
         <v>2.76</v>
       </c>
       <c r="M11">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1256,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>-1.35</v>
+        <v>0.47</v>
       </c>
       <c r="F12">
-        <v>0.42499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1268,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1277,12 +1267,12 @@
         <v>2.76</v>
       </c>
       <c r="M12">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1294,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-1.35</v>
+        <v>0.47</v>
       </c>
       <c r="F13">
-        <v>1.0249999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1306,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1315,12 +1305,12 @@
         <v>2.76</v>
       </c>
       <c r="M13">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1332,10 +1322,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-0.35</v>
+        <v>0.47</v>
       </c>
       <c r="F14">
-        <v>1.0249999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1344,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1353,12 +1343,12 @@
         <v>2.76</v>
       </c>
       <c r="M14">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1373,7 +1363,7 @@
         <v>0.47</v>
       </c>
       <c r="F15">
-        <v>0.42499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1382,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1391,12 +1381,12 @@
         <v>2.76</v>
       </c>
       <c r="M15">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1408,10 +1398,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="F16">
-        <v>-0.77500000000000002</v>
+        <v>1.025</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1420,7 +1410,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1429,12 +1419,12 @@
         <v>2.76</v>
       </c>
       <c r="M16">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1449,7 +1439,7 @@
         <v>0.49</v>
       </c>
       <c r="F17">
-        <v>1.0249999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1458,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1467,12 +1457,12 @@
         <v>2.76</v>
       </c>
       <c r="M17">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1487,7 +1477,7 @@
         <v>0.49</v>
       </c>
       <c r="F18">
-        <v>0.42499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1496,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1505,12 +1495,12 @@
         <v>2.76</v>
       </c>
       <c r="M18">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1525,7 +1515,7 @@
         <v>0.49</v>
       </c>
       <c r="F19">
-        <v>-0.17499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1534,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1543,12 +1533,12 @@
         <v>2.76</v>
       </c>
       <c r="M19">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1560,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.49</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F20">
-        <v>-0.77500000000000002</v>
+        <v>1.025</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1572,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1581,12 +1571,12 @@
         <v>2.76</v>
       </c>
       <c r="M20">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1598,10 +1588,10 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F21">
-        <v>1.0249999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1610,7 +1600,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1619,12 +1609,12 @@
         <v>2.76</v>
       </c>
       <c r="M21">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1636,10 +1626,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F22">
-        <v>0.42499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1648,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1657,12 +1647,12 @@
         <v>2.76</v>
       </c>
       <c r="M22">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1674,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F23">
-        <v>-0.17499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1686,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1695,12 +1685,12 @@
         <v>2.76</v>
       </c>
       <c r="M23">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1712,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.93500000000000005</v>
+        <v>-1.35</v>
       </c>
       <c r="F24">
-        <v>-0.77500000000000002</v>
+        <v>0.425</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1724,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1733,12 +1723,12 @@
         <v>2.76</v>
       </c>
       <c r="M24">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1750,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0.47</v>
+        <v>-1.35</v>
       </c>
       <c r="F25">
-        <v>-0.17499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1762,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1771,12 +1761,12 @@
         <v>2.76</v>
       </c>
       <c r="M25">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1788,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="F26">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1800,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1809,12 +1799,12 @@
         <v>1.2</v>
       </c>
       <c r="M26">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1838,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1847,12 +1837,12 @@
         <v>1.2</v>
       </c>
       <c r="M27">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -1864,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="F28">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1876,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1885,12 +1875,12 @@
         <v>1.2</v>
       </c>
       <c r="M28">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -1914,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1923,12 +1913,12 @@
         <v>1.2</v>
       </c>
       <c r="M29">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
@@ -1940,10 +1930,10 @@
         <v>0.6</v>
       </c>
       <c r="E30">
-        <v>-0.93500000000000005</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F30">
-        <v>0.42499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -1952,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1961,12 +1951,12 @@
         <v>0.96</v>
       </c>
       <c r="M30">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -1978,10 +1968,10 @@
         <v>0.6</v>
       </c>
       <c r="E31">
-        <v>-0.93500000000000005</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F31">
-        <v>-0.77500000000000002</v>
+        <v>-0.175</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -1990,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1999,12 +1989,12 @@
         <v>0.96</v>
       </c>
       <c r="M31">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -2016,10 +2006,10 @@
         <v>0.6</v>
       </c>
       <c r="E32">
-        <v>-0.93500000000000005</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F32">
-        <v>-0.17499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -2028,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2037,12 +2027,12 @@
         <v>0.96</v>
       </c>
       <c r="M32">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -2054,10 +2044,10 @@
         <v>0.6</v>
       </c>
       <c r="E33">
-        <v>-0.93500000000000005</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F33">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -2066,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2075,12 +2065,12 @@
         <v>0.96</v>
       </c>
       <c r="M33">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -2095,7 +2085,7 @@
         <v>0.3</v>
       </c>
       <c r="F34">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -2104,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2113,12 +2103,12 @@
         <v>0.6</v>
       </c>
       <c r="M34">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2133,7 +2123,7 @@
         <v>0.3</v>
       </c>
       <c r="F35">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G35">
         <v>4</v>
@@ -2142,7 +2132,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2151,12 +2141,12 @@
         <v>0.6</v>
       </c>
       <c r="M35">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2171,7 +2161,7 @@
         <v>0.3</v>
       </c>
       <c r="F36">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -2180,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2189,12 +2179,12 @@
         <v>0.6</v>
       </c>
       <c r="M36">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -2209,7 +2199,7 @@
         <v>0.3</v>
       </c>
       <c r="F37">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -2218,7 +2208,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2227,12 +2217,12 @@
         <v>0.6</v>
       </c>
       <c r="M37">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2244,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>1.155</v>
+        <v>0.93</v>
       </c>
       <c r="F38">
-        <v>1.0249999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -2256,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2265,12 +2255,12 @@
         <v>1.8</v>
       </c>
       <c r="M38">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
@@ -2282,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>1.155</v>
+        <v>0.48</v>
       </c>
       <c r="F39">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -2294,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2303,12 +2293,12 @@
         <v>1.8</v>
       </c>
       <c r="M39">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2320,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>1.155</v>
+        <v>0.03</v>
       </c>
       <c r="F40">
-        <v>-0.17499999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -2332,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2341,12 +2331,12 @@
         <v>1.8</v>
       </c>
       <c r="M40">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B41" t="s">
         <v>14</v>
@@ -2358,10 +2348,10 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0.03</v>
+        <v>1.155</v>
       </c>
       <c r="F41">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -2370,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -2379,12 +2369,12 @@
         <v>1.8</v>
       </c>
       <c r="M41">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
@@ -2396,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0.48</v>
+        <v>1.155</v>
       </c>
       <c r="F42">
-        <v>-0.77500000000000002</v>
+        <v>-0.175</v>
       </c>
       <c r="G42">
         <v>5</v>
@@ -2408,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2417,12 +2407,12 @@
         <v>1.8</v>
       </c>
       <c r="M42">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2434,10 +2424,10 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0.93</v>
+        <v>1.155</v>
       </c>
       <c r="F43">
-        <v>-0.77500000000000002</v>
+        <v>0.425</v>
       </c>
       <c r="G43">
         <v>5</v>
@@ -2446,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2455,12 +2445,12 @@
         <v>1.8</v>
       </c>
       <c r="M43">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2475,7 +2465,7 @@
         <v>1.155</v>
       </c>
       <c r="F44">
-        <v>0.42499999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G44">
         <v>5</v>
@@ -2484,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2493,10 +2483,10 @@
         <v>1.8</v>
       </c>
       <c r="M44">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="1">
         <v>207</v>
       </c>
@@ -2510,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F45">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -2522,7 +2512,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2531,12 +2521,12 @@
         <v>1.8</v>
       </c>
       <c r="M45">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
@@ -2548,10 +2538,10 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F46">
-        <v>0.42499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G46">
         <v>6</v>
@@ -2560,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -2569,12 +2559,12 @@
         <v>1.8</v>
       </c>
       <c r="M46">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -2586,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="F47">
-        <v>-0.17499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G47">
         <v>6</v>
@@ -2598,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2607,12 +2597,12 @@
         <v>1.8</v>
       </c>
       <c r="M47">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
@@ -2627,7 +2617,7 @@
         <v>-0.3</v>
       </c>
       <c r="F48">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -2636,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2645,12 +2635,12 @@
         <v>1.8</v>
       </c>
       <c r="M48">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -2665,7 +2655,7 @@
         <v>0.3</v>
       </c>
       <c r="F49">
-        <v>1.0249999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G49">
         <v>6</v>
@@ -2674,7 +2664,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2683,12 +2673,12 @@
         <v>1.8</v>
       </c>
       <c r="M49">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="1">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2700,10 +2690,10 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F50">
-        <v>-0.17499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G50">
         <v>6</v>
@@ -2712,7 +2702,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2721,12 +2711,12 @@
         <v>1.8</v>
       </c>
       <c r="M50">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="1">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2738,10 +2728,10 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F51">
-        <v>-0.77500000000000002</v>
+        <v>1.025</v>
       </c>
       <c r="G51">
         <v>6</v>
@@ -2750,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -2759,12 +2749,12 @@
         <v>1.8</v>
       </c>
       <c r="M51">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="1">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
@@ -2776,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F52">
-        <v>0.42499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G52">
         <v>6</v>
@@ -2788,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2797,12 +2787,12 @@
         <v>1.8</v>
       </c>
       <c r="M52">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="1">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
@@ -2826,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2838,9 +2828,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13">
       <c r="A54" s="1">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2855,7 +2845,7 @@
         <v>0.6</v>
       </c>
       <c r="F54">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G54" t="s">
         <v>86</v>
@@ -2864,7 +2854,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2876,9 +2866,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13">
       <c r="A55" s="1">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
@@ -2902,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2914,9 +2904,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13">
       <c r="A56" s="1">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2940,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2952,9 +2942,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13">
       <c r="A57" s="1">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
@@ -2978,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2990,9 +2980,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13">
       <c r="A58" s="1">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
@@ -3016,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -3028,9 +3018,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13">
       <c r="A59" s="1">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -3054,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -3066,9 +3056,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13">
       <c r="A60" s="1">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -3092,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -3104,9 +3094,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13">
       <c r="A61" s="1">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
@@ -3115,13 +3105,13 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>0.72</v>
+        <v>2.61</v>
       </c>
       <c r="E61">
-        <v>0.15</v>
+        <v>1.2</v>
       </c>
       <c r="F61">
-        <v>-0.05</v>
+        <v>-0.025</v>
       </c>
       <c r="G61" t="s">
         <v>86</v>
@@ -3130,7 +3120,7 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -3142,9 +3132,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13">
       <c r="A62" s="1">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
@@ -3156,7 +3146,7 @@
         <v>0.72</v>
       </c>
       <c r="E62">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F62">
         <v>-0.05</v>
@@ -3168,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3180,9 +3170,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13">
       <c r="A63" s="1">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
@@ -3206,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3218,9 +3208,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13">
       <c r="A64" s="1">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B64" t="s">
         <v>14</v>
@@ -3244,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3256,9 +3246,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13">
       <c r="A65" s="1">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
@@ -3282,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3294,9 +3284,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13">
       <c r="A66" s="1">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
@@ -3320,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3332,9 +3322,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13">
       <c r="A67" s="1">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
@@ -3358,7 +3348,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3370,9 +3360,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13">
       <c r="A68" s="1">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
@@ -3387,7 +3377,7 @@
         <v>0.6</v>
       </c>
       <c r="F68">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G68" t="s">
         <v>86</v>
@@ -3396,7 +3386,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3408,9 +3398,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13">
       <c r="A69" s="1">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
@@ -3425,7 +3415,7 @@
         <v>1.2</v>
       </c>
       <c r="F69">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G69" t="s">
         <v>86</v>
@@ -3434,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3446,9 +3436,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13">
       <c r="A70" s="1">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
@@ -3457,13 +3447,13 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>2.0099999999999998</v>
+        <v>2.01</v>
       </c>
       <c r="E70">
         <v>0.6</v>
       </c>
       <c r="F70">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G70" t="s">
         <v>86</v>
@@ -3472,7 +3462,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3484,9 +3474,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13">
       <c r="A71" s="1">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -3495,13 +3485,13 @@
         <v>84</v>
       </c>
       <c r="D71">
-        <v>2.0099999999999998</v>
+        <v>2.01</v>
       </c>
       <c r="E71">
         <v>1.2</v>
       </c>
       <c r="F71">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G71" t="s">
         <v>86</v>
@@ -3510,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3522,9 +3512,9 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13">
       <c r="A72" s="1">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -3533,13 +3523,13 @@
         <v>85</v>
       </c>
       <c r="D72">
-        <v>2.61</v>
+        <v>0.72</v>
       </c>
       <c r="E72">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="F72">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.05</v>
       </c>
       <c r="G72" t="s">
         <v>86</v>
@@ -3548,7 +3538,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3566,17 +3556,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3620,100 +3604,100 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
-        <v>230</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0.06</v>
+      </c>
+      <c r="F2">
+        <v>0.175</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2.76</v>
+      </c>
+      <c r="M2">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="1">
+        <v>235</v>
+      </c>
+      <c r="B3" t="s">
         <v>89</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>-0.255</v>
+      </c>
+      <c r="F3">
+        <v>0.137</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2.76</v>
+      </c>
+      <c r="M3">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="1">
+        <v>234</v>
+      </c>
+      <c r="B4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>0.375</v>
       </c>
-      <c r="F2">
-        <v>0.13700000000000001</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2.76</v>
-      </c>
-      <c r="M2">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>228</v>
-      </c>
-      <c r="B3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0.375</v>
-      </c>
-      <c r="F3">
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>2.76</v>
-      </c>
-      <c r="M3">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>231</v>
-      </c>
-      <c r="B4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>-0.255</v>
-      </c>
       <c r="F4">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -3722,7 +3706,7 @@
         <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -3731,18 +3715,18 @@
         <v>2.76</v>
       </c>
       <c r="M4">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -3751,7 +3735,7 @@
         <v>-0.255</v>
       </c>
       <c r="F5">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3760,7 +3744,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -3769,65 +3753,65 @@
         <v>2.76</v>
       </c>
       <c r="M5">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
         <v>232</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>-1.012</v>
+        <v>0.375</v>
       </c>
       <c r="F6">
-        <v>0.96199999999999997</v>
+        <v>0.213</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>0.96</v>
+        <v>2.76</v>
       </c>
       <c r="M6">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7">
         <v>0.6</v>
       </c>
       <c r="E7">
-        <v>-0.81200000000000006</v>
+        <v>-0.795</v>
       </c>
       <c r="F7">
-        <v>0.96199999999999997</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -3836,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -3845,18 +3829,18 @@
         <v>0.96</v>
       </c>
       <c r="M7">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8">
         <v>0.6</v>
@@ -3865,7 +3849,7 @@
         <v>-1.012</v>
       </c>
       <c r="F8">
-        <v>-0.188</v>
+        <v>0.962</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -3874,7 +3858,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -3883,27 +3867,27 @@
         <v>0.96</v>
       </c>
       <c r="M8">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9">
         <v>0.6</v>
       </c>
       <c r="E9">
-        <v>-0.81200000000000006</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="F9">
-        <v>-0.188</v>
+        <v>0.962</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -3912,7 +3896,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -3921,27 +3905,27 @@
         <v>0.96</v>
       </c>
       <c r="M9">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10">
         <v>0.6</v>
       </c>
       <c r="E10">
-        <v>-0.79500000000000004</v>
+        <v>-1.012</v>
       </c>
       <c r="F10">
-        <v>-1.4E-2</v>
+        <v>-0.188</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -3950,7 +3934,7 @@
         <v>6</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -3959,27 +3943,27 @@
         <v>0.96</v>
       </c>
       <c r="M10">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11">
         <v>0.6</v>
       </c>
       <c r="E11">
-        <v>-0.65500000000000003</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="F11">
-        <v>-1.4E-2</v>
+        <v>-0.188</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -3988,7 +3972,7 @@
         <v>6</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -3997,27 +3981,27 @@
         <v>0.96</v>
       </c>
       <c r="M11">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>0.6</v>
       </c>
       <c r="E12">
-        <v>-0.79500000000000004</v>
+        <v>-0.795</v>
       </c>
       <c r="F12">
-        <v>-8.5999999999999993E-2</v>
+        <v>-0.014</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -4026,7 +4010,7 @@
         <v>6</v>
       </c>
       <c r="I12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -4035,27 +4019,27 @@
         <v>0.96</v>
       </c>
       <c r="M12">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13">
         <v>0.6</v>
       </c>
       <c r="E13">
-        <v>-0.65500000000000003</v>
+        <v>-0.655</v>
       </c>
       <c r="F13">
-        <v>-8.5999999999999993E-2</v>
+        <v>-0.014</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -4064,7 +4048,7 @@
         <v>6</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -4073,141 +4057,141 @@
         <v>0.96</v>
       </c>
       <c r="M13">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14">
+        <v>0.6</v>
+      </c>
+      <c r="E14">
+        <v>-0.912</v>
+      </c>
+      <c r="F14">
+        <v>0.387</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+      <c r="I14" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="L14">
         <v>0.96</v>
       </c>
-      <c r="E14">
-        <v>0.40500000000000003</v>
-      </c>
-      <c r="F14">
+      <c r="M14">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="1">
+        <v>243</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15">
+        <v>0.6</v>
+      </c>
+      <c r="E15">
+        <v>-0.655</v>
+      </c>
+      <c r="F15">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15" t="s">
+        <v>88</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0.96</v>
+      </c>
+      <c r="M15">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="1">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16">
+        <v>0.6</v>
+      </c>
+      <c r="E16">
+        <v>-0.725</v>
+      </c>
+      <c r="F16">
+        <v>-0.05</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>6</v>
+      </c>
+      <c r="I16" t="s">
+        <v>88</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0.96</v>
+      </c>
+      <c r="M16">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="1">
+        <v>245</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17">
+        <v>0.96</v>
+      </c>
+      <c r="E17">
+        <v>0.455</v>
+      </c>
+      <c r="F17">
         <v>-0.375</v>
-      </c>
-      <c r="G14">
-        <v>4</v>
-      </c>
-      <c r="H14">
-        <v>6</v>
-      </c>
-      <c r="I14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <v>0.6</v>
-      </c>
-      <c r="M14">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>241</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15">
-        <v>0.96</v>
-      </c>
-      <c r="E15">
-        <v>0.45500000000000002</v>
-      </c>
-      <c r="F15">
-        <v>-0.375</v>
-      </c>
-      <c r="G15">
-        <v>4</v>
-      </c>
-      <c r="H15">
-        <v>6</v>
-      </c>
-      <c r="I15" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>0.6</v>
-      </c>
-      <c r="M15">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>40</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16">
-        <v>0.93700000000000006</v>
-      </c>
-      <c r="E16">
-        <v>0.84299999999999997</v>
-      </c>
-      <c r="F16">
-        <v>-0.8</v>
-      </c>
-      <c r="G16">
-        <v>4</v>
-      </c>
-      <c r="H16">
-        <v>6</v>
-      </c>
-      <c r="I16" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>0.6</v>
-      </c>
-      <c r="M16">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>89</v>
-      </c>
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17">
-        <v>0.86</v>
-      </c>
-      <c r="E17">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="F17">
-        <v>1.468</v>
       </c>
       <c r="G17">
         <v>4</v>
@@ -4216,7 +4200,7 @@
         <v>6</v>
       </c>
       <c r="I17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -4225,94 +4209,94 @@
         <v>0.6</v>
       </c>
       <c r="M17">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
-        <v>251</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18">
-        <v>0.183</v>
+        <v>0.96</v>
       </c>
       <c r="E18">
-        <v>0.03</v>
+        <v>0.43</v>
       </c>
       <c r="F18">
-        <v>-0.61599999999999999</v>
+        <v>-0.375</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18">
         <v>6</v>
       </c>
       <c r="I18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="L18">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="M18">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E19">
-        <v>1.38</v>
+        <v>0.405</v>
       </c>
       <c r="F19">
-        <v>1.4</v>
+        <v>-0.375</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H19">
         <v>6</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
       <c r="L19">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="M19">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -4330,7 +4314,7 @@
         <v>6</v>
       </c>
       <c r="I20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -4339,18 +4323,18 @@
         <v>1.8</v>
       </c>
       <c r="M20">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4368,7 +4352,7 @@
         <v>6</v>
       </c>
       <c r="I21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -4377,18 +4361,18 @@
         <v>1.8</v>
       </c>
       <c r="M21">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -4406,7 +4390,7 @@
         <v>6</v>
       </c>
       <c r="I22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -4415,24 +4399,24 @@
         <v>1.8</v>
       </c>
       <c r="M22">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>1.38</v>
+        <v>-0.42</v>
       </c>
       <c r="F23">
         <v>-0.15</v>
@@ -4444,7 +4428,7 @@
         <v>6</v>
       </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -4453,24 +4437,24 @@
         <v>1.8</v>
       </c>
       <c r="M23">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>-0.42</v>
+        <v>1.38</v>
       </c>
       <c r="F24">
         <v>-0.15</v>
@@ -4482,7 +4466,7 @@
         <v>6</v>
       </c>
       <c r="I24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -4491,27 +4475,27 @@
         <v>1.8</v>
       </c>
       <c r="M24">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25">
-        <v>8.7999999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0.27500000000000002</v>
+        <v>1.38</v>
       </c>
       <c r="F25">
-        <v>2.5999999999999999E-2</v>
+        <v>1.4</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -4520,7 +4504,7 @@
         <v>6</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -4529,27 +4513,27 @@
         <v>1.8</v>
       </c>
       <c r="M25">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E26">
-        <v>-0.42</v>
+        <v>0.025</v>
       </c>
       <c r="F26">
-        <v>-0.75</v>
+        <v>-0.22</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -4558,7 +4542,7 @@
         <v>6</v>
       </c>
       <c r="I26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -4567,27 +4551,27 @@
         <v>1.8</v>
       </c>
       <c r="M26">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D27">
-        <v>8.7999999999999995E-2</v>
+        <v>0.183</v>
       </c>
       <c r="E27">
-        <v>-0.22500000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="F27">
-        <v>-0.46600000000000003</v>
+        <v>-0.402</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -4596,7 +4580,7 @@
         <v>6</v>
       </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -4605,27 +4589,27 @@
         <v>1.8</v>
       </c>
       <c r="M27">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D28">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E28">
-        <v>0.27500000000000002</v>
+        <v>-0.225</v>
       </c>
       <c r="F28">
-        <v>-0.46600000000000003</v>
+        <v>0.026</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -4634,7 +4618,7 @@
         <v>6</v>
       </c>
       <c r="I28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -4643,27 +4627,27 @@
         <v>1.8</v>
       </c>
       <c r="M28">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E29">
-        <v>2.5000000000000001E-2</v>
+        <v>0.275</v>
       </c>
       <c r="F29">
-        <v>-0.22</v>
+        <v>0.026</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -4672,7 +4656,7 @@
         <v>6</v>
       </c>
       <c r="I29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -4681,27 +4665,27 @@
         <v>1.8</v>
       </c>
       <c r="M29">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E30">
-        <v>-0.15</v>
+        <v>-0.225</v>
       </c>
       <c r="F30">
-        <v>-0.40200000000000002</v>
+        <v>-0.466</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -4710,7 +4694,7 @@
         <v>6</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -4719,27 +4703,27 @@
         <v>1.8</v>
       </c>
       <c r="M30">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D31">
-        <v>0.183</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E31">
-        <v>0.21</v>
+        <v>0.275</v>
       </c>
       <c r="F31">
-        <v>-0.40200000000000002</v>
+        <v>-0.466</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -4748,7 +4732,7 @@
         <v>6</v>
       </c>
       <c r="I31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -4757,27 +4741,27 @@
         <v>1.8</v>
       </c>
       <c r="M31">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D32">
-        <v>8.7999999999999995E-2</v>
+        <v>0.183</v>
       </c>
       <c r="E32">
-        <v>-0.22500000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="F32">
-        <v>2.5999999999999999E-2</v>
+        <v>-0.402</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -4786,7 +4770,7 @@
         <v>6</v>
       </c>
       <c r="I32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -4795,24 +4779,24 @@
         <v>1.8</v>
       </c>
       <c r="M32">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>1.38</v>
+        <v>-0.42</v>
       </c>
       <c r="F33">
         <v>-0.75</v>
@@ -4824,7 +4808,7 @@
         <v>6</v>
       </c>
       <c r="I33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -4833,24 +4817,24 @@
         <v>1.8</v>
       </c>
       <c r="M33">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D34">
         <v>0.183</v>
       </c>
       <c r="E34">
-        <v>0.21</v>
+        <v>-0.15</v>
       </c>
       <c r="F34">
         <v>-0.83</v>
@@ -4862,7 +4846,7 @@
         <v>6</v>
       </c>
       <c r="I34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -4871,27 +4855,27 @@
         <v>1.8</v>
       </c>
       <c r="M34">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D35">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>-0.15</v>
+        <v>1.38</v>
       </c>
       <c r="F35">
-        <v>-0.83</v>
+        <v>-0.75</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -4900,7 +4884,7 @@
         <v>6</v>
       </c>
       <c r="I35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -4909,27 +4893,27 @@
         <v>1.8</v>
       </c>
       <c r="M35">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D36">
-        <v>0.20799999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="E36">
-        <v>-9.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="F36">
-        <v>-1.024</v>
+        <v>-0.616</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -4938,7 +4922,7 @@
         <v>6</v>
       </c>
       <c r="I36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -4947,18 +4931,18 @@
         <v>1.8</v>
       </c>
       <c r="M36">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D37">
         <v>0.108</v>
@@ -4967,7 +4951,7 @@
         <v>0.03</v>
       </c>
       <c r="F37">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -4976,7 +4960,7 @@
         <v>6</v>
       </c>
       <c r="I37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -4985,100 +4969,100 @@
         <v>1.8</v>
       </c>
       <c r="M37">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1">
-        <v>272</v>
+        <v>158</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D38">
-        <v>0.96</v>
+        <v>0.208</v>
       </c>
       <c r="E38">
-        <v>1.585</v>
+        <v>-0.095</v>
       </c>
       <c r="F38">
-        <v>-2.5000000000000001E-2</v>
-      </c>
-      <c r="G38" t="s">
-        <v>86</v>
+        <v>-1.024</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
       </c>
       <c r="H38">
         <v>6</v>
       </c>
       <c r="I38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="L38">
-        <v>2.76</v>
+        <v>1.8</v>
       </c>
       <c r="M38">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D39">
-        <v>1.06</v>
+        <v>0.183</v>
       </c>
       <c r="E39">
-        <v>1.585</v>
+        <v>0.21</v>
       </c>
       <c r="F39">
-        <v>-2.5000000000000001E-2</v>
-      </c>
-      <c r="G39" t="s">
-        <v>86</v>
+        <v>-0.83</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
       </c>
       <c r="H39">
         <v>6</v>
       </c>
       <c r="I39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>2.76</v>
+        <v>1.8</v>
       </c>
       <c r="M39">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D40">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="F40">
         <v>-0.05</v>
@@ -5090,7 +5074,7 @@
         <v>6</v>
       </c>
       <c r="I40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -5102,21 +5086,21 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13">
       <c r="A41" s="1">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D41">
-        <v>0.72</v>
+        <v>0.57</v>
       </c>
       <c r="E41">
-        <v>1.1499999999999999</v>
+        <v>1</v>
       </c>
       <c r="F41">
         <v>-0.05</v>
@@ -5128,7 +5112,7 @@
         <v>6</v>
       </c>
       <c r="I41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -5140,24 +5124,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13">
       <c r="A42" s="1">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D42">
-        <v>0.56999999999999995</v>
+        <v>1.06</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>1.585</v>
       </c>
       <c r="F42">
-        <v>-0.05</v>
+        <v>-0.025</v>
       </c>
       <c r="G42" t="s">
         <v>86</v>
@@ -5166,7 +5150,7 @@
         <v>6</v>
       </c>
       <c r="I42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -5178,21 +5162,21 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13">
       <c r="A43" s="1">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D43">
-        <v>0.56999999999999995</v>
+        <v>0.72</v>
       </c>
       <c r="E43">
-        <v>1.1499999999999999</v>
+        <v>1</v>
       </c>
       <c r="F43">
         <v>-0.05</v>
@@ -5204,7 +5188,7 @@
         <v>6</v>
       </c>
       <c r="I43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -5216,24 +5200,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13">
       <c r="A44" s="1">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D44">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="E44">
-        <v>1.4850000000000001</v>
+        <v>1.585</v>
       </c>
       <c r="F44">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G44" t="s">
         <v>86</v>
@@ -5242,7 +5226,7 @@
         <v>6</v>
       </c>
       <c r="I44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -5254,24 +5238,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13">
       <c r="A45" s="1">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D45">
         <v>0.96</v>
       </c>
       <c r="E45">
-        <v>1.4850000000000001</v>
+        <v>1.485</v>
       </c>
       <c r="F45">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G45" t="s">
         <v>86</v>
@@ -5280,7 +5264,7 @@
         <v>6</v>
       </c>
       <c r="I45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -5292,24 +5276,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13">
       <c r="A46" s="1">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D46">
-        <v>0.64500000000000002</v>
+        <v>1.06</v>
       </c>
       <c r="E46">
-        <v>1.1120000000000001</v>
+        <v>1.485</v>
       </c>
       <c r="F46">
-        <v>-7.6999999999999999E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G46" t="s">
         <v>86</v>
@@ -5318,7 +5302,7 @@
         <v>6</v>
       </c>
       <c r="I46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -5330,24 +5314,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13">
       <c r="A47" s="1">
-        <v>1</v>
+        <v>273</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D47">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="E47">
-        <v>1.5349999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="F47">
-        <v>-7.6999999999999999E-2</v>
+        <v>-0.05</v>
       </c>
       <c r="G47" t="s">
         <v>86</v>
@@ -5356,7 +5340,7 @@
         <v>6</v>
       </c>
       <c r="I47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -5368,24 +5352,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13">
       <c r="A48" s="1">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D48">
         <v>1.01</v>
       </c>
       <c r="E48">
-        <v>1.5349999999999999</v>
+        <v>1.535</v>
       </c>
       <c r="F48">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G48" t="s">
         <v>86</v>
@@ -5394,7 +5378,7 @@
         <v>6</v>
       </c>
       <c r="I48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -5406,18 +5390,18 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13">
       <c r="A49" s="1">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D49">
-        <v>0.64500000000000002</v>
+        <v>0.645</v>
       </c>
       <c r="E49">
         <v>1.075</v>
@@ -5432,7 +5416,7 @@
         <v>6</v>
       </c>
       <c r="I49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -5450,31 +5434,31 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:O1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACAE0D87-4419-4FE4-863D-5B1C23EEFF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
     <sheet name="Stage 3" sheetId="2" r:id="rId2"/>
     <sheet name="Obstacles" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="142">
   <si>
     <t>Marking type</t>
   </si>
@@ -279,9 +285,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>+</t>
-  </si>
-  <si>
     <t>blank</t>
   </si>
   <si>
@@ -430,9 +433,6 @@
   </si>
   <si>
     <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
   <si>
     <t>Point number/name</t>
@@ -453,8 +453,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -517,13 +517,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -561,7 +569,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -595,6 +603,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -629,9 +638,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -804,11 +814,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O72"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -852,7 +876,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>182</v>
       </c>
@@ -869,7 +893,7 @@
         <v>-1.35</v>
       </c>
       <c r="F2">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -878,7 +902,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -887,10 +911,10 @@
         <v>2.76</v>
       </c>
       <c r="M2">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>181</v>
       </c>
@@ -907,7 +931,7 @@
         <v>-1.35</v>
       </c>
       <c r="F3">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -916,7 +940,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -925,10 +949,10 @@
         <v>2.76</v>
       </c>
       <c r="M3">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>180</v>
       </c>
@@ -945,7 +969,7 @@
         <v>-0.35</v>
       </c>
       <c r="F4">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -954,7 +978,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -963,10 +987,10 @@
         <v>2.76</v>
       </c>
       <c r="M4">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>179</v>
       </c>
@@ -983,7 +1007,7 @@
         <v>-0.35</v>
       </c>
       <c r="F5">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -992,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1001,10 +1025,10 @@
         <v>2.76</v>
       </c>
       <c r="M5">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>178</v>
       </c>
@@ -1021,7 +1045,7 @@
         <v>-0.35</v>
       </c>
       <c r="F6">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1030,7 +1054,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1039,10 +1063,10 @@
         <v>2.76</v>
       </c>
       <c r="M6">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>177</v>
       </c>
@@ -1059,7 +1083,7 @@
         <v>-0.35</v>
       </c>
       <c r="F7">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1068,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1077,10 +1101,10 @@
         <v>2.76</v>
       </c>
       <c r="M7">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>176</v>
       </c>
@@ -1097,7 +1121,7 @@
         <v>-0.03</v>
       </c>
       <c r="F8">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1106,7 +1130,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1115,10 +1139,10 @@
         <v>2.76</v>
       </c>
       <c r="M8">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>175</v>
       </c>
@@ -1135,7 +1159,7 @@
         <v>-0.03</v>
       </c>
       <c r="F9">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1144,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1153,10 +1177,10 @@
         <v>2.76</v>
       </c>
       <c r="M9">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>174</v>
       </c>
@@ -1173,7 +1197,7 @@
         <v>-0.03</v>
       </c>
       <c r="F10">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1182,7 +1206,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1191,10 +1215,10 @@
         <v>2.76</v>
       </c>
       <c r="M10">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>173</v>
       </c>
@@ -1211,7 +1235,7 @@
         <v>-0.03</v>
       </c>
       <c r="F11">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1220,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1229,10 +1253,10 @@
         <v>2.76</v>
       </c>
       <c r="M11">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>172</v>
       </c>
@@ -1249,7 +1273,7 @@
         <v>0.47</v>
       </c>
       <c r="F12">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1258,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1267,10 +1291,10 @@
         <v>2.76</v>
       </c>
       <c r="M12">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>171</v>
       </c>
@@ -1287,7 +1311,7 @@
         <v>0.47</v>
       </c>
       <c r="F13">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1296,7 +1320,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1305,10 +1329,10 @@
         <v>2.76</v>
       </c>
       <c r="M13">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>170</v>
       </c>
@@ -1325,7 +1349,7 @@
         <v>0.47</v>
       </c>
       <c r="F14">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1334,7 +1358,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1343,10 +1367,10 @@
         <v>2.76</v>
       </c>
       <c r="M14">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>169</v>
       </c>
@@ -1363,7 +1387,7 @@
         <v>0.47</v>
       </c>
       <c r="F15">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1372,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1381,10 +1405,10 @@
         <v>2.76</v>
       </c>
       <c r="M15">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>168</v>
       </c>
@@ -1401,7 +1425,7 @@
         <v>0.49</v>
       </c>
       <c r="F16">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1410,7 +1434,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1419,10 +1443,10 @@
         <v>2.76</v>
       </c>
       <c r="M16">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>167</v>
       </c>
@@ -1439,7 +1463,7 @@
         <v>0.49</v>
       </c>
       <c r="F17">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1448,7 +1472,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1457,10 +1481,10 @@
         <v>2.76</v>
       </c>
       <c r="M17">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>166</v>
       </c>
@@ -1477,7 +1501,7 @@
         <v>0.49</v>
       </c>
       <c r="F18">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1486,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1495,10 +1519,10 @@
         <v>2.76</v>
       </c>
       <c r="M18">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>165</v>
       </c>
@@ -1515,7 +1539,7 @@
         <v>0.49</v>
       </c>
       <c r="F19">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1524,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1533,10 +1557,10 @@
         <v>2.76</v>
       </c>
       <c r="M19">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>164</v>
       </c>
@@ -1550,10 +1574,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F20">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1562,7 +1586,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1571,10 +1595,10 @@
         <v>2.76</v>
       </c>
       <c r="M20">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>163</v>
       </c>
@@ -1588,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F21">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1600,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1609,10 +1633,10 @@
         <v>2.76</v>
       </c>
       <c r="M21">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>162</v>
       </c>
@@ -1626,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F22">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1638,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1647,10 +1671,10 @@
         <v>2.76</v>
       </c>
       <c r="M22">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>161</v>
       </c>
@@ -1664,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="F23">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1676,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1685,10 +1709,10 @@
         <v>2.76</v>
       </c>
       <c r="M23">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>183</v>
       </c>
@@ -1705,7 +1729,7 @@
         <v>-1.35</v>
       </c>
       <c r="F24">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1714,7 +1738,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1723,10 +1747,10 @@
         <v>2.76</v>
       </c>
       <c r="M24">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>184</v>
       </c>
@@ -1743,7 +1767,7 @@
         <v>-1.35</v>
       </c>
       <c r="F25">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1752,7 +1776,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1761,10 +1785,10 @@
         <v>2.76</v>
       </c>
       <c r="M25">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>185</v>
       </c>
@@ -1790,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1799,10 +1823,10 @@
         <v>1.2</v>
       </c>
       <c r="M26">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>186</v>
       </c>
@@ -1828,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1837,10 +1861,10 @@
         <v>1.2</v>
       </c>
       <c r="M27">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>188</v>
       </c>
@@ -1866,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1875,10 +1899,10 @@
         <v>1.2</v>
       </c>
       <c r="M28">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>187</v>
       </c>
@@ -1904,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1913,10 +1937,10 @@
         <v>1.2</v>
       </c>
       <c r="M29">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>189</v>
       </c>
@@ -1930,10 +1954,10 @@
         <v>0.6</v>
       </c>
       <c r="E30">
-        <v>-0.9350000000000001</v>
+        <v>-0.93500000000000005</v>
       </c>
       <c r="F30">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -1942,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1951,10 +1975,10 @@
         <v>0.96</v>
       </c>
       <c r="M30">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>190</v>
       </c>
@@ -1968,10 +1992,10 @@
         <v>0.6</v>
       </c>
       <c r="E31">
-        <v>-0.9350000000000001</v>
+        <v>-0.93500000000000005</v>
       </c>
       <c r="F31">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -1980,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -1989,10 +2013,10 @@
         <v>0.96</v>
       </c>
       <c r="M31">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>191</v>
       </c>
@@ -2006,10 +2030,10 @@
         <v>0.6</v>
       </c>
       <c r="E32">
-        <v>-0.9350000000000001</v>
+        <v>-0.93500000000000005</v>
       </c>
       <c r="F32">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -2018,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2027,10 +2051,10 @@
         <v>0.96</v>
       </c>
       <c r="M32">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>192</v>
       </c>
@@ -2044,10 +2068,10 @@
         <v>0.6</v>
       </c>
       <c r="E33">
-        <v>-0.9350000000000001</v>
+        <v>-0.93500000000000005</v>
       </c>
       <c r="F33">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -2056,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2065,10 +2089,10 @@
         <v>0.96</v>
       </c>
       <c r="M33">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>196</v>
       </c>
@@ -2085,7 +2109,7 @@
         <v>0.3</v>
       </c>
       <c r="F34">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -2094,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2103,10 +2127,10 @@
         <v>0.6</v>
       </c>
       <c r="M34">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>195</v>
       </c>
@@ -2123,7 +2147,7 @@
         <v>0.3</v>
       </c>
       <c r="F35">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G35">
         <v>4</v>
@@ -2132,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2141,10 +2165,10 @@
         <v>0.6</v>
       </c>
       <c r="M35">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>194</v>
       </c>
@@ -2161,7 +2185,7 @@
         <v>0.3</v>
       </c>
       <c r="F36">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -2170,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2179,10 +2203,10 @@
         <v>0.6</v>
       </c>
       <c r="M36">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>193</v>
       </c>
@@ -2199,7 +2223,7 @@
         <v>0.3</v>
       </c>
       <c r="F37">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -2208,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2217,10 +2241,10 @@
         <v>0.6</v>
       </c>
       <c r="M37">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>197</v>
       </c>
@@ -2237,7 +2261,7 @@
         <v>0.93</v>
       </c>
       <c r="F38">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -2246,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2255,10 +2279,10 @@
         <v>1.8</v>
       </c>
       <c r="M38">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>198</v>
       </c>
@@ -2275,7 +2299,7 @@
         <v>0.48</v>
       </c>
       <c r="F39">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -2284,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2293,10 +2317,10 @@
         <v>1.8</v>
       </c>
       <c r="M39">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>199</v>
       </c>
@@ -2313,7 +2337,7 @@
         <v>0.03</v>
       </c>
       <c r="F40">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -2322,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2331,10 +2355,10 @@
         <v>1.8</v>
       </c>
       <c r="M40">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>200</v>
       </c>
@@ -2351,7 +2375,7 @@
         <v>1.155</v>
       </c>
       <c r="F41">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -2360,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -2369,10 +2393,10 @@
         <v>1.8</v>
       </c>
       <c r="M41">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>201</v>
       </c>
@@ -2389,7 +2413,7 @@
         <v>1.155</v>
       </c>
       <c r="F42">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G42">
         <v>5</v>
@@ -2398,7 +2422,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2407,10 +2431,10 @@
         <v>1.8</v>
       </c>
       <c r="M42">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>202</v>
       </c>
@@ -2427,7 +2451,7 @@
         <v>1.155</v>
       </c>
       <c r="F43">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G43">
         <v>5</v>
@@ -2436,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2445,10 +2469,10 @@
         <v>1.8</v>
       </c>
       <c r="M43">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>203</v>
       </c>
@@ -2465,7 +2489,7 @@
         <v>1.155</v>
       </c>
       <c r="F44">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G44">
         <v>5</v>
@@ -2474,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2483,10 +2507,10 @@
         <v>1.8</v>
       </c>
       <c r="M44">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>207</v>
       </c>
@@ -2503,7 +2527,7 @@
         <v>0.3</v>
       </c>
       <c r="F45">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -2512,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2521,10 +2545,10 @@
         <v>1.8</v>
       </c>
       <c r="M45">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>205</v>
       </c>
@@ -2541,7 +2565,7 @@
         <v>0.3</v>
       </c>
       <c r="F46">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G46">
         <v>6</v>
@@ -2550,7 +2574,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -2559,10 +2583,10 @@
         <v>1.8</v>
       </c>
       <c r="M46">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>206</v>
       </c>
@@ -2579,7 +2603,7 @@
         <v>0.3</v>
       </c>
       <c r="F47">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G47">
         <v>6</v>
@@ -2588,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2597,10 +2621,10 @@
         <v>1.8</v>
       </c>
       <c r="M47">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>208</v>
       </c>
@@ -2617,7 +2641,7 @@
         <v>-0.3</v>
       </c>
       <c r="F48">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -2626,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2635,10 +2659,10 @@
         <v>1.8</v>
       </c>
       <c r="M48">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>204</v>
       </c>
@@ -2655,7 +2679,7 @@
         <v>0.3</v>
       </c>
       <c r="F49">
-        <v>-0.775</v>
+        <v>-0.77500000000000002</v>
       </c>
       <c r="G49">
         <v>6</v>
@@ -2664,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2673,10 +2697,10 @@
         <v>1.8</v>
       </c>
       <c r="M49">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>210</v>
       </c>
@@ -2693,7 +2717,7 @@
         <v>-0.3</v>
       </c>
       <c r="F50">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G50">
         <v>6</v>
@@ -2702,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2711,10 +2735,10 @@
         <v>1.8</v>
       </c>
       <c r="M50">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>211</v>
       </c>
@@ -2731,7 +2755,7 @@
         <v>-0.3</v>
       </c>
       <c r="F51">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G51">
         <v>6</v>
@@ -2740,7 +2764,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -2749,10 +2773,10 @@
         <v>1.8</v>
       </c>
       <c r="M51">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>209</v>
       </c>
@@ -2769,7 +2793,7 @@
         <v>-0.3</v>
       </c>
       <c r="F52">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G52">
         <v>6</v>
@@ -2778,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2787,10 +2811,10 @@
         <v>1.8</v>
       </c>
       <c r="M52">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>216</v>
       </c>
@@ -2816,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2828,7 +2852,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>230</v>
       </c>
@@ -2845,7 +2869,7 @@
         <v>0.6</v>
       </c>
       <c r="F54">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G54" t="s">
         <v>86</v>
@@ -2854,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2866,7 +2890,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>212</v>
       </c>
@@ -2892,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2904,7 +2928,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>213</v>
       </c>
@@ -2930,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2942,7 +2966,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>214</v>
       </c>
@@ -2968,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2980,7 +3004,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>215</v>
       </c>
@@ -3006,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -3018,7 +3042,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>217</v>
       </c>
@@ -3044,7 +3068,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -3056,7 +3080,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>218</v>
       </c>
@@ -3082,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -3094,7 +3118,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>231</v>
       </c>
@@ -3111,7 +3135,7 @@
         <v>1.2</v>
       </c>
       <c r="F61">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G61" t="s">
         <v>86</v>
@@ -3120,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -3132,7 +3156,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>219</v>
       </c>
@@ -3158,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3170,7 +3194,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>221</v>
       </c>
@@ -3196,7 +3220,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3208,7 +3232,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>222</v>
       </c>
@@ -3234,7 +3258,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3246,7 +3270,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>223</v>
       </c>
@@ -3272,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3284,7 +3308,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>224</v>
       </c>
@@ -3310,7 +3334,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3322,7 +3346,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>225</v>
       </c>
@@ -3348,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3360,7 +3384,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>226</v>
       </c>
@@ -3377,7 +3401,7 @@
         <v>0.6</v>
       </c>
       <c r="F68">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G68" t="s">
         <v>86</v>
@@ -3386,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3398,7 +3422,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>227</v>
       </c>
@@ -3415,7 +3439,7 @@
         <v>1.2</v>
       </c>
       <c r="F69">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G69" t="s">
         <v>86</v>
@@ -3424,7 +3448,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3436,7 +3460,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>228</v>
       </c>
@@ -3447,13 +3471,13 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E70">
         <v>0.6</v>
       </c>
       <c r="F70">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G70" t="s">
         <v>86</v>
@@ -3462,7 +3486,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3474,7 +3498,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>229</v>
       </c>
@@ -3485,13 +3509,13 @@
         <v>84</v>
       </c>
       <c r="D71">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E71">
         <v>1.2</v>
       </c>
       <c r="F71">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G71" t="s">
         <v>86</v>
@@ -3500,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3512,7 +3536,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>220</v>
       </c>
@@ -3538,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3556,11 +3580,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="78.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3604,15 +3642,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
         <v>89</v>
-      </c>
-      <c r="C2" t="s">
-        <v>90</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3621,7 +3659,7 @@
         <v>0.06</v>
       </c>
       <c r="F2">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -3630,7 +3668,7 @@
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -3639,18 +3677,18 @@
         <v>2.76</v>
       </c>
       <c r="M2">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>235</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3659,7 +3697,7 @@
         <v>-0.255</v>
       </c>
       <c r="F3">
-        <v>0.137</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -3668,7 +3706,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3677,18 +3715,18 @@
         <v>2.76</v>
       </c>
       <c r="M3">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>234</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -3697,7 +3735,7 @@
         <v>0.375</v>
       </c>
       <c r="F4">
-        <v>0.137</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -3706,7 +3744,7 @@
         <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -3715,18 +3753,18 @@
         <v>2.76</v>
       </c>
       <c r="M4">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>233</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -3735,7 +3773,7 @@
         <v>-0.255</v>
       </c>
       <c r="F5">
-        <v>0.213</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3744,7 +3782,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -3753,18 +3791,18 @@
         <v>2.76</v>
       </c>
       <c r="M5">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>232</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -3773,7 +3811,7 @@
         <v>0.375</v>
       </c>
       <c r="F6">
-        <v>0.213</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3782,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -3791,27 +3829,27 @@
         <v>2.76</v>
       </c>
       <c r="M6">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>242</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D7">
         <v>0.6</v>
       </c>
       <c r="E7">
-        <v>-0.795</v>
+        <v>-0.79500000000000004</v>
       </c>
       <c r="F7">
-        <v>-0.08599999999999999</v>
+        <v>-8.5999999999999993E-2</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -3820,7 +3858,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -3829,18 +3867,18 @@
         <v>0.96</v>
       </c>
       <c r="M7">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8">
         <v>0.6</v>
@@ -3849,7 +3887,7 @@
         <v>-1.012</v>
       </c>
       <c r="F8">
-        <v>0.962</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -3858,7 +3896,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -3867,27 +3905,27 @@
         <v>0.96</v>
       </c>
       <c r="M8">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>237</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9">
         <v>0.6</v>
       </c>
       <c r="E9">
-        <v>-0.8120000000000001</v>
+        <v>-0.81200000000000006</v>
       </c>
       <c r="F9">
-        <v>0.962</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -3896,7 +3934,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -3905,18 +3943,18 @@
         <v>0.96</v>
       </c>
       <c r="M9">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>238</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D10">
         <v>0.6</v>
@@ -3934,7 +3972,7 @@
         <v>6</v>
       </c>
       <c r="I10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -3943,24 +3981,24 @@
         <v>0.96</v>
       </c>
       <c r="M10">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>239</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11">
         <v>0.6</v>
       </c>
       <c r="E11">
-        <v>-0.8120000000000001</v>
+        <v>-0.81200000000000006</v>
       </c>
       <c r="F11">
         <v>-0.188</v>
@@ -3972,7 +4010,7 @@
         <v>6</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -3981,27 +4019,27 @@
         <v>0.96</v>
       </c>
       <c r="M11">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>240</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D12">
         <v>0.6</v>
       </c>
       <c r="E12">
-        <v>-0.795</v>
+        <v>-0.79500000000000004</v>
       </c>
       <c r="F12">
-        <v>-0.014</v>
+        <v>-1.4E-2</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -4010,7 +4048,7 @@
         <v>6</v>
       </c>
       <c r="I12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -4019,27 +4057,27 @@
         <v>0.96</v>
       </c>
       <c r="M12">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>241</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>0.6</v>
       </c>
       <c r="E13">
-        <v>-0.655</v>
+        <v>-0.65500000000000003</v>
       </c>
       <c r="F13">
-        <v>-0.014</v>
+        <v>-1.4E-2</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -4048,7 +4086,7 @@
         <v>6</v>
       </c>
       <c r="I13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -4057,27 +4095,27 @@
         <v>0.96</v>
       </c>
       <c r="M13">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D14">
         <v>0.6</v>
       </c>
       <c r="E14">
-        <v>-0.912</v>
+        <v>-0.91200000000000003</v>
       </c>
       <c r="F14">
-        <v>0.387</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -4086,7 +4124,7 @@
         <v>6</v>
       </c>
       <c r="I14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -4095,27 +4133,27 @@
         <v>0.96</v>
       </c>
       <c r="M14">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>243</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15">
         <v>0.6</v>
       </c>
       <c r="E15">
-        <v>-0.655</v>
+        <v>-0.65500000000000003</v>
       </c>
       <c r="F15">
-        <v>-0.08599999999999999</v>
+        <v>-8.5999999999999993E-2</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -4124,7 +4162,7 @@
         <v>6</v>
       </c>
       <c r="I15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -4133,24 +4171,24 @@
         <v>0.96</v>
       </c>
       <c r="M15">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D16">
         <v>0.6</v>
       </c>
       <c r="E16">
-        <v>-0.725</v>
+        <v>-0.72499999999999998</v>
       </c>
       <c r="F16">
         <v>-0.05</v>
@@ -4162,7 +4200,7 @@
         <v>6</v>
       </c>
       <c r="I16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -4171,24 +4209,24 @@
         <v>0.96</v>
       </c>
       <c r="M16">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>245</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D17">
         <v>0.96</v>
       </c>
       <c r="E17">
-        <v>0.455</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="F17">
         <v>-0.375</v>
@@ -4200,7 +4238,7 @@
         <v>6</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -4209,18 +4247,18 @@
         <v>0.6</v>
       </c>
       <c r="M17">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D18">
         <v>0.96</v>
@@ -4238,7 +4276,7 @@
         <v>6</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -4247,24 +4285,24 @@
         <v>0.6</v>
       </c>
       <c r="M18">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>244</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19">
         <v>0.96</v>
       </c>
       <c r="E19">
-        <v>0.405</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="F19">
         <v>-0.375</v>
@@ -4276,7 +4314,7 @@
         <v>6</v>
       </c>
       <c r="I19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -4285,18 +4323,18 @@
         <v>0.6</v>
       </c>
       <c r="M19">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>256</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -4314,7 +4352,7 @@
         <v>6</v>
       </c>
       <c r="I20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -4323,18 +4361,18 @@
         <v>1.8</v>
       </c>
       <c r="M20">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>258</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4352,7 +4390,7 @@
         <v>6</v>
       </c>
       <c r="I21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -4361,18 +4399,18 @@
         <v>1.8</v>
       </c>
       <c r="M21">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>259</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -4390,7 +4428,7 @@
         <v>6</v>
       </c>
       <c r="I22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -4399,18 +4437,18 @@
         <v>1.8</v>
       </c>
       <c r="M22">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>260</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -4428,7 +4466,7 @@
         <v>6</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -4437,18 +4475,18 @@
         <v>1.8</v>
       </c>
       <c r="M23">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>261</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -4466,7 +4504,7 @@
         <v>6</v>
       </c>
       <c r="I24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -4475,18 +4513,18 @@
         <v>1.8</v>
       </c>
       <c r="M24">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>257</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -4504,7 +4542,7 @@
         <v>6</v>
       </c>
       <c r="I25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -4513,24 +4551,24 @@
         <v>1.8</v>
       </c>
       <c r="M25">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>250</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D26">
-        <v>0.08799999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E26">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F26">
         <v>-0.22</v>
@@ -4542,7 +4580,7 @@
         <v>6</v>
       </c>
       <c r="I26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -4551,18 +4589,18 @@
         <v>1.8</v>
       </c>
       <c r="M26">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>252</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D27">
         <v>0.183</v>
@@ -4571,7 +4609,7 @@
         <v>0.21</v>
       </c>
       <c r="F27">
-        <v>-0.402</v>
+        <v>-0.40200000000000002</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -4580,7 +4618,7 @@
         <v>6</v>
       </c>
       <c r="I27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -4589,27 +4627,27 @@
         <v>1.8</v>
       </c>
       <c r="M27">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>246</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D28">
-        <v>0.08799999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E28">
-        <v>-0.225</v>
+        <v>-0.22500000000000001</v>
       </c>
       <c r="F28">
-        <v>0.026</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -4618,7 +4656,7 @@
         <v>6</v>
       </c>
       <c r="I28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -4627,27 +4665,27 @@
         <v>1.8</v>
       </c>
       <c r="M28">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>247</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D29">
-        <v>0.08799999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E29">
-        <v>0.275</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="F29">
-        <v>0.026</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -4656,7 +4694,7 @@
         <v>6</v>
       </c>
       <c r="I29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -4665,27 +4703,27 @@
         <v>1.8</v>
       </c>
       <c r="M29">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>248</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D30">
-        <v>0.08799999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E30">
-        <v>-0.225</v>
+        <v>-0.22500000000000001</v>
       </c>
       <c r="F30">
-        <v>-0.466</v>
+        <v>-0.46600000000000003</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -4694,7 +4732,7 @@
         <v>6</v>
       </c>
       <c r="I30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -4703,27 +4741,27 @@
         <v>1.8</v>
       </c>
       <c r="M30">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>249</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D31">
-        <v>0.08799999999999999</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E31">
-        <v>0.275</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="F31">
-        <v>-0.466</v>
+        <v>-0.46600000000000003</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -4732,7 +4770,7 @@
         <v>6</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -4741,18 +4779,18 @@
         <v>1.8</v>
       </c>
       <c r="M31">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>251</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D32">
         <v>0.183</v>
@@ -4761,7 +4799,7 @@
         <v>-0.15</v>
       </c>
       <c r="F32">
-        <v>-0.402</v>
+        <v>-0.40200000000000002</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -4770,7 +4808,7 @@
         <v>6</v>
       </c>
       <c r="I32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -4779,18 +4817,18 @@
         <v>1.8</v>
       </c>
       <c r="M32">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>262</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -4808,7 +4846,7 @@
         <v>6</v>
       </c>
       <c r="I33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -4817,18 +4855,18 @@
         <v>1.8</v>
       </c>
       <c r="M33">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>253</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D34">
         <v>0.183</v>
@@ -4846,7 +4884,7 @@
         <v>6</v>
       </c>
       <c r="I34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -4855,18 +4893,18 @@
         <v>1.8</v>
       </c>
       <c r="M34">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>263</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -4884,7 +4922,7 @@
         <v>6</v>
       </c>
       <c r="I35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -4893,18 +4931,18 @@
         <v>1.8</v>
       </c>
       <c r="M35">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>255</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D36">
         <v>0.183</v>
@@ -4913,7 +4951,7 @@
         <v>0.03</v>
       </c>
       <c r="F36">
-        <v>-0.616</v>
+        <v>-0.61599999999999999</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -4922,7 +4960,7 @@
         <v>6</v>
       </c>
       <c r="I36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -4931,18 +4969,18 @@
         <v>1.8</v>
       </c>
       <c r="M36">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>156</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D37">
         <v>0.108</v>
@@ -4951,7 +4989,7 @@
         <v>0.03</v>
       </c>
       <c r="F37">
-        <v>-0.175</v>
+        <v>-0.17499999999999999</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -4960,7 +4998,7 @@
         <v>6</v>
       </c>
       <c r="I37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -4969,24 +5007,24 @@
         <v>1.8</v>
       </c>
       <c r="M37">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>158</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D38">
-        <v>0.208</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="E38">
-        <v>-0.095</v>
+        <v>-9.5000000000000001E-2</v>
       </c>
       <c r="F38">
         <v>-1.024</v>
@@ -4998,7 +5036,7 @@
         <v>6</v>
       </c>
       <c r="I38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -5007,18 +5045,18 @@
         <v>1.8</v>
       </c>
       <c r="M38">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>254</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D39">
         <v>0.183</v>
@@ -5036,7 +5074,7 @@
         <v>6</v>
       </c>
       <c r="I39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -5045,24 +5083,24 @@
         <v>1.8</v>
       </c>
       <c r="M39">
-        <v>2.655</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>2.6549999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>264</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D40">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E40">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F40">
         <v>-0.05</v>
@@ -5074,7 +5112,7 @@
         <v>6</v>
       </c>
       <c r="I40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -5086,18 +5124,18 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>266</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D41">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -5112,7 +5150,7 @@
         <v>6</v>
       </c>
       <c r="I41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -5124,15 +5162,15 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>277</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D42">
         <v>1.06</v>
@@ -5141,7 +5179,7 @@
         <v>1.585</v>
       </c>
       <c r="F42">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G42" t="s">
         <v>86</v>
@@ -5150,7 +5188,7 @@
         <v>6</v>
       </c>
       <c r="I42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -5162,15 +5200,15 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>267</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D43">
         <v>0.72</v>
@@ -5188,7 +5226,7 @@
         <v>6</v>
       </c>
       <c r="I43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -5200,15 +5238,15 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>276</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D44">
         <v>0.96</v>
@@ -5217,7 +5255,7 @@
         <v>1.585</v>
       </c>
       <c r="F44">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G44" t="s">
         <v>86</v>
@@ -5226,7 +5264,7 @@
         <v>6</v>
       </c>
       <c r="I44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -5238,24 +5276,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>270</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D45">
         <v>0.96</v>
       </c>
       <c r="E45">
-        <v>1.485</v>
+        <v>1.4850000000000001</v>
       </c>
       <c r="F45">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G45" t="s">
         <v>86</v>
@@ -5264,7 +5302,7 @@
         <v>6</v>
       </c>
       <c r="I45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -5276,24 +5314,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>271</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D46">
         <v>1.06</v>
       </c>
       <c r="E46">
-        <v>1.485</v>
+        <v>1.4850000000000001</v>
       </c>
       <c r="F46">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G46" t="s">
         <v>86</v>
@@ -5302,7 +5340,7 @@
         <v>6</v>
       </c>
       <c r="I46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -5314,21 +5352,21 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>273</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D47">
         <v>0.72</v>
       </c>
       <c r="E47">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F47">
         <v>-0.05</v>
@@ -5340,7 +5378,7 @@
         <v>6</v>
       </c>
       <c r="I47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -5352,24 +5390,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>157</v>
       </c>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D48">
         <v>1.01</v>
       </c>
       <c r="E48">
-        <v>1.535</v>
+        <v>1.5349999999999999</v>
       </c>
       <c r="F48">
-        <v>-0.025</v>
+        <v>-2.5000000000000001E-2</v>
       </c>
       <c r="G48" t="s">
         <v>86</v>
@@ -5378,7 +5416,7 @@
         <v>6</v>
       </c>
       <c r="I48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -5390,18 +5428,18 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>159</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D49">
-        <v>0.645</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="E49">
         <v>1.075</v>
@@ -5416,7 +5454,7 @@
         <v>6</v>
       </c>
       <c r="I49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -5434,31 +5472,31 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:O1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:15">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACAE0D87-4419-4FE4-863D-5B1C23EEFF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stage 2" sheetId="1" r:id="rId1"/>
     <sheet name="Stage 3" sheetId="2" r:id="rId2"/>
     <sheet name="Obstacles" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="144">
   <si>
     <t>Marking type</t>
   </si>
@@ -285,6 +279,9 @@
     <t>F</t>
   </si>
   <si>
+    <t>+</t>
+  </si>
+  <si>
     <t>blank</t>
   </si>
   <si>
@@ -433,6 +430,9 @@
   </si>
   <si>
     <t>BSS.FLOOR DRAIN_150:BSS.FLOOR DRAIN_150:1091065</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>Point number/name</t>
@@ -453,8 +453,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -517,21 +517,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -569,7 +561,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -603,7 +595,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -638,10 +629,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -814,25 +804,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -876,7 +852,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
         <v>182</v>
       </c>
@@ -893,7 +869,7 @@
         <v>-1.35</v>
       </c>
       <c r="F2">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -902,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -911,10 +887,10 @@
         <v>2.76</v>
       </c>
       <c r="M2">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1">
         <v>181</v>
       </c>
@@ -931,7 +907,7 @@
         <v>-1.35</v>
       </c>
       <c r="F3">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -940,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -949,10 +925,10 @@
         <v>2.76</v>
       </c>
       <c r="M3">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1">
         <v>180</v>
       </c>
@@ -969,7 +945,7 @@
         <v>-0.35</v>
       </c>
       <c r="F4">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -978,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -987,10 +963,10 @@
         <v>2.76</v>
       </c>
       <c r="M4">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
         <v>179</v>
       </c>
@@ -1007,7 +983,7 @@
         <v>-0.35</v>
       </c>
       <c r="F5">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1016,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1025,10 +1001,10 @@
         <v>2.76</v>
       </c>
       <c r="M5">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
         <v>178</v>
       </c>
@@ -1045,7 +1021,7 @@
         <v>-0.35</v>
       </c>
       <c r="F6">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1054,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1063,10 +1039,10 @@
         <v>2.76</v>
       </c>
       <c r="M6">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
         <v>177</v>
       </c>
@@ -1083,7 +1059,7 @@
         <v>-0.35</v>
       </c>
       <c r="F7">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1092,7 +1068,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1101,10 +1077,10 @@
         <v>2.76</v>
       </c>
       <c r="M7">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>176</v>
       </c>
@@ -1121,7 +1097,7 @@
         <v>-0.03</v>
       </c>
       <c r="F8">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1130,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1139,10 +1115,10 @@
         <v>2.76</v>
       </c>
       <c r="M8">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
         <v>175</v>
       </c>
@@ -1159,7 +1135,7 @@
         <v>-0.03</v>
       </c>
       <c r="F9">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1168,7 +1144,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1177,10 +1153,10 @@
         <v>2.76</v>
       </c>
       <c r="M9">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1">
         <v>174</v>
       </c>
@@ -1197,7 +1173,7 @@
         <v>-0.03</v>
       </c>
       <c r="F10">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1206,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1215,10 +1191,10 @@
         <v>2.76</v>
       </c>
       <c r="M10">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1">
         <v>173</v>
       </c>
@@ -1235,7 +1211,7 @@
         <v>-0.03</v>
       </c>
       <c r="F11">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1244,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1253,10 +1229,10 @@
         <v>2.76</v>
       </c>
       <c r="M11">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1">
         <v>172</v>
       </c>
@@ -1273,7 +1249,7 @@
         <v>0.47</v>
       </c>
       <c r="F12">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1282,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1291,10 +1267,10 @@
         <v>2.76</v>
       </c>
       <c r="M12">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1">
         <v>171</v>
       </c>
@@ -1311,7 +1287,7 @@
         <v>0.47</v>
       </c>
       <c r="F13">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1320,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1329,10 +1305,10 @@
         <v>2.76</v>
       </c>
       <c r="M13">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1">
         <v>170</v>
       </c>
@@ -1349,7 +1325,7 @@
         <v>0.47</v>
       </c>
       <c r="F14">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1358,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1367,10 +1343,10 @@
         <v>2.76</v>
       </c>
       <c r="M14">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1">
         <v>169</v>
       </c>
@@ -1387,7 +1363,7 @@
         <v>0.47</v>
       </c>
       <c r="F15">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1396,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1405,10 +1381,10 @@
         <v>2.76</v>
       </c>
       <c r="M15">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="1">
         <v>168</v>
       </c>
@@ -1425,7 +1401,7 @@
         <v>0.49</v>
       </c>
       <c r="F16">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1434,7 +1410,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1443,10 +1419,10 @@
         <v>2.76</v>
       </c>
       <c r="M16">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>167</v>
       </c>
@@ -1463,7 +1439,7 @@
         <v>0.49</v>
       </c>
       <c r="F17">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1472,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1481,10 +1457,10 @@
         <v>2.76</v>
       </c>
       <c r="M17">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>166</v>
       </c>
@@ -1501,7 +1477,7 @@
         <v>0.49</v>
       </c>
       <c r="F18">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1510,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1519,10 +1495,10 @@
         <v>2.76</v>
       </c>
       <c r="M18">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>165</v>
       </c>
@@ -1539,7 +1515,7 @@
         <v>0.49</v>
       </c>
       <c r="F19">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1548,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1557,10 +1533,10 @@
         <v>2.76</v>
       </c>
       <c r="M19">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>164</v>
       </c>
@@ -1574,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F20">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1586,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1595,10 +1571,10 @@
         <v>2.76</v>
       </c>
       <c r="M20">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>163</v>
       </c>
@@ -1612,10 +1588,10 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F21">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1624,7 +1600,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1633,10 +1609,10 @@
         <v>2.76</v>
       </c>
       <c r="M21">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>162</v>
       </c>
@@ -1650,10 +1626,10 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F22">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1662,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1671,10 +1647,10 @@
         <v>2.76</v>
       </c>
       <c r="M22">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <v>161</v>
       </c>
@@ -1688,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F23">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1700,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1709,10 +1685,10 @@
         <v>2.76</v>
       </c>
       <c r="M23">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>183</v>
       </c>
@@ -1729,7 +1705,7 @@
         <v>-1.35</v>
       </c>
       <c r="F24">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1738,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1747,10 +1723,10 @@
         <v>2.76</v>
       </c>
       <c r="M24">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <v>184</v>
       </c>
@@ -1767,7 +1743,7 @@
         <v>-1.35</v>
       </c>
       <c r="F25">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1776,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1785,10 +1761,10 @@
         <v>2.76</v>
       </c>
       <c r="M25">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
         <v>185</v>
       </c>
@@ -1814,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1823,10 +1799,10 @@
         <v>1.2</v>
       </c>
       <c r="M26">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
         <v>186</v>
       </c>
@@ -1852,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1861,10 +1837,10 @@
         <v>1.2</v>
       </c>
       <c r="M27">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
         <v>188</v>
       </c>
@@ -1890,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1899,10 +1875,10 @@
         <v>1.2</v>
       </c>
       <c r="M28">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
         <v>187</v>
       </c>
@@ -1928,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1937,10 +1913,10 @@
         <v>1.2</v>
       </c>
       <c r="M29">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
         <v>189</v>
       </c>
@@ -1954,10 +1930,10 @@
         <v>0.6</v>
       </c>
       <c r="E30">
-        <v>-0.93500000000000005</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F30">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G30">
         <v>3</v>
@@ -1966,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -1975,10 +1951,10 @@
         <v>0.96</v>
       </c>
       <c r="M30">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
         <v>190</v>
       </c>
@@ -1992,10 +1968,10 @@
         <v>0.6</v>
       </c>
       <c r="E31">
-        <v>-0.93500000000000005</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F31">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G31">
         <v>3</v>
@@ -2004,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2013,10 +1989,10 @@
         <v>0.96</v>
       </c>
       <c r="M31">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
         <v>191</v>
       </c>
@@ -2030,10 +2006,10 @@
         <v>0.6</v>
       </c>
       <c r="E32">
-        <v>-0.93500000000000005</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F32">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -2042,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2051,10 +2027,10 @@
         <v>0.96</v>
       </c>
       <c r="M32">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
         <v>192</v>
       </c>
@@ -2068,10 +2044,10 @@
         <v>0.6</v>
       </c>
       <c r="E33">
-        <v>-0.93500000000000005</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="F33">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G33">
         <v>3</v>
@@ -2080,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2089,10 +2065,10 @@
         <v>0.96</v>
       </c>
       <c r="M33">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
         <v>196</v>
       </c>
@@ -2109,7 +2085,7 @@
         <v>0.3</v>
       </c>
       <c r="F34">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -2118,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2127,10 +2103,10 @@
         <v>0.6</v>
       </c>
       <c r="M34">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
         <v>195</v>
       </c>
@@ -2147,7 +2123,7 @@
         <v>0.3</v>
       </c>
       <c r="F35">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G35">
         <v>4</v>
@@ -2156,7 +2132,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2165,10 +2141,10 @@
         <v>0.6</v>
       </c>
       <c r="M35">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
         <v>194</v>
       </c>
@@ -2185,7 +2161,7 @@
         <v>0.3</v>
       </c>
       <c r="F36">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -2194,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2203,10 +2179,10 @@
         <v>0.6</v>
       </c>
       <c r="M36">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1">
         <v>193</v>
       </c>
@@ -2223,7 +2199,7 @@
         <v>0.3</v>
       </c>
       <c r="F37">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -2232,7 +2208,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2241,10 +2217,10 @@
         <v>0.6</v>
       </c>
       <c r="M37">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1">
         <v>197</v>
       </c>
@@ -2261,7 +2237,7 @@
         <v>0.93</v>
       </c>
       <c r="F38">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -2270,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2279,10 +2255,10 @@
         <v>1.8</v>
       </c>
       <c r="M38">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
         <v>198</v>
       </c>
@@ -2299,7 +2275,7 @@
         <v>0.48</v>
       </c>
       <c r="F39">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -2308,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2317,10 +2293,10 @@
         <v>1.8</v>
       </c>
       <c r="M39">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
         <v>199</v>
       </c>
@@ -2337,7 +2313,7 @@
         <v>0.03</v>
       </c>
       <c r="F40">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -2346,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2355,10 +2331,10 @@
         <v>1.8</v>
       </c>
       <c r="M40">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="1">
         <v>200</v>
       </c>
@@ -2375,7 +2351,7 @@
         <v>1.155</v>
       </c>
       <c r="F41">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -2384,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -2393,10 +2369,10 @@
         <v>1.8</v>
       </c>
       <c r="M41">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="1">
         <v>201</v>
       </c>
@@ -2413,7 +2389,7 @@
         <v>1.155</v>
       </c>
       <c r="F42">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G42">
         <v>5</v>
@@ -2422,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2431,10 +2407,10 @@
         <v>1.8</v>
       </c>
       <c r="M42">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="1">
         <v>202</v>
       </c>
@@ -2451,7 +2427,7 @@
         <v>1.155</v>
       </c>
       <c r="F43">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G43">
         <v>5</v>
@@ -2460,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2469,10 +2445,10 @@
         <v>1.8</v>
       </c>
       <c r="M43">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="1">
         <v>203</v>
       </c>
@@ -2489,7 +2465,7 @@
         <v>1.155</v>
       </c>
       <c r="F44">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G44">
         <v>5</v>
@@ -2498,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2507,10 +2483,10 @@
         <v>1.8</v>
       </c>
       <c r="M44">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="1">
         <v>207</v>
       </c>
@@ -2527,7 +2503,7 @@
         <v>0.3</v>
       </c>
       <c r="F45">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -2536,7 +2512,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2545,10 +2521,10 @@
         <v>1.8</v>
       </c>
       <c r="M45">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="1">
         <v>205</v>
       </c>
@@ -2565,7 +2541,7 @@
         <v>0.3</v>
       </c>
       <c r="F46">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G46">
         <v>6</v>
@@ -2574,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -2583,10 +2559,10 @@
         <v>1.8</v>
       </c>
       <c r="M46">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="1">
         <v>206</v>
       </c>
@@ -2603,7 +2579,7 @@
         <v>0.3</v>
       </c>
       <c r="F47">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G47">
         <v>6</v>
@@ -2612,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2621,10 +2597,10 @@
         <v>1.8</v>
       </c>
       <c r="M47">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="1">
         <v>208</v>
       </c>
@@ -2641,7 +2617,7 @@
         <v>-0.3</v>
       </c>
       <c r="F48">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -2650,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2659,10 +2635,10 @@
         <v>1.8</v>
       </c>
       <c r="M48">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="1">
         <v>204</v>
       </c>
@@ -2679,7 +2655,7 @@
         <v>0.3</v>
       </c>
       <c r="F49">
-        <v>-0.77500000000000002</v>
+        <v>-0.775</v>
       </c>
       <c r="G49">
         <v>6</v>
@@ -2688,7 +2664,7 @@
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2697,10 +2673,10 @@
         <v>1.8</v>
       </c>
       <c r="M49">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="1">
         <v>210</v>
       </c>
@@ -2717,7 +2693,7 @@
         <v>-0.3</v>
       </c>
       <c r="F50">
-        <v>0.42499999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="G50">
         <v>6</v>
@@ -2726,7 +2702,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2735,10 +2711,10 @@
         <v>1.8</v>
       </c>
       <c r="M50">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="1">
         <v>211</v>
       </c>
@@ -2755,7 +2731,7 @@
         <v>-0.3</v>
       </c>
       <c r="F51">
-        <v>1.0249999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="G51">
         <v>6</v>
@@ -2764,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -2773,10 +2749,10 @@
         <v>1.8</v>
       </c>
       <c r="M51">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="1">
         <v>209</v>
       </c>
@@ -2793,7 +2769,7 @@
         <v>-0.3</v>
       </c>
       <c r="F52">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G52">
         <v>6</v>
@@ -2802,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2811,10 +2787,10 @@
         <v>1.8</v>
       </c>
       <c r="M52">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="1">
         <v>216</v>
       </c>
@@ -2840,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2852,7 +2828,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13">
       <c r="A54" s="1">
         <v>230</v>
       </c>
@@ -2869,7 +2845,7 @@
         <v>0.6</v>
       </c>
       <c r="F54">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G54" t="s">
         <v>86</v>
@@ -2878,7 +2854,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2890,7 +2866,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13">
       <c r="A55" s="1">
         <v>212</v>
       </c>
@@ -2916,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2928,7 +2904,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13">
       <c r="A56" s="1">
         <v>213</v>
       </c>
@@ -2954,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2966,7 +2942,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13">
       <c r="A57" s="1">
         <v>214</v>
       </c>
@@ -2992,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -3004,7 +2980,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13">
       <c r="A58" s="1">
         <v>215</v>
       </c>
@@ -3030,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -3042,7 +3018,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13">
       <c r="A59" s="1">
         <v>217</v>
       </c>
@@ -3068,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -3080,7 +3056,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13">
       <c r="A60" s="1">
         <v>218</v>
       </c>
@@ -3106,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -3118,7 +3094,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13">
       <c r="A61" s="1">
         <v>231</v>
       </c>
@@ -3135,7 +3111,7 @@
         <v>1.2</v>
       </c>
       <c r="F61">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G61" t="s">
         <v>86</v>
@@ -3144,7 +3120,7 @@
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -3156,7 +3132,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13">
       <c r="A62" s="1">
         <v>219</v>
       </c>
@@ -3182,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3194,7 +3170,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13">
       <c r="A63" s="1">
         <v>221</v>
       </c>
@@ -3220,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3232,7 +3208,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13">
       <c r="A64" s="1">
         <v>222</v>
       </c>
@@ -3258,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3270,7 +3246,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13">
       <c r="A65" s="1">
         <v>223</v>
       </c>
@@ -3296,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3308,7 +3284,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13">
       <c r="A66" s="1">
         <v>224</v>
       </c>
@@ -3334,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3346,7 +3322,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13">
       <c r="A67" s="1">
         <v>225</v>
       </c>
@@ -3372,7 +3348,7 @@
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3384,7 +3360,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13">
       <c r="A68" s="1">
         <v>226</v>
       </c>
@@ -3401,7 +3377,7 @@
         <v>0.6</v>
       </c>
       <c r="F68">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G68" t="s">
         <v>86</v>
@@ -3410,7 +3386,7 @@
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3422,7 +3398,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13">
       <c r="A69" s="1">
         <v>227</v>
       </c>
@@ -3439,7 +3415,7 @@
         <v>1.2</v>
       </c>
       <c r="F69">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G69" t="s">
         <v>86</v>
@@ -3448,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3460,7 +3436,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13">
       <c r="A70" s="1">
         <v>228</v>
       </c>
@@ -3471,13 +3447,13 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>2.0099999999999998</v>
+        <v>2.01</v>
       </c>
       <c r="E70">
         <v>0.6</v>
       </c>
       <c r="F70">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G70" t="s">
         <v>86</v>
@@ -3486,7 +3462,7 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3498,7 +3474,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13">
       <c r="A71" s="1">
         <v>229</v>
       </c>
@@ -3509,13 +3485,13 @@
         <v>84</v>
       </c>
       <c r="D71">
-        <v>2.0099999999999998</v>
+        <v>2.01</v>
       </c>
       <c r="E71">
         <v>1.2</v>
       </c>
       <c r="F71">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G71" t="s">
         <v>86</v>
@@ -3524,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3536,7 +3512,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13">
       <c r="A72" s="1">
         <v>220</v>
       </c>
@@ -3562,7 +3538,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3580,25 +3556,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="78.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3642,15 +3604,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3659,7 +3621,7 @@
         <v>0.06</v>
       </c>
       <c r="F2">
-        <v>0.17499999999999999</v>
+        <v>0.175</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -3668,7 +3630,7 @@
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -3677,18 +3639,18 @@
         <v>2.76</v>
       </c>
       <c r="M2">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1">
         <v>235</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3697,7 +3659,7 @@
         <v>-0.255</v>
       </c>
       <c r="F3">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -3706,7 +3668,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3715,18 +3677,18 @@
         <v>2.76</v>
       </c>
       <c r="M3">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1">
         <v>234</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -3735,7 +3697,7 @@
         <v>0.375</v>
       </c>
       <c r="F4">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -3744,7 +3706,7 @@
         <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -3753,18 +3715,18 @@
         <v>2.76</v>
       </c>
       <c r="M4">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
         <v>233</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -3773,7 +3735,7 @@
         <v>-0.255</v>
       </c>
       <c r="F5">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3782,7 +3744,7 @@
         <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -3791,18 +3753,18 @@
         <v>2.76</v>
       </c>
       <c r="M5">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
         <v>232</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -3811,7 +3773,7 @@
         <v>0.375</v>
       </c>
       <c r="F6">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3820,7 +3782,7 @@
         <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -3829,27 +3791,27 @@
         <v>2.76</v>
       </c>
       <c r="M6">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
         <v>242</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7">
         <v>0.6</v>
       </c>
       <c r="E7">
-        <v>-0.79500000000000004</v>
+        <v>-0.795</v>
       </c>
       <c r="F7">
-        <v>-8.5999999999999993E-2</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -3858,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -3867,18 +3829,18 @@
         <v>0.96</v>
       </c>
       <c r="M7">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8">
         <v>0.6</v>
@@ -3887,7 +3849,7 @@
         <v>-1.012</v>
       </c>
       <c r="F8">
-        <v>0.96199999999999997</v>
+        <v>0.962</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -3896,7 +3858,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -3905,27 +3867,27 @@
         <v>0.96</v>
       </c>
       <c r="M8">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
         <v>237</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9">
         <v>0.6</v>
       </c>
       <c r="E9">
-        <v>-0.81200000000000006</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="F9">
-        <v>0.96199999999999997</v>
+        <v>0.962</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -3934,7 +3896,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -3943,18 +3905,18 @@
         <v>0.96</v>
       </c>
       <c r="M9">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1">
         <v>238</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10">
         <v>0.6</v>
@@ -3972,7 +3934,7 @@
         <v>6</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -3981,24 +3943,24 @@
         <v>0.96</v>
       </c>
       <c r="M10">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1">
         <v>239</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11">
         <v>0.6</v>
       </c>
       <c r="E11">
-        <v>-0.81200000000000006</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="F11">
         <v>-0.188</v>
@@ -4010,7 +3972,7 @@
         <v>6</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -4019,27 +3981,27 @@
         <v>0.96</v>
       </c>
       <c r="M11">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1">
         <v>240</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>0.6</v>
       </c>
       <c r="E12">
-        <v>-0.79500000000000004</v>
+        <v>-0.795</v>
       </c>
       <c r="F12">
-        <v>-1.4E-2</v>
+        <v>-0.014</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -4048,7 +4010,7 @@
         <v>6</v>
       </c>
       <c r="I12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -4057,27 +4019,27 @@
         <v>0.96</v>
       </c>
       <c r="M12">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1">
         <v>241</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13">
         <v>0.6</v>
       </c>
       <c r="E13">
-        <v>-0.65500000000000003</v>
+        <v>-0.655</v>
       </c>
       <c r="F13">
-        <v>-1.4E-2</v>
+        <v>-0.014</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -4086,7 +4048,7 @@
         <v>6</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -4095,27 +4057,27 @@
         <v>0.96</v>
       </c>
       <c r="M13">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1">
         <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14">
         <v>0.6</v>
       </c>
       <c r="E14">
-        <v>-0.91200000000000003</v>
+        <v>-0.912</v>
       </c>
       <c r="F14">
-        <v>0.38700000000000001</v>
+        <v>0.387</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -4124,7 +4086,7 @@
         <v>6</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -4133,27 +4095,27 @@
         <v>0.96</v>
       </c>
       <c r="M14">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1">
         <v>243</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15">
         <v>0.6</v>
       </c>
       <c r="E15">
-        <v>-0.65500000000000003</v>
+        <v>-0.655</v>
       </c>
       <c r="F15">
-        <v>-8.5999999999999993E-2</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -4162,7 +4124,7 @@
         <v>6</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -4171,24 +4133,24 @@
         <v>0.96</v>
       </c>
       <c r="M15">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="1">
         <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D16">
         <v>0.6</v>
       </c>
       <c r="E16">
-        <v>-0.72499999999999998</v>
+        <v>-0.725</v>
       </c>
       <c r="F16">
         <v>-0.05</v>
@@ -4200,7 +4162,7 @@
         <v>6</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -4209,24 +4171,24 @@
         <v>0.96</v>
       </c>
       <c r="M16">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>245</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D17">
         <v>0.96</v>
       </c>
       <c r="E17">
-        <v>0.45500000000000002</v>
+        <v>0.455</v>
       </c>
       <c r="F17">
         <v>-0.375</v>
@@ -4238,7 +4200,7 @@
         <v>6</v>
       </c>
       <c r="I17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -4247,18 +4209,18 @@
         <v>0.6</v>
       </c>
       <c r="M17">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18">
         <v>0.96</v>
@@ -4276,7 +4238,7 @@
         <v>6</v>
       </c>
       <c r="I18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -4285,24 +4247,24 @@
         <v>0.6</v>
       </c>
       <c r="M18">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>244</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19">
         <v>0.96</v>
       </c>
       <c r="E19">
-        <v>0.40500000000000003</v>
+        <v>0.405</v>
       </c>
       <c r="F19">
         <v>-0.375</v>
@@ -4314,7 +4276,7 @@
         <v>6</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -4323,18 +4285,18 @@
         <v>0.6</v>
       </c>
       <c r="M19">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>256</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -4352,7 +4314,7 @@
         <v>6</v>
       </c>
       <c r="I20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -4361,18 +4323,18 @@
         <v>1.8</v>
       </c>
       <c r="M20">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>258</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4390,7 +4352,7 @@
         <v>6</v>
       </c>
       <c r="I21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -4399,18 +4361,18 @@
         <v>1.8</v>
       </c>
       <c r="M21">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>259</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -4428,7 +4390,7 @@
         <v>6</v>
       </c>
       <c r="I22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -4437,18 +4399,18 @@
         <v>1.8</v>
       </c>
       <c r="M22">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="1">
         <v>260</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -4466,7 +4428,7 @@
         <v>6</v>
       </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -4475,18 +4437,18 @@
         <v>1.8</v>
       </c>
       <c r="M23">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="1">
         <v>261</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -4504,7 +4466,7 @@
         <v>6</v>
       </c>
       <c r="I24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -4513,18 +4475,18 @@
         <v>1.8</v>
       </c>
       <c r="M24">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="1">
         <v>257</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -4542,7 +4504,7 @@
         <v>6</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -4551,24 +4513,24 @@
         <v>1.8</v>
       </c>
       <c r="M25">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="1">
         <v>250</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D26">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E26">
-        <v>2.5000000000000001E-2</v>
+        <v>0.025</v>
       </c>
       <c r="F26">
         <v>-0.22</v>
@@ -4580,7 +4542,7 @@
         <v>6</v>
       </c>
       <c r="I26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -4589,18 +4551,18 @@
         <v>1.8</v>
       </c>
       <c r="M26">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="1">
         <v>252</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D27">
         <v>0.183</v>
@@ -4609,7 +4571,7 @@
         <v>0.21</v>
       </c>
       <c r="F27">
-        <v>-0.40200000000000002</v>
+        <v>-0.402</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -4618,7 +4580,7 @@
         <v>6</v>
       </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -4627,27 +4589,27 @@
         <v>1.8</v>
       </c>
       <c r="M27">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1">
         <v>246</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D28">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E28">
-        <v>-0.22500000000000001</v>
+        <v>-0.225</v>
       </c>
       <c r="F28">
-        <v>2.5999999999999999E-2</v>
+        <v>0.026</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -4656,7 +4618,7 @@
         <v>6</v>
       </c>
       <c r="I28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -4665,27 +4627,27 @@
         <v>1.8</v>
       </c>
       <c r="M28">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1">
         <v>247</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E29">
-        <v>0.27500000000000002</v>
+        <v>0.275</v>
       </c>
       <c r="F29">
-        <v>2.5999999999999999E-2</v>
+        <v>0.026</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -4694,7 +4656,7 @@
         <v>6</v>
       </c>
       <c r="I29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -4703,27 +4665,27 @@
         <v>1.8</v>
       </c>
       <c r="M29">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="1">
         <v>248</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E30">
-        <v>-0.22500000000000001</v>
+        <v>-0.225</v>
       </c>
       <c r="F30">
-        <v>-0.46600000000000003</v>
+        <v>-0.466</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -4732,7 +4694,7 @@
         <v>6</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -4741,27 +4703,27 @@
         <v>1.8</v>
       </c>
       <c r="M30">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1">
         <v>249</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D31">
-        <v>8.7999999999999995E-2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E31">
-        <v>0.27500000000000002</v>
+        <v>0.275</v>
       </c>
       <c r="F31">
-        <v>-0.46600000000000003</v>
+        <v>-0.466</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -4770,7 +4732,7 @@
         <v>6</v>
       </c>
       <c r="I31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -4779,18 +4741,18 @@
         <v>1.8</v>
       </c>
       <c r="M31">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="1">
         <v>251</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D32">
         <v>0.183</v>
@@ -4799,7 +4761,7 @@
         <v>-0.15</v>
       </c>
       <c r="F32">
-        <v>-0.40200000000000002</v>
+        <v>-0.402</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -4808,7 +4770,7 @@
         <v>6</v>
       </c>
       <c r="I32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -4817,18 +4779,18 @@
         <v>1.8</v>
       </c>
       <c r="M32">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
         <v>262</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -4846,7 +4808,7 @@
         <v>6</v>
       </c>
       <c r="I33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -4855,18 +4817,18 @@
         <v>1.8</v>
       </c>
       <c r="M33">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
         <v>253</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D34">
         <v>0.183</v>
@@ -4884,7 +4846,7 @@
         <v>6</v>
       </c>
       <c r="I34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -4893,18 +4855,18 @@
         <v>1.8</v>
       </c>
       <c r="M34">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
         <v>263</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -4922,7 +4884,7 @@
         <v>6</v>
       </c>
       <c r="I35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -4931,18 +4893,18 @@
         <v>1.8</v>
       </c>
       <c r="M35">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
         <v>255</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D36">
         <v>0.183</v>
@@ -4951,7 +4913,7 @@
         <v>0.03</v>
       </c>
       <c r="F36">
-        <v>-0.61599999999999999</v>
+        <v>-0.616</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -4960,7 +4922,7 @@
         <v>6</v>
       </c>
       <c r="I36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -4969,18 +4931,18 @@
         <v>1.8</v>
       </c>
       <c r="M36">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="1">
         <v>156</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D37">
         <v>0.108</v>
@@ -4989,7 +4951,7 @@
         <v>0.03</v>
       </c>
       <c r="F37">
-        <v>-0.17499999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -4998,7 +4960,7 @@
         <v>6</v>
       </c>
       <c r="I37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -5007,24 +4969,24 @@
         <v>1.8</v>
       </c>
       <c r="M37">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="1">
         <v>158</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D38">
-        <v>0.20799999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="E38">
-        <v>-9.5000000000000001E-2</v>
+        <v>-0.095</v>
       </c>
       <c r="F38">
         <v>-1.024</v>
@@ -5036,7 +4998,7 @@
         <v>6</v>
       </c>
       <c r="I38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -5045,18 +5007,18 @@
         <v>1.8</v>
       </c>
       <c r="M38">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="1">
         <v>254</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D39">
         <v>0.183</v>
@@ -5074,7 +5036,7 @@
         <v>6</v>
       </c>
       <c r="I39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -5083,24 +5045,24 @@
         <v>1.8</v>
       </c>
       <c r="M39">
-        <v>2.6549999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>2.655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="1">
         <v>264</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D40">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="E40">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="F40">
         <v>-0.05</v>
@@ -5112,7 +5074,7 @@
         <v>6</v>
       </c>
       <c r="I40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -5124,18 +5086,18 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13">
       <c r="A41" s="1">
         <v>266</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D41">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -5150,7 +5112,7 @@
         <v>6</v>
       </c>
       <c r="I41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -5162,15 +5124,15 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13">
       <c r="A42" s="1">
         <v>277</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D42">
         <v>1.06</v>
@@ -5179,7 +5141,7 @@
         <v>1.585</v>
       </c>
       <c r="F42">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G42" t="s">
         <v>86</v>
@@ -5188,7 +5150,7 @@
         <v>6</v>
       </c>
       <c r="I42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -5200,15 +5162,15 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13">
       <c r="A43" s="1">
         <v>267</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D43">
         <v>0.72</v>
@@ -5226,7 +5188,7 @@
         <v>6</v>
       </c>
       <c r="I43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -5238,15 +5200,15 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13">
       <c r="A44" s="1">
         <v>276</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D44">
         <v>0.96</v>
@@ -5255,7 +5217,7 @@
         <v>1.585</v>
       </c>
       <c r="F44">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G44" t="s">
         <v>86</v>
@@ -5264,7 +5226,7 @@
         <v>6</v>
       </c>
       <c r="I44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -5276,24 +5238,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13">
       <c r="A45" s="1">
         <v>270</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D45">
         <v>0.96</v>
       </c>
       <c r="E45">
-        <v>1.4850000000000001</v>
+        <v>1.485</v>
       </c>
       <c r="F45">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G45" t="s">
         <v>86</v>
@@ -5302,7 +5264,7 @@
         <v>6</v>
       </c>
       <c r="I45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -5314,24 +5276,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13">
       <c r="A46" s="1">
         <v>271</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D46">
         <v>1.06</v>
       </c>
       <c r="E46">
-        <v>1.4850000000000001</v>
+        <v>1.485</v>
       </c>
       <c r="F46">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G46" t="s">
         <v>86</v>
@@ -5340,7 +5302,7 @@
         <v>6</v>
       </c>
       <c r="I46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -5352,21 +5314,21 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13">
       <c r="A47" s="1">
         <v>273</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D47">
         <v>0.72</v>
       </c>
       <c r="E47">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="F47">
         <v>-0.05</v>
@@ -5378,7 +5340,7 @@
         <v>6</v>
       </c>
       <c r="I47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -5390,24 +5352,24 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13">
       <c r="A48" s="1">
         <v>157</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D48">
         <v>1.01</v>
       </c>
       <c r="E48">
-        <v>1.5349999999999999</v>
+        <v>1.535</v>
       </c>
       <c r="F48">
-        <v>-2.5000000000000001E-2</v>
+        <v>-0.025</v>
       </c>
       <c r="G48" t="s">
         <v>86</v>
@@ -5416,7 +5378,7 @@
         <v>6</v>
       </c>
       <c r="I48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -5428,18 +5390,18 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13">
       <c r="A49" s="1">
         <v>159</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D49">
-        <v>0.64500000000000002</v>
+        <v>0.645</v>
       </c>
       <c r="E49">
         <v>1.075</v>
@@ -5454,7 +5416,7 @@
         <v>6</v>
       </c>
       <c r="I49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -5472,31 +5434,31 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:O1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>

--- a/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
+++ b/Greyform/Python_Application/exporteddatassss(with TMP)(draft)(tetra).xlsx
@@ -863,10 +863,10 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="E2">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>-0.175</v>
@@ -901,10 +901,10 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="E3">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>-0.775</v>
@@ -939,10 +939,10 @@
         <v>17</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E4">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>1.025</v>
@@ -977,10 +977,10 @@
         <v>18</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E5">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0.425</v>
@@ -1015,10 +1015,10 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E6">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>-0.175</v>
@@ -1053,10 +1053,10 @@
         <v>20</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E7">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>-0.775</v>
@@ -1091,10 +1091,10 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E8">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>1.025</v>
@@ -1129,10 +1129,10 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E9">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0.425</v>
@@ -1167,10 +1167,10 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E10">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>-0.175</v>
@@ -1205,10 +1205,10 @@
         <v>24</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E11">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>-0.775</v>
@@ -1243,10 +1243,10 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="E12">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>1.025</v>
@@ -1281,10 +1281,10 @@
         <v>26</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="E13">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0.425</v>
@@ -1319,10 +1319,10 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="E14">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>-0.175</v>
@@ -1357,10 +1357,10 @@
         <v>28</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>-0.47</v>
       </c>
       <c r="E15">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>-0.775</v>
@@ -1395,10 +1395,10 @@
         <v>29</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="E16">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>1.025</v>
@@ -1433,10 +1433,10 @@
         <v>30</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="E17">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0.425</v>
@@ -1471,10 +1471,10 @@
         <v>31</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="E18">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>-0.175</v>
@@ -1509,10 +1509,10 @@
         <v>32</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="E19">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>-0.775</v>
@@ -1547,10 +1547,10 @@
         <v>33</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="E20">
-        <v>0.9350000000000001</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>1.025</v>
@@ -1585,10 +1585,10 @@
         <v>34</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="E21">
-        <v>0.9350000000000001</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>0.425</v>
@@ -1623,10 +1623,10 @@
         <v>35</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="E22">
-        <v>0.9350000000000001</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>-0.175</v>
@@ -1661,10 +1661,10 @@
         <v>36</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="E23">
-        <v>0.9350000000000001</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>-0.775</v>
@@ -1699,10 +1699,10 @@
         <v>37</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="E24">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>0.425</v>
@@ -1737,10 +1737,10 @@
         <v>38</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="E25">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>1.025</v>
@@ -1775,10 +1775,10 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E26">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>-0.75</v>
@@ -1813,10 +1813,10 @@
         <v>40</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E27">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>-0.15</v>
@@ -1851,10 +1851,10 @@
         <v>41</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E28">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>-0.15</v>
@@ -1889,10 +1889,10 @@
         <v>42</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E29">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>-0.75</v>
@@ -1927,10 +1927,10 @@
         <v>43</v>
       </c>
       <c r="D30">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E30">
         <v>0.6</v>
-      </c>
-      <c r="E30">
-        <v>-0.9350000000000001</v>
       </c>
       <c r="F30">
         <v>-0.775</v>
@@ -1965,10 +1965,10 @@
         <v>44</v>
       </c>
       <c r="D31">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E31">
         <v>0.6</v>
-      </c>
-      <c r="E31">
-        <v>-0.9350000000000001</v>
       </c>
       <c r="F31">
         <v>-0.175</v>
@@ -2003,10 +2003,10 @@
         <v>45</v>
       </c>
       <c r="D32">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E32">
         <v>0.6</v>
-      </c>
-      <c r="E32">
-        <v>-0.9350000000000001</v>
       </c>
       <c r="F32">
         <v>0.425</v>
@@ -2041,10 +2041,10 @@
         <v>46</v>
       </c>
       <c r="D33">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E33">
         <v>0.6</v>
-      </c>
-      <c r="E33">
-        <v>-0.9350000000000001</v>
       </c>
       <c r="F33">
         <v>1.025</v>
@@ -2079,10 +2079,10 @@
         <v>47</v>
       </c>
       <c r="D34">
+        <v>-0.3</v>
+      </c>
+      <c r="E34">
         <v>0.96</v>
-      </c>
-      <c r="E34">
-        <v>0.3</v>
       </c>
       <c r="F34">
         <v>1.025</v>
@@ -2117,10 +2117,10 @@
         <v>48</v>
       </c>
       <c r="D35">
+        <v>-0.3</v>
+      </c>
+      <c r="E35">
         <v>0.96</v>
-      </c>
-      <c r="E35">
-        <v>0.3</v>
       </c>
       <c r="F35">
         <v>0.425</v>
@@ -2155,10 +2155,10 @@
         <v>49</v>
       </c>
       <c r="D36">
+        <v>-0.3</v>
+      </c>
+      <c r="E36">
         <v>0.96</v>
-      </c>
-      <c r="E36">
-        <v>0.3</v>
       </c>
       <c r="F36">
         <v>-0.175</v>
@@ -2193,10 +2193,10 @@
         <v>50</v>
       </c>
       <c r="D37">
+        <v>-0.3</v>
+      </c>
+      <c r="E37">
         <v>0.96</v>
-      </c>
-      <c r="E37">
-        <v>0.3</v>
       </c>
       <c r="F37">
         <v>-0.775</v>
@@ -2231,10 +2231,10 @@
         <v>51</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="E38">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>-0.775</v>
@@ -2269,10 +2269,10 @@
         <v>52</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>-0.48</v>
       </c>
       <c r="E39">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>-0.775</v>
@@ -2307,10 +2307,10 @@
         <v>53</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="E40">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>-0.775</v>
@@ -2345,10 +2345,10 @@
         <v>54</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>-1.155</v>
       </c>
       <c r="E41">
-        <v>1.155</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>-0.775</v>
@@ -2383,10 +2383,10 @@
         <v>55</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>-1.155</v>
       </c>
       <c r="E42">
-        <v>1.155</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>-0.175</v>
@@ -2421,10 +2421,10 @@
         <v>56</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>-1.155</v>
       </c>
       <c r="E43">
-        <v>1.155</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>0.425</v>
@@ -2459,10 +2459,10 @@
         <v>57</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>-1.155</v>
       </c>
       <c r="E44">
-        <v>1.155</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>1.025</v>
@@ -2497,10 +2497,10 @@
         <v>58</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E45">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>1.025</v>
@@ -2535,10 +2535,10 @@
         <v>59</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E46">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>-0.175</v>
@@ -2573,10 +2573,10 @@
         <v>60</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E47">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>0.425</v>
@@ -2611,10 +2611,10 @@
         <v>61</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E48">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>-0.775</v>
@@ -2649,10 +2649,10 @@
         <v>62</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E49">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>-0.775</v>
@@ -2687,10 +2687,10 @@
         <v>63</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E50">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>0.425</v>
@@ -2725,10 +2725,10 @@
         <v>64</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E51">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>1.025</v>
@@ -2763,10 +2763,10 @@
         <v>65</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E52">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>-0.175</v>
@@ -2801,13 +2801,13 @@
         <v>66</v>
       </c>
       <c r="D53">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E53">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="F53">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G53" t="s">
         <v>86</v>
@@ -2839,13 +2839,13 @@
         <v>67</v>
       </c>
       <c r="D54">
-        <v>2.61</v>
+        <v>1.305</v>
       </c>
       <c r="E54">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F54">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G54" t="s">
         <v>86</v>
@@ -2877,13 +2877,13 @@
         <v>68</v>
       </c>
       <c r="D55">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E55">
-        <v>0.15</v>
+        <v>0.075</v>
       </c>
       <c r="F55">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G55" t="s">
         <v>86</v>
@@ -2915,13 +2915,13 @@
         <v>69</v>
       </c>
       <c r="D56">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E56">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F56">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G56" t="s">
         <v>86</v>
@@ -2953,13 +2953,13 @@
         <v>70</v>
       </c>
       <c r="D57">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E57">
-        <v>0.45</v>
+        <v>0.225</v>
       </c>
       <c r="F57">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G57" t="s">
         <v>86</v>
@@ -2991,13 +2991,13 @@
         <v>71</v>
       </c>
       <c r="D58">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E58">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F58">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G58" t="s">
         <v>86</v>
@@ -3029,13 +3029,13 @@
         <v>72</v>
       </c>
       <c r="D59">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E59">
-        <v>0.9</v>
+        <v>0.45</v>
       </c>
       <c r="F59">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G59" t="s">
         <v>86</v>
@@ -3067,13 +3067,13 @@
         <v>73</v>
       </c>
       <c r="D60">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="E60">
-        <v>1.05</v>
+        <v>0.525</v>
       </c>
       <c r="F60">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G60" t="s">
         <v>86</v>
@@ -3105,13 +3105,13 @@
         <v>74</v>
       </c>
       <c r="D61">
-        <v>2.61</v>
+        <v>1.305</v>
       </c>
       <c r="E61">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F61">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G61" t="s">
         <v>86</v>
@@ -3143,13 +3143,13 @@
         <v>75</v>
       </c>
       <c r="D62">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="E62">
-        <v>0.15</v>
+        <v>0.075</v>
       </c>
       <c r="F62">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G62" t="s">
         <v>86</v>
@@ -3181,13 +3181,13 @@
         <v>76</v>
       </c>
       <c r="D63">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="E63">
-        <v>0.45</v>
+        <v>0.225</v>
       </c>
       <c r="F63">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G63" t="s">
         <v>86</v>
@@ -3219,13 +3219,13 @@
         <v>77</v>
       </c>
       <c r="D64">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="E64">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F64">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G64" t="s">
         <v>86</v>
@@ -3257,13 +3257,13 @@
         <v>78</v>
       </c>
       <c r="D65">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="E65">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="F65">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G65" t="s">
         <v>86</v>
@@ -3295,13 +3295,13 @@
         <v>79</v>
       </c>
       <c r="D66">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="E66">
-        <v>0.9</v>
+        <v>0.45</v>
       </c>
       <c r="F66">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G66" t="s">
         <v>86</v>
@@ -3333,13 +3333,13 @@
         <v>80</v>
       </c>
       <c r="D67">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="E67">
-        <v>1.05</v>
+        <v>0.525</v>
       </c>
       <c r="F67">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G67" t="s">
         <v>86</v>
@@ -3371,13 +3371,13 @@
         <v>81</v>
       </c>
       <c r="D68">
-        <v>1.41</v>
+        <v>0.705</v>
       </c>
       <c r="E68">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F68">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G68" t="s">
         <v>86</v>
@@ -3409,13 +3409,13 @@
         <v>82</v>
       </c>
       <c r="D69">
-        <v>1.41</v>
+        <v>0.705</v>
       </c>
       <c r="E69">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F69">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G69" t="s">
         <v>86</v>
@@ -3447,13 +3447,13 @@
         <v>83</v>
       </c>
       <c r="D70">
-        <v>2.01</v>
+        <v>1.005</v>
       </c>
       <c r="E70">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F70">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G70" t="s">
         <v>86</v>
@@ -3485,13 +3485,13 @@
         <v>84</v>
       </c>
       <c r="D71">
-        <v>2.01</v>
+        <v>1.005</v>
       </c>
       <c r="E71">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F71">
-        <v>-0.025</v>
+        <v>-1</v>
       </c>
       <c r="G71" t="s">
         <v>86</v>
@@ -3523,13 +3523,13 @@
         <v>85</v>
       </c>
       <c r="D72">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="E72">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F72">
-        <v>-0.05</v>
+        <v>-1.02</v>
       </c>
       <c r="G72" t="s">
         <v>86</v>
@@ -3615,10 +3615,10 @@
         <v>90</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E2">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0.175</v>
@@ -3653,10 +3653,10 @@
         <v>91</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="E3">
-        <v>-0.255</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0.137</v>
@@ -3691,10 +3691,10 @@
         <v>92</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-0.375</v>
       </c>
       <c r="E4">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0.137</v>
@@ -3729,10 +3729,10 @@
         <v>93</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="E5">
-        <v>-0.255</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0.213</v>
@@ -3767,10 +3767,10 @@
         <v>94</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-0.375</v>
       </c>
       <c r="E6">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0.213</v>
@@ -3805,10 +3805,10 @@
         <v>95</v>
       </c>
       <c r="D7">
+        <v>0.795</v>
+      </c>
+      <c r="E7">
         <v>0.6</v>
-      </c>
-      <c r="E7">
-        <v>-0.795</v>
       </c>
       <c r="F7">
         <v>-0.08599999999999999</v>
@@ -3843,10 +3843,10 @@
         <v>96</v>
       </c>
       <c r="D8">
+        <v>1.012</v>
+      </c>
+      <c r="E8">
         <v>0.6</v>
-      </c>
-      <c r="E8">
-        <v>-1.012</v>
       </c>
       <c r="F8">
         <v>0.962</v>
@@ -3881,10 +3881,10 @@
         <v>97</v>
       </c>
       <c r="D9">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="E9">
         <v>0.6</v>
-      </c>
-      <c r="E9">
-        <v>-0.8120000000000001</v>
       </c>
       <c r="F9">
         <v>0.962</v>
@@ -3919,10 +3919,10 @@
         <v>98</v>
       </c>
       <c r="D10">
+        <v>1.012</v>
+      </c>
+      <c r="E10">
         <v>0.6</v>
-      </c>
-      <c r="E10">
-        <v>-1.012</v>
       </c>
       <c r="F10">
         <v>-0.188</v>
@@ -3957,10 +3957,10 @@
         <v>99</v>
       </c>
       <c r="D11">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="E11">
         <v>0.6</v>
-      </c>
-      <c r="E11">
-        <v>-0.8120000000000001</v>
       </c>
       <c r="F11">
         <v>-0.188</v>
@@ -3995,10 +3995,10 @@
         <v>100</v>
       </c>
       <c r="D12">
+        <v>0.795</v>
+      </c>
+      <c r="E12">
         <v>0.6</v>
-      </c>
-      <c r="E12">
-        <v>-0.795</v>
       </c>
       <c r="F12">
         <v>-0.014</v>
@@ -4033,10 +4033,10 @@
         <v>101</v>
       </c>
       <c r="D13">
+        <v>0.655</v>
+      </c>
+      <c r="E13">
         <v>0.6</v>
-      </c>
-      <c r="E13">
-        <v>-0.655</v>
       </c>
       <c r="F13">
         <v>-0.014</v>
@@ -4071,10 +4071,10 @@
         <v>102</v>
       </c>
       <c r="D14">
+        <v>0.912</v>
+      </c>
+      <c r="E14">
         <v>0.6</v>
-      </c>
-      <c r="E14">
-        <v>-0.912</v>
       </c>
       <c r="F14">
         <v>0.387</v>
@@ -4109,10 +4109,10 @@
         <v>103</v>
       </c>
       <c r="D15">
+        <v>0.655</v>
+      </c>
+      <c r="E15">
         <v>0.6</v>
-      </c>
-      <c r="E15">
-        <v>-0.655</v>
       </c>
       <c r="F15">
         <v>-0.08599999999999999</v>
@@ -4147,10 +4147,10 @@
         <v>104</v>
       </c>
       <c r="D16">
+        <v>0.725</v>
+      </c>
+      <c r="E16">
         <v>0.6</v>
-      </c>
-      <c r="E16">
-        <v>-0.725</v>
       </c>
       <c r="F16">
         <v>-0.05</v>
@@ -4185,10 +4185,10 @@
         <v>105</v>
       </c>
       <c r="D17">
+        <v>-0.455</v>
+      </c>
+      <c r="E17">
         <v>0.96</v>
-      </c>
-      <c r="E17">
-        <v>0.455</v>
       </c>
       <c r="F17">
         <v>-0.375</v>
@@ -4223,10 +4223,10 @@
         <v>106</v>
       </c>
       <c r="D18">
+        <v>-0.43</v>
+      </c>
+      <c r="E18">
         <v>0.96</v>
-      </c>
-      <c r="E18">
-        <v>0.43</v>
       </c>
       <c r="F18">
         <v>-0.375</v>
@@ -4261,10 +4261,10 @@
         <v>107</v>
       </c>
       <c r="D19">
+        <v>-0.405</v>
+      </c>
+      <c r="E19">
         <v>0.96</v>
-      </c>
-      <c r="E19">
-        <v>0.405</v>
       </c>
       <c r="F19">
         <v>-0.375</v>
@@ -4299,10 +4299,10 @@
         <v>108</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="E20">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>1.4</v>
@@ -4337,10 +4337,10 @@
         <v>109</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="E21">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>1.4</v>
@@ -4375,10 +4375,10 @@
         <v>110</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>-1.38</v>
       </c>
       <c r="E22">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>1.4</v>
@@ -4413,10 +4413,10 @@
         <v>111</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="E23">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>-0.15</v>
@@ -4451,10 +4451,10 @@
         <v>112</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>-1.38</v>
       </c>
       <c r="E24">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>-0.15</v>
@@ -4489,10 +4489,10 @@
         <v>113</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>-1.38</v>
       </c>
       <c r="E25">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>1.4</v>
@@ -4527,10 +4527,10 @@
         <v>114</v>
       </c>
       <c r="D26">
+        <v>-0.025</v>
+      </c>
+      <c r="E26">
         <v>0.08799999999999999</v>
-      </c>
-      <c r="E26">
-        <v>0.025</v>
       </c>
       <c r="F26">
         <v>-0.22</v>
@@ -4565,10 +4565,10 @@
         <v>115</v>
       </c>
       <c r="D27">
+        <v>-0.21</v>
+      </c>
+      <c r="E27">
         <v>0.183</v>
-      </c>
-      <c r="E27">
-        <v>0.21</v>
       </c>
       <c r="F27">
         <v>-0.402</v>
@@ -4603,10 +4603,10 @@
         <v>116</v>
       </c>
       <c r="D28">
+        <v>0.225</v>
+      </c>
+      <c r="E28">
         <v>0.08799999999999999</v>
-      </c>
-      <c r="E28">
-        <v>-0.225</v>
       </c>
       <c r="F28">
         <v>0.026</v>
@@ -4641,10 +4641,10 @@
         <v>117</v>
       </c>
       <c r="D29">
+        <v>-0.275</v>
+      </c>
+      <c r="E29">
         <v>0.08799999999999999</v>
-      </c>
-      <c r="E29">
-        <v>0.275</v>
       </c>
       <c r="F29">
         <v>0.026</v>
@@ -4679,10 +4679,10 @@
         <v>118</v>
       </c>
       <c r="D30">
+        <v>0.225</v>
+      </c>
+      <c r="E30">
         <v>0.08799999999999999</v>
-      </c>
-      <c r="E30">
-        <v>-0.225</v>
       </c>
       <c r="F30">
         <v>-0.466</v>
@@ -4717,10 +4717,10 @@
         <v>119</v>
       </c>
       <c r="D31">
+        <v>-0.275</v>
+      </c>
+      <c r="E31">
         <v>0.08799999999999999</v>
-      </c>
-      <c r="E31">
-        <v>0.275</v>
       </c>
       <c r="F31">
         <v>-0.466</v>
@@ -4755,10 +4755,10 @@
         <v>120</v>
       </c>
       <c r="D32">
+        <v>0.15</v>
+      </c>
+      <c r="E32">
         <v>0.183</v>
-      </c>
-      <c r="E32">
-        <v>-0.15</v>
       </c>
       <c r="F32">
         <v>-0.402</v>
@@ -4793,10 +4793,10 @@
         <v>121</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="E33">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>-0.75</v>
@@ -4831,10 +4831,10 @@
         <v>122</v>
       </c>
       <c r="D34">
+        <v>0.15</v>
+      </c>
+      <c r="E34">
         <v>0.183</v>
-      </c>
-      <c r="E34">
-        <v>-0.15</v>
       </c>
       <c r="F34">
         <v>-0.83</v>
@@ -4869,10 +4869,10 @@
         <v>123</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>-1.38</v>
       </c>
       <c r="E35">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>-0.75</v>
@@ -4907,10 +4907,10 @@
         <v>124</v>
       </c>
       <c r="D36">
+        <v>-0.03</v>
+      </c>
+      <c r="E36">
         <v>0.183</v>
-      </c>
-      <c r="E36">
-        <v>0.03</v>
       </c>
       <c r="F36">
         <v>-0.616</v>
@@ -4945,10 +4945,10 @@
         <v>125</v>
       </c>
       <c r="D37">
+        <v>-0.03</v>
+      </c>
+      <c r="E37">
         <v>0.108</v>
-      </c>
-      <c r="E37">
-        <v>0.03</v>
       </c>
       <c r="F37">
         <v>-0.175</v>
@@ -4983,10 +4983,10 @@
         <v>126</v>
       </c>
       <c r="D38">
+        <v>0.095</v>
+      </c>
+      <c r="E38">
         <v>0.208</v>
-      </c>
-      <c r="E38">
-        <v>-0.095</v>
       </c>
       <c r="F38">
         <v>-1.024</v>
@@ -5021,10 +5021,10 @@
         <v>127</v>
       </c>
       <c r="D39">
+        <v>-0.21</v>
+      </c>
+      <c r="E39">
         <v>0.183</v>
-      </c>
-      <c r="E39">
-        <v>0.21</v>
       </c>
       <c r="F39">
         <v>-0.83</v>
@@ -5059,13 +5059,13 @@
         <v>128</v>
       </c>
       <c r="D40">
-        <v>0.57</v>
+        <v>0.285</v>
       </c>
       <c r="E40">
-        <v>1.15</v>
+        <v>0.575</v>
       </c>
       <c r="F40">
-        <v>-0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="G40" t="s">
         <v>86</v>
@@ -5097,13 +5097,13 @@
         <v>129</v>
       </c>
       <c r="D41">
-        <v>0.57</v>
+        <v>0.285</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F41">
-        <v>-0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="G41" t="s">
         <v>86</v>
@@ -5135,13 +5135,13 @@
         <v>130</v>
       </c>
       <c r="D42">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="E42">
-        <v>1.585</v>
+        <v>0.7925</v>
       </c>
       <c r="F42">
-        <v>-0.025</v>
+        <v>-1.025</v>
       </c>
       <c r="G42" t="s">
         <v>86</v>
@@ -5173,13 +5173,13 @@
         <v>131</v>
       </c>
       <c r="D43">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F43">
-        <v>-0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="G43" t="s">
         <v>86</v>
@@ -5211,13 +5211,13 @@
         <v>132</v>
       </c>
       <c r="D44">
-        <v>0.96</v>
+        <v>0.48</v>
       </c>
       <c r="E44">
-        <v>1.585</v>
+        <v>0.7925</v>
       </c>
       <c r="F44">
-        <v>-0.025</v>
+        <v>-1.025</v>
       </c>
       <c r="G44" t="s">
         <v>86</v>
@@ -5249,13 +5249,13 @@
         <v>133</v>
       </c>
       <c r="D45">
-        <v>0.96</v>
+        <v>0.48</v>
       </c>
       <c r="E45">
-        <v>1.485</v>
+        <v>0.7425</v>
       </c>
       <c r="F45">
-        <v>-0.025</v>
+        <v>-1.025</v>
       </c>
       <c r="G45" t="s">
         <v>86</v>
@@ -5287,13 +5287,13 @@
         <v>134</v>
       </c>
       <c r="D46">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="E46">
-        <v>1.485</v>
+        <v>0.7425</v>
       </c>
       <c r="F46">
-        <v>-0.025</v>
+        <v>-1.025</v>
       </c>
       <c r="G46" t="s">
         <v>86</v>
@@ -5325,13 +5325,13 @@
         <v>135</v>
       </c>
       <c r="D47">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="E47">
-        <v>1.15</v>
+        <v>0.575</v>
       </c>
       <c r="F47">
-        <v>-0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="G47" t="s">
         <v>86</v>
@@ -5363,13 +5363,13 @@
         <v>136</v>
       </c>
       <c r="D48">
-        <v>1.01</v>
+        <v>0.505</v>
       </c>
       <c r="E48">
-        <v>1.535</v>
+        <v>0.7675</v>
       </c>
       <c r="F48">
-        <v>-0.025</v>
+        <v>-1.025</v>
       </c>
       <c r="G48" t="s">
         <v>86</v>
@@ -5401,13 +5401,13 @@
         <v>137</v>
       </c>
       <c r="D49">
-        <v>0.645</v>
+        <v>0.3225</v>
       </c>
       <c r="E49">
-        <v>1.075</v>
+        <v>0.5375</v>
       </c>
       <c r="F49">
-        <v>-0.05</v>
+        <v>-1.05</v>
       </c>
       <c r="G49" t="s">
         <v>86</v>
